--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,232 +476,188 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某仓库指定区域的总重量</t>
+          <t>第 1 题：统计某销售员的总销售额</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIFS</t>
+          <t>练习函数：SUMIF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你负责管理一个仓库的货物重量记录。表格中有货物名称、存放区域、重量（公斤）。现在需要知道“A区”所有货物的总重量。</t>
+          <t>要求：你是销售助理，有一张本周各销售员的销售额记录表，需要快速汇总指定销售员的合计销售额。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：请在单元格 B8 输入公式，计算区域为“A区”的重量总和。</t>
+          <t>任务：在E2单元格输入公式，统计“张三”的总销售额。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>货物名称</t>
+          <t>销售员</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>区域</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
+          <t>销售额</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>零件X</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>A区</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>12.5</v>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>零件Y</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>B区</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>8.199999999999999</v>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>850</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>零件Z</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>A区</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>15</v>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>900</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>零件W</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>C区</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>9.800000000000001</v>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>零件Q</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>A区</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>20.3</v>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>700</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：根据订单号查找发货地址</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>练习函数：XLOOKUP</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：查找员工对应部门并处理错误</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>要求：你有一份客户订单表，包含订单号、客户名称、发货地址。现在需要根据某个订单号（例如订单号“1003”）快速查找对应的发货地址。</t>
+          <t>要求：公司有员工名单和部门对照表，你需要在工资表中根据员工姓名填充部门，但有些员工可能不在对照表中，要显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：请在单元格 E1 输入订单号（如1003），在单元格 F1 输入公式，根据E1中的订单号查找对应的发货地址。</t>
+          <t>任务：在F2单元格输入公式，根据E2（员工姓名）在A2:B5中查找部门，如果找不到则显示“未找到”。假设E2中已输入“李强”。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>订单号</t>
+          <t>员工姓名</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>客户名称</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>发货地址</t>
+          <t>部门</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>1001</v>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>王芳</t>
+        </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>客户甲</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>上海市浦东新区</t>
+          <t>销售部</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>1002</v>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>李强</t>
+        </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>客户乙</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>北京市朝阳区</t>
+          <t>技术部</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>1003</v>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>赵敏</t>
+        </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>客户丙</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>广州市天河区</t>
+          <t>行政部</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>1004</v>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>陈杰</t>
+        </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>客户丁</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>深圳市南山区</t>
+          <t>财务部</t>
         </is>
       </c>
     </row>
@@ -715,40 +671,40 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算员工工龄并判断是否满5年</t>
+          <t>第 3 题：统计符合条件的订单数量</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>练习函数：DATEDIF</t>
+          <t>练习函数：COUNTIFS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>要求：公司人事表中有每位员工的入职日期。请计算每位员工截至今天（2025年4月1日）的工龄（整年数），并判断是否满5年（满5年显示“是”，否则显示“否”）。假设今天固定为2025年4月1日。</t>
+          <t>要求：物流公司记录了一周的订单，需要统计指定销售员且发货状态为“已发货”的订单数量。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>任务：请在 C2 单元格输入公式计算张三的工龄（年），在 D2 单元格输入公式判断是否满5年（返回“是”或“否”），然后向下填充到C5:D5。</t>
+          <t>任务：在H2单元格输入公式，统计“张三”且“已发货”的订单数。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>员工姓名</t>
+          <t>销售员</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>入职日期</t>
+          <t>发货状态</t>
         </is>
       </c>
     </row>
@@ -760,7 +716,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>2018年6月15日</t>
+          <t>已发货</t>
         </is>
       </c>
     </row>
@@ -772,236 +728,246 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>2020年3月1日</t>
+          <t>未发货</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2019年11月20日</t>
+          <t>已发货</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>赵六</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>2021年7月10日</t>
+          <t>已发货</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>未发货</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：提取货物批次并查找对应单价</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流表格中有一列货物编号，编号格式为“字母+批次号”，例如“ABC2301”中的“2301”是批次号，需要提取批次号，然后根据批次号从另一个价格表中查找该批次的单价（元/件）。</t>
-        </is>
-      </c>
-    </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 B2 单元格输入公式提取批次号（后4位），在 C2 单元格输入公式根据批次号在右侧价格表（F2:G5）中查找单价，并向下填充。</t>
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：计算年龄和到港天数</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>货物编号</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>数量</t>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>要求：人事部需要计算员工的年龄（以年为单位），同时物流部需要计算货物到今天已存放的天数。</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>ABC2301</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>50</v>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>任务：在D2单元格输入公式计算刘洋的年龄（整年），在E2单元格输入公式计算刘洋的货物到港天数（今天设为2025-04-01）。</t>
+        </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>DEF2302</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>30</v>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>出生日期</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>货物到港日期</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>GHI2303</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>20</v>
+          <t>刘洋</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>1990-05-15</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>JKL2304</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>10</v>
+          <t>陈静</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>1985-08-20</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>赵磊</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>2000-12-01</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：根据产品名和月份同时筛选销售额</t>
-        </is>
-      </c>
-    </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>要求：销售明细表记录了每个产品在不同月份的销售额。你需要计算“产品A”在“1月”的总销售额，但找数据时可能因为产品名或月份写错导致无匹配，要求若查不到结果则显示“未找到”。</t>
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：根据产品编号匹配名称和价格</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>任务：请在单元格 B8 输入公式，计算“产品A”且“1月”的销售额总和，若结果为0（无匹配）则显示“未找到”。</t>
+          <t>要求：商品表中有产品编号对应的名称和单价，现在有一份订单需要快速填充名称和单价。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>产品</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>月份</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>销售额</t>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>任务：在F2单元格输入公式，根据E2中的产品编号（假设为“B02”）查找产品名称；在G2输入公式，使用INDEX+MATCH查找单价。</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>产品A</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>1月</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>1200</v>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>产品编号</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>产品B</t>
+          <t>A01</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>1月</t>
+          <t>苹果</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>800</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>产品A</t>
+          <t>B02</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>2月</t>
+          <t>香蕉</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>1500</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>产品C</t>
+          <t>C03</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>1月</t>
+          <t>橙子</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>600</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>产品A</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>3月</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1028,7 +994,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某仓库指定区域的总重量</t>
+          <t>第 1 题：统计某销售员的总销售额</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1005,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIFS(C2:C6,B2:B6,"A区")</f>
+        <f>SUMIF(A2:A7,"张三",B2:B7)</f>
         <v/>
       </c>
     </row>
@@ -1053,7 +1019,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：根据订单号查找发货地址</t>
+          <t>第 2 题：查找员工对应部门并处理错误</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1030,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>XLOOKUP(E1,A2:A5,C2:C5)</f>
+        <f>IFERROR(VLOOKUP(E2,A2:B5,2,FALSE),"未找到")</f>
         <v/>
       </c>
     </row>
@@ -1078,7 +1044,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算员工工龄并判断是否满5年</t>
+          <t>第 3 题：统计符合条件的订单数量</t>
         </is>
       </c>
     </row>
@@ -1088,10 +1054,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>C2: =DATEDIF(B2,"2025-4-1","y")  D2: =IF(C2&gt;=5,"是","否")</t>
-        </is>
+      <c r="B10" s="2">
+        <f>COUNTIFS(A2:A7,"张三",B2:B7,"已发货")</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1104,7 +1069,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：提取货物批次并查找对应单价</t>
+          <t>第 4 题：计算年龄和到港天数</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1079,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>B2: =RIGHT(A2,4)  C2: =VLOOKUP(B2,$F$2:$G$5,2,FALSE)</t>
-        </is>
+      <c r="B14" s="2">
+        <f>DATEDIF(B2,TODAY(),"Y") 和 =TODAY()-C2</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1130,7 +1094,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据产品名和月份同时筛选销售额</t>
+          <t>第 5 题：根据产品编号匹配名称和价格</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1105,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>IFERROR(SUMIFS(C2:C6,A2:A6,"产品A",B2:B6,"1月"),"未找到")</f>
+        <f>XLOOKUP(E2,A2:A4,B2:B4) 和 =INDEX(C2:C4,MATCH(E2,A2:A4,0))</f>
         <v/>
       </c>
     </row>
@@ -1173,7 +1137,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某仓库指定区域的总重量</t>
+          <t>第 1 题：统计某销售员的总销售额</t>
         </is>
       </c>
     </row>
@@ -1185,14 +1149,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS函数用于按多个条件求和，语法为SUMIFS(求和区域,条件区域1,条件1,...)。本题中，求和区域是C2:C6（重量），条件区域是B2:B6（区域），条件为"A区"，因此公式会筛选区域为A区的行，将对应重量加总。</t>
+          <t>SUMIF函数语法：SUMIF(条件区域, 条件, 求和区域)。本题中A2:A7是销售员列表，条件为“张三”，B2:B7是对应销售额，函数会筛选出所有“张三”的行并求和，结果为3200。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：根据订单号查找发货地址</t>
+          <t>第 2 题：查找员工对应部门并处理错误</t>
         </is>
       </c>
     </row>
@@ -1204,14 +1168,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP是新一代查找函数，语法为XLOOKUP(查找值,查找数组,返回数组)。本题在A2:A5中查找E1的值，找到后返回C2:C5中对应行的发货地址。相比VLOOKUP，XLOOKUP不需要指定列号，且可以向左查找。</t>
+          <t>VLOOKUP(查找值,表格区域,返回列号,精确匹配)用于查找“李强”的部门。IFERROR函数捕获错误，当查找不到时返回“未找到”。本题中“李强”存在，所以返回“技术部”。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算员工工龄并判断是否满5年</t>
+          <t>第 3 题：统计符合条件的订单数量</t>
         </is>
       </c>
     </row>
@@ -1223,14 +1187,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF计算两个日期之间的间隔，语法为DATEDIF(开始日期,结束日期,单位)。单位"y"表示整年数。这里用入职日期到指定日期2025-4-1的年数。然后IF函数判断工龄是否&gt;=5，满足返回"是"，否则返回"否"。</t>
+          <t>COUNTIFS函数语法：COUNTIFS(条件区域1,条件1,条件区域2,条件2,...)。分别对销售员列和状态列设置条件，同时满足的行计数。结果为2（第一行和第三行）。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：提取货物批次并查找对应单价</t>
+          <t>第 4 题：计算年龄和到港天数</t>
         </is>
       </c>
     </row>
@@ -1242,14 +1206,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>RIGHT函数从文本右侧提取指定字符数，语法RIGHT(文本,位数)，这里提取后4位。VLOOKUP用于精确查找，语法VLOOKUP(查找值,表格区域,列号,精确/近似)，本题用FALSE精确匹配批次号，返回第2列单价。</t>
+          <t>DATEDIF(起始日期,结束日期,单位)返回两个日期之间的完整年数，年龄计算用"Y"。TODAY()返回当前日期。到港天数直接用当前日期减到港日期，得到天数差。假设今天为2025-04-01，则年龄为34岁，天数为81天。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据产品名和月份同时筛选销售额</t>
+          <t>第 5 题：根据产品编号匹配名称和价格</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1225,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS多条件求和：求和区域C2:C6，条件区域1为A2:A6条件"产品A"，条件区域2为B2:B6条件"1月"。如果没有任何行满足条件，SUMIFS返回0。用IFERROR包裹，当SUMIFS结果为错误时（本公式中不会出错，但若条件写错单元格引用则可能），或想将0显示为“未找到”，可以改用IF判断，但这里用IFERROR演示容错。实际若要处理0，可用IF(SUMIFS=0,"未找到",SUMIFS)，但题目要求IFERROR，所以假设无匹配时SUMIFS会返回错误（实际如果条件区域有文本但无匹配则返回0，不会报错，因此此公式会返回0，不会显示“未找到”。但为了演示IFERROR，我们可将题目改为：当产品名或月份不存在时，SUMIFS返回0，而IFERROR无法捕获0。这里调整：使用VLOOKUP查找，但为符合SUMIFS+IFERROR，我们可让用户输入产品名和月份，若输入不存在则SUMIFS返回0，但IFERROR只捕获错误。因此此答案其实不会显示“未找到”。建议修改为：=IF(SUMIFS(...)=0,"未找到",SUMIFS(...))，但题重要求IFERROR，所以只能作为示例，讲解时可说明IFERROR用于捕获错误，而SUMIFS本身不会产生错误，所以更常用IF。本答案按题要求给出。</t>
+          <t>XLOOKUP(查找值,查找数组,返回数组)直接返回对应名称，比VLOOKUP更简单。INDEX+MATCH组合：MATCH找到E2在编号列中的位置（第2行），INDEX根据位置返回单价列的值。两者结果分别为“香蕉”和3.2。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：统计某销售员的总销售额</t>
+          <t>第 1 题：第1题（入门）：统计各部门的报销总金额</t>
         </is>
       </c>
     </row>
@@ -490,33 +490,33 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是销售助理，有一张本周各销售员的销售额记录表，需要快速汇总指定销售员的合计销售额。</t>
+          <t>要求：你是一家小公司的行政助理，需要统计公司各部门的报销总金额。表格中有部门名称和报销金额两列，现在要求用 SUMIF 函数统计“销售部”的报销总金额。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格输入公式，统计“张三”的总销售额。</t>
+          <t>任务：在 E1 单元格输入公式，统计“销售部”的报销总金额（用 SUMIF 函数）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>销售员</t>
+          <t>部门</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>报销金额</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
@@ -526,51 +526,51 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>市场部</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>850</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>900</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>行政部</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1100</v>
+        <v>900</v>
       </c>
     </row>
     <row r="12">
@@ -583,81 +583,96 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：查找员工对应部门并处理错误</t>
+          <t>第 2 题：第2题（基础）：计算两个日期的间隔天数</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>要求：公司有员工名单和部门对照表，你需要在工资表中根据员工姓名填充部门，但有些员工可能不在对照表中，要显示“未找到”。</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>练习函数：DATEDIF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：在F2单元格输入公式，根据E2（员工姓名）在A2:B5中查找部门，如果找不到则显示“未找到”。假设E2中已输入“李强”。</t>
+          <t>要求：你负责项目管理，需要跟踪每个项目的实际执行天数。表格中有项目名称、开始日期和结束日期，请用 DATEDIF 函数计算每个项目的持续天数（天为整数）。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>员工姓名</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>部门</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 D2 单元格输入公式，计算第一个项目的天数（DATEDIF），然后下拉填充至 D4</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>王芳</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>销售部</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>项目名称</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>开始日期</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>结束日期</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>李强</t>
+          <t>A项目</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>技术部</t>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-15</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>赵敏</t>
+          <t>B项目</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>行政部</t>
+          <t>2024-02-10</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>2024-04-05</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>陈杰</t>
+          <t>C项目</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>财务部</t>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-28</t>
         </is>
       </c>
     </row>
@@ -671,7 +686,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：统计符合条件的订单数量</t>
+          <t>第 3 题：第3题（进阶）：多条件统计发货单量</t>
         </is>
       </c>
     </row>
@@ -685,98 +700,133 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>要求：物流公司记录了一周的订单，需要统计指定销售员且发货状态为“已发货”的订单数量。</t>
+          <t>要求：你是物流仓库管理员，需要统计符合多个条件的发货记录数量。表格有“发货地区”、“是否加急”、“是否损坏”三列，要求统计“华东地区”并且“加急”的发货单数量。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>任务：在H2单元格输入公式，统计“张三”且“已发货”的订单数。</t>
+          <t>任务：在 F1 单元格输入公式，统计“华东”且“加急”的发货单数量</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>销售员</t>
+          <t>发货地区</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>发货状态</t>
+          <t>是否加急</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>是否损坏</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>已发货</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>未发货</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>已发货</t>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>已发货</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>已发货</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>未发货</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -790,184 +840,218 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：计算年龄和到港天数</t>
+          <t>第 4 题：第4题（中高级）：查找员工信息并处理错误</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>要求：人事部需要计算员工的年龄（以年为单位），同时物流部需要计算货物到今天已存放的天数。</t>
+          <t>要求：你是人事专员，根据员工编号查找对应的工资。表格中有员工编号和工资列，另外有一列需要查找的员工编号，其中有一个编号不存在。请用 VLOOKUP 和 IFERROR 配合，当找不到时显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>任务：在D2单元格输入公式计算刘洋的年龄（整年），在E2单元格输入公式计算刘洋的货物到港天数（今天设为2025-04-01）。</t>
+          <t>任务：在 B6 单元格输入公式，查找 E003 的工资；在 B7 输入公式查找 E777 的工资（用 VLOOKUP+IFERROR）</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>姓名</t>
+          <t>员工编号</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>出生日期</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>货物到港日期</t>
+          <t>工资</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>刘洋</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>1990-05-15</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>2025-01-10</t>
-        </is>
+          <t>E001</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>5000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>陈静</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>1985-08-20</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>2025-02-14</t>
-        </is>
+          <t>E002</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>6500</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>赵磊</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>2000-12-01</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-01</t>
-        </is>
+          <t>E003</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>7200</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>E004</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>待查编号</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>E003</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>E777</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：根据产品编号匹配名称和价格</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>要求：商品表中有产品编号对应的名称和单价，现在有一份订单需要快速填充名称和单价。</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>任务：在F2单元格输入公式，根据E2中的产品编号（假设为“B02”）查找产品名称；在G2输入公式，使用INDEX+MATCH查找单价。</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>产品编号</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>产品名称</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
-      </c>
-    </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>A01</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>苹果</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>5.5</v>
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题（高级）：物流重量查询与多函数组合</t>
+        </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>B02</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>香蕉</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>3.2</v>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是物流公司操作员，需要根据运单号查询运费单价，并计算含税总价（重量×单价×1.1，结果保留2位小数）。表格有两部分：运费单价表（运单号和单价），以及运单明细（运单号和重量）。请用 XLOOKUP 查询单价，用 ROUND 四舍五入。</t>
+        </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>C03</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>橙子</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>4.8</v>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 D7 单元格输入公式，计算 A300 运单的含税总价（单价×重量×1.1 并保留2位小数），使用 XLOOKUP 和 ROUND</t>
+        </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>运单号</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>单价(元/kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>A200</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>A300</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>运单号</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>A200</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>A300</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -994,7 +1078,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：统计某销售员的总销售额</t>
+          <t>第 1 题：第1题（入门）：统计各部门的报销总金额</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1089,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A7,"张三",B2:B7)</f>
+        <f>SUMIF(A2:A7,"销售部",B2:B7)</f>
         <v/>
       </c>
     </row>
@@ -1019,7 +1103,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：查找员工对应部门并处理错误</t>
+          <t>第 2 题：第2题（基础）：计算两个日期的间隔天数</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1114,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>IFERROR(VLOOKUP(E2,A2:B5,2,FALSE),"未找到")</f>
+        <f>DATEDIF(B2,C2,"d")</f>
         <v/>
       </c>
     </row>
@@ -1044,7 +1128,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：统计符合条件的订单数量</t>
+          <t>第 3 题：第3题（进阶）：多条件统计发货单量</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1139,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(A2:A7,"张三",B2:B7,"已发货")</f>
+        <f>COUNTIFS(A2:A7,"华东",B2:B7,"是")</f>
         <v/>
       </c>
     </row>
@@ -1069,7 +1153,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：计算年龄和到港天数</t>
+          <t>第 4 题：第4题（中高级）：查找员工信息并处理错误</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1164,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>DATEDIF(B2,TODAY(),"Y") 和 =TODAY()-C2</f>
+        <f>IFERROR(VLOOKUP(A6,$A$2:$B$5,2,FALSE),"未找到")</f>
         <v/>
       </c>
     </row>
@@ -1094,7 +1178,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：根据产品编号匹配名称和价格</t>
+          <t>第 5 题：第5题（高级）：物流重量查询与多函数组合</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1189,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>XLOOKUP(E2,A2:A4,B2:B4) 和 =INDEX(C2:C4,MATCH(E2,A2:A4,0))</f>
+        <f>ROUND(XLOOKUP(A7,$A$2:$A$4,$B$2:$B$4)*B7*1.1,2)</f>
         <v/>
       </c>
     </row>
@@ -1137,7 +1221,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：统计某销售员的总销售额</t>
+          <t>第 1 题：第1题（入门）：统计各部门的报销总金额</t>
         </is>
       </c>
     </row>
@@ -1149,14 +1233,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF函数语法：SUMIF(条件区域, 条件, 求和区域)。本题中A2:A7是销售员列表，条件为“张三”，B2:B7是对应销售额，函数会筛选出所有“张三”的行并求和，结果为3200。</t>
+          <t>SUMIF 函数用于按条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。本题中条件区域是A2:A7（部门），条件是"销售部"，求和区域是B2:B7（金额）。公式先检查部门列中哪些是销售部，然后对对应的金额求和，结果为1200+1500+900=3600。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：查找员工对应部门并处理错误</t>
+          <t>第 2 题：第2题（基础）：计算两个日期的间隔天数</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1252,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP(查找值,表格区域,返回列号,精确匹配)用于查找“李强”的部门。IFERROR函数捕获错误，当查找不到时返回“未找到”。本题中“李强”存在，所以返回“技术部”。</t>
+          <t>DATEDIF 函数用于计算两个日期之间的差值，语法为 DATEDIF(开始日期, 结束日期, 单位)。单位用"d"表示天数。注意开始日期要小于等于结束日期。本题中B2是开始日期，C2是结束日期，返回天数。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：统计符合条件的订单数量</t>
+          <t>第 3 题：第3题（进阶）：多条件统计发货单量</t>
         </is>
       </c>
     </row>
@@ -1187,14 +1271,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS函数语法：COUNTIFS(条件区域1,条件1,条件区域2,条件2,...)。分别对销售员列和状态列设置条件，同时满足的行计数。结果为2（第一行和第三行）。</t>
+          <t>COUNTIFS 函数用于满足多个条件的计数，语法为 COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2...)。本题第一个条件是地区列A2:A7等于"华东"，第二个条件是加急列B2:B7等于"是"，两个条件同时满足才计数。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：计算年龄和到港天数</t>
+          <t>第 4 题：第4题（中高级）：查找员工信息并处理错误</t>
         </is>
       </c>
     </row>
@@ -1206,14 +1290,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF(起始日期,结束日期,单位)返回两个日期之间的完整年数，年龄计算用"Y"。TODAY()返回当前日期。到港天数直接用当前日期减到港日期，得到天数差。假设今天为2025-04-01，则年龄为34岁，天数为81天。</t>
+          <t>VLOOKUP 语法为 VLOOKUP(查找值, 表格区域, 列号, 精确匹配)。这里查找值在A6，区域$A$2:$B$5，列号2，FALSE表示精确匹配。IFERROR 包裹后，如果 VLOOKUP 返回错误（如#N/A），则显示“未找到”。注意区域要用绝对引用。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：根据产品编号匹配名称和价格</t>
+          <t>第 5 题：第5题（高级）：物流重量查询与多函数组合</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1309,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP(查找值,查找数组,返回数组)直接返回对应名称，比VLOOKUP更简单。INDEX+MATCH组合：MATCH找到E2在编号列中的位置（第2行），INDEX根据位置返回单价列的值。两者结果分别为“香蕉”和3.2。</t>
+          <t>XLOOKUP 语法为 XLOOKUP(查找值, 查找数组, 返回数组)，本题用运单号A7在区域$A$2:$A$4中查找，返回对应的单价$B$2:$B$4。然后乘以重量B7，再乘以1.1得到含税价。ROUND 函数四舍五入到2位小数。公式结果为9.0*5.8*1.1=57.42。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题（入门）：统计各部门的报销总金额</t>
+          <t>第 1 题：第1题：计算某业务员的总销售额（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -490,33 +490,33 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家小公司的行政助理，需要统计公司各部门的报销总金额。表格中有部门名称和报销金额两列，现在要求用 SUMIF 函数统计“销售部”的报销总金额。</t>
+          <t>要求：你是一家小公司的销售助理，需要根据销售记录表，快速计算指定业务员（如张三）的总销售额。样例数据中A列是业务员姓名，B列是销售额（元）。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在 E1 单元格输入公式，统计“销售部”的报销总金额（用 SUMIF 函数）</t>
+          <t>任务：在E2单元格输入公式，计算张三的总销售额。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>部门</t>
+          <t>业务员</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>报销金额</t>
+          <t>销售额</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>销售部</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
@@ -526,51 +526,51 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>市场部</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>800</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>销售部</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>1500</v>
+        <v>800</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>行政部</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>300</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>财务部</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>销售部</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>900</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="12">
@@ -583,475 +583,363 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题（基础）：计算两个日期的间隔天数</t>
+          <t>第 2 题：第2题：统计满足多个条件的订单数量（COUNTIFS）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>练习函数：DATEDIF</t>
+          <t>练习函数：COUNTIFS</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>要求：你负责项目管理，需要跟踪每个项目的实际执行天数。表格中有项目名称、开始日期和结束日期，请用 DATEDIF 函数计算每个项目的持续天数（天为整数）。</t>
+          <t>要求：你在一家电商公司做运营，需要统计在特定地区（华东）且订单金额大于500的订单数量。样例数据中A列是地区，B列是订单金额。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>任务：在 D2 单元格输入公式，计算第一个项目的天数（DATEDIF），然后下拉填充至 D4</t>
+          <t>任务：在E2单元格输入公式，统计“华东”且订单金额大于500的订单数量。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>项目名称</t>
+          <t>地区</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>开始日期</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>结束日期</t>
+          <t>订单金额</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A项目</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-01</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-15</t>
-        </is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>B项目</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-10</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>2024-04-05</t>
-        </is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>C项目</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>2023-12-20</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-28</t>
-        </is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>700</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>西南</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题（进阶）：多条件统计发货单量</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIFS</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是物流仓库管理员，需要统计符合多个条件的发货记录数量。表格有“发货地区”、“是否加急”、“是否损坏”三列，要求统计“华东地区”并且“加急”的发货单数量。</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 F1 单元格输入公式，统计“华东”且“加急”的发货单数量</t>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：根据单号查找发货日期（XLOOKUP）</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>发货地区</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>是否加急</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>是否损坏</t>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>练习函数：XLOOKUP</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>要求：你在一家物流公司工作，需要根据运单号快速查找发货日期。样例数据中A列是运单号，B列是发货日期（文本格式）。</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>任务：在E2单元格输入公式，查找运单号为"SF003"的发货日期。</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>运单号</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>发货日期</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>SF001</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>是</t>
+          <t>2025-03-10</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>SF002</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
+          <t>2025-03-12</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>SF003</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>是</t>
+          <t>2025-03-15</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SF004</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>SF005</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题（中高级）：查找员工信息并处理错误</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是人事专员，根据员工编号查找对应的工资。表格中有员工编号和工资列，另外有一列需要查找的员工编号，其中有一个编号不存在。请用 VLOOKUP 和 IFERROR 配合，当找不到时显示“未找到”。</t>
-        </is>
-      </c>
-    </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 B6 单元格输入公式，查找 E003 的工资；在 B7 输入公式查找 E777 的工资（用 VLOOKUP+IFERROR）</t>
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：计算货物到港天数（TODAY和DATEDIF）</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>员工编号</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>工资</t>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>要求：你在一家进出口公司工作，需要计算每批货物从发运日到今天（当前日期）已过去的天数。样例数据中A列是货物批号，B列是发运日期（日期格式）。</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>E001</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>5000</v>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>任务：在E2单元格输入公式，计算B001货物从发运日期到今天的实际天数（假设今天为2025年4月20日）。</t>
+        </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>E002</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>6500</v>
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>批号</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>发运日期</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>E003</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>7200</v>
+          <t>B001</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>E004</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="n">
-        <v>4800</v>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>待查编号</t>
+          <t>B003</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>结果</t>
+          <t>2025-03-01</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>E003</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr"/>
+          <t>B004</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>E777</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：从身份证号提取出生年月（MID和DATE）</t>
+        </is>
+      </c>
+    </row>
     <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题（高级）：物流重量查询与多函数组合</t>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>练习函数：MID</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>要求：你是物流公司操作员，需要根据运单号查询运费单价，并计算含税总价（重量×单价×1.1，结果保留2位小数）。表格有两部分：运费单价表（运单号和单价），以及运单明细（运单号和重量）。请用 XLOOKUP 查询单价，用 ROUND 四舍五入。</t>
+          <t>要求：你负责员工信息管理，需要从身份证号码中提取出生日期。样例数据中A列是身份证号（18位），出生日期从第7位开始，共8位（如19900101）。</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>任务：在 D7 单元格输入公式，计算 A300 运单的含税总价（单价×重量×1.1 并保留2位小数），使用 XLOOKUP 和 ROUND</t>
+          <t>任务：在E2单元格输入公式，提取第一个身份证号对应的出生日期（显示为日期格式，如1990/3/7）。</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>运单号</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>单价(元/kg)</t>
+          <t>身份证号</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>A100</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="n">
-        <v>8.5</v>
+          <t>110101199003078811</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>A200</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="n">
-        <v>7.2</v>
+          <t>320102198512123456</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>A300</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n">
-        <v>9</v>
+          <t>440301200010015678</t>
+        </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>运单号</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>A100</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>A200</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>A300</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="n">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1078,7 +966,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题（入门）：统计各部门的报销总金额</t>
+          <t>第 1 题：第1题：计算某业务员的总销售额（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1089,7 +977,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A7,"销售部",B2:B7)</f>
+        <f>SUMIF(A2:A7,"张三",B2:B7)</f>
         <v/>
       </c>
     </row>
@@ -1103,7 +991,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题（基础）：计算两个日期的间隔天数</t>
+          <t>第 2 题：第2题：统计满足多个条件的订单数量（COUNTIFS）</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1002,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>DATEDIF(B2,C2,"d")</f>
+        <f>COUNTIFS(A2:A7,"华东",B2:B7,"&gt;500")</f>
         <v/>
       </c>
     </row>
@@ -1128,7 +1016,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题（进阶）：多条件统计发货单量</t>
+          <t>第 3 题：第3题：根据单号查找发货日期（XLOOKUP）</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1027,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(A2:A7,"华东",B2:B7,"是")</f>
+        <f>XLOOKUP("SF003", A2:A6, B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -1153,7 +1041,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题（中高级）：查找员工信息并处理错误</t>
+          <t>第 4 题：第4题：计算货物到港天数（TODAY和DATEDIF）</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1052,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>IFERROR(VLOOKUP(A6,$A$2:$B$5,2,FALSE),"未找到")</f>
+        <f>DATEDIF(B2, TODAY(), "d")</f>
         <v/>
       </c>
     </row>
@@ -1178,7 +1066,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题（高级）：物流重量查询与多函数组合</t>
+          <t>第 5 题：第5题：从身份证号提取出生年月（MID和DATE）</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1077,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>ROUND(XLOOKUP(A7,$A$2:$A$4,$B$2:$B$4)*B7*1.1,2)</f>
+        <f>DATE(MID(A2,7,4), MID(A2,11,2), MID(A2,13,2))</f>
         <v/>
       </c>
     </row>
@@ -1221,7 +1109,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题（入门）：统计各部门的报销总金额</t>
+          <t>第 1 题：第1题：计算某业务员的总销售额（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1233,14 +1121,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 函数用于按条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。本题中条件区域是A2:A7（部门），条件是"销售部"，求和区域是B2:B7（金额）。公式先检查部门列中哪些是销售部，然后对对应的金额求和，结果为1200+1500+900=3600。</t>
+          <t>SUMIF函数用于对满足单个条件的单元格求和。语法：SUMIF(条件区域, 条件, 求和区域)。这里的条件区域是A2:A7，条件是"张三"，求和区域是B2:B7。函数会扫描A列，凡是等于"张三"的，就把对应B列的数值加起来，结果为3100（1200+800+1100）。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题（基础）：计算两个日期的间隔天数</t>
+          <t>第 2 题：第2题：统计满足多个条件的订单数量（COUNTIFS）</t>
         </is>
       </c>
     </row>
@@ -1252,14 +1140,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF 函数用于计算两个日期之间的差值，语法为 DATEDIF(开始日期, 结束日期, 单位)。单位用"d"表示天数。注意开始日期要小于等于结束日期。本题中B2是开始日期，C2是结束日期，返回天数。</t>
+          <t>COUNTIFS函数用于统计满足多个条件的单元格个数。语法：COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2, ...)。这里第一个条件是A列等于"华东"，第二个条件是B列大于500。函数会同时满足两个条件的行数，结果有2行（第3行700，第5行550）。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题（进阶）：多条件统计发货单量</t>
+          <t>第 3 题：第3题：根据单号查找发货日期（XLOOKUP）</t>
         </is>
       </c>
     </row>
@@ -1271,14 +1159,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 函数用于满足多个条件的计数，语法为 COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2...)。本题第一个条件是地区列A2:A7等于"华东"，第二个条件是加急列B2:B7等于"是"，两个条件同时满足才计数。</t>
+          <t>XLOOKUP是Excel 365和2021中的新函数，用于查找并返回匹配项。语法：XLOOKUP(查找值, 查找数组, 返回数组)。这里查找值是"SF003"，在A2:A6中查找，找到后返回对应B2:B6的值，结果为"2025-03-15"。如果找不到，默认返回#N/A。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题（中高级）：查找员工信息并处理错误</t>
+          <t>第 4 题：第4题：计算货物到港天数（TODAY和DATEDIF）</t>
         </is>
       </c>
     </row>
@@ -1290,14 +1178,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP 语法为 VLOOKUP(查找值, 表格区域, 列号, 精确匹配)。这里查找值在A6，区域$A$2:$B$5，列号2，FALSE表示精确匹配。IFERROR 包裹后，如果 VLOOKUP 返回错误（如#N/A），则显示“未找到”。注意区域要用绝对引用。</t>
+          <t>TODAY函数返回当前日期，DATEDIF函数计算两个日期之间的差值。语法：DATEDIF(开始日期, 结束日期, 单位)。这里开始日期是B2（发运日期），结束日期是TODAY()，单位"d"表示天数。如果当前日期是2025年4月20日，则B001的发运日期是2025-01-15，结果为95天。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题（高级）：物流重量查询与多函数组合</t>
+          <t>第 5 题：第5题：从身份证号提取出生年月（MID和DATE）</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1197,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP 语法为 XLOOKUP(查找值, 查找数组, 返回数组)，本题用运单号A7在区域$A$2:$A$4中查找，返回对应的单价$B$2:$B$4。然后乘以重量B7，再乘以1.1得到含税价。ROUND 函数四舍五入到2位小数。公式结果为9.0*5.8*1.1=57.42。</t>
+          <t>MID函数用于从文本的指定位置提取指定数量的字符。语法：MID(文本, 开始位置, 字符个数)。身份证号第7-10位是年份，第11-12位是月份，第13-14位是日期。先分别用MID提取年、月、日，再用DATE函数组合成日期。例如MID(A2,7,4)返回"1990"，MID(A2,11,2)返回"03"，MID(A2,13,2)返回"07"，最后得到日期1990/3/7。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：计算某业务员的总销售额（SUMIF）</t>
+          <t>第 1 题：第1题：计算办公用品的总费用</t>
         </is>
       </c>
     </row>
@@ -490,87 +490,122 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家小公司的销售助理，需要根据销售记录表，快速计算指定业务员（如张三）的总销售额。样例数据中A列是业务员姓名，B列是销售额（元）。</t>
+          <t>要求：你是一家小公司的行政助理，需要统计某月购买办公用品的总费用。表格中有物品名称、类别和费用。请计算“打印纸”这一类别的总费用。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格输入公式，计算张三的总销售额。</t>
+          <t>任务：在E2单元格输入公式，计算类别为“打印纸”的费用总和。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>业务员</t>
+          <t>物品</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>费用</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>1200</v>
+          <t>A4打印纸</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>打印纸</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>1500</v>
+          <t>签字笔</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>文具</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>800</v>
+          <t>A3打印纸</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>打印纸</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>2000</v>
+          <t>文件夹</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>文具</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>900</v>
+          <t>墨盒</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>耗材</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>1100</v>
+          <t>彩色打印纸</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>打印纸</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="12">
@@ -583,101 +618,101 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计满足多个条件的订单数量（COUNTIFS）</t>
+          <t>第 2 题：第2题：统计到货超过3天的订单数</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>练习函数：COUNTIFS</t>
+          <t>练习函数：COUNTIF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>要求：你在一家电商公司做运营，需要统计在特定地区（华东）且订单金额大于500的订单数量。样例数据中A列是地区，B列是订单金额。</t>
+          <t>要求：物流公司有一个订单到货记录表，记录每个订单的到货天数。你需要统计到货天数大于3天的订单数量，以便跟进延迟情况。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格输入公式，统计“华东”且订单金额大于500的订单数量。</t>
+          <t>任务：在D2单元格输入公式，统计到货天数大于3的订单个数。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>地区</t>
+          <t>订单号</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>订单金额</t>
+          <t>到货天数</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>ORD001</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>300</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>ORD002</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>600</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>ORD003</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>700</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>ORD004</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>200</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>ORD005</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>550</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>ORD006</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>800</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -690,256 +725,331 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据单号查找发货日期（XLOOKUP）</t>
+          <t>第 3 题：第3题：查找客户的城市和联系电话</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>练习函数：XLOOKUP</t>
+          <t>练习函数：VLOOKUP</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>要求：你在一家物流公司工作，需要根据运单号快速查找发货日期。样例数据中A列是运单号，B列是发货日期（文本格式）。</t>
+          <t>要求：你有一份客户信息表，包含客户ID、姓名、城市和电话。现在需要根据客户ID查找某个客户的联系电话。请使用VLOOKUP函数实现。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格输入公式，查找运单号为"SF003"的发货日期。</t>
+          <t>任务：在F2单元格输入客户ID（例如C002），在G2单元格输入公式，根据F2的ID查找并返回该客户的电话。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>运单号</t>
+          <t>客户ID</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>发货日期</t>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>电话</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>SF001</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>13800001111</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>SF002</t>
+          <t>C002</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>13900002222</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>SF003</t>
+          <t>C003</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>13700003333</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>SF004</t>
+          <t>C004</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>13600004444</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>SF005</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：计算员工工龄和今日日期</t>
+        </is>
+      </c>
+    </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：计算货物到港天数（TODAY和DATEDIF）</t>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>要求：公司需要计算员工从入职日期到今天的工龄（整年数），并显示今天的日期。表格中已有员工姓名和入职日期。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>要求：你在一家进出口公司工作，需要计算每批货物从发运日到今天（当前日期）已过去的天数。样例数据中A列是货物批号，B列是发运日期（日期格式）。</t>
+          <t>任务：在C2单元格输入公式计算工龄（整年），在E1单元格输入公式显示今天的日期。</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>任务：在E2单元格输入公式，计算B001货物从发运日期到今天的实际天数（假设今天为2025年4月20日）。</t>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>入职日期</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>批号</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>发运日期</t>
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>2018-03-15</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>B001</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2020-07-01</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>B002</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2015-11-20</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>B003</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>B004</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-20</t>
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：根据产品编号查找价格并计算折扣后金额</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>要求：销售记录表中有产品编号和销售数量，价格表中有产品编号和单价。你需要根据产品编号查找单价，然后计算折扣后的金额（打9折），并保留两位小数。</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：从身份证号提取出生年月（MID和DATE）</t>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>任务：在C2单元格输入公式，根据A2的产品编号查找单价，乘以B2数量，再乘以0.9折扣，结果保留两位小数。</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>练习函数：MID</t>
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>产品编号</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>销售数量</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>要求：你负责员工信息管理，需要从身份证号码中提取出生日期。样例数据中A列是身份证号（18位），出生日期从第7位开始，共8位（如19900101）。</t>
-        </is>
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>任务：在E2单元格输入公式，提取第一个身份证号对应的出生日期（显示为日期格式，如1990/3/7）。</t>
-        </is>
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>身份证号</t>
-        </is>
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>110101199003078811</t>
+          <t>价格表</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>单价</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>320102198512123456</t>
-        </is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>440301200010015678</t>
-        </is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -966,7 +1076,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：计算某业务员的总销售额（SUMIF）</t>
+          <t>第 1 题：第1题：计算办公用品的总费用</t>
         </is>
       </c>
     </row>
@@ -977,7 +1087,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A7,"张三",B2:B7)</f>
+        <f>SUMIF(B2:B7,"打印纸",C2:C7)</f>
         <v/>
       </c>
     </row>
@@ -991,7 +1101,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计满足多个条件的订单数量（COUNTIFS）</t>
+          <t>第 2 题：第2题：统计到货超过3天的订单数</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1112,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(A2:A7,"华东",B2:B7,"&gt;500")</f>
+        <f>COUNTIF(B2:B7,"&gt;3")</f>
         <v/>
       </c>
     </row>
@@ -1016,7 +1126,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据单号查找发货日期（XLOOKUP）</t>
+          <t>第 3 题：第3题：查找客户的城市和联系电话</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1137,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>XLOOKUP("SF003", A2:A6, B2:B6)</f>
+        <f>VLOOKUP(F2,A2:D5,4,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -1041,7 +1151,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算货物到港天数（TODAY和DATEDIF）</t>
+          <t>第 4 题：第4题：计算员工工龄和今日日期</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1162,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>DATEDIF(B2, TODAY(), "d")</f>
+        <f>DATEDIF(B2,TODAY(),"Y")  (在C2输入) ; =TODAY() (在E1输入)</f>
         <v/>
       </c>
     </row>
@@ -1066,7 +1176,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：从身份证号提取出生年月（MID和DATE）</t>
+          <t>第 5 题：第5题：根据产品编号查找价格并计算折扣后金额</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1187,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>DATE(MID(A2,7,4), MID(A2,11,2), MID(A2,13,2))</f>
+        <f>ROUND(XLOOKUP(A2,A5:A7,B5:B7)*B2*0.9,2)</f>
         <v/>
       </c>
     </row>
@@ -1109,7 +1219,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：计算某业务员的总销售额（SUMIF）</t>
+          <t>第 1 题：第1题：计算办公用品的总费用</t>
         </is>
       </c>
     </row>
@@ -1121,14 +1231,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF函数用于对满足单个条件的单元格求和。语法：SUMIF(条件区域, 条件, 求和区域)。这里的条件区域是A2:A7，条件是"张三"，求和区域是B2:B7。函数会扫描A列，凡是等于"张三"的，就把对应B列的数值加起来，结果为3100（1200+800+1100）。</t>
+          <t>SUMIF函数用于按条件求和，语法为SUMIF(条件区域, 条件, 求和区域)。这里条件区域是B2:B7（类别列），条件是“打印纸”，求和区域是C2:C7（费用列）。函数会扫描条件区域中等于“打印纸”的行，并将对应的费用求和，结果为120+80+60=260。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计满足多个条件的订单数量（COUNTIFS）</t>
+          <t>第 2 题：第2题：统计到货超过3天的订单数</t>
         </is>
       </c>
     </row>
@@ -1140,14 +1250,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS函数用于统计满足多个条件的单元格个数。语法：COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2, ...)。这里第一个条件是A列等于"华东"，第二个条件是B列大于500。函数会同时满足两个条件的行数，结果有2行（第3行700，第5行550）。</t>
+          <t>COUNTIF函数用于按条件计数，语法为COUNTIF(条件区域, 条件)。这里条件区域是B2:B7（到货天数），条件是“&gt;3”（注意条件要用引号括起来，且大于号是文本比较符）。函数会统计满足条件的单元格个数，结果为3（ORD002、ORD004、ORD006）。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据单号查找发货日期（XLOOKUP）</t>
+          <t>第 3 题：第3题：查找客户的城市和联系电话</t>
         </is>
       </c>
     </row>
@@ -1159,14 +1269,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP是Excel 365和2021中的新函数，用于查找并返回匹配项。语法：XLOOKUP(查找值, 查找数组, 返回数组)。这里查找值是"SF003"，在A2:A6中查找，找到后返回对应B2:B6的值，结果为"2025-03-15"。如果找不到，默认返回#N/A。</t>
+          <t>VLOOKUP函数用于垂直查找，语法为VLOOKUP(查找值, 表格区域, 返回列号, [近似/精确匹配])。这里查找值是F2中的客户ID，表格区域是A2:D5（包含ID到电话的所有列），返回列号是4（电话在第四列），使用FALSE表示精确匹配。例如F2=C002时，返回13900002222。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算货物到港天数（TODAY和DATEDIF）</t>
+          <t>第 4 题：第4题：计算员工工龄和今日日期</t>
         </is>
       </c>
     </row>
@@ -1178,14 +1288,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>TODAY函数返回当前日期，DATEDIF函数计算两个日期之间的差值。语法：DATEDIF(开始日期, 结束日期, 单位)。这里开始日期是B2（发运日期），结束日期是TODAY()，单位"d"表示天数。如果当前日期是2025年4月20日，则B001的发运日期是2025-01-15，结果为95天。</t>
+          <t>DATEDIF函数计算两个日期之间的差值，语法为DATEDIF(开始日期, 结束日期, 单位)，单位"Y"表示整年数。TODAY()返回当前日期，作为结束日期。例如B2是2018-03-15，今天如果是2023-10-01，工龄为5年。TODAY()函数无需参数，直接输入=TODAY()即可显示当天日期。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：从身份证号提取出生年月（MID和DATE）</t>
+          <t>第 5 题：第5题：根据产品编号查找价格并计算折扣后金额</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1307,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MID函数用于从文本的指定位置提取指定数量的字符。语法：MID(文本, 开始位置, 字符个数)。身份证号第7-10位是年份，第11-12位是月份，第13-14位是日期。先分别用MID提取年、月、日，再用DATE函数组合成日期。例如MID(A2,7,4)返回"1990"，MID(A2,11,2)返回"03"，MID(A2,13,2)返回"07"，最后得到日期1990/3/7。</t>
+          <t>XLOOKUP函数用于查找并返回匹配值，语法为XLOOKUP(查找值, 查找数组, 返回数组)。这里查找值是A2，查找数组是A5:A7（价格表的产品编号），返回数组是B5:B7（单价）。然后乘以B2（数量）再乘以0.9折扣，最后用ROUND函数保留两位小数，语法为ROUND(数值, 小数位数)。例如A2=P001，B2=3，计算为100*3*0.9=270，结果270.00。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：计算办公用品的总费用</t>
+          <t>第 1 题：第1题：统计苹果的总销量（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -490,566 +490,469 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家小公司的行政助理，需要统计某月购买办公用品的总费用。表格中有物品名称、类别和费用。请计算“打印纸”这一类别的总费用。</t>
+          <t>要求：你是一家水果店的店员，每天记录各种水果的销量。现在想知道苹果一共卖了多少斤。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格输入公式，计算类别为“打印纸”的费用总和。</t>
+          <t>任务：在E2单元格输入公式，统计“苹果”的总销量。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>物品</t>
+          <t>水果</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>类别</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>费用</t>
+          <t>销量(斤)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>A4打印纸</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>打印纸</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>120</v>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>签字笔</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>文具</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>30</v>
+          <t>香蕉</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>A3打印纸</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>打印纸</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>80</v>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>文件夹</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>文具</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>45</v>
+          <t>橙子</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>墨盒</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>耗材</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>200</v>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>彩色打印纸</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>打印纸</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：根据工号查找员工姓名（VLOOKUP）</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：统计到货超过3天的订单数</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>练习函数：VLOOKUP</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIF</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>要求：公司员工信息表里记录了工号和姓名，现在给你一个工号，需要你快速找出对应的员工姓名。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>要求：物流公司有一个订单到货记录表，记录每个订单的到货天数。你需要统计到货天数大于3天的订单数量，以便跟进延迟情况。</t>
+          <t>任务：在D2单元格输入工号E003，在E2单元格输入公式，返回该工号对应的姓名。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>任务：在D2单元格输入公式，统计到货天数大于3的订单个数。</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>工号</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>到货天数</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>E001</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>ORD001</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>2</v>
+          <t>E002</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>ORD002</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>5</v>
+          <t>E003</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>ORD003</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>3</v>
+          <t>E004</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>ORD004</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>ORD005</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>1</v>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>ORD006</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>4</v>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：计算订单到货天数（DATEDIF 和 TODAY）</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>要求：你负责跟进订单物流，每个订单有下单日期，需要计算从下单到今天已经过了多少天（到货天数），方便判断是否延误。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>任务：在C2单元格输入公式，计算A001订单从下单日期到今天的实际天数，并下拉填充到C4。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>下单日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：查找客户的城市和联系电话</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>练习函数：VLOOKUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一份客户信息表，包含客户ID、姓名、城市和电话。现在需要根据客户ID查找某个客户的联系电话。请使用VLOOKUP函数实现。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>任务：在F2单元格输入客户ID（例如C002），在G2单元格输入公式，根据F2的ID查找并返回该客户的电话。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>客户ID</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>城市</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>电话</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>C001</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>13800001111</t>
-        </is>
-      </c>
-    </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>C002</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>13900002222</t>
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：多条件统计华东区A产品的销售额（SUMIFS）</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>C003</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>13700003333</t>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>练习函数：SUMIFS</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>C004</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>13600004444</t>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一张销售流水表，包含区域、产品、销售额。需要统计“华东区”且“产品A”的总销售额，用于销售分析。</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>任务：在F2单元格输入公式，统计区域为“华东”且产品为“A”的销售额总和。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>销售额</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：计算员工工龄和今日日期</t>
-        </is>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>要求：公司需要计算员工从入职日期到今天的工龄（整年数），并显示今天的日期。表格中已有员工姓名和入职日期。</t>
-        </is>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>任务：在C2单元格输入公式计算工龄（整年），在E1单元格输入公式显示今天的日期。</t>
-        </is>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>入职日期</t>
-        </is>
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>2018-03-15</t>
-        </is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>2020-07-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>2015-11-20</t>
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：用INDEX和MATCH查找指定日期的最晚温度</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一周每天的记录温度，需要根据输入的日期（如周三）找出该日期的最高温度（假设温度数据按每天一行，每天只有一个温度数值）。</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：根据产品编号查找价格并计算折扣后金额</t>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>任务：在D2单元格输入“周三”，在E2单元格输入公式，返回周三的温度。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>要求：销售记录表中有产品编号和销售数量，价格表中有产品编号和单价。你需要根据产品编号查找单价，然后计算折扣后的金额（打9折），并保留两位小数。</t>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>星期</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>温度</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>任务：在C2单元格输入公式，根据A2的产品编号查找单价，乘以B2数量，再乘以0.9折扣，结果保留两位小数。</t>
-        </is>
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>周一</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>产品编号</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>销售数量</t>
-        </is>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>P001</t>
+          <t>周三</t>
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>周四</t>
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>P003</t>
+          <t>周五</t>
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>价格表</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>P001</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>P002</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>P003</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1076,7 +979,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：计算办公用品的总费用</t>
+          <t>第 1 题：第1题：统计苹果的总销量（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1087,7 +990,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(B2:B7,"打印纸",C2:C7)</f>
+        <f>SUMIF(A2:A6,"苹果",B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -1101,7 +1004,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计到货超过3天的订单数</t>
+          <t>第 2 题：第2题：根据工号查找员工姓名（VLOOKUP）</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1015,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF(B2:B7,"&gt;3")</f>
+        <f>VLOOKUP(D2, A2:B5, 2, FALSE)</f>
         <v/>
       </c>
     </row>
@@ -1126,7 +1029,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查找客户的城市和联系电话</t>
+          <t>第 3 题：第3题：计算订单到货天数（DATEDIF 和 TODAY）</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1040,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>VLOOKUP(F2,A2:D5,4,FALSE)</f>
+        <f>DATEDIF(B2, TODAY(), "d")</f>
         <v/>
       </c>
     </row>
@@ -1151,7 +1054,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算员工工龄和今日日期</t>
+          <t>第 4 题：第4题：多条件统计华东区A产品的销售额（SUMIFS）</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1065,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>DATEDIF(B2,TODAY(),"Y")  (在C2输入) ; =TODAY() (在E1输入)</f>
+        <f>SUMIFS(C2:C6, A2:A6, "华东", B2:B6, "A")</f>
         <v/>
       </c>
     </row>
@@ -1176,7 +1079,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据产品编号查找价格并计算折扣后金额</t>
+          <t>第 5 题：第5题：用INDEX和MATCH查找指定日期的最晚温度</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1090,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>ROUND(XLOOKUP(A2,A5:A7,B5:B7)*B2*0.9,2)</f>
+        <f>INDEX(B2:B6, MATCH(D2, A2:A6, 0))</f>
         <v/>
       </c>
     </row>
@@ -1219,7 +1122,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：计算办公用品的总费用</t>
+          <t>第 1 题：第1题：统计苹果的总销量（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1231,14 +1134,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF函数用于按条件求和，语法为SUMIF(条件区域, 条件, 求和区域)。这里条件区域是B2:B7（类别列），条件是“打印纸”，求和区域是C2:C7（费用列）。函数会扫描条件区域中等于“打印纸”的行，并将对应的费用求和，结果为120+80+60=260。</t>
+          <t>SUMIF(条件区域, 条件, 求和区域)。此公式在A2:A6中查找等于“苹果”的行，然后将对应的B2:B6销量相加，结果是12+15+9=36。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计到货超过3天的订单数</t>
+          <t>第 2 题：第2题：根据工号查找员工姓名（VLOOKUP）</t>
         </is>
       </c>
     </row>
@@ -1250,14 +1153,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF函数用于按条件计数，语法为COUNTIF(条件区域, 条件)。这里条件区域是B2:B7（到货天数），条件是“&gt;3”（注意条件要用引号括起来，且大于号是文本比较符）。函数会统计满足条件的单元格个数，结果为3（ORD002、ORD004、ORD006）。</t>
+          <t>VLOOKUP(查找值, 表格区域, 返回列号, 精确匹配)。查找D2的值E003，在A2:B5区域的第一列中找，找到后返回该行第2列的值，即“王五”。FALSE表示精确匹配。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查找客户的城市和联系电话</t>
+          <t>第 3 题：第3题：计算订单到货天数（DATEDIF 和 TODAY）</t>
         </is>
       </c>
     </row>
@@ -1269,14 +1172,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP函数用于垂直查找，语法为VLOOKUP(查找值, 表格区域, 返回列号, [近似/精确匹配])。这里查找值是F2中的客户ID，表格区域是A2:D5（包含ID到电话的所有列），返回列号是4（电话在第四列），使用FALSE表示精确匹配。例如F2=C002时，返回13900002222。</t>
+          <t>DATEDIF(开始日期, 结束日期, 单位) 计算两个日期之间的天数差。TODAY()返回当前日期。单位"d"表示天数。此公式动态计算，每天打开表格都会自动更新。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算员工工龄和今日日期</t>
+          <t>第 4 题：第4题：多条件统计华东区A产品的销售额（SUMIFS）</t>
         </is>
       </c>
     </row>
@@ -1288,14 +1191,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF函数计算两个日期之间的差值，语法为DATEDIF(开始日期, 结束日期, 单位)，单位"Y"表示整年数。TODAY()返回当前日期，作为结束日期。例如B2是2018-03-15，今天如果是2023-10-01，工龄为5年。TODAY()函数无需参数，直接输入=TODAY()即可显示当天日期。</t>
+          <t>SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2)。先对C2:C6求和，但只包括同时满足A列为“华东”和B列为“A”的行，即100+120=220。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据产品编号查找价格并计算折扣后金额</t>
+          <t>第 5 题：第5题：用INDEX和MATCH查找指定日期的最晚温度</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1210,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP函数用于查找并返回匹配值，语法为XLOOKUP(查找值, 查找数组, 返回数组)。这里查找值是A2，查找数组是A5:A7（价格表的产品编号），返回数组是B5:B7（单价）。然后乘以B2（数量）再乘以0.9折扣，最后用ROUND函数保留两位小数，语法为ROUND(数值, 小数位数)。例如A2=P001，B2=3，计算为100*3*0.9=270，结果270.00。</t>
+          <t>MATCH(D2, A2:A6, 0) 在A2:A6中找到“周三”的位置，返回3（第3行）。INDEX(B2:B6, 3) 返回B列第3个值，即28。这样组合可以实现按名称查找，比VLOOKUP更灵活，尤其适合列顺序变化时。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计苹果的总销量（SUMIF）</t>
+          <t>第 1 题：第1题：统计某业务员的销售总额（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -490,469 +490,504 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家水果店的店员，每天记录各种水果的销量。现在想知道苹果一共卖了多少斤。</t>
+          <t>要求：你是一家小公司的销售助理，表格中记录了每位销售员的销售额。现在需要快速算出“张三”这个月的总销售额，以便发提成。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格输入公式，统计“苹果”的总销量。</t>
+          <t>任务：在E2单元格输入公式，计算“张三”的销售额总和。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>水果</t>
+          <t>销售员</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>销量(斤)</t>
+          <t>销售额</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>12</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>香蕉</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>8</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>15</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>橙子</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>10</v>
+        <v>900</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：根据工号查找员工姓名（VLOOKUP）</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>练习函数：VLOOKUP</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：统计迟到次数和平均分（COUNTIF与ROUND）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>要求：公司员工信息表里记录了工号和姓名，现在给你一个工号，需要你快速找出对应的员工姓名。</t>
+          <t>要求：你是一个培训班的班主任，记录了学员的出勤情况和考试成绩。需要统计每个学员的迟到次数，并计算班级平均分（保留1位小数）。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：在D2单元格输入工号E003，在E2单元格输入公式，返回该工号对应的姓名。</t>
+          <t>任务：在E2单元格用COUNTIF统计“迟到”的次数；在E3单元格用ROUND计算平均成绩并保留1位小数。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>工号</t>
+          <t>学员</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>姓名</t>
+          <t>出勤状态</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>成绩</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>E001</t>
+          <t>小美</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
-        </is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>88</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>E002</t>
+          <t>小刚</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
-        </is>
+          <t>迟到</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>E003</t>
+          <t>小丽</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
-        </is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>E004</t>
+          <t>小强</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>赵六</t>
-        </is>
+          <t>迟到</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>91</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>小华</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>小军</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>迟到</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：计算订单到货天数（DATEDIF 和 TODAY）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>要求：你负责跟进订单物流，每个订单有下单日期，需要计算从下单到今天已经过了多少天（到货天数），方便判断是否延误。</t>
-        </is>
-      </c>
-    </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>任务：在C2单元格输入公式，计算A001订单从下单日期到今天的实际天数，并下拉填充到C4。</t>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：查询商品单价（VLOOKUP精确匹配）</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>下单日期</t>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>练习函数：VLOOKUP</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-01</t>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>要求：你在一家文具店工作，商品价格表在A列和B列。客户报出商品名称，你需要快速找到对应单价来开单。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-10</t>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>任务：在E2单元格输入公式，根据D2中的商品名称（比如“文件夹”）查找其单价。</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>A003</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-20</t>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>商品</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>笔记本</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>签字笔</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>文件夹</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>胶带</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>便利贴</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：多条件统计华东区A产品的销售额（SUMIFS）</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>练习函数：SUMIFS</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一张销售流水表，包含区域、产品、销售额。需要统计“华东区”且“产品A”的总销售额，用于销售分析。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>任务：在F2单元格输入公式，统计区域为“华东”且产品为“A”的销售额总和。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>区域</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>产品</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>销售额</t>
-        </is>
-      </c>
-    </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>100</v>
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：计算到港天数和判断是否延误（TODAY与DATEDIF）</t>
+        </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>150</v>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是一家物流公司的跟单员，表格记录了每批货物的计划到港日期。需要计算今天距离计划到港还有多少天（若已过则为负数），并判断是否延误（超过5天算延误）。</t>
+        </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>200</v>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>任务：在C2单元格输入公式，计算从今天到计划日期的天数差（提示：用DATEDIF，但注意方向）。在D2单元格用IF判断是否延误（若天数差小于-5则“延误”，否则“正常”）。</t>
+        </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>120</v>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>货物编号</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>计划到港日期</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>A001</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>180</v>
+          <t>2025-03-20</t>
+        </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：用INDEX和MATCH查找指定日期的最晚温度</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一周每天的记录温度，需要根据输入的日期（如周三）找出该日期的最高温度（假设温度数据按每天一行，每天只有一个温度数值）。</t>
-        </is>
-      </c>
-    </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>任务：在D2单元格输入“周三”，在E2单元格输入公式，返回周三的温度。</t>
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：根据订单号提取客户和金额（INDEX与MATCH）</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>星期</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>温度</t>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>要求：你在一家电商公司，订单表包含订单号、客户名和金额。现在需要根据输入的订单号，自动返回对应的客户名和金额，用于对账。</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>周一</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="n">
-        <v>22</v>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>任务：在E2单元格输入订单号（如D003），在F2输入公式返回客户名，在G2输入公式返回金额。</t>
+        </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>周二</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>25</v>
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>客户</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>周三</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>28</v>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>王芳</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>周四</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n">
-        <v>24</v>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>李伟</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>周五</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="n">
-        <v>27</v>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>陈静</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>赵磊</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -979,7 +1014,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计苹果的总销量（SUMIF）</t>
+          <t>第 1 题：第1题：统计某业务员的销售总额（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -990,7 +1025,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"苹果",B2:B6)</f>
+        <f>SUMIF(A2:A7,"张三",B2:B7)</f>
         <v/>
       </c>
     </row>
@@ -1004,7 +1039,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：根据工号查找员工姓名（VLOOKUP）</t>
+          <t>第 2 题：第2题：统计迟到次数和平均分（COUNTIF与ROUND）</t>
         </is>
       </c>
     </row>
@@ -1014,9 +1049,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B6" s="2">
-        <f>VLOOKUP(D2, A2:B5, 2, FALSE)</f>
-        <v/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>E2: =COUNTIF(B2:B7,"迟到") ; E3: =ROUND(AVERAGE(C2:C7),1)</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1029,7 +1065,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算订单到货天数（DATEDIF 和 TODAY）</t>
+          <t>第 3 题：第3题：查询商品单价（VLOOKUP精确匹配）</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1076,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>DATEDIF(B2, TODAY(), "d")</f>
+        <f>VLOOKUP(D2,A2:B6,2,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -1054,7 +1090,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：多条件统计华东区A产品的销售额（SUMIFS）</t>
+          <t>第 4 题：第4题：计算到港天数和判断是否延误（TODAY与DATEDIF）</t>
         </is>
       </c>
     </row>
@@ -1064,9 +1100,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <f>SUMIFS(C2:C6, A2:A6, "华东", B2:B6, "A")</f>
-        <v/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>C2: =IF(B2&gt;=TODAY(), DATEDIF(TODAY(),B2,"d"), -DATEDIF(B2,TODAY(),"d")) ; D2: =IF(C2&lt;-5,"延误","正常")</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1079,7 +1116,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用INDEX和MATCH查找指定日期的最晚温度</t>
+          <t>第 5 题：第5题：根据订单号提取客户和金额（INDEX与MATCH）</t>
         </is>
       </c>
     </row>
@@ -1089,9 +1126,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2">
-        <f>INDEX(B2:B6, MATCH(D2, A2:A6, 0))</f>
-        <v/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>F2: =INDEX(B2:B5, MATCH(E2,A2:A5,0)) ; G2: =INDEX(C2:C5, MATCH(E2,A2:A5,0))</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1122,7 +1160,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计苹果的总销量（SUMIF）</t>
+          <t>第 1 题：第1题：统计某业务员的销售总额（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1134,14 +1172,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF(条件区域, 条件, 求和区域)。此公式在A2:A6中查找等于“苹果”的行，然后将对应的B2:B6销量相加，结果是12+15+9=36。</t>
+          <t>SUMIF函数用于按条件求和，语法为SUMIF(条件区域, 条件, 求和区域)。本题中条件区域是A2:A7，条件是“张三”，求和区域是B2:B7，Excel会找出所有销售员为“张三”的行，并把对应销售额相加，结果为3800。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：根据工号查找员工姓名（VLOOKUP）</t>
+          <t>第 2 题：第2题：统计迟到次数和平均分（COUNTIF与ROUND）</t>
         </is>
       </c>
     </row>
@@ -1153,14 +1191,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP(查找值, 表格区域, 返回列号, 精确匹配)。查找D2的值E003，在A2:B5区域的第一列中找，找到后返回该行第2列的值，即“王五”。FALSE表示精确匹配。</t>
+          <t>COUNTIF用于计数，语法COUNTIF(区域, 条件)，这里区域B2:B7，条件“迟到”，结果为3。ROUND用于四舍五入，语法ROUND(数值, 小数位数)，先用AVERAGE算出平均分(88+72+65+91+84+59)/6=76.5，保留1位小数仍为76.5。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算订单到货天数（DATEDIF 和 TODAY）</t>
+          <t>第 3 题：第3题：查询商品单价（VLOOKUP精确匹配）</t>
         </is>
       </c>
     </row>
@@ -1172,14 +1210,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF(开始日期, 结束日期, 单位) 计算两个日期之间的天数差。TODAY()返回当前日期。单位"d"表示天数。此公式动态计算，每天打开表格都会自动更新。</t>
+          <t>VLOOKUP语法：VLOOKUP(查找值, 表格区域, 返回列号, 匹配方式)。查找值D2，区域A2:B6，返回第2列单价，FALSE表示精确匹配。若D2为“文件夹”，则返回8。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：多条件统计华东区A产品的销售额（SUMIFS）</t>
+          <t>第 4 题：第4题：计算到港天数和判断是否延误（TODAY与DATEDIF）</t>
         </is>
       </c>
     </row>
@@ -1191,14 +1229,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2)。先对C2:C6求和，但只包括同时满足A列为“华东”和B列为“A”的行，即100+120=220。</t>
+          <t>TODAY()返回当前日期。DATEDIF计算两个日期之间的天数差，语法DATEDIF(开始日期, 结束日期, "d")。这里用IF处理正负号：如果计划日期在今天之后，计算从今天到计划日期的天数；否则计算负数。然后D2判断是否小于-5。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用INDEX和MATCH查找指定日期的最晚温度</t>
+          <t>第 5 题：第5题：根据订单号提取客户和金额（INDEX与MATCH）</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1248,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MATCH(D2, A2:A6, 0) 在A2:A6中找到“周三”的位置，返回3（第3行）。INDEX(B2:B6, 3) 返回B列第3个值，即28。这样组合可以实现按名称查找，比VLOOKUP更灵活，尤其适合列顺序变化时。</t>
+          <t>MATCH找到订单号在A列中的位置，语法MATCH(查找值, 查找区域, 0精确匹配)。INDEX根据行号返回对应列的值，语法INDEX(列区域, 行号)。例如E2为D003，MATCH返回3，INDEX(B2:B5,3)返回“陈静”，INDEX(C2:C5,3)返回120。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某业务员的销售总额（SUMIF）</t>
+          <t>第 1 题：第1题：统计指定商品的销售总量</t>
         </is>
       </c>
     </row>
@@ -490,87 +490,87 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家小公司的销售助理，表格中记录了每位销售员的销售额。现在需要快速算出“张三”这个月的总销售额，以便发提成。</t>
+          <t>要求：你是一家小商店的老板，有一个销售明细表，包含商品名称和销售数量。现在你想快速知道“苹果”这种商品一共卖出了多少件。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格输入公式，计算“张三”的销售额总和。</t>
+          <t>任务：请在E2单元格输入公式，统计“苹果”的总数量。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>销售员</t>
+          <t>商品</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>数量</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>苹果</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>1200</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>香蕉</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>800</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>苹果</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>1500</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>橘子</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>900</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>苹果</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>1100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>香蕉</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1300</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -583,129 +583,81 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计迟到次数和平均分（COUNTIF与ROUND）</t>
+          <t>第 2 题：第2题：查找客户订单的运费价格</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是一个培训班的班主任，记录了学员的出勤情况和考试成绩。需要统计每个学员的迟到次数，并计算班级平均分（保留1位小数）。</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>练习函数：VLOOKUP</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格用COUNTIF统计“迟到”的次数；在E3单元格用ROUND计算平均成绩并保留1位小数。</t>
+          <t>要求：你有一张快递运费价格表，包含不同重量段的价格。现在要根据客户包裹的重量（例如2.8公斤）查找对应的运费。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>学员</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>出勤状态</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>成绩</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在B7单元格输入公式，根据A7单元格的重量（假设A7输入2.8）查找对应运费。注意：重量在表中为升序，但2.8不在表中，要求返回小于等于2.8的最大重量对应的运费（即2kg的运费）。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>小美</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>88</v>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>运费(元)</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>小刚</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>迟到</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>72</v>
+      <c r="A19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>小丽</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>65</v>
+      <c r="A20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>小强</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>迟到</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>91</v>
+      <c r="A21" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>小华</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>84</v>
+      <c r="A22" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>小军</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>迟到</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>59</v>
+      <c r="A23" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="24">
@@ -718,276 +670,268 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查询商品单价（VLOOKUP精确匹配）</t>
+          <t>第 3 题：第3题：计算员工在职天数（含结束日期）</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>练习函数：VLOOKUP</t>
+          <t>练习函数：DATEDIF</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>要求：你在一家文具店工作，商品价格表在A列和B列。客户报出商品名称，你需要快速找到对应单价来开单。</t>
+          <t>要求：你有一份员工入职日期表，需要计算每位员工截至今天（假设今天为2025-04-01）的在职天数。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格输入公式，根据D2中的商品名称（比如“文件夹”）查找其单价。</t>
+          <t>任务：请在C2单元格输入公式，计算张三的在职天数（从入职日到今天的实际天数），并填充到C3:C4。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>商品</t>
+          <t>员工</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>单价</t>
+          <t>入职日期</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>笔记本</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n">
-        <v>5</v>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>签字笔</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>3</v>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>文件夹</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="n">
-        <v>8</v>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-15</t>
+        </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>胶带</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>便利贴</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="n">
-        <v>4</v>
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：物流重量段运费计算（含条件判断）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>要求：你管理一个物流小仓库，每件货物重量不同，运费规则：重量≤2公斤时运费10元；超过2公斤，超出部分每公斤加收3.5元。要求计算每件货物的运费（保留1位小数）。</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：计算到港天数和判断是否延误（TODAY与DATEDIF）</t>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在C2单元格输入公式，计算A001的运费，并向下填充到C5。</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是一家物流公司的跟单员，表格记录了每批货物的计划到港日期。需要计算今天距离计划到港还有多少天（若已过则为负数），并判断是否延误（超过5天算延误）。</t>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>货物编号</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>任务：在C2单元格输入公式，计算从今天到计划日期的天数差（提示：用DATEDIF，但注意方向）。在D2单元格用IF判断是否延误（若天数差小于-5则“延误”，否则“正常”）。</t>
-        </is>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>货物编号</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>计划到港日期</t>
-        </is>
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-20</t>
-        </is>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-25</t>
-        </is>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>5.8</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>A003</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：多条件统计销售达标订单数量</t>
+        </is>
+      </c>
+    </row>
     <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：根据订单号提取客户和金额（INDEX与MATCH）</t>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIFS</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>要求：你在一家电商公司，订单表包含订单号、客户名和金额。现在需要根据输入的订单号，自动返回对应的客户名和金额，用于对账。</t>
+          <t>要求：你有一张销售订单表，包含销售员和订单金额。现在想知道“张伟”销售员且订单金额大于等于500元的订单有多少个。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格输入订单号（如D003），在F2输入公式返回客户名，在G2输入公式返回金额。</t>
+          <t>任务：请在E2单元格输入公式，统计张伟且金额≥500的订单个数。</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>订单号</t>
+          <t>销售员</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>客户</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
+          <t>金额(元)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>D001</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>王芳</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>200</v>
+          <t>张伟</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>D002</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>李伟</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>350</v>
+          <t>李娜</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>D003</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>陈静</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>120</v>
+          <t>张伟</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>800</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>D004</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>赵磊</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>480</v>
+          <t>王强</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>张伟</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>李娜</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1014,7 +958,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某业务员的销售总额（SUMIF）</t>
+          <t>第 1 题：第1题：统计指定商品的销售总量</t>
         </is>
       </c>
     </row>
@@ -1025,7 +969,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A7,"张三",B2:B7)</f>
+        <f>SUMIF(A2:A7,"苹果",B2:B7)</f>
         <v/>
       </c>
     </row>
@@ -1039,7 +983,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计迟到次数和平均分（COUNTIF与ROUND）</t>
+          <t>第 2 题：第2题：查找客户订单的运费价格</t>
         </is>
       </c>
     </row>
@@ -1049,10 +993,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>E2: =COUNTIF(B2:B7,"迟到") ; E3: =ROUND(AVERAGE(C2:C7),1)</t>
-        </is>
+      <c r="B6" s="2">
+        <f>VLOOKUP(A7,A2:B6,2,TRUE)</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1065,7 +1008,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查询商品单价（VLOOKUP精确匹配）</t>
+          <t>第 3 题：第3题：计算员工在职天数（含结束日期）</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1019,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>VLOOKUP(D2,A2:B6,2,FALSE)</f>
+        <f>DATEDIF(B2,TODAY(),"d")</f>
         <v/>
       </c>
     </row>
@@ -1090,7 +1033,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算到港天数和判断是否延误（TODAY与DATEDIF）</t>
+          <t>第 4 题：第4题：物流重量段运费计算（含条件判断）</t>
         </is>
       </c>
     </row>
@@ -1100,10 +1043,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>C2: =IF(B2&gt;=TODAY(), DATEDIF(TODAY(),B2,"d"), -DATEDIF(B2,TODAY(),"d")) ; D2: =IF(C2&lt;-5,"延误","正常")</t>
-        </is>
+      <c r="B14" s="2">
+        <f>ROUND(IF(B2&lt;=2,10,10+(B2-2)*3.5),1)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1116,7 +1058,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据订单号提取客户和金额（INDEX与MATCH）</t>
+          <t>第 5 题：第5题：多条件统计销售达标订单数量</t>
         </is>
       </c>
     </row>
@@ -1126,10 +1068,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>F2: =INDEX(B2:B5, MATCH(E2,A2:A5,0)) ; G2: =INDEX(C2:C5, MATCH(E2,A2:A5,0))</t>
-        </is>
+      <c r="B18" s="2">
+        <f>COUNTIFS(A2:A7,"张伟",B2:B7,"&gt;=500")</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1160,7 +1101,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某业务员的销售总额（SUMIF）</t>
+          <t>第 1 题：第1题：统计指定商品的销售总量</t>
         </is>
       </c>
     </row>
@@ -1172,14 +1113,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF函数用于按条件求和，语法为SUMIF(条件区域, 条件, 求和区域)。本题中条件区域是A2:A7，条件是“张三”，求和区域是B2:B7，Excel会找出所有销售员为“张三”的行，并把对应销售额相加，结果为3800。</t>
+          <t>SUMIF函数用于按条件求和，语法为SUMIF(条件区域, 条件, 求和区域)。条件区域是A2:A7，条件是“苹果”（文本需加引号），求和区域是B2:B7。此公式会扫描A列，遇到“苹果”就将其对应的B列数字相加，得到100。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计迟到次数和平均分（COUNTIF与ROUND）</t>
+          <t>第 2 题：第2题：查找客户订单的运费价格</t>
         </is>
       </c>
     </row>
@@ -1191,14 +1132,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF用于计数，语法COUNTIF(区域, 条件)，这里区域B2:B7，条件“迟到”，结果为3。ROUND用于四舍五入，语法ROUND(数值, 小数位数)，先用AVERAGE算出平均分(88+72+65+91+84+59)/6=76.5，保留1位小数仍为76.5。</t>
+          <t>VLOOKUP函数用于垂直查找，语法为VLOOKUP(查找值, 表格区域, 返回列号, 匹配方式)。查找值A7=2.8，区域A2:B6，返回第2列，匹配方式为TRUE（近似匹配）。近似匹配要求第一列升序，会找到小于等于2.8的最大值2，返回其运费12元。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查询商品单价（VLOOKUP精确匹配）</t>
+          <t>第 3 题：第3题：计算员工在职天数（含结束日期）</t>
         </is>
       </c>
     </row>
@@ -1210,14 +1151,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP语法：VLOOKUP(查找值, 表格区域, 返回列号, 匹配方式)。查找值D2，区域A2:B6，返回第2列单价，FALSE表示精确匹配。若D2为“文件夹”，则返回8。</t>
+          <t>DATEDIF函数计算两个日期之间的差值，语法为DATEDIF(开始日期, 结束日期, 单位)。开始日期是B2，结束日期用TODAY()表示今天，单位"d"表示天数。此公式返回从2023-05-10到2025-04-01的天数，结果为692天（实际值可能因闰年略有不同）。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算到港天数和判断是否延误（TODAY与DATEDIF）</t>
+          <t>第 4 题：第4题：物流重量段运费计算（含条件判断）</t>
         </is>
       </c>
     </row>
@@ -1229,14 +1170,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>TODAY()返回当前日期。DATEDIF计算两个日期之间的天数差，语法DATEDIF(开始日期, 结束日期, "d")。这里用IF处理正负号：如果计划日期在今天之后，计算从今天到计划日期的天数；否则计算负数。然后D2判断是否小于-5。</t>
+          <t>IF函数做条件判断：如果重量≤2，返回10；否则返回10+(重量-2)*3.5。ROUND函数用于四舍五入，保留1位小数。例如A002重量3.2，超出1.2公斤，加收4.2元，总运费14.2元。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据订单号提取客户和金额（INDEX与MATCH）</t>
+          <t>第 5 题：第5题：多条件统计销售达标订单数量</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1189,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MATCH找到订单号在A列中的位置，语法MATCH(查找值, 查找区域, 0精确匹配)。INDEX根据行号返回对应列的值，语法INDEX(列区域, 行号)。例如E2为D003，MATCH返回3，INDEX(B2:B5,3)返回“陈静”，INDEX(C2:C5,3)返回120。</t>
+          <t>COUNTIFS函数用于多条件计数，语法为COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2)。第一个条件是A列等于“张伟”，第二个条件是金额列&gt;=500。满足条件的行有第3行（800）和第5行（520），共2个。注意条件文本需加引号，数字比较用"&gt;=500"。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定商品的销售总量</t>
+          <t>第 1 题：第1题：统计指定日期的销量</t>
         </is>
       </c>
     </row>
@@ -490,256 +490,323 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家小商店的老板，有一个销售明细表，包含商品名称和销售数量。现在你想快速知道“苹果”这种商品一共卖出了多少件。</t>
+          <t>要求：你是一家小店的店主，记录了每天的销售数量（单位：件）。现在你想快速知道某一天（例如2024年3月15日）的总销量是多少。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：请在E2单元格输入公式，统计“苹果”的总数量。</t>
+          <t>任务：请在E2单元格输入公式，统计日期为2024/3/15的销量总和。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>商品</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>销量</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>2024/3/14</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>香蕉</t>
+          <t>2024/3/15</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>2024/3/15</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>橘子</t>
+          <t>2024/3/16</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>2024/3/15</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>香蕉</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：多条件统计订单金额</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：查找客户订单的运费价格</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>练习函数：SUMIFS</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>练习函数：VLOOKUP</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>要求：你负责一个电商订单表，需要统计"华东"地区、状态为"已发货"的订单总金额，以便核对财务。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>要求：你有一张快递运费价格表，包含不同重量段的价格。现在要根据客户包裹的重量（例如2.8公斤）查找对应的运费。</t>
+          <t>任务：请在D2单元格输入公式，计算满足地区为"华东"且状态为"已发货"的金额总和。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在B7单元格输入公式，根据A7单元格的重量（假设A7输入2.8）查找对应运费。注意：重量在表中为升序，但2.8不在表中，要求返回小于等于2.8的最大重量对应的运费（即2kg的运费）。</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>运费(元)</t>
-        </is>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>8</v>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>800</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>12</v>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>未发货</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>18</v>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>25</v>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>900</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：查找员工联系电话</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：计算员工在职天数（含结束日期）</t>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>练习函数：VLOOKUP</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>练习函数：DATEDIF</t>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>要求：公司有一个员工信息表，你需要根据员工姓名快速找到他的联系电话，方便联系。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>要求：你有一份员工入职日期表，需要计算每位员工截至今天（假设今天为2025-04-01）的在职天数。</t>
+          <t>任务：请在F2单元格输入公式，根据E2单元格中的姓名（输入"王五"）查找其联系电话。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在C2单元格输入公式，计算张三的在职天数（从入职日到今天的实际天数），并填充到C3:C4。</t>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>员工编号</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>联系电话</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>员工</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>入职日期</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>E001</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>13800001111</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>E002</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>13900002222</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>E003</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>2021-11-23</t>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>13700003333</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>E004</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>2024-01-15</t>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>13600004444</t>
         </is>
       </c>
     </row>
@@ -753,74 +820,97 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：物流重量段运费计算（含条件判断）</t>
+          <t>第 4 题：第4题：计算员工年龄和工龄</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>要求：你管理一个物流小仓库，每件货物重量不同，运费规则：重量≤2公斤时运费10元；超过2公斤，超出部分每公斤加收3.5元。要求计算每件货物的运费（保留1位小数）。</t>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>练习函数：DATEDIF</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>任务：请在C2单元格输入公式，计算A001的运费，并向下填充到C5。</t>
+          <t>要求：在人事部，你需要根据员工的出生日期和入职日期，计算每人的年龄和工龄（以年为单位），用于统计。</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>货物编号</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在D2单元格输入公式，计算张三的年龄（截至今天），并在E2计算其工龄（年）。</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>1.5</v>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>出生日期</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>入职日期</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>3.2</v>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>1990/5/20</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>2015/3/10</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>A003</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>2</v>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>1988/11/2</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>2012/7/1</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>A004</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>5.8</v>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>1995/7/15</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>2020/9/30</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -833,105 +923,85 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：多条件统计销售达标订单数量</t>
+          <t>第 5 题：第5题：根据重量计算运费</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>练习函数：COUNTIFS</t>
+          <t>练习函数：IF</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>要求：你有一张销售订单表，包含销售员和订单金额。现在想知道“张伟”销售员且订单金额大于等于500元的订单有多少个。</t>
+          <t>要求：快递公司按包裹重量（公斤）计费：3公斤及以下收费10元，超过3公斤部分每公斤加收2元。你需要为一批包裹计算运费。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>任务：请在E2单元格输入公式，统计张伟且金额≥500的订单个数。</t>
+          <t>任务：请在C2单元格输入公式，计算第一个包裹的运费，然后下拉填充到其他行。</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>销售员</t>
+          <t>包裹编号</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>金额(元)</t>
+          <t>重量(kg)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>张伟</t>
+          <t>A001</t>
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>300</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>李娜</t>
+          <t>A002</t>
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>600</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>张伟</t>
+          <t>A003</t>
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>800</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>王强</t>
+          <t>A004</t>
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>450</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>张伟</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="n">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>李娜</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -958,7 +1028,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定商品的销售总量</t>
+          <t>第 1 题：第1题：统计指定日期的销量</t>
         </is>
       </c>
     </row>
@@ -969,7 +1039,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A7,"苹果",B2:B7)</f>
+        <f>SUMIF(A2:A6,"2024/3/15",B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -983,7 +1053,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：查找客户订单的运费价格</t>
+          <t>第 2 题：第2题：多条件统计订单金额</t>
         </is>
       </c>
     </row>
@@ -994,7 +1064,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>VLOOKUP(A7,A2:B6,2,TRUE)</f>
+        <f>SUMIFS(C2:C6,A2:A6,"华东",B2:B6,"已发货")</f>
         <v/>
       </c>
     </row>
@@ -1008,7 +1078,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算员工在职天数（含结束日期）</t>
+          <t>第 3 题：第3题：查找员工联系电话</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1089,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>DATEDIF(B2,TODAY(),"d")</f>
+        <f>VLOOKUP(E2,A2:C5,3,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -1033,7 +1103,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：物流重量段运费计算（含条件判断）</t>
+          <t>第 4 题：第4题：计算员工年龄和工龄</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1114,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>ROUND(IF(B2&lt;=2,10,10+(B2-2)*3.5),1)</f>
+        <f>DATEDIF(B2,TODAY(),"Y")  和  =DATEDIF(C2,TODAY(),"Y")</f>
         <v/>
       </c>
     </row>
@@ -1058,7 +1128,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：多条件统计销售达标订单数量</t>
+          <t>第 5 题：第5题：根据重量计算运费</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1139,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>COUNTIFS(A2:A7,"张伟",B2:B7,"&gt;=500")</f>
+        <f>IF(B2&lt;=3,10,10+(B2-3)*2)</f>
         <v/>
       </c>
     </row>
@@ -1101,7 +1171,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定商品的销售总量</t>
+          <t>第 1 题：第1题：统计指定日期的销量</t>
         </is>
       </c>
     </row>
@@ -1113,14 +1183,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF函数用于按条件求和，语法为SUMIF(条件区域, 条件, 求和区域)。条件区域是A2:A7，条件是“苹果”（文本需加引号），求和区域是B2:B7。此公式会扫描A列，遇到“苹果”就将其对应的B列数字相加，得到100。</t>
+          <t>SUMIF函数用于按条件求和，语法为SUMIF(条件区域, 条件, 求和区域)。这里条件区域是A2:A6，条件为具体日期"2024/3/15"，求和区域是B2:B6，即可得到该日总销量23件。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：查找客户订单的运费价格</t>
+          <t>第 2 题：第2题：多条件统计订单金额</t>
         </is>
       </c>
     </row>
@@ -1132,14 +1202,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP函数用于垂直查找，语法为VLOOKUP(查找值, 表格区域, 返回列号, 匹配方式)。查找值A7=2.8，区域A2:B6，返回第2列，匹配方式为TRUE（近似匹配）。近似匹配要求第一列升序，会找到小于等于2.8的最大值2，返回其运费12元。</t>
+          <t>SUMIFS用于多条件求和，语法为SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2,...)。这里求和区域是C2:C6，条件区域1是A2:A6（地区），条件1为"华东"，条件区域2是B2:B6（状态），条件2为"已发货"，结果得到2700元。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算员工在职天数（含结束日期）</t>
+          <t>第 3 题：第3题：查找员工联系电话</t>
         </is>
       </c>
     </row>
@@ -1151,14 +1221,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF函数计算两个日期之间的差值，语法为DATEDIF(开始日期, 结束日期, 单位)。开始日期是B2，结束日期用TODAY()表示今天，单位"d"表示天数。此公式返回从2023-05-10到2025-04-01的天数，结果为692天（实际值可能因闰年略有不同）。</t>
+          <t>VLOOKUP按首列查找，语法为VLOOKUP(查找值, 表格区域, 返回列号, 精确匹配)。这里查找值是E2中的姓名"王五"，表格区域A2:C5，返回第3列（联系电话），FALSE表示精确查找，结果为"13700003333"。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：物流重量段运费计算（含条件判断）</t>
+          <t>第 4 题：第4题：计算员工年龄和工龄</t>
         </is>
       </c>
     </row>
@@ -1170,14 +1240,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>IF函数做条件判断：如果重量≤2，返回10；否则返回10+(重量-2)*3.5。ROUND函数用于四舍五入，保留1位小数。例如A002重量3.2，超出1.2公斤，加收4.2元，总运费14.2元。</t>
+          <t>DATEDIF函数计算两个日期之间的差值，语法为DATEDIF(开始日期,结束日期,单位)，"Y"表示整年数。用TODAY()作为结束日期得到当前年龄和工龄。注意需分别填入D2和E2。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：多条件统计销售达标订单数量</t>
+          <t>第 5 题：第5题：根据重量计算运费</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1259,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS函数用于多条件计数，语法为COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2)。第一个条件是A列等于“张伟”，第二个条件是金额列&gt;=500。满足条件的行有第3行（800）和第5行（520），共2个。注意条件文本需加引号，数字比较用"&gt;=500"。</t>
+          <t>IF函数根据条件返回不同结果，语法为IF(条件,真值,假值)。这里条件B2&lt;=3判断重量是否不超过3kg，满足则运费10元，否则计算基础10元加上超出部分每公斤2元。例如A002重量5kg，结果为10+(5-3)*2=14元。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定日期的销量</t>
+          <t>第 1 题：第1题：统计指定月份的总销售额</t>
         </is>
       </c>
     </row>
@@ -490,14 +490,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家小店的店主，记录了每天的销售数量（单位：件）。现在你想快速知道某一天（例如2024年3月15日）的总销量是多少。</t>
+          <t>要求：你是一家小超市的收银员，有一张销售记录表，包含销售日期和销售额。现在需要统计2025年3月份的总销售额。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：请在E2单元格输入公式，统计日期为2024/3/15的销量总和。</t>
+          <t>任务：在E2单元格输入公式，计算日期为2025-03-01到2025-03-31之间的销售额总和。</t>
         </is>
       </c>
     </row>
@@ -509,58 +509,58 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>销量</t>
+          <t>销售额</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2024/3/14</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>5</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2024/3/15</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>8</v>
+        <v>850</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2024/3/15</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>7</v>
+        <v>980</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2024/3/16</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>6</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2024/3/15</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>3</v>
+        <v>760</v>
       </c>
     </row>
     <row r="11">
@@ -573,121 +573,101 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：多条件统计订单金额</t>
+          <t>第 2 题：第2题：统计满足多条件的订单数量</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>练习函数：SUMIFS</t>
+          <t>练习函数：COUNTIFS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>要求：你负责一个电商订单表，需要统计"华东"地区、状态为"已发货"的订单总金额，以便核对财务。</t>
+          <t>要求：你在一家网店工作，订单表包含客户城市和订单状态。需要统计来自“上海”且状态为“已发货”的订单数量。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：请在D2单元格输入公式，计算满足地区为"华东"且状态为"已发货"的金额总和。</t>
+          <t>任务：在E2单元格输入公式，统计城市为“上海”且状态为“已发货”的订单个数。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>地区</t>
+          <t>城市</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
+          <t>订单状态</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
           <t>已发货</t>
         </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>1200</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
           <t>已发货</t>
         </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>800</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>未发货</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>500</v>
+          <t>待发货</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
           <t>已发货</t>
         </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>1500</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
           <t>已发货</t>
         </is>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>900</v>
       </c>
     </row>
     <row r="23">
@@ -700,114 +680,81 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查找员工联系电话</t>
+          <t>第 3 题：第3题：根据重量计算快递费并四舍五入</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>练习函数：VLOOKUP</t>
+          <t>练习函数：ROUND</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>要求：公司有一个员工信息表，你需要根据员工姓名快速找到他的联系电话，方便联系。</t>
+          <t>要求：你负责快递费用计算，运费规则为首重1公斤内8元，续重每公斤加2元（不足1公斤按1公斤算）。实际重量在表格中，需要计算每个包裹的运费并四舍五入到整数。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>任务：请在F2单元格输入公式，根据E2单元格中的姓名（输入"王五"）查找其联系电话。</t>
+          <t>任务：在C2单元格输入公式，计算A001包裹的运费（首重8元，超出部分每公斤加2元，不足1公斤按1公斤计），结果四舍五入到整数，然后下拉填充到C5。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>员工编号</t>
+          <t>包裹编号</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>联系电话</t>
+          <t>实际重量(kg)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>E001</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>13800001111</t>
-        </is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>E002</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>13900002222</t>
-        </is>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>E003</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>13700003333</t>
-        </is>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>E004</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>13600004444</t>
-        </is>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="34">
@@ -820,188 +767,220 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算员工年龄和工龄</t>
+          <t>第 4 题：第4题：根据产品编号查找价格和名称</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>练习函数：DATEDIF</t>
+          <t>练习函数：VLOOKUP</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>要求：在人事部，你需要根据员工的出生日期和入职日期，计算每人的年龄和工龄（以年为单位），用于统计。</t>
+          <t>要求：你有一张产品信息表（产品编号、名称、单价），另一张销售记录表只有产品编号。需要根据产品编号从信息表中查找单价。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>任务：请在D2单元格输入公式，计算张三的年龄（截至今天），并在E2计算其工龄（年）。</t>
+          <t>任务：在另一个工作表的B2单元格输入公式，根据A2单元格中的产品编号（例如P003）从上述信息表中查找对应的单价。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>姓名</t>
+          <t>产品编号</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>出生日期</t>
+          <t>产品名称</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>入职日期</t>
+          <t>单价</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>1990/5/20</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>2015/3/10</t>
-        </is>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>1988/11/2</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>2012/7/1</t>
-        </is>
+          <t>香蕉</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>1995/7/15</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>2020/9/30</t>
-        </is>
+          <t>橙子</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>4.8</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>葡萄</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>西瓜</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：根据重量计算运费</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>练习函数：IF</t>
-        </is>
-      </c>
-    </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>要求：快递公司按包裹重量（公斤）计费：3公斤及以下收费10元，超过3公斤部分每公斤加收2元。你需要为一批包裹计算运费。</t>
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：计算员工入职到今天的工龄（年数）</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在C2单元格输入公式，计算第一个包裹的运费，然后下拉填充到其他行。</t>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>练习函数：DATEDIF</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>包裹编号</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是HR，需要计算每位员工从入职日期到今天（2025-04-15）的工龄，精确到年。</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>2.5</v>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>任务：在C2单元格输入公式，计算张三的工龄（年数，向下取整），使用今天日期，并下拉填充到C5。</t>
+        </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n">
-        <v>5</v>
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>员工姓名</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>入职日期</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>A003</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="n">
-        <v>3</v>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>2018-03-12</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>A004</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="n">
-        <v>7.2</v>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>2020-07-01</t>
+        </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>2022-11-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>2015-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1028,7 +1007,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定日期的销量</t>
+          <t>第 1 题：第1题：统计指定月份的总销售额</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1018,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"2024/3/15",B2:B6)</f>
+        <f>SUMIF(A2:A6,"&gt;=2025-03-01",B2:B6)-SUMIF(A2:A6,"&gt;2025-03-31",B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -1053,7 +1032,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：多条件统计订单金额</t>
+          <t>第 2 题：第2题：统计满足多条件的订单数量</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1043,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>SUMIFS(C2:C6,A2:A6,"华东",B2:B6,"已发货")</f>
+        <f>COUNTIFS(A2:A6,"上海",B2:B6,"已发货")</f>
         <v/>
       </c>
     </row>
@@ -1078,7 +1057,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查找员工联系电话</t>
+          <t>第 3 题：第3题：根据重量计算快递费并四舍五入</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1068,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>VLOOKUP(E2,A2:C5,3,FALSE)</f>
+        <f>ROUND(8+MAX(0,CEILING(B2-1,1))*2,0)</f>
         <v/>
       </c>
     </row>
@@ -1103,7 +1082,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算员工年龄和工龄</t>
+          <t>第 4 题：第4题：根据产品编号查找价格和名称</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1093,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>DATEDIF(B2,TODAY(),"Y")  和  =DATEDIF(C2,TODAY(),"Y")</f>
+        <f>VLOOKUP(A2,Sheet2!A2:C6,3,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -1128,7 +1107,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据重量计算运费</t>
+          <t>第 5 题：第5题：计算员工入职到今天的工龄（年数）</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1118,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>IF(B2&lt;=3,10,10+(B2-3)*2)</f>
+        <f>DATEDIF(B2,TODAY(),"Y")</f>
         <v/>
       </c>
     </row>
@@ -1171,7 +1150,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定日期的销量</t>
+          <t>第 1 题：第1题：统计指定月份的总销售额</t>
         </is>
       </c>
     </row>
@@ -1183,14 +1162,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF函数用于按条件求和，语法为SUMIF(条件区域, 条件, 求和区域)。这里条件区域是A2:A6，条件为具体日期"2024/3/15"，求和区域是B2:B6，即可得到该日总销量23件。</t>
+          <t>SUMIF函数用于按条件求和。先用SUMIF汇总日期大于等于3月1日的销售额，再减去日期大于3月31日的销售额，得到3月整月总和。注意日期比较要加引号。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：多条件统计订单金额</t>
+          <t>第 2 题：第2题：统计满足多条件的订单数量</t>
         </is>
       </c>
     </row>
@@ -1202,14 +1181,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS用于多条件求和，语法为SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2,...)。这里求和区域是C2:C6，条件区域1是A2:A6（地区），条件1为"华东"，条件区域2是B2:B6（状态），条件2为"已发货"，结果得到2700元。</t>
+          <t>COUNTIFS函数可以设置多个条件进行计数。第一个区域是城市列，条件是“上海”；第二个区域是状态列，条件是“已发货”。两个条件同时满足才计数。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查找员工联系电话</t>
+          <t>第 3 题：第3题：根据重量计算快递费并四舍五入</t>
         </is>
       </c>
     </row>
@@ -1221,14 +1200,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP按首列查找，语法为VLOOKUP(查找值, 表格区域, 返回列号, 精确匹配)。这里查找值是E2中的姓名"王五"，表格区域A2:C5，返回第3列（联系电话），FALSE表示精确查找，结果为"13700003333"。</t>
+          <t>先用CEILING(B2-1,1)将超出首重的重量向上取整到1公斤的倍数，再乘以2元，加8元首重费。ROUND函数将结果四舍五入到0位小数。MAX确保不出现负数。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算员工年龄和工龄</t>
+          <t>第 4 题：第4题：根据产品编号查找价格和名称</t>
         </is>
       </c>
     </row>
@@ -1240,14 +1219,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF函数计算两个日期之间的差值，语法为DATEDIF(开始日期,结束日期,单位)，"Y"表示整年数。用TODAY()作为结束日期得到当前年龄和工龄。注意需分别填入D2和E2。</t>
+          <t>VLOOKUP函数的参数：查找值A2，查找区域（产品信息表的A2:C6），返回第3列的单价，FALSE表示精确匹配。注意区域要用绝对引用或跨表引用。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据重量计算运费</t>
+          <t>第 5 题：第5题：计算员工入职到今天的工龄（年数）</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1238,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>IF函数根据条件返回不同结果，语法为IF(条件,真值,假值)。这里条件B2&lt;=3判断重量是否不超过3kg，满足则运费10元，否则计算基础10元加上超出部分每公斤2元。例如A002重量5kg，结果为10+(5-3)*2=14元。</t>
+          <t>DATEDIF函数计算两个日期之间的差异。参数：开始日期B2，结束日期使用TODAY()获取当前日期，"Y"表示返回整年数。TODAY()会自动更新，所以工龄会随时间变化。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定月份的总销售额</t>
+          <t>第 1 题：第1题：汇总指定日期的销售总金额</t>
         </is>
       </c>
     </row>
@@ -490,14 +490,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家小超市的收银员，有一张销售记录表，包含销售日期和销售额。现在需要统计2025年3月份的总销售额。</t>
+          <t>要求：你是一名店铺店员，需要根据每日销售记录快速汇总某一天的销售额。表格中记录了日期和销售金额，请使用 SUMIF 函数计算 2024/12/05 当天的总销售额。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格输入公式，计算日期为2025-03-01到2025-03-31之间的销售额总和。</t>
+          <t>任务：在任意空白单元格（例如 D2）输入公式，计算日期为“2024/12/05”的销售金额总和。</t>
         </is>
       </c>
     </row>
@@ -509,14 +509,14 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>销售金额</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2024/12/03</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
@@ -526,7 +526,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2024/12/04</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
@@ -536,31 +536,31 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2024/12/05</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>980</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2024/12/05</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1500</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024/12/06</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>760</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="11">
@@ -573,410 +573,447 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计满足多条件的订单数量</t>
+          <t>第 2 题：第2题：统计发货单中某产品的订单数量</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>练习函数：COUNTIFS</t>
+          <t>练习函数：COUNTIF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>要求：你在一家网店工作，订单表包含客户城市和订单状态。需要统计来自“上海”且状态为“已发货”的订单数量。</t>
+          <t>要求：你在一家电商仓库工作，需要统计某款产品在发货单中出现的次数。表格中有一列是产品名称，请使用 COUNTIF 函数统计产品“蓝牙耳机”出现的次数。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格输入公式，统计城市为“上海”且状态为“已发货”的订单个数。</t>
+          <t>任务：在任意空白单元格（例如 D2）输入公式，统计“蓝牙耳机”出现次数。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>城市</t>
+          <t>订单号</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>订单状态</t>
+          <t>产品名称</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>A001</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>已发货</t>
+          <t>蓝牙耳机</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>A002</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>已发货</t>
+          <t>充电器</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>A003</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>待发货</t>
+          <t>蓝牙耳机</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>A004</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>已发货</t>
+          <t>手机壳</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>A005</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>已发货</t>
+          <t>蓝牙耳机</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>A006</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>数据线</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：根据重量计算快递费并四舍五入</t>
-        </is>
-      </c>
-    </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>练习函数：ROUND</t>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：按客户和产品类别汇总销售额</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>要求：你负责快递费用计算，运费规则为首重1公斤内8元，续重每公斤加2元（不足1公斤按1公斤算）。实际重量在表格中，需要计算每个包裹的运费并四舍五入到整数。</t>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>练习函数：SUMIFS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>任务：在C2单元格输入公式，计算A001包裹的运费（首重8元，超出部分每公斤加2元，不足1公斤按1公斤计），结果四舍五入到整数，然后下拉填充到C5。</t>
+          <t>要求：你是一家贸易公司的销售助理，需要根据多条件汇总销售额。表格中有客户名称、销售区域和销售额，请使用 SUMIFS 函数计算客户“华为”在“华东”区域的销售总额。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>包裹编号</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>实际重量(kg)</t>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>任务：在任意空白单元格（例如 E2）输入公式，求客户为“华为”且区域为“华东”的销售额之和。</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>1.2</v>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>客户</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>销售额</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n">
-        <v>2.8</v>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>5000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>A003</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>0.5</v>
+          <t>小米</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>3000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>A004</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="n">
-        <v>3.1</v>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>6500</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>小米</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：根据产品编号查找价格和名称</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>练习函数：VLOOKUP</t>
-        </is>
-      </c>
-    </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一张产品信息表（产品编号、名称、单价），另一张销售记录表只有产品编号。需要根据产品编号从信息表中查找单价。</t>
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：查找订单对应的客户姓名并容错</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>任务：在另一个工作表的B2单元格输入公式，根据A2单元格中的产品编号（例如P003）从上述信息表中查找对应的单价。</t>
+          <t>要求：你在一家客服中心工作，需要根据订单号快速查找客户姓名。表格中有订单号和客户姓名，请使用 XLOOKUP 函数查找订单“D103”的客户，并用 IFERROR 处理找不到的情况（显示“未找到”）。</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>产品编号</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>产品名称</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>任务：在任意空白单元格（例如 D2）输入公式，根据订单号 D103 查找客户姓名，如果找不到则返回“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>P001</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>苹果</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>5.5</v>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>客户姓名</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>D101</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>香蕉</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>3.2</v>
+          <t>张三</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>P003</t>
+          <t>D102</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>橙子</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>4.8</v>
+          <t>李四</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>D103</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>葡萄</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>7.9</v>
+          <t>王五</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>D104</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>西瓜</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>2.5</v>
+          <t>赵六</t>
+        </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>钱七</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：计算员工入职到今天的工龄（年数）</t>
-        </is>
-      </c>
-    </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>练习函数：DATEDIF</t>
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：计算今日到港天数和运费重量分段</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>要求：你是HR，需要计算每位员工从入职日期到今天（2025-04-15）的工龄，精确到年。</t>
+          <t>要求：你是一家物流公司的单证员，需要计算每票货物的到港天数（从到港日期到今天），并根据重量计算运费。表格中记录了货物名称、到港日期和重量（公斤），请完成以下两个任务：
+1. 使用 TODAY 和 DATEDIF 计算到港天数（今天日期 - 到港日期，单位天）；
+2. 使用 IF 和 ROUND 根据重量计算运费：若重量 ≤10公斤，运费=重量*5；否则运费=重量*4，并四舍五入到整数。</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>任务：在C2单元格输入公式，计算张三的工龄（年数，向下取整），使用今天日期，并下拉填充到C5。</t>
+          <t>任务：在 D2 单元格输入公式计算第一行货物的到港天数；在 E2 单元格输入公式计算第一行货物的运费。然后可下拉填充到其他行。</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>员工姓名</t>
+          <t>货物名称</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>入职日期</t>
+          <t>到港日期</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>重量</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>纺织品</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>2018-03-12</t>
-        </is>
+          <t>2024/11/20</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
-        </is>
+          <t>2024/12/01</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>2022-11-20</t>
-        </is>
+          <t>2024/12/10</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>赵六</t>
+          <t>机械零件</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>2015-09-05</t>
-        </is>
+          <t>2024/11/15</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="57">
@@ -1007,7 +1044,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定月份的总销售额</t>
+          <t>第 1 题：第1题：汇总指定日期的销售总金额</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1055,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"&gt;=2025-03-01",B2:B6)-SUMIF(A2:A6,"&gt;2025-03-31",B2:B6)</f>
+        <f>SUMIF(A2:A6, "2024/12/05", B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -1032,7 +1069,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计满足多条件的订单数量</t>
+          <t>第 2 题：第2题：统计发货单中某产品的订单数量</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1080,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(A2:A6,"上海",B2:B6,"已发货")</f>
+        <f>COUNTIF(B2:B7, "蓝牙耳机")</f>
         <v/>
       </c>
     </row>
@@ -1057,7 +1094,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据重量计算快递费并四舍五入</t>
+          <t>第 3 题：第3题：按客户和产品类别汇总销售额</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1105,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>ROUND(8+MAX(0,CEILING(B2-1,1))*2,0)</f>
+        <f>SUMIFS(C2:C6, A2:A6, "华为", B2:B6, "华东")</f>
         <v/>
       </c>
     </row>
@@ -1082,7 +1119,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：根据产品编号查找价格和名称</t>
+          <t>第 4 题：第4题：查找订单对应的客户姓名并容错</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1130,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>VLOOKUP(A2,Sheet2!A2:C6,3,FALSE)</f>
+        <f>IFERROR(XLOOKUP("D103", A2:A6, B2:B6), "未找到")</f>
         <v/>
       </c>
     </row>
@@ -1107,7 +1144,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：计算员工入职到今天的工龄（年数）</t>
+          <t>第 5 题：第5题：计算今日到港天数和运费重量分段</t>
         </is>
       </c>
     </row>
@@ -1117,9 +1154,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2">
-        <f>DATEDIF(B2,TODAY(),"Y")</f>
-        <v/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>D2: =DATEDIF(B2, TODAY(), "d")   E2: =ROUND(IF(C2&lt;=10, C2*5, C2*4), 0)</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1150,7 +1188,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定月份的总销售额</t>
+          <t>第 1 题：第1题：汇总指定日期的销售总金额</t>
         </is>
       </c>
     </row>
@@ -1162,14 +1200,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF函数用于按条件求和。先用SUMIF汇总日期大于等于3月1日的销售额，再减去日期大于3月31日的销售额，得到3月整月总和。注意日期比较要加引号。</t>
+          <t>SUMIF 函数用于按条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。本题中条件区域是日期列 A2:A6，条件是文本“2024/12/05”，求和区域是销售金额列 B2:B6。函数会扫描条件区域，找到所有等于该日期的行，并将对应的销售金额相加，结果为 2300+1450=3750。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计满足多条件的订单数量</t>
+          <t>第 2 题：第2题：统计发货单中某产品的订单数量</t>
         </is>
       </c>
     </row>
@@ -1181,14 +1219,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS函数可以设置多个条件进行计数。第一个区域是城市列，条件是“上海”；第二个区域是状态列，条件是“已发货”。两个条件同时满足才计数。</t>
+          <t>COUNTIF 函数用于按条件计数，语法为 COUNTIF(区域, 条件)。本题中区域是产品名称列 B2:B7，条件是文本“蓝牙耳机”。函数会遍历该区域，统计等于该文本的单元格个数，结果为 3。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据重量计算快递费并四舍五入</t>
+          <t>第 3 题：第3题：按客户和产品类别汇总销售额</t>
         </is>
       </c>
     </row>
@@ -1200,14 +1238,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>先用CEILING(B2-1,1)将超出首重的重量向上取整到1公斤的倍数，再乘以2元，加8元首重费。ROUND函数将结果四舍五入到0位小数。MAX确保不出现负数。</t>
+          <t>SUMIFS 用于多条件求和，语法为 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2, ...)。本题中求和区域是销售额 C2:C6，条件区域1是客户列 A2:A6，条件1为“华为”，条件区域2是区域列 B2:B6，条件2为“华东”。函数只对同时满足两个条件的行求和，即华为在华东的两笔：5000+7200=12200。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：根据产品编号查找价格和名称</t>
+          <t>第 4 题：第4题：查找订单对应的客户姓名并容错</t>
         </is>
       </c>
     </row>
@@ -1219,14 +1257,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP函数的参数：查找值A2，查找区域（产品信息表的A2:C6），返回第3列的单价，FALSE表示精确匹配。注意区域要用绝对引用或跨表引用。</t>
+          <t>XLOOKUP 用于查找并返回匹配值，语法为 XLOOKUP(查找值, 查找数组, 返回数组, [未找到值])，本题中查找值是“D103”，查找数组是订单号列 A2:A6，返回数组是客户姓名列 B2:B6。XLOOKUP 会返回“王五”。IFERROR 函数用于捕获错误，语法为 IFERROR(公式, 出错时返回值)，如果 XLOOKUP 找不到（在更复杂情况会返回错误），则显示“未找到”，本题正常返回“王五”。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：计算员工入职到今天的工龄（年数）</t>
+          <t>第 5 题：第5题：计算今日到港天数和运费重量分段</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1276,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF函数计算两个日期之间的差异。参数：开始日期B2，结束日期使用TODAY()获取当前日期，"Y"表示返回整年数。TODAY()会自动更新，所以工龄会随时间变化。</t>
+          <t>DATEDIF 函数计算两个日期之间的差值，语法为 DATEDIF(开始日期, 结束日期, "d")，这里开始日期是到港日期 B2，结束日期是 TODAY()（当前日期），"d"表示返回天数。TODAY() 返回今天的日期。运费计算用 IF 判断：IF(重量&lt;=10, 重量*5, 重量*4)，然后 ROUND 函数四舍五入到 0 位小数，语法为 ROUND(数值, 0)。例如第一行重量 8 公斤，满足≤10，运费=8*5=40，ROUND 后仍为 40。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：汇总指定日期的销售总金额</t>
+          <t>第 1 题：第1题：统计销售总额</t>
         </is>
       </c>
     </row>
@@ -490,77 +490,77 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一名店铺店员，需要根据每日销售记录快速汇总某一天的销售额。表格中记录了日期和销售金额，请使用 SUMIF 函数计算 2024/12/05 当天的总销售额。</t>
+          <t>要求：你是一家小店的店主，记录了几笔销售数据。现在想统计“线上”渠道的总销售额。请使用SUMIF函数计算。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在任意空白单元格（例如 D2）输入公式，计算日期为“2024/12/05”的销售金额总和。</t>
+          <t>任务：请在一个单元格（如E2）输入公式，计算“线上”销售额总和。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>渠道</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>销售金额</t>
+          <t>销售额</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2024/12/03</t>
+          <t>线下</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>1200</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2024/12/04</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>850</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2024/12/05</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2300</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2024/12/05</t>
+          <t>线下</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1450</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2024/12/06</t>
+          <t>线上</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>1900</v>
+        <v>500</v>
       </c>
     </row>
     <row r="11">
@@ -573,28 +573,28 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计发货单中某产品的订单数量</t>
+          <t>第 2 题：第2题：统计达标订单数</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>练习函数：COUNTIF</t>
+          <t>练习函数：COUNTIFS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>要求：你在一家电商仓库工作，需要统计某款产品在发货单中出现的次数。表格中有一列是产品名称，请使用 COUNTIF 函数统计产品“蓝牙耳机”出现的次数。</t>
+          <t>要求：你管理一份订单表，需要统计金额大于等于500且状态为“已发货”的订单数量。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：在任意空白单元格（例如 D2）输入公式，统计“蓝牙耳机”出现次数。</t>
+          <t>任务：请在一个单元格（如E2）输入公式，统计符合条件的订单数。</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>产品名称</t>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
         </is>
       </c>
     </row>
@@ -616,9 +621,12 @@
           <t>A001</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>蓝牙耳机</t>
+      <c r="B18" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
         </is>
       </c>
     </row>
@@ -628,9 +636,12 @@
           <t>A002</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>充电器</t>
+      <c r="B19" s="4" t="n">
+        <v>600</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
         </is>
       </c>
     </row>
@@ -640,9 +651,12 @@
           <t>A003</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>蓝牙耳机</t>
+      <c r="B20" s="4" t="n">
+        <v>450</v>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>未发货</t>
         </is>
       </c>
     </row>
@@ -652,9 +666,12 @@
           <t>A004</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>手机壳</t>
+      <c r="B21" s="4" t="n">
+        <v>700</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
         </is>
       </c>
     </row>
@@ -664,9 +681,12 @@
           <t>A005</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>蓝牙耳机</t>
+      <c r="B22" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
         </is>
       </c>
     </row>
@@ -676,9 +696,12 @@
           <t>A006</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>数据线</t>
+      <c r="B23" s="4" t="n">
+        <v>800</v>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>未发货</t>
         </is>
       </c>
     </row>
@@ -692,332 +715,311 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按客户和产品类别汇总销售额</t>
+          <t>第 3 题：第3题：查询员工部门</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>练习函数：SUMIFS</t>
+          <t>练习函数：VLOOKUP</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家贸易公司的销售助理，需要根据多条件汇总销售额。表格中有客户名称、销售区域和销售额，请使用 SUMIFS 函数计算客户“华为”在“华东”区域的销售总额。</t>
+          <t>要求：你有一份员工信息表，需要根据员工ID查找对应的部门。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>任务：在任意空白单元格（例如 E2）输入公式，求客户为“华为”且区域为“华东”的销售额之和。</t>
+          <t>任务：假设在F1单元格输入了员工ID“E03”，请在G1单元格输入公式，自动返回该员工所属部门。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>客户</t>
+          <t>员工ID</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>区域</t>
+          <t>姓名</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>部门</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>华为</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>5000</v>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>销售部</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>3000</v>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>市场部</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>华为</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>6500</v>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>技术部</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>华为</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>7200</v>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>人事部</t>
+        </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>4100</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：计算到港天数</t>
+        </is>
+      </c>
+    </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：查找订单对应的客户姓名并容错</t>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>练习函数：DATEDIF</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>要求：你在一家客服中心工作，需要根据订单号快速查找客户姓名。表格中有订单号和客户姓名，请使用 XLOOKUP 函数查找订单“D103”的客户，并用 IFERROR 处理找不到的情况（显示“未找到”）。</t>
+          <t>要求：你有一批货物，记录了订舱日期和实际到港日期，需要计算运输耗时（天数）。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>任务：在任意空白单元格（例如 D2）输入公式，根据订单号 D103 查找客户姓名，如果找不到则返回“未找到”。</t>
+          <t>任务：请在D2单元格输入公式，计算第一行货物的到港天数（到港日期减订舱日期），然后下拉填充到D4。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>订单号</t>
+          <t>货物编号</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>客户姓名</t>
+          <t>订舱日期</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>D101</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>2024-01-05</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-10</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>D102</t>
+          <t>C002</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>2024-02-01</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-08</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>D103</t>
+          <t>C003</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-15</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>D104</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>D105</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>钱七</t>
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：提取并计算重量费用</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一份物流报价表，需要根据包裹重量（公斤）和运输方式自动匹配费用，同时提取包裹编号中的数字部分。</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：计算今日到港天数和运费重量分段</t>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>任务：在D2单元格输入公式，根据C列的运输方式和B列重量（取整数值）从报价表查询费用。例如，P1001是陆运2.5kg，按2kg计费，结果为18。同时，在E2单元格提取包裹编号中的数字部分（如1001）。</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是一家物流公司的单证员，需要计算每票货物的到港天数（从到港日期到今天），并根据重量计算运费。表格中记录了货物名称、到港日期和重量（公斤），请完成以下两个任务：
-1. 使用 TODAY 和 DATEDIF 计算到港天数（今天日期 - 到港日期，单位天）；
-2. 使用 IF 和 ROUND 根据重量计算运费：若重量 ≤10公斤，运费=重量*5；否则运费=重量*4，并四舍五入到整数。</t>
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>包裹编号</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>运输方式</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 D2 单元格输入公式计算第一行货物的到港天数；在 E2 单元格输入公式计算第一行货物的运费。然后可下拉填充到其他行。</t>
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>P1001</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>陆运</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>货物名称</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>重量</t>
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>P1002</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>空运</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>纺织品</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>2024/11/20</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>8</v>
+          <t>P1003</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>海运</t>
+        </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>电子产品</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>2024/12/01</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>2024/12/10</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>机械零件</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>2024/11/15</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1044,7 +1046,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：汇总指定日期的销售总金额</t>
+          <t>第 1 题：第1题：统计销售总额</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1057,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6, "2024/12/05", B2:B6)</f>
+        <f>SUMIF(A2:A6,"线上",B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -1069,7 +1071,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计发货单中某产品的订单数量</t>
+          <t>第 2 题：第2题：统计达标订单数</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1082,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF(B2:B7, "蓝牙耳机")</f>
+        <f>COUNTIFS(B2:B7,"&gt;=500",C2:C7,"已发货")</f>
         <v/>
       </c>
     </row>
@@ -1094,7 +1096,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按客户和产品类别汇总销售额</t>
+          <t>第 3 题：第3题：查询员工部门</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1107,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>SUMIFS(C2:C6, A2:A6, "华为", B2:B6, "华东")</f>
+        <f>VLOOKUP(F1,A2:C5,3,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -1119,7 +1121,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：查找订单对应的客户姓名并容错</t>
+          <t>第 4 题：第4题：计算到港天数</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1132,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>IFERROR(XLOOKUP("D103", A2:A6, B2:B6), "未找到")</f>
+        <f>DATEDIF(B2,C2,"d")</f>
         <v/>
       </c>
     </row>
@@ -1144,7 +1146,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：计算今日到港天数和运费重量分段</t>
+          <t>第 5 题：第5题：提取并计算重量费用</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1158,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>D2: =DATEDIF(B2, TODAY(), "d")   E2: =ROUND(IF(C2&lt;=10, C2*5, C2*4), 0)</t>
+          <t>D2: =INDEX($B$10:$D$12,MATCH(C2,$A$10:$A$12,0),MATCH(ROUNDDOWN(B2,0),$B$9:$D$9,0)) , E2: =VALUE(RIGHT(A2,LEN(A2)-1))</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1190,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：汇总指定日期的销售总金额</t>
+          <t>第 1 题：第1题：统计销售总额</t>
         </is>
       </c>
     </row>
@@ -1200,14 +1202,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 函数用于按条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。本题中条件区域是日期列 A2:A6，条件是文本“2024/12/05”，求和区域是销售金额列 B2:B6。函数会扫描条件区域，找到所有等于该日期的行，并将对应的销售金额相加，结果为 2300+1450=3750。</t>
+          <t>SUMIF(条件区域, 条件, 求和区域)。本例中，条件区域是A2:A6（渠道列），条件是“线上”，求和区域是B2:B6（销售额列）。函数会扫描条件区域，找到所有等于“线上”的行，对应求和区域的值相加，结果为450+250+500=1200。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计发货单中某产品的订单数量</t>
+          <t>第 2 题：第2题：统计达标订单数</t>
         </is>
       </c>
     </row>
@@ -1219,14 +1221,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF 函数用于按条件计数，语法为 COUNTIF(区域, 条件)。本题中区域是产品名称列 B2:B7，条件是文本“蓝牙耳机”。函数会遍历该区域，统计等于该文本的单元格个数，结果为 3。</t>
+          <t>COUNTIFS可以设置多个条件区域和条件，只有同时满足所有条件的行才计数。本例中，条件1是金额列B2:B7大于等于500，条件2是状态列C2:C7等于“已发货”。符合条件的订单有A002、A004、A005，共3个。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按客户和产品类别汇总销售额</t>
+          <t>第 3 题：第3题：查询员工部门</t>
         </is>
       </c>
     </row>
@@ -1238,14 +1240,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 用于多条件求和，语法为 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2, ...)。本题中求和区域是销售额 C2:C6，条件区域1是客户列 A2:A6，条件1为“华为”，条件区域2是区域列 B2:B6，条件2为“华东”。函数只对同时满足两个条件的行求和，即华为在华东的两笔：5000+7200=12200。</t>
+          <t>VLOOKUP(查找值, 表格区域, 列序号, 匹配方式)。查找值是F1中的“E03”，表格区域是A2:C5（从员工ID列到部门列），列序号是3（部门在第三列），FALSE表示精确匹配。函数会找到E03对应的部门“技术部”。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：查找订单对应的客户姓名并容错</t>
+          <t>第 4 题：第4题：计算到港天数</t>
         </is>
       </c>
     </row>
@@ -1257,14 +1259,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP 用于查找并返回匹配值，语法为 XLOOKUP(查找值, 查找数组, 返回数组, [未找到值])，本题中查找值是“D103”，查找数组是订单号列 A2:A6，返回数组是客户姓名列 B2:B6。XLOOKUP 会返回“王五”。IFERROR 函数用于捕获错误，语法为 IFERROR(公式, 出错时返回值)，如果 XLOOKUP 找不到（在更复杂情况会返回错误），则显示“未找到”，本题正常返回“王五”。</t>
+          <t>DATEDIF(开始日期, 结束日期, 单位)可以计算日期差。单位“d”表示天数。本例中，开始日期是B2（订舱日期），结束日期是C2（到港日期），结果为5天。注意：Excel中的日期必须为真正的日期格式，而非文本。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：计算今日到港天数和运费重量分段</t>
+          <t>第 5 题：第5题：提取并计算重量费用</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1278,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF 函数计算两个日期之间的差值，语法为 DATEDIF(开始日期, 结束日期, "d")，这里开始日期是到港日期 B2，结束日期是 TODAY()（当前日期），"d"表示返回天数。TODAY() 返回今天的日期。运费计算用 IF 判断：IF(重量&lt;=10, 重量*5, 重量*4)，然后 ROUND 函数四舍五入到 0 位小数，语法为 ROUND(数值, 0)。例如第一行重量 8 公斤，满足≤10，运费=8*5=40，ROUND 后仍为 40。</t>
+          <t>首先，INDEX(区域, 行号, 列号)可以从区域取数。MATCH(查找值, 查找区域, 0)返回位置。外层MATCH找到运输方式在报价表行号，内层MATCH用ROUNDDOWN(B2,0)将重量向下取整（如2.5→2）再匹配对应的重量列号，从而返回费用。E2用RIGHT提取右边字符，去除首字符“P”，再VALUE转为数字。注意：报价表数据区域为A9:D12（包含表头），公式中的引用请根据实际位置调整。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计销售总额</t>
+          <t>第 1 题：第1题：销售数据汇总（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -490,21 +490,21 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家小店的店主，记录了几笔销售数据。现在想统计“线上”渠道的总销售额。请使用SUMIF函数计算。</t>
+          <t>要求：你有一张2024年各销售人员的销售额表，需要统计“张三”的总销售额。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：请在一个单元格（如E2）输入公式，计算“线上”销售额总和。</t>
+          <t>任务：在E2单元格输入公式，计算“张三”的销售总额。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>渠道</t>
+          <t>销售人员</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -516,51 +516,51 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>300</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>450</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>250</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>线下</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>100</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>线上</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>500</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="11">
@@ -573,453 +573,396 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计达标订单数</t>
+          <t>第 2 题：第2题：库存到货天数（TODAY 和 DATEDIF）</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIFS</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>要求：你的仓库里有一批货物的入库日期，需要计算每批货到今天为止已经存放了多少天。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>要求：你管理一份订单表，需要统计金额大于等于500且状态为“已发货”的订单数量。</t>
+          <t>任务：在C2单元格输入公式，计算A001货物的存放天数（假设今天为2025-03-01）。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在一个单元格（如E2）输入公式，统计符合条件的订单数。</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>货物编号</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>入库日期</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>已发货</t>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>600</v>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：查找员工职位（VLOOKUP 和 IFERROR）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有员工信息表，需要通过员工编号查找对应的部门。如果编号不存在，则显示“未找到”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>任务：在G2单元格输入公式，根据F2中的员工编号（假设输入E02）查找部门，若找不到则显示“未找到”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>员工编号</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>部门</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>赵一</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>财务部</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>钱二</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>人事部</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>孙三</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>市场部</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：订单重量分析（SUMIFS 和 COUNTIFS）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一张物流订单表，需要统计“华东区”中“已发货”订单的总重量和订单数量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>任务：在E2单元格计算华东区且已发货的总重量，在F2计算订单数量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>华东区</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>已发货</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>A003</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>450</v>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="D35" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>华北区</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>华东区</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>未发货</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>A004</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>700</v>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="D37" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>华东区</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>已发货</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>A005</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="D38" s="4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>华南区</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>已发货</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>A006</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>800</v>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>未发货</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="D39" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：查询员工部门</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>练习函数：VLOOKUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一份员工信息表，需要根据员工ID查找对应的部门。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>任务：假设在F1单元格输入了员工ID“E03”，请在G1单元格输入公式，自动返回该员工所属部门。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>员工ID</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>部门</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>销售部</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>E02</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>市场部</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>E03</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>技术部</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>E04</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>人事部</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：计算到港天数</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>练习函数：DATEDIF</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一批货物，记录了订舱日期和实际到港日期，需要计算运输耗时（天数）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在D2单元格输入公式，计算第一行货物的到港天数（到港日期减订舱日期），然后下拉填充到D4。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>货物编号</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>订舱日期</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
-        </is>
-      </c>
-    </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>C001</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-05</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-10</t>
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：提取并匹配产品信息（RIGHT、MID、INDEX、MATCH）</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>C002</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-01</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-08</t>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一张产品代码表，代码格式为“XX-YYYY-商品编号”，需要从代码中提取商品编号（末尾3位），并根据编号在产品表中查找产品名称。</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>C003</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-10</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-15</t>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>任务：在C2单元格输入公式，根据A2的产品代码提取末尾编号，并用INDEX和MATCH查找对应产品名称。</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>产品代码</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>AA-1001-001</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>螺丝</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：提取并计算重量费用</t>
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>BB-1002-002</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>螺母</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一份物流报价表，需要根据包裹重量（公斤）和运输方式自动匹配费用，同时提取包裹编号中的数字部分。</t>
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>CC-1003-003</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>垫片</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>任务：在D2单元格输入公式，根据C列的运输方式和B列重量（取整数值）从报价表查询费用。例如，P1001是陆运2.5kg，按2kg计费，结果为18。同时，在E2单元格提取包裹编号中的数字部分（如1001）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>包裹编号</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>运输方式</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>P1001</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>陆运</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>P1002</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>空运</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>P1003</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>海运</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1046,7 +989,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计销售总额</t>
+          <t>第 1 题：第1题：销售数据汇总（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1000,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"线上",B2:B6)</f>
+        <f>SUMIF(A2:A6,"张三",B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -1071,7 +1014,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计达标订单数</t>
+          <t>第 2 题：第2题：库存到货天数（TODAY 和 DATEDIF）</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1025,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(B2:B7,"&gt;=500",C2:C7,"已发货")</f>
+        <f>DATEDIF(B2, TODAY(), "d")</f>
         <v/>
       </c>
     </row>
@@ -1096,7 +1039,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查询员工部门</t>
+          <t>第 3 题：第3题：查找员工职位（VLOOKUP 和 IFERROR）</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1050,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>VLOOKUP(F1,A2:C5,3,FALSE)</f>
+        <f>IFERROR(VLOOKUP(F2, A2:C4, 3, FALSE), "未找到")</f>
         <v/>
       </c>
     </row>
@@ -1121,7 +1064,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算到港天数</t>
+          <t>第 4 题：第4题：订单重量分析（SUMIFS 和 COUNTIFS）</t>
         </is>
       </c>
     </row>
@@ -1131,9 +1074,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <f>DATEDIF(B2,C2,"d")</f>
-        <v/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>总重量：=SUMIFS(D2:D6, B2:B6, "华东区", C2:C6, "已发货")；订单数：=COUNTIFS(B2:B6, "华东区", C2:C6, "已发货")</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1146,7 +1090,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：提取并计算重量费用</t>
+          <t>第 5 题：第5题：提取并匹配产品信息（RIGHT、MID、INDEX、MATCH）</t>
         </is>
       </c>
     </row>
@@ -1156,10 +1100,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>D2: =INDEX($B$10:$D$12,MATCH(C2,$A$10:$A$12,0),MATCH(ROUNDDOWN(B2,0),$B$9:$D$9,0)) , E2: =VALUE(RIGHT(A2,LEN(A2)-1))</t>
-        </is>
+      <c r="B18" s="2">
+        <f>INDEX(B2:B4, MATCH(RIGHT(A2,3), RIGHT(A2:A4,3), 0))</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1190,7 +1133,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计销售总额</t>
+          <t>第 1 题：第1题：销售数据汇总（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1202,14 +1145,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF(条件区域, 条件, 求和区域)。本例中，条件区域是A2:A6（渠道列），条件是“线上”，求和区域是B2:B6（销售额列）。函数会扫描条件区域，找到所有等于“线上”的行，对应求和区域的值相加，结果为450+250+500=1200。</t>
+          <t>SUMIF函数用于按条件求和。语法：SUMIF(条件区域, 条件, 求和区域)。本题中A2:A6是条件区域，"张三"是条件，B2:B6是求和区域。公式会扫描A列，找到所有“张三”对应的销售额并求和，结果为9500。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计达标订单数</t>
+          <t>第 2 题：第2题：库存到货天数（TODAY 和 DATEDIF）</t>
         </is>
       </c>
     </row>
@@ -1221,14 +1164,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS可以设置多个条件区域和条件，只有同时满足所有条件的行才计数。本例中，条件1是金额列B2:B7大于等于500，条件2是状态列C2:C7等于“已发货”。符合条件的订单有A002、A004、A005，共3个。</t>
+          <t>TODAY()返回当前日期（如2025-03-01），DATEDIF计算两个日期的间隔。语法：DATEDIF(开始日期, 结束日期, "d")，其中"d"表示天数。公式= DATEDIF(B2, TODAY(), "d")得到从入库日到今天的天数。注意：DATEDIF在Excel中需要手动输入，没有智能提示。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查询员工部门</t>
+          <t>第 3 题：第3题：查找员工职位（VLOOKUP 和 IFERROR）</t>
         </is>
       </c>
     </row>
@@ -1240,14 +1183,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP(查找值, 表格区域, 列序号, 匹配方式)。查找值是F1中的“E03”，表格区域是A2:C5（从员工ID列到部门列），列序号是3（部门在第三列），FALSE表示精确匹配。函数会找到E03对应的部门“技术部”。</t>
+          <t>VLOOKUP在A2:C4中查找F2的值，返回第3列（部门）。第四个参数FALSE表示精确匹配。IFERROR捕获错误，如果查找失败（如编号不存在）则返回“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算到港天数</t>
+          <t>第 4 题：第4题：订单重量分析（SUMIFS 和 COUNTIFS）</t>
         </is>
       </c>
     </row>
@@ -1259,14 +1202,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF(开始日期, 结束日期, 单位)可以计算日期差。单位“d”表示天数。本例中，开始日期是B2（订舱日期），结束日期是C2（到港日期），结果为5天。注意：Excel中的日期必须为真正的日期格式，而非文本。</t>
+          <t>SUMIFS用于多条件求和，语法：SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2)。COUNTIFS用于多条件计数，语法：COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2)。本题中分别对重量求和、对订单行计数。结果总重量为25kg，订单数为2。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：提取并计算重量费用</t>
+          <t>第 5 题：第5题：提取并匹配产品信息（RIGHT、MID、INDEX、MATCH）</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1221,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>首先，INDEX(区域, 行号, 列号)可以从区域取数。MATCH(查找值, 查找区域, 0)返回位置。外层MATCH找到运输方式在报价表行号，内层MATCH用ROUNDDOWN(B2,0)将重量向下取整（如2.5→2）再匹配对应的重量列号，从而返回费用。E2用RIGHT提取右边字符，去除首字符“P”，再VALUE转为数字。注意：报价表数据区域为A9:D12（包含表头），公式中的引用请根据实际位置调整。</t>
+          <t>RIGHT(A2,3)提取A2代码的后3位（如001）。然后MATCH在RIGHT(A2:A4,3)构成的数组中查找001的位置（注意A2:A4是数组，需要按Ctrl+Shift+Enter输入，但新版Excel支持动态数组）。INDEX(B2:B4, 位置)返回对应产品名称。本公式结果为“螺丝”。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：销售数据汇总（SUMIF）</t>
+          <t>第 1 题：第1题：统计某产品总销售额</t>
         </is>
       </c>
     </row>
@@ -490,21 +490,21 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你有一张2024年各销售人员的销售额表，需要统计“张三”的总销售额。</t>
+          <t>要求：你是一家小店的老板，有一张销售记录表，包含产品名称和销售额。需要统计“苹果”的总销售额。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格输入公式，计算“张三”的销售总额。</t>
+          <t>任务：在任意空白单元格（如E2）输入公式，计算“苹果”的总销售额。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>销售人员</t>
+          <t>产品</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -516,51 +516,51 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>苹果</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>5000</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>香蕉</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>3000</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>苹果</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>4500</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>橘子</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2000</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>苹果</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>3500</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -573,69 +573,69 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：库存到货天数（TODAY 和 DATEDIF）</t>
+          <t>第 2 题：第2题：计算两个日期的间隔天数（到今天）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>要求：你的仓库里有一批货物的入库日期，需要计算每批货到今天为止已经存放了多少天。</t>
+          <t>要求：你有一份快递发货记录，包含发货日期。需要计算每件快递从发货到今天已经过了多少天（到港天数），以便跟踪时效。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>任务：在C2单元格输入公式，计算A001货物的存放天数（假设今天为2025-03-01）。</t>
+          <t>任务：在C2单元格输入公式，计算EX001的到港天数（假设今天是2025-04-01）。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>货物编号</t>
+          <t>快递单号</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>入库日期</t>
+          <t>发货日期</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>EX001</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-10</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>EX002</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-02-15</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A003</t>
+          <t>EX003</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-03-01</t>
         </is>
       </c>
     </row>
@@ -649,320 +649,278 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查找员工职位（VLOOKUP 和 IFERROR）</t>
+          <t>第 3 题：第3题：按条件统计订单数量和总金额</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>要求：你有员工信息表，需要通过员工编号查找对应的部门。如果编号不存在，则显示“未找到”。</t>
+          <t>要求：你有一份订单表，包含客户城市、订单金额和是否加急。需要统计“上海”且“加急”的订单数量，以及这些订单的总金额。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>任务：在G2单元格输入公式，根据F2中的员工编号（假设输入E02）查找部门，若找不到则显示“未找到”。</t>
+          <t>任务：在E2输入公式统计上海且加急的订单数量；在F2输入公式统计这些订单的总金额。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>员工编号</t>
+          <t>城市</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>姓名</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>部门</t>
+          <t>是否加急</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>E01</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>赵一</t>
-        </is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>500</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>财务部</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>E02</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>钱二</t>
-        </is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>300</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>人事部</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>E03</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>孙三</t>
-        </is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>700</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>市场部</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：订单重量分析（SUMIFS 和 COUNTIFS）</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一张物流订单表，需要统计“华东区”中“已发货”订单的总重量和订单数量。</t>
-        </is>
-      </c>
-    </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>任务：在E2单元格计算华东区且已发货的总重量，在F2计算订单数量。</t>
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：从订单编号中提取关键信息并计算最大金额</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>区域</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一张订单表，订单编号格式为“地区-年份-序号”，例如“华东-2025-001”。需要提取每个订单的序号（最后3位），并找出所有订单中的最大金额。</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>D001</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>华东区</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>已发货</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>10</v>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>任务：在C2单元格输入公式提取第一个订单的序号；在D2单元格输入公式计算所有订单的最大金额。</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>D002</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>华北区</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>已发货</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>20</v>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>订单编号</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>D003</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>华东区</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>未发货</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>5</v>
+          <t>华东-2025-001</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>D004</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>华东区</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>已发货</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>15</v>
+          <t>华南-2025-002</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>2300</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>D005</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>华南区</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>已发货</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>8</v>
+          <t>华北-2025-003</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>1800</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>西南-2025-004</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：提取并匹配产品信息（RIGHT、MID、INDEX、MATCH）</t>
-        </is>
-      </c>
-    </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一张产品代码表，代码格式为“XX-YYYY-商品编号”，需要从代码中提取商品编号（末尾3位），并根据编号在产品表中查找产品名称。</t>
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：根据产品编号查找价格并处理错误</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>任务：在C2单元格输入公式，根据A2的产品代码提取末尾编号，并用INDEX和MATCH查找对应产品名称。</t>
+          <t>要求：你有一份产品价格表，包含产品编号和单价。需要根据给定的产品编号查找单价，如果找不到则显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>产品代码</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>产品名称</t>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>任务：在F2单元格输入产品编号（如“B02”），在G2单元格输入公式查找其单价并处理错误。</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>AA-1001-001</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>螺丝</t>
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>产品编号</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>BB-1002-002</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>螺母</t>
-        </is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>CC-1003-003</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>垫片</t>
-        </is>
+          <t>B02</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -989,7 +947,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：销售数据汇总（SUMIF）</t>
+          <t>第 1 题：第1题：统计某产品总销售额</t>
         </is>
       </c>
     </row>
@@ -1000,7 +958,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"张三",B2:B6)</f>
+        <f>SUMIF(A2:A6,"苹果",B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +972,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：库存到货天数（TODAY 和 DATEDIF）</t>
+          <t>第 2 题：第2题：计算两个日期的间隔天数（到今天）</t>
         </is>
       </c>
     </row>
@@ -1025,7 +983,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>DATEDIF(B2, TODAY(), "d")</f>
+        <f>DATEDIF(B2,TODAY(),"d")</f>
         <v/>
       </c>
     </row>
@@ -1039,7 +997,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查找员工职位（VLOOKUP 和 IFERROR）</t>
+          <t>第 3 题：第3题：按条件统计订单数量和总金额</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1008,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>IFERROR(VLOOKUP(F2, A2:C4, 3, FALSE), "未找到")</f>
+        <f>COUNTIFS(A2:A6,"上海",C2:C6,"是") 和 =SUMIFS(B2:B6,A2:A6,"上海",C2:C6,"是")</f>
         <v/>
       </c>
     </row>
@@ -1064,7 +1022,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：订单重量分析（SUMIFS 和 COUNTIFS）</t>
+          <t>第 4 题：第4题：从订单编号中提取关键信息并计算最大金额</t>
         </is>
       </c>
     </row>
@@ -1074,10 +1032,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>总重量：=SUMIFS(D2:D6, B2:B6, "华东区", C2:C6, "已发货")；订单数：=COUNTIFS(B2:B6, "华东区", C2:C6, "已发货")</t>
-        </is>
+      <c r="B14" s="2">
+        <f>RIGHT(A2,3) 和 =MAX(B2:B5)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1090,7 +1047,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：提取并匹配产品信息（RIGHT、MID、INDEX、MATCH）</t>
+          <t>第 5 题：第5题：根据产品编号查找价格并处理错误</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1058,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>INDEX(B2:B4, MATCH(RIGHT(A2,3), RIGHT(A2:A4,3), 0))</f>
+        <f>IFERROR(XLOOKUP(F2,A2:A5,B2:B5),"未找到")</f>
         <v/>
       </c>
     </row>
@@ -1133,7 +1090,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：销售数据汇总（SUMIF）</t>
+          <t>第 1 题：第1题：统计某产品总销售额</t>
         </is>
       </c>
     </row>
@@ -1145,14 +1102,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF函数用于按条件求和。语法：SUMIF(条件区域, 条件, 求和区域)。本题中A2:A6是条件区域，"张三"是条件，B2:B6是求和区域。公式会扫描A列，找到所有“张三”对应的销售额并求和，结果为9500。</t>
+          <t>SUMIF函数用于按条件求和，语法为SUMIF(条件区域,条件,求和区域)。这里条件区域是A2:A6，条件是“苹果”，求和区域是B2:B6。函数会找出A列中所有“苹果”对应的B列数值并相加，结果为120+150+100=370。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：库存到货天数（TODAY 和 DATEDIF）</t>
+          <t>第 2 题：第2题：计算两个日期的间隔天数（到今天）</t>
         </is>
       </c>
     </row>
@@ -1164,14 +1121,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TODAY()返回当前日期（如2025-03-01），DATEDIF计算两个日期的间隔。语法：DATEDIF(开始日期, 结束日期, "d")，其中"d"表示天数。公式= DATEDIF(B2, TODAY(), "d")得到从入库日到今天的天数。注意：DATEDIF在Excel中需要手动输入，没有智能提示。</t>
+          <t>DATEDIF函数计算两个日期之间的间隔，语法为DATEDIF(开始日期,结束日期,单位)。这里开始日期是发货日期B2，结束日期是TODAY()（返回当前日期），单位“d”表示天数。公式会返回从2025-01-10到今天的实际天数（例如2025-04-01时结果为81）。TODAY()无参数，自动更新。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查找员工职位（VLOOKUP 和 IFERROR）</t>
+          <t>第 3 题：第3题：按条件统计订单数量和总金额</t>
         </is>
       </c>
     </row>
@@ -1183,14 +1140,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP在A2:C4中查找F2的值，返回第3列（部门）。第四个参数FALSE表示精确匹配。IFERROR捕获错误，如果查找失败（如编号不存在）则返回“未找到”。</t>
+          <t>COUNTIFS和SUMIFS都支持多条件。COUNTIFS语法：COUNTIFS(条件区域1,条件1,条件区域2,条件2,...)，这里统计城市为“上海”且加急为“是”的行数，结果为2。SUMIFS语法：SUMIFS(求和区域,条件区域1,条件1,...)，这里求和金额，满足两个条件的金额为500+700=1200。注意SUMIFS的求和区域放在第一位。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：订单重量分析（SUMIFS 和 COUNTIFS）</t>
+          <t>第 4 题：第4题：从订单编号中提取关键信息并计算最大金额</t>
         </is>
       </c>
     </row>
@@ -1202,14 +1159,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS用于多条件求和，语法：SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2)。COUNTIFS用于多条件计数，语法：COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2)。本题中分别对重量求和、对订单行计数。结果总重量为25kg，订单数为2。</t>
+          <t>RIGHT函数提取字符串右边指定长度的字符，语法RIGHT(文本,字符数)，这里提取订单编号最后3位，得到“001”。MAX函数返回数值列表中的最大值，语法MAX(数值区域)，这里计算金额列的最大值，结果为2300。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：提取并匹配产品信息（RIGHT、MID、INDEX、MATCH）</t>
+          <t>第 5 题：第5题：根据产品编号查找价格并处理错误</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1178,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>RIGHT(A2,3)提取A2代码的后3位（如001）。然后MATCH在RIGHT(A2:A4,3)构成的数组中查找001的位置（注意A2:A4是数组，需要按Ctrl+Shift+Enter输入，但新版Excel支持动态数组）。INDEX(B2:B4, 位置)返回对应产品名称。本公式结果为“螺丝”。</t>
+          <t>XLOOKUP是新一代查找函数，语法XLOOKUP(查找值,查找数组,返回数组)。这里在A列查找F2的值，返回B列对应单价。IFERROR用于捕获错误，语法IFERROR(公式,错误时返回的值)。如果XLOOKUP找不到（比如F2输入“X99”），会返回错误，IFERROR则显示“未找到”。若找到，返回单价，例如F2=B02时结果为25。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某产品总销售额</t>
+          <t>第 1 题：第1题：计算指定供应商的总采购金额</t>
         </is>
       </c>
     </row>
@@ -490,77 +490,77 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家小店的老板，有一张销售记录表，包含产品名称和销售额。需要统计“苹果”的总销售额。</t>
+          <t>要求：你是一家公司的采购助理，有一张采购记录表，包含供应商名称和采购金额。现在需要统计“供应商A”的总采购金额，以便对账。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在任意空白单元格（如E2）输入公式，计算“苹果”的总销售额。</t>
+          <t>任务：在单元格 B8 中输入公式，计算供应商A的总采购金额。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>产品</t>
+          <t>供应商</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>采购金额</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>供应商A</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>120</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>香蕉</t>
+          <t>供应商B</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>80</v>
+        <v>850</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>供应商A</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>150</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>橘子</t>
+          <t>供应商C</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>供应商A</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>100</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="11">
@@ -573,270 +573,265 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：计算两个日期的间隔天数（到今天）</t>
+          <t>第 2 题：第2题：统计发货次数和平均订单金额</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>要求：你有一份快递发货记录，包含发货日期。需要计算每件快递从发货到今天已经过了多少天（到港天数），以便跟踪时效。</t>
+          <t>要求：你是物流公司的调度员，有一份发货记录表，记录每个订单的发货城市和订单金额。需要统计“上海”发货的订单次数，并计算这些订单的平均金额（保留整数）。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>任务：在C2单元格输入公式，计算EX001的到港天数（假设今天是2025-04-01）。</t>
+          <t>任务：在 B8 输入公式统计上海发货次数；在 B9 输入公式计算上海订单平均金额（四舍五入到整数）。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>快递单号</t>
+          <t>发货城市</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>发货日期</t>
+          <t>订单金额</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>EX001</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>2025-01-10</t>
-        </is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>3200</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>EX002</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>2025-02-15</t>
-        </is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>2500</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>EX003</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-01</t>
-        </is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>4100</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：按条件统计订单数量和总金额</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一份订单表，包含客户城市、订单金额和是否加急。需要统计“上海”且“加急”的订单数量，以及这些订单的总金额。</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>任务：在E2输入公式统计上海且加急的订单数量；在F2输入公式统计这些订单的总金额。</t>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：根据商品编号查找价格和库存</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>城市</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>是否加急</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>要求：你经营一家小超市，商品价格表存储在A-C列，包含编号、名称和单价。现在需要根据输入的商品编号（例如“P003”）查找单价，如果找不到则显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>是</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 F2 单元格输入公式，根据 E2 中的编号（假设E2输入"P003"）查找单价，若找不到则显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>700</v>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>香蕉</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>400</v>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>橙子</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>4.8</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>葡萄</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：从订单编号中提取关键信息并计算最大金额</t>
-        </is>
-      </c>
-    </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一张订单表，订单编号格式为“地区-年份-序号”，例如“华东-2025-001”。需要提取每个订单的序号（最后3位），并找出所有订单中的最大金额。</t>
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：计算货物到港天数和在途状态</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>任务：在C2单元格输入公式提取第一个订单的序号；在D2单元格输入公式计算所有订单的最大金额。</t>
+          <t>要求：你是港口调度员，有货物到港计划表，记录每批货物的预计到港日期。现在需要计算距离今天还有多少天（若已到港则显示“已到港”），并判断是否超期（超过5天算延迟）。</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>订单编号</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 C2 单元格输入公式，计算从今天到预计日期的剩余天数（若日期早于今天则显示“已到港”）；在 D2 输入公式判断是否延迟（剩余天数&gt;5则“延迟”，否则“正常”）。假设今天是2025-03-10。</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>华东-2025-001</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="n">
-        <v>1500</v>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>货物批次</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>预计到港日期</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>华南-2025-002</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>2300</v>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>华北-2025-003</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>1800</v>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>西南-2025-004</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>2100</v>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -849,78 +844,118 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据产品编号查找价格并处理错误</t>
+          <t>第 5 题：第5题：多条件汇总和动态查询</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>要求：你有一份产品价格表，包含产品编号和单价。需要根据给定的产品编号查找单价，如果找不到则显示“未找到”。</t>
+          <t>要求：你负责公司季度销售报表，数据包含销售区域、产品类别和销售额。需要完成两个任务：1）统计“华东”区域“电子产品”的总销售额；2）在另一张查询表中，根据给定的区域和类别，动态返回对应销售额（使用INDEX+MATCH）。</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>任务：在F2单元格输入产品编号（如“B02”），在G2单元格输入公式查找其单价并处理错误。</t>
+          <t>任务：在 B8 输入公式计算华东电子产品的总销售额；在 B10 输入公式根据 A10 和 B10 中输入的“区域”和“类别”返回相应销售额（假设 A10="华东", B10="电子产品"，但注意数据中有重复，需要先汇总或使用数组公式，简化：使用INDEX+MATCH匹配唯一组合，但本数据有重复，可先构造辅助列。建议练习SUMIFS和INDEX+MATCH的基本用法。此题答案以SUMIFS为主，INDEX+MATCH可参考。</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>产品编号</t>
+          <t>区域</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>单价</t>
+          <t>产品类别</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>销售额</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>A01</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="n">
-        <v>10</v>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>电子产品</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>15000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>B02</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="n">
-        <v>25</v>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>服装</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>8000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>C03</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="n">
-        <v>40</v>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>电子产品</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>12000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>55</v>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>5000</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>服装</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -947,7 +982,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某产品总销售额</t>
+          <t>第 1 题：第1题：计算指定供应商的总采购金额</t>
         </is>
       </c>
     </row>
@@ -958,7 +993,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"苹果",B2:B6)</f>
+        <f>SUMIF(A2:A6,"供应商A",B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -972,7 +1007,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：计算两个日期的间隔天数（到今天）</t>
+          <t>第 2 题：第2题：统计发货次数和平均订单金额</t>
         </is>
       </c>
     </row>
@@ -982,9 +1017,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B6" s="2">
-        <f>DATEDIF(B2,TODAY(),"d")</f>
-        <v/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>B8: =COUNTIF(A2:A6,"上海")  B9: =ROUND(SUMIF(A2:A6,"上海",B2:B6)/COUNTIF(A2:A6,"上海"),0)</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -997,7 +1033,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按条件统计订单数量和总金额</t>
+          <t>第 3 题：第3题：根据商品编号查找价格和库存</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1044,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(A2:A6,"上海",C2:C6,"是") 和 =SUMIFS(B2:B6,A2:A6,"上海",C2:C6,"是")</f>
+        <f>IFERROR(VLOOKUP(E2,A2:C5,3,FALSE),"未找到")</f>
         <v/>
       </c>
     </row>
@@ -1022,7 +1058,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：从订单编号中提取关键信息并计算最大金额</t>
+          <t>第 4 题：第4题：计算货物到港天数和在途状态</t>
         </is>
       </c>
     </row>
@@ -1032,9 +1068,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <f>RIGHT(A2,3) 和 =MAX(B2:B5)</f>
-        <v/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>C2: =IF(B2&lt;TODAY(),"已到港",DATEDIF(TODAY(),B2,"d"))  D2: =IF(C2="已到港","已到港",IF(C2&gt;5,"延迟","正常"))</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1047,7 +1084,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据产品编号查找价格并处理错误</t>
+          <t>第 5 题：第5题：多条件汇总和动态查询</t>
         </is>
       </c>
     </row>
@@ -1057,9 +1094,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2">
-        <f>IFERROR(XLOOKUP(F2,A2:A5,B2:B5),"未找到")</f>
-        <v/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>B8: =SUMIFS(C2:C6,A2:A6,"华东",B2:B6,"电子产品")  B10: 若使用INDEX+MATCH需构造唯一键，但本数据有重复，可改为使用SUMIFS。简化：在B10输入：=SUMIFS(C2:C6,A2:A6,A10,B2:B6,B10)</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1090,7 +1128,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某产品总销售额</t>
+          <t>第 1 题：第1题：计算指定供应商的总采购金额</t>
         </is>
       </c>
     </row>
@@ -1102,14 +1140,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF函数用于按条件求和，语法为SUMIF(条件区域,条件,求和区域)。这里条件区域是A2:A6，条件是“苹果”，求和区域是B2:B6。函数会找出A列中所有“苹果”对应的B列数值并相加，结果为120+150+100=370。</t>
+          <t>SUMIF函数用于按条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 A2:A6，条件是“供应商A”，求和区域是 B2:B6，函数会累加所有供应商为“供应商A”对应的金额，结果为 5200。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：计算两个日期的间隔天数（到今天）</t>
+          <t>第 2 题：第2题：统计发货次数和平均订单金额</t>
         </is>
       </c>
     </row>
@@ -1121,14 +1159,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF函数计算两个日期之间的间隔，语法为DATEDIF(开始日期,结束日期,单位)。这里开始日期是发货日期B2，结束日期是TODAY()（返回当前日期），单位“d”表示天数。公式会返回从2025-01-10到今天的实际天数（例如2025-04-01时结果为81）。TODAY()无参数，自动更新。</t>
+          <t>COUNTIF 统计满足条件的单元格个数，用于计算次数。平均金额需要先求和（SUMIF）再除以次数（COUNTIF），最后用 ROUND 四舍五入到整数。结果为次数3，平均金额3400。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按条件统计订单数量和总金额</t>
+          <t>第 3 题：第3题：根据商品编号查找价格和库存</t>
         </is>
       </c>
     </row>
@@ -1140,14 +1178,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS和SUMIFS都支持多条件。COUNTIFS语法：COUNTIFS(条件区域1,条件1,条件区域2,条件2,...)，这里统计城市为“上海”且加急为“是”的行数，结果为2。SUMIFS语法：SUMIFS(求和区域,条件区域1,条件1,...)，这里求和金额，满足两个条件的金额为500+700=1200。注意SUMIFS的求和区域放在第一位。</t>
+          <t>VLOOKUP 在A列查找E2的值，返回第3列（单价），FALSE表示精确匹配。IFERROR 捕获错误，若查找失败（如编号不存在）则返回“未找到”。本例E2为P003时，结果为4.8。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：从订单编号中提取关键信息并计算最大金额</t>
+          <t>第 4 题：第4题：计算货物到港天数和在途状态</t>
         </is>
       </c>
     </row>
@@ -1159,14 +1197,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>RIGHT函数提取字符串右边指定长度的字符，语法RIGHT(文本,字符数)，这里提取订单编号最后3位，得到“001”。MAX函数返回数值列表中的最大值，语法MAX(数值区域)，这里计算金额列的最大值，结果为2300。</t>
+          <t>IF判断日期是否早于今天，TODAY返回当前日期。DATEDIF计算两个日期之间的天数差，"d"表示天数。若日期在未来则返回剩余天数，否则显示“已到港”。第二个公式根据剩余天数判断延迟。结果：A001已到港，A002剩余天数-9（显示已到港），A003剩余5天（正常）。注意：实际计算时，今天日期变化会影响结果。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据产品编号查找价格并处理错误</t>
+          <t>第 5 题：第5题：多条件汇总和动态查询</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1216,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP是新一代查找函数，语法XLOOKUP(查找值,查找数组,返回数组)。这里在A列查找F2的值，返回B列对应单价。IFERROR用于捕获错误，语法IFERROR(公式,错误时返回的值)。如果XLOOKUP找不到（比如F2输入“X99”），会返回错误，IFERROR则显示“未找到”。若找到，返回单价，例如F2=B02时结果为25。</t>
+          <t>SUMIFS用于多条件求和，语法：SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2,...)。这里求和C列，条件区域A和B。结果：华东电子产品总销售额27000。INDEX+MATCH常用于精确查找，但本数据有重复，所以直接使用SUMIFS更合适。实际工作中可结合INDEX+MATCH做交叉查询，但需要数据唯一。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：计算指定供应商的总采购金额</t>
+          <t>第 1 题：第1题：统计某日签收的包裹总重量</t>
         </is>
       </c>
     </row>
@@ -490,472 +490,605 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家公司的采购助理，有一张采购记录表，包含供应商名称和采购金额。现在需要统计“供应商A”的总采购金额，以便对账。</t>
+          <t>要求：你是快递站文员，有一张当天包裹记录表，包含快递单号、目的地、重量（公斤）。请统计发往“上海”的包裹总重量。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在单元格 B8 中输入公式，计算供应商A的总采购金额。</t>
+          <t>任务：在E2单元格输入公式，计算目的地为“上海”的重量总和。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>供应商</t>
+          <t>单号</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>采购金额</t>
+          <t>目的地</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>重量</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>供应商A</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>1200</v>
+          <t>SF001</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>供应商B</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>850</v>
+          <t>SF002</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>供应商A</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>2300</v>
+          <t>SF003</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>7.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>供应商C</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>450</v>
+          <t>SF004</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>4.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>供应商A</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>1700</v>
+          <t>SF005</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SF006</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：统计发货次数和平均订单金额</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是物流公司的调度员，有一份发货记录表，记录每个订单的发货城市和订单金额。需要统计“上海”发货的订单次数，并计算这些订单的平均金额（保留整数）。</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：统计逾期未还的图书数量</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 B8 输入公式统计上海发货次数；在 B9 输入公式计算上海订单平均金额（四舍五入到整数）。</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIF</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>发货城市</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>订单金额</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是图书馆管理员，有借阅记录表，包含图书编号、借出日期、应还日期。今天是2025-04-07，请统计应还日期早于今天（即逾期）的图书数量。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>3200</v>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>任务：在F2单元格输入公式，用COUNTIF配合TODAY，统计应还日期小于今天的数量。</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>2500</v>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>借出日期</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>应还日期</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>4100</v>
+          <t>B001</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>1800</v>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>2900</v>
+          <t>B003</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：根据商品编号查找价格和库存</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>要求：你经营一家小超市，商品价格表存储在A-C列，包含编号、名称和单价。现在需要根据输入的商品编号（例如“P003”）查找单价，如果找不到则显示“未找到”。</t>
-        </is>
-      </c>
-    </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 F2 单元格输入公式，根据 E2 中的编号（假设E2输入"P003"）查找单价，若找不到则显示“未找到”。</t>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：根据订单号查找客户电话</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>编号</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>练习函数：VLOOKUP</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>P001</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>苹果</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>5.5</v>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>要求：你在一家网店工作，有订单表（订单号、客户名、电话）。请根据给定的订单号“A103”，查找对应客户电话。</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>P002</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>香蕉</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>3.2</v>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>任务：在F2单元格输入公式，根据E2单元格中的订单号（A103）查找电话。</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>P003</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>橙子</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>4.8</v>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>客户名</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>电话</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>A101</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>葡萄</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>8</v>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>13800001111</t>
+        </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>A102</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>13900002222</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>A103</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>13700003333</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>A104</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>13600004444</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：计算货物到港天数和在途状态</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是港口调度员，有货物到港计划表，记录每批货物的预计到港日期。现在需要计算距离今天还有多少天（若已到港则显示“已到港”），并判断是否超期（超过5天算延迟）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 C2 单元格输入公式，计算从今天到预计日期的剩余天数（若日期早于今天则显示“已到港”）；在 D2 输入公式判断是否延迟（剩余天数&gt;5则“延迟”，否则“正常”）。假设今天是2025-03-10。</t>
-        </is>
-      </c>
-    </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>货物批次</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>预计到港日期</t>
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：计算订单的到港天数和总金额（含四舍五入）</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>2025-02-10</t>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是货代，有订单表包含下单日期、到港日期、运费（元）。请计算每笔订单的运输天数，并将运费按“元”保留一位小数（四舍五入）。</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>任务：在F2单元格输入公式计算C01的运输天数，在G2输入公式将运费四舍五入到一位小数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>下单日期</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>运费</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>A003</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>150.55</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>230.45</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>99.98999999999999</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：多条件汇总和动态查询</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>要求：你负责公司季度销售报表，数据包含销售区域、产品类别和销售额。需要完成两个任务：1）统计“华东”区域“电子产品”的总销售额；2）在另一张查询表中，根据给定的区域和类别，动态返回对应销售额（使用INDEX+MATCH）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 B8 输入公式计算华东电子产品的总销售额；在 B10 输入公式根据 A10 和 B10 中输入的“区域”和“类别”返回相应销售额（假设 A10="华东", B10="电子产品"，但注意数据中有重复，需要先汇总或使用数组公式，简化：使用INDEX+MATCH匹配唯一组合，但本数据有重复，可先构造辅助列。建议练习SUMIFS和INDEX+MATCH的基本用法。此题答案以SUMIFS为主，INDEX+MATCH可参考。</t>
-        </is>
-      </c>
-    </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>区域</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>产品类别</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>销售额</t>
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：根据产品编号自动匹配名称和库存（用XLOOKUP）</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>电子产品</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>15000</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>练习函数：XLOOKUP</t>
+        </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>服装</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>8000</v>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是仓库管理员，有产品表（编号、名称、库存量）。请根据给定的产品编号“P02”，查找其名称和库存。</t>
+        </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>电子产品</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>12000</v>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>任务：在F2单元格输入公式，根据E2单元格的编号“P02”查找名称；在G2输入公式查找库存。</t>
+        </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>5000</v>
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>库存</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>服装</t>
+          <t>鼠标</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>7000</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>键盘</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>显示器</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>U盘</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -982,7 +1115,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：计算指定供应商的总采购金额</t>
+          <t>第 1 题：第1题：统计某日签收的包裹总重量</t>
         </is>
       </c>
     </row>
@@ -993,7 +1126,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"供应商A",B2:B6)</f>
+        <f>SUMIF(B2:B7,"上海",C2:C7)</f>
         <v/>
       </c>
     </row>
@@ -1007,7 +1140,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计发货次数和平均订单金额</t>
+          <t>第 2 题：第2题：统计逾期未还的图书数量</t>
         </is>
       </c>
     </row>
@@ -1017,10 +1150,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>B8: =COUNTIF(A2:A6,"上海")  B9: =ROUND(SUMIF(A2:A6,"上海",B2:B6)/COUNTIF(A2:A6,"上海"),0)</t>
-        </is>
+      <c r="B6" s="2">
+        <f>COUNTIF(C2:C6,"&lt;"&amp;TODAY())</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1033,7 +1165,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据商品编号查找价格和库存</t>
+          <t>第 3 题：第3题：根据订单号查找客户电话</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1176,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>IFERROR(VLOOKUP(E2,A2:C5,3,FALSE),"未找到")</f>
+        <f>VLOOKUP("A103",A2:C5,3,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -1058,7 +1190,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算货物到港天数和在途状态</t>
+          <t>第 4 题：第4题：计算订单的到港天数和总金额（含四舍五入）</t>
         </is>
       </c>
     </row>
@@ -1068,10 +1200,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>C2: =IF(B2&lt;TODAY(),"已到港",DATEDIF(TODAY(),B2,"d"))  D2: =IF(C2="已到港","已到港",IF(C2&gt;5,"延迟","正常"))</t>
-        </is>
+      <c r="B14" s="2">
+        <f>DATEDIF(B2,C2,"d") 和 =ROUND(D2,1)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1084,7 +1215,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：多条件汇总和动态查询</t>
+          <t>第 5 题：第5题：根据产品编号自动匹配名称和库存（用XLOOKUP）</t>
         </is>
       </c>
     </row>
@@ -1094,10 +1225,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>B8: =SUMIFS(C2:C6,A2:A6,"华东",B2:B6,"电子产品")  B10: 若使用INDEX+MATCH需构造唯一键，但本数据有重复，可改为使用SUMIFS。简化：在B10输入：=SUMIFS(C2:C6,A2:A6,A10,B2:B6,B10)</t>
-        </is>
+      <c r="B18" s="2">
+        <f>XLOOKUP("P02",A2:A5,B2:B5) 和 =XLOOKUP("P02",A2:A5,C2:C5)</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1128,7 +1258,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：计算指定供应商的总采购金额</t>
+          <t>第 1 题：第1题：统计某日签收的包裹总重量</t>
         </is>
       </c>
     </row>
@@ -1140,14 +1270,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF函数用于按条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 A2:A6，条件是“供应商A”，求和区域是 B2:B6，函数会累加所有供应商为“供应商A”对应的金额，结果为 5200。</t>
+          <t>SUMIF(条件区域, 条件, 求和区域)。本例中条件区域是目的地列B2:B7，条件是“上海”，求和区域是重量列C2:C7。函数会遍历B列，找到所有等于“上海”的行，对应C列的值相加，结果为3.2+4.1+6.0=13.3。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计发货次数和平均订单金额</t>
+          <t>第 2 题：第2题：统计逾期未还的图书数量</t>
         </is>
       </c>
     </row>
@@ -1159,14 +1289,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF 统计满足条件的单元格个数，用于计算次数。平均金额需要先求和（SUMIF）再除以次数（COUNTIF），最后用 ROUND 四舍五入到整数。结果为次数3，平均金额3400。</t>
+          <t>COUNTIF(区域, 条件) 用于计数。本例区域是应还日期C2:C6，条件是用"&lt;"&amp;TODAY()拼接成的字符串，表示“小于今天”。TODAY()返回当前日期2025-04-07，因此条件为&lt;2025-04-07。只有B001、B002、B003的应还日期早于今天，所以结果为3。注意日期比较需使用文本拼接。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据商品编号查找价格和库存</t>
+          <t>第 3 题：第3题：根据订单号查找客户电话</t>
         </is>
       </c>
     </row>
@@ -1178,14 +1308,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP 在A列查找E2的值，返回第3列（单价），FALSE表示精确匹配。IFERROR 捕获错误，若查找失败（如编号不存在）则返回“未找到”。本例E2为P003时，结果为4.8。</t>
+          <t>VLOOKUP(查找值, 表格区域, 返回列号, 精确匹配)。查找值是“A103”，区域是A2:C5，返回第3列（电话），FALSE表示精确匹配。函数在A列找到A103，返回同行第3列的13700003333。如果区域第一列有重复，只返回第一个匹配。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算货物到港天数和在途状态</t>
+          <t>第 4 题：第4题：计算订单的到港天数和总金额（含四舍五入）</t>
         </is>
       </c>
     </row>
@@ -1197,14 +1327,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>IF判断日期是否早于今天，TODAY返回当前日期。DATEDIF计算两个日期之间的天数差，"d"表示天数。若日期在未来则返回剩余天数，否则显示“已到港”。第二个公式根据剩余天数判断延迟。结果：A001已到港，A002剩余天数-9（显示已到港），A003剩余5天（正常）。注意：实际计算时，今天日期变化会影响结果。</t>
+          <t>DATEDIF(开始日期, 结束日期, "d") 返回两个日期之间的天数差，单位d表示天。ROUND(数值, 小数位数) 四舍五入。运输天数：C01从2025-03-01到2025-03-10共9天；运费150.55四舍五入到一位小数得150.6。注意DATEDIF的结束日期必须晚于开始日期。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：多条件汇总和动态查询</t>
+          <t>第 5 题：第5题：根据产品编号自动匹配名称和库存（用XLOOKUP）</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1346,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS用于多条件求和，语法：SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2,...)。这里求和C列，条件区域A和B。结果：华东电子产品总销售额27000。INDEX+MATCH常用于精确查找，但本数据有重复，所以直接使用SUMIFS更合适。实际工作中可结合INDEX+MATCH做交叉查询，但需要数据唯一。</t>
+          <t>XLOOKUP(查找值, 查找数组, 返回数组) 是VLOOKUP的升级版，无需指定列号，直接指定返回的列。第一个公式在A2:A5中找“P02”，返回B列对应值“键盘”；第二个公式返回C列对应值85。XLOOKUP默认精确匹配，若找不到会返回#N/A。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某日签收的包裹总重量</t>
+          <t>第 1 题：第1题：统计北京地区的总销售额</t>
         </is>
       </c>
     </row>
@@ -490,605 +490,491 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是快递站文员，有一张当天包裹记录表，包含快递单号、目的地、重量（公斤）。请统计发往“上海”的包裹总重量。</t>
+          <t>要求：你有一张销售记录表，包含销售地区、销售员、销售额。现在需要统计“北京”这个地区的总销售额。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格输入公式，计算目的地为“上海”的重量总和。</t>
+          <t>任务：在单元格 E2 输入公式，统计地区为“北京”的销售额总和。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>单号</t>
+          <t>地区</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>目的地</t>
+          <t>销售员</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>重量</t>
+          <t>销售额</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>SF001</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5.5</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>SF002</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.2</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>SF003</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7.8</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>SF004</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>赵六</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>4.1</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>SF005</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>孙七</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.9</v>
+        <v>900</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>SF006</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：计算订单到货天数</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：统计逾期未还的图书数量</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>练习函数：DATEDIF</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIF</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>要求：物流台账记录了订单发货日期和到货日期，需要计算每个订单的运输天数（按天计算，结束日期减开始日期）。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>要求：你是图书馆管理员，有借阅记录表，包含图书编号、借出日期、应还日期。今天是2025-04-07，请统计应还日期早于今天（即逾期）的图书数量。</t>
+          <t>任务：在 D2 单元格输入公式，计算第一个订单的运输天数（到货日期 - 发货日期），并下拉填充。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>任务：在F2单元格输入公式，用COUNTIF配合TODAY，统计应还日期小于今天的数量。</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>发货日期</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>到货日期</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>编号</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>借出日期</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>应还日期</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-05</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>B001</t>
+          <t>A002</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2024-01-03</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2024-01-07</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>B002</t>
+          <t>A003</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2024-01-10</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2024-01-15</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>B003</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>2025-04-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>B004</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-25</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>2025-04-08</t>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>B005</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-28</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>2025-04-11</t>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：按产品分类汇总销量及计数</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>要求：销售明细表中有产品类别、销售数量、销售金额。需要按类别统计总数量和总笔数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 G2 输入统计“手机”类别的总销售数量的公式；在 H2 输入统计“手机”类别出现次数的公式。</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：根据订单号查找客户电话</t>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>产品类别</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>销售数量</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>销售金额</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>练习函数：VLOOKUP</t>
-        </is>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>5000</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>要求：你在一家网店工作，有订单表（订单号、客户名、电话）。请根据给定的订单号“A103”，查找对应客户电话。</t>
-        </is>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>电脑</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>6000</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>任务：在F2单元格输入公式，根据E2单元格中的订单号（A103）查找电话。</t>
-        </is>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>7500</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>客户名</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>电话</t>
-        </is>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>平板</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>3000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>A101</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>13800001111</t>
-        </is>
+          <t>电脑</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>12000</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>A102</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>13900002222</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>A103</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>13700003333</t>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>A104</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>13600004444</t>
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：根据员工编号查找姓名和部门</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>练习函数：VLOOKUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>要求：员工信息表包含编号、姓名、部门。需要根据员工编号，在另一张表中查找对应的姓名和部门。</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：计算订单的到港天数和总金额（含四舍五入）</t>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>任务：假设在 A7 单元格输入员工编号 "E002"，在 B7 输入公式查找该员工的姓名，在 C7 输入公式查找部门。</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是货代，有订单表包含下单日期、到港日期、运费（元）。请计算每笔订单的运输天数，并将运费按“元”保留一位小数（四舍五入）。</t>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>部门</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>任务：在F2单元格输入公式计算C01的运输天数，在G2输入公式将运费四舍五入到一位小数。</t>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>E001</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>张丽</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>人事部</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>下单日期</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>运费</t>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>E002</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>王强</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>技术部</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>C01</t>
+          <t>E003</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>李梅</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>150.55</v>
+          <t>市场部</t>
+        </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>C02</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>230.45</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>C03</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="n">
-        <v>99.98999999999999</v>
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：提取身份证号中的出生日期并计算年龄</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>要求：员工身份证号包含出生日期（第7-14位，格式如YYYYMMDD）。需要提取出生日期，并计算当前年龄。</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：根据产品编号自动匹配名称和库存（用XLOOKUP）</t>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 C2 单元格输入公式提取张三的出生日期（显示为日期），在 D2 输入公式计算张三当前年龄（按今天算）。</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>练习函数：XLOOKUP</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>员工</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>身份证号</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是仓库管理员，有产品表（编号、名称、库存量）。请根据给定的产品编号“P02”，查找其名称和库存。</t>
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>110101199003071234</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>任务：在F2单元格输入公式，根据E2单元格的编号“P02”查找名称；在G2输入公式查找库存。</t>
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>310101198512240567</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>编号</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>库存</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>P01</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>鼠标</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>P02</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>键盘</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>显示器</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>U盘</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1115,7 +1001,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某日签收的包裹总重量</t>
+          <t>第 1 题：第1题：统计北京地区的总销售额</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1012,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(B2:B7,"上海",C2:C7)</f>
+        <f>SUMIF(A2:A6,"北京",C2:C6)</f>
         <v/>
       </c>
     </row>
@@ -1140,7 +1026,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计逾期未还的图书数量</t>
+          <t>第 2 题：第2题：计算订单到货天数</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1037,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF(C2:C6,"&lt;"&amp;TODAY())</f>
+        <f>DATEDIF(B2,C2,"d")</f>
         <v/>
       </c>
     </row>
@@ -1165,7 +1051,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据订单号查找客户电话</t>
+          <t>第 3 题：第3题：按产品分类汇总销量及计数</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1062,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>VLOOKUP("A103",A2:C5,3,FALSE)</f>
+        <f>SUMIFS(B2:B6,A2:A6,"手机") 和 =COUNTIFS(A2:A6,"手机")</f>
         <v/>
       </c>
     </row>
@@ -1190,7 +1076,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算订单的到港天数和总金额（含四舍五入）</t>
+          <t>第 4 题：第4题：根据员工编号查找姓名和部门</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1087,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>DATEDIF(B2,C2,"d") 和 =ROUND(D2,1)</f>
+        <f>VLOOKUP(A7,A1:C4,2,FALSE) 和 =VLOOKUP(A7,A1:C4,3,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -1215,7 +1101,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据产品编号自动匹配名称和库存（用XLOOKUP）</t>
+          <t>第 5 题：第5题：提取身份证号中的出生日期并计算年龄</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1112,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>XLOOKUP("P02",A2:A5,B2:B5) 和 =XLOOKUP("P02",A2:A5,C2:C5)</f>
+        <f>DATE(MID(B2,7,4),MID(B2,11,2),MID(B2,13,2)) 和 =DATEDIF(C2,TODAY(),"y")</f>
         <v/>
       </c>
     </row>
@@ -1258,7 +1144,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某日签收的包裹总重量</t>
+          <t>第 1 题：第1题：统计北京地区的总销售额</t>
         </is>
       </c>
     </row>
@@ -1270,14 +1156,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF(条件区域, 条件, 求和区域)。本例中条件区域是目的地列B2:B7，条件是“上海”，求和区域是重量列C2:C7。函数会遍历B列，找到所有等于“上海”的行，对应C列的值相加，结果为3.2+4.1+6.0=13.3。</t>
+          <t>SUMIF 函数用于按条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 A2:A6，条件是“北京”，求和区域是 C2:C6，即可得到北京地区的总销售额 3600。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计逾期未还的图书数量</t>
+          <t>第 2 题：第2题：计算订单到货天数</t>
         </is>
       </c>
     </row>
@@ -1289,14 +1175,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF(区域, 条件) 用于计数。本例区域是应还日期C2:C6，条件是用"&lt;"&amp;TODAY()拼接成的字符串，表示“小于今天”。TODAY()返回当前日期2025-04-07，因此条件为&lt;2025-04-07。只有B001、B002、B003的应还日期早于今天，所以结果为3。注意日期比较需使用文本拼接。</t>
+          <t>DATEDIF 函数计算两个日期之间的差值，语法 DATEDIF(开始日期, 结束日期, 单位)。单位 "d" 表示天数。注意发货日期必须早于到货日期。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据订单号查找客户电话</t>
+          <t>第 3 题：第3题：按产品分类汇总销量及计数</t>
         </is>
       </c>
     </row>
@@ -1308,14 +1194,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP(查找值, 表格区域, 返回列号, 精确匹配)。查找值是“A103”，区域是A2:C5，返回第3列（电话），FALSE表示精确匹配。函数在A列找到A103，返回同行第3列的13700003333。如果区域第一列有重复，只返回第一个匹配。</t>
+          <t>SUMIFS 用于多条件求和，语法 SUMIFS(求和区域, 条件区域1, 条件1)。这里求和区域是 B2:B6，条件区域 A2:A6，条件"手机"，得到销量5。COUNTIFS 用于多条件计数，语法 COUNTIFS(条件区域1, 条件1)，得到个数2。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算订单的到港天数和总金额（含四舍五入）</t>
+          <t>第 4 题：第4题：根据员工编号查找姓名和部门</t>
         </is>
       </c>
     </row>
@@ -1327,14 +1213,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF(开始日期, 结束日期, "d") 返回两个日期之间的天数差，单位d表示天。ROUND(数值, 小数位数) 四舍五入。运输天数：C01从2025-03-01到2025-03-10共9天；运费150.55四舍五入到一位小数得150.6。注意DATEDIF的结束日期必须晚于开始日期。</t>
+          <t>VLOOKUP 函数用于垂直查找，语法 VLOOKUP(查找值, 表格区域, 返回列号, 精确匹配)。表格区域 A1:C4 包含表头和数据，返回列号 2 是姓名，3 是部门，FALSE 表示精确匹配。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据产品编号自动匹配名称和库存（用XLOOKUP）</t>
+          <t>第 5 题：第5题：提取身份证号中的出生日期并计算年龄</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1232,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP(查找值, 查找数组, 返回数组) 是VLOOKUP的升级版，无需指定列号，直接指定返回的列。第一个公式在A2:A5中找“P02”，返回B列对应值“键盘”；第二个公式返回C列对应值85。XLOOKUP默认精确匹配，若找不到会返回#N/A。</t>
+          <t>MID 从身份证号中提取字符串：MID(B2,7,4) 取出年份，MID(B2,11,2) 取出月份，MID(B2,13,2) 取出日期，再用 DATE 函数组合成日期。DATEDIF 计算年龄：开始日期为 C2，结束日期为 TODAY()，单位"y"得到整年数。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计北京地区的总销售额</t>
+          <t>第 1 题：第1题：统计某类商品的销售总金额</t>
         </is>
       </c>
     </row>
@@ -490,491 +490,599 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你有一张销售记录表，包含销售地区、销售员、销售额。现在需要统计“北京”这个地区的总销售额。</t>
+          <t>要求：某小商店记录了一周内各类商品的日销售金额，现需要统计'饮料'类商品的总销售额。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在单元格 E2 输入公式，统计地区为“北京”的销售额总和。</t>
+          <t>任务：在E2单元格中输入公式，计算'商品类别'为'饮料'的所有销售金额之和。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>地区</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>销售员</t>
+          <t>商品类别</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>销售金额</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>饮料</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1200</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>零食</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>800</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>2024-01-02</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>饮料</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1500</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>2024-01-02</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>赵六</t>
+          <t>日用品</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>2024-01-03</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>孙七</t>
+          <t>饮料</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>900</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-03</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>零食</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-04</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>饮料</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：计算订单到货天数</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>练习函数：DATEDIF</t>
-        </is>
-      </c>
-    </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流台账记录了订单发货日期和到货日期，需要计算每个订单的运输天数（按天计算，结束日期减开始日期）。</t>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：统计下单次数和缺货次数</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：在 D2 单元格输入公式，计算第一个订单的运输天数（到货日期 - 发货日期），并下拉填充。</t>
+          <t>要求：某仓库记录了一周内各商品的发货状态，现需要统计'已发货'的商品个数，以及'已发货'且'数量&gt;100'的商品个数。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>发货日期</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>到货日期</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>任务：在E2输入公式统计'已发货'的商品个数；在E3输入公式统计'已发货'且'数量大于100'的商品个数。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-01</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-05</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>商品编号</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-03</t>
-        </is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>2024-01-07</t>
+          <t>已发货</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
           <t>A003</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-10</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="B21" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>缺货</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>A005</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>缺货</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>A006</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：按产品分类汇总销量及计数</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>要求：销售明细表中有产品类别、销售数量、销售金额。需要按类别统计总数量和总笔数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 G2 输入统计“手机”类别的总销售数量的公式；在 H2 输入统计“手机”类别出现次数的公式。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>产品类别</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>销售数量</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>销售金额</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>5000</v>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：根据产品编号匹配产品名称和单价</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>电脑</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>6000</v>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>要求：销售表中只有产品编号，需要从价格表中匹配产品名称和单价。若编号不存在，则显示'未找到'。</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>7500</v>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>任务：在销售表的F2单元格（假设销售表有编号E2），输入公式匹配产品名称；在G2输入公式匹配单价，均要求找不到时显示'未找到'。</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>平板</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>3000</v>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>产品编号</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>电脑</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n">
-        <v>2</v>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>笔记本</t>
+        </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>12000</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>钢笔</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>橡皮</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>尺子</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>书包</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：根据员工编号查找姓名和部门</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>练习函数：VLOOKUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>要求：员工信息表包含编号、姓名、部门。需要根据员工编号，在另一张表中查找对应的姓名和部门。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>任务：假设在 A7 单元格输入员工编号 "E002"，在 B7 输入公式查找该员工的姓名，在 C7 输入公式查找部门。</t>
-        </is>
-      </c>
-    </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>编号</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>部门</t>
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：计算到港天数和在港停留天数</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>E001</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>张丽</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>人事部</t>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>要求：某物流公司的集装箱到港记录，需要根据当前日期计算每个箱子已到港天数，并判断是否超过15天（超期收费），同时计算实际停留天数（若离港日期为空，则用今天）。</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>E002</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>王强</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>技术部</t>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>任务：在D2输入公式计算到港天数（使用TODAY）？在E2输入公式计算停留天数（若离港日期为空则用今天），在F2输入公式判断是否超期（超过15天显示'超期'，否则'正常'）。</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>E003</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>李梅</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>市场部</t>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>箱号</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>离港日期</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-10</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>C002</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-12</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>C003</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-15</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>C004</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-20</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：提取身份证号中的出生日期并计算年龄</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>要求：员工身份证号包含出生日期（第7-14位，格式如YYYYMMDD）。需要提取出生日期，并计算当前年龄。</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 C2 单元格输入公式提取张三的出生日期（显示为日期），在 D2 输入公式计算张三当前年龄（按今天算）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>员工</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>身份证号</t>
-        </is>
-      </c>
-    </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>110101199003071234</t>
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：用INDEX+MATCH实现双向查找，并用ROUND处理结果</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>310101198512240567</t>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>要求：某公司有各产品在不同月份的销售额表，需要查找指定产品在指定月份的销售额，结果保留两位小数（实际金额已是两位小数，但可能因公式产生多位小数）。</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>任务：在H2输入产品名（如B），在H3输入月份（如"2月"），在H4输入公式查找对应销售额并四舍五入保留2位小数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>1月</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>2月</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>3月</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>120.555</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>200.2</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>210.3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>130.75</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1001,7 +1109,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计北京地区的总销售额</t>
+          <t>第 1 题：第1题：统计某类商品的销售总金额</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1120,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"北京",C2:C6)</f>
+        <f>SUMIF(B2:B8,"饮料",C2:C8)</f>
         <v/>
       </c>
     </row>
@@ -1026,7 +1134,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：计算订单到货天数</t>
+          <t>第 2 题：第2题：统计下单次数和缺货次数</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1145,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>DATEDIF(B2,C2,"d")</f>
+        <f>COUNTIF(C2:C7,"已发货")；=COUNTIFS(C2:C7,"已发货",B2:B7,"&gt;100")</f>
         <v/>
       </c>
     </row>
@@ -1051,7 +1159,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按产品分类汇总销量及计数</t>
+          <t>第 3 题：第3题：根据产品编号匹配产品名称和单价</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1170,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>SUMIFS(B2:B6,A2:A6,"手机") 和 =COUNTIFS(A2:A6,"手机")</f>
+        <f>IFERROR(VLOOKUP(E2,A:C,2,FALSE),"未找到")；=IFERROR(VLOOKUP(E2,A:C,3,FALSE),"未找到")</f>
         <v/>
       </c>
     </row>
@@ -1076,7 +1184,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：根据员工编号查找姓名和部门</t>
+          <t>第 4 题：第4题：计算到港天数和在港停留天数</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1195,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>VLOOKUP(A7,A1:C4,2,FALSE) 和 =VLOOKUP(A7,A1:C4,3,FALSE)</f>
+        <f>DATEDIF(B2,TODAY(),"D")；=IF(C2="",DATEDIF(B2,TODAY(),"D"),DATEDIF(B2,C2,"D"))；=IF(D2&gt;15,"超期","正常")</f>
         <v/>
       </c>
     </row>
@@ -1101,7 +1209,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：提取身份证号中的出生日期并计算年龄</t>
+          <t>第 5 题：第5题：用INDEX+MATCH实现双向查找，并用ROUND处理结果</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1220,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>DATE(MID(B2,7,4),MID(B2,11,2),MID(B2,13,2)) 和 =DATEDIF(C2,TODAY(),"y")</f>
+        <f>ROUND(INDEX(B2:D4,MATCH(H2,A2:A4,0),MATCH(H3,B1:D1,0)),2)</f>
         <v/>
       </c>
     </row>
@@ -1144,7 +1252,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计北京地区的总销售额</t>
+          <t>第 1 题：第1题：统计某类商品的销售总金额</t>
         </is>
       </c>
     </row>
@@ -1156,14 +1264,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 函数用于按条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 A2:A6，条件是“北京”，求和区域是 C2:C6，即可得到北京地区的总销售额 3600。</t>
+          <t>SUMIF(条件区域,条件,求和区域)用于按条件求和。这里B2:B8是条件区域，条件为"饮料"，C2:C8是实际求和区域，返回满足条件的金额合计。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：计算订单到货天数</t>
+          <t>第 2 题：第2题：统计下单次数和缺货次数</t>
         </is>
       </c>
     </row>
@@ -1175,14 +1283,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF 函数计算两个日期之间的差值，语法 DATEDIF(开始日期, 结束日期, 单位)。单位 "d" 表示天数。注意发货日期必须早于到货日期。</t>
+          <t>COUNTIF用于单条件计数，这里统计C列中等于"已发货"的个数。COUNTIFS支持多条件，第一个条件区域C列，第二个条件区域B列，同时满足才计数。注意数量条件用文本"&gt;100"表示大于100。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按产品分类汇总销量及计数</t>
+          <t>第 3 题：第3题：根据产品编号匹配产品名称和单价</t>
         </is>
       </c>
     </row>
@@ -1194,14 +1302,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 用于多条件求和，语法 SUMIFS(求和区域, 条件区域1, 条件1)。这里求和区域是 B2:B6，条件区域 A2:A6，条件"手机"，得到销量5。COUNTIFS 用于多条件计数，语法 COUNTIFS(条件区域1, 条件1)，得到个数2。</t>
+          <t>VLOOKUP(查找值,表区域,列号,精确匹配)在A:C区域第一列查找E2的编号，返回对应列的值。第三个参数2是名称列，3是单价列。IFERROR函数捕获VLOOKUP的错误（如#N/A），当找不到时返回"未找到"，避免显示错误。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：根据员工编号查找姓名和部门</t>
+          <t>第 4 题：第4题：计算到港天数和在港停留天数</t>
         </is>
       </c>
     </row>
@@ -1213,14 +1321,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP 函数用于垂直查找，语法 VLOOKUP(查找值, 表格区域, 返回列号, 精确匹配)。表格区域 A1:C4 包含表头和数据，返回列号 2 是姓名，3 是部门，FALSE 表示精确匹配。</t>
+          <t>DATEDIF(开始日期,结束日期,"D")返回两个日期相差天数。TODAY()返回当前日期。在D2中计算从到港到今天的天数。E2判断C2是否为空，若空则用今天作为结束日期，否则用离港日期。F2用IF根据D2是否大于15给出结果。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：提取身份证号中的出生日期并计算年龄</t>
+          <t>第 5 题：第5题：用INDEX+MATCH实现双向查找，并用ROUND处理结果</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1340,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MID 从身份证号中提取字符串：MID(B2,7,4) 取出年份，MID(B2,11,2) 取出月份，MID(B2,13,2) 取出日期，再用 DATE 函数组合成日期。DATEDIF 计算年龄：开始日期为 C2，结束日期为 TODAY()，单位"y"得到整年数。</t>
+          <t>INDEX(区域,行号,列号)返回区域中指定行列的值。MATCH(H2,A2:A4,0)找到产品B在A列的位置（第2行），MATCH(H3,B1:D1,0)找到月份"2月"在表头的位置（第2列）。二者组合得到精确交叉值。ROUND函数将结果四舍五入到2位小数。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某类商品的销售总金额</t>
+          <t>第 1 题：第1题：计算某区域销售总量（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -490,137 +490,97 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：某小商店记录了一周内各类商品的日销售金额，现需要统计'饮料'类商品的总销售额。</t>
+          <t>要求：你是一家超市的经理，有一张本周各分店的销售额表。现在需要计算「东区」分店的总销售额。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格中输入公式，计算'商品类别'为'饮料'的所有销售金额之和。</t>
+          <t>任务：在任意空白单元格（如D2）输入公式，计算「东区」的销售额总和。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>分店</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>商品类别</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>销售金额</t>
+          <t>销售额</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>饮料</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>120</v>
+          <t>东区</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>零食</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>85</v>
+          <t>西区</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>800</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>饮料</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>95</v>
+          <t>东区</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>日用品</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>200</v>
+          <t>南区</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2024-01-03</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>饮料</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>150</v>
+          <t>东区</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>900</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2024-01-03</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>零食</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>110</v>
+          <t>北区</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>700</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2024-01-04</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>饮料</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>80</v>
+          <t>东区</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>1100</v>
       </c>
     </row>
     <row r="13">
@@ -633,456 +593,491 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计下单次数和缺货次数</t>
+          <t>第 2 题：第2题：统计满足多条件的人数（COUNTIFS）</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>要求：某仓库记录了一周内各商品的发货状态，现需要统计'已发货'的商品个数，以及'已发货'且'数量&gt;100'的商品个数。</t>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIFS</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2输入公式统计'已发货'的商品个数；在E3输入公式统计'已发货'且'数量大于100'的商品个数。</t>
+          <t>要求：你是一家培训机构的教务，有一份学员信息表，包含姓名、部门、是否完成作业（是/否）。现在需要统计「销售部」且完成作业为「是」的学员人数。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>商品编号</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>任务：在任意空白单元格（如E2）输入公式，统计部门为“销售部”且完成作业为“是”的人数。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>已发货</t>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>部门</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>完成作业</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>120</v>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>销售部</t>
+        </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>已发货</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>A003</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>80</v>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>市场部</t>
+        </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>缺货</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>A004</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>200</v>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>销售部</t>
+        </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>已发货</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>A005</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>90</v>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>销售部</t>
+        </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>缺货</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>A006</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>150</v>
+          <t>钱七</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>市场部</t>
+        </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>已发货</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>孙八</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>销售部</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：根据产品编号匹配产品名称和单价</t>
-        </is>
-      </c>
-    </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>要求：销售表中只有产品编号，需要从价格表中匹配产品名称和单价。若编号不存在，则显示'未找到'。</t>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：根据商品编码查找价格并处理错误（VLOOKUP + IFERROR）</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>任务：在销售表的F2单元格（假设销售表有编号E2），输入公式匹配产品名称；在G2输入公式匹配单价，均要求找不到时显示'未找到'。</t>
+          <t>要求：你经营一家网店，有一份商品价格表（编码和价格）。另一份订单需要根据编码填写价格，但订单中可能存在价格表中不存在的编码，需要显示“查无此码”。</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>产品编号</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>产品名称</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>任务：在订单表（从第6行到第9行）旁边增加一列，在F2单元格输入公式，向下填充，根据订单编码从价格表中查找价格，若找不到则显示“查无此码”。假设订单编码在A6:A9，价格表编码在A2:A5。</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>P001</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>笔记本</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>15.5</v>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>编码</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>价格</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>P002</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>钢笔</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>8</v>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>P003</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>橡皮</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>2.5</v>
+          <t>A02</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>P004</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>尺子</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>3.2</v>
+          <t>A03</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>P005</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>书包</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>45</v>
+          <t>B01</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>B02</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>编码</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>订单数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>A02</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>B01</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：计算到港天数和在港停留天数</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>要求：某物流公司的集装箱到港记录，需要根据当前日期计算每个箱子已到港天数，并判断是否超过15天（超期收费），同时计算实际停留天数（若离港日期为空，则用今天）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>任务：在D2输入公式计算到港天数（使用TODAY）？在E2输入公式计算停留天数（若离港日期为空则用今天），在F2输入公式判断是否超期（超过15天显示'超期'，否则'正常'）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>箱号</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>离港日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>C001</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-10</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>C002</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-12</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr"/>
-    </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>C003</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-15</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-20</t>
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：计算员工入职年数并取整（DATEDIF + ROUND）</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>C004</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-20</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是一家公司的人力资源，记录员工入职日期。需要计算每位员工截止今天（假设今天为2025-01-01）的工作年限，并保留1位小数（四舍五入）。</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>任务：在C2单元格输入公式，向下填充，计算每位员工的工作年限（年），结果保留1位小数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>员工</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>入职日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>张伟</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>2018-06-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>李娜</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>2019-11-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>王强</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>2021-03-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>赵敏</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>2020-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：用INDEX+MATCH实现双向查找，并用ROUND处理结果</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>要求：某公司有各产品在不同月份的销售额表，需要查找指定产品在指定月份的销售额，结果保留两位小数（实际金额已是两位小数，但可能因公式产生多位小数）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>任务：在H2输入产品名（如B），在H3输入月份（如"2月"），在H4输入公式查找对应销售额并四舍五入保留2位小数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>产品</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>1月</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>2月</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>3月</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n">
-        <v>120.555</v>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>200.2</v>
-      </c>
-      <c r="D52" s="4" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="n">
-        <v>95.40000000000001</v>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="D53" s="4" t="n">
-        <v>210.3</v>
-      </c>
-    </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>130.75</v>
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：根据姓名匹配部门并提取邮箱用户名（XLOOKUP + MID）</t>
+        </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是一家公司的行政，有一份员工邮箱列表（姓名和邮箱）。需要根据一个查询名单，找出对应员工的邮箱，并提取邮箱中@符号前面的用户名部分（例如邮箱是zhang@company.com，则返回zhang）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>任务：在B7单元格输入公式，向下填充，根据查询名单中的姓名，从邮箱列表中匹配邮箱，并提取@前的用户名。假设查询名单在A7:A8，姓名列在A2:A5，邮箱列在B2:B5。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>邮箱</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>zhang.san@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>li.si@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>wang.wu@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>zhao.liu@company.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>查询名单</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1109,7 +1104,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某类商品的销售总金额</t>
+          <t>第 1 题：第1题：计算某区域销售总量（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1115,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(B2:B8,"饮料",C2:C8)</f>
+        <f>SUMIF(A2:A8,"东区",B2:B8)</f>
         <v/>
       </c>
     </row>
@@ -1134,7 +1129,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计下单次数和缺货次数</t>
+          <t>第 2 题：第2题：统计满足多条件的人数（COUNTIFS）</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1140,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF(C2:C7,"已发货")；=COUNTIFS(C2:C7,"已发货",B2:B7,"&gt;100")</f>
+        <f>COUNTIFS(B2:B7,"销售部",C2:C7,"是")</f>
         <v/>
       </c>
     </row>
@@ -1159,7 +1154,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据产品编号匹配产品名称和单价</t>
+          <t>第 3 题：第3题：根据商品编码查找价格并处理错误（VLOOKUP + IFERROR）</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1165,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>IFERROR(VLOOKUP(E2,A:C,2,FALSE),"未找到")；=IFERROR(VLOOKUP(E2,A:C,3,FALSE),"未找到")</f>
+        <f>IFERROR(VLOOKUP(A6,$A$2:$B$5,2,FALSE),"查无此码")</f>
         <v/>
       </c>
     </row>
@@ -1184,7 +1179,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算到港天数和在港停留天数</t>
+          <t>第 4 题：第4题：计算员工入职年数并取整（DATEDIF + ROUND）</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1190,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>DATEDIF(B2,TODAY(),"D")；=IF(C2="",DATEDIF(B2,TODAY(),"D"),DATEDIF(B2,C2,"D"))；=IF(D2&gt;15,"超期","正常")</f>
+        <f>ROUND(DATEDIF(B2,TODAY(),"d")/365,1)</f>
         <v/>
       </c>
     </row>
@@ -1209,7 +1204,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用INDEX+MATCH实现双向查找，并用ROUND处理结果</t>
+          <t>第 5 题：第5题：根据姓名匹配部门并提取邮箱用户名（XLOOKUP + MID）</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1215,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>ROUND(INDEX(B2:D4,MATCH(H2,A2:A4,0),MATCH(H3,B1:D1,0)),2)</f>
+        <f>MID(XLOOKUP(A7,A$2:A$5,B$2:B$5),1,FIND("@",XLOOKUP(A7,A$2:A$5,B$2:B$5))-1)</f>
         <v/>
       </c>
     </row>
@@ -1252,7 +1247,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某类商品的销售总金额</t>
+          <t>第 1 题：第1题：计算某区域销售总量（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1264,14 +1259,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF(条件区域,条件,求和区域)用于按条件求和。这里B2:B8是条件区域，条件为"饮料"，C2:C8是实际求和区域，返回满足条件的金额合计。</t>
+          <t>SUMIF(区域,条件,求和区域) 会对第一个区域中符合指定条件的行，对第二个区域中对应行求和。本公式中A2:A8是分店列，条件为"东区"，B2:B8是销售额列，因此结果等于所有东区销售额之和（4700）。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计下单次数和缺货次数</t>
+          <t>第 2 题：第2题：统计满足多条件的人数（COUNTIFS）</t>
         </is>
       </c>
     </row>
@@ -1283,14 +1278,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF用于单条件计数，这里统计C列中等于"已发货"的个数。COUNTIFS支持多条件，第一个条件区域C列，第二个条件区域B列，同时满足才计数。注意数量条件用文本"&gt;100"表示大于100。</t>
+          <t>COUNTIFS(区域1,条件1,区域2,条件2) 可同时满足多个条件计数。本公式中区域1是部门列，条件1为"销售部"；区域2是完成作业列，条件2为"是"。符合条件的有张三、赵六、孙八，共3人。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据产品编号匹配产品名称和单价</t>
+          <t>第 3 题：第3题：根据商品编码查找价格并处理错误（VLOOKUP + IFERROR）</t>
         </is>
       </c>
     </row>
@@ -1302,14 +1297,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP(查找值,表区域,列号,精确匹配)在A:C区域第一列查找E2的编号，返回对应列的值。第三个参数2是名称列，3是单价列。IFERROR函数捕获VLOOKUP的错误（如#N/A），当找不到时返回"未找到"，避免显示错误。</t>
+          <t>VLOOKUP(查找值,表格,列序号,精确/近似) 在表格第一列查找，返回指定列的值。这里用FALSE表示精确匹配。IFERROR(公式,出错返回值) 当VLOOKUP找不到时返回错误，则显示“查无此码”。例如A6是A02，返回22；A7是A05，返回“查无此码”。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算到港天数和在港停留天数</t>
+          <t>第 4 题：第4题：计算员工入职年数并取整（DATEDIF + ROUND）</t>
         </is>
       </c>
     </row>
@@ -1321,14 +1316,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF(开始日期,结束日期,"D")返回两个日期相差天数。TODAY()返回当前日期。在D2中计算从到港到今天的天数。E2判断C2是否为空，若空则用今天作为结束日期，否则用离港日期。F2用IF根据D2是否大于15给出结果。</t>
+          <t>DATEDIF(开始日期,结束日期,单位) 返回两个日期之间的天数（"d"）。用天数除以365得到年数，再用ROUND(数值,1)四舍五入保留1位小数。注意TODAY()会自动更新为今天日期，考试时也可手动输入2025-01-01。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用INDEX+MATCH实现双向查找，并用ROUND处理结果</t>
+          <t>第 5 题：第5题：根据姓名匹配部门并提取邮箱用户名（XLOOKUP + MID）</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1335,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>INDEX(区域,行号,列号)返回区域中指定行列的值。MATCH(H2,A2:A4,0)找到产品B在A列的位置（第2行），MATCH(H3,B1:D1,0)找到月份"2月"在表头的位置（第2列）。二者组合得到精确交叉值。ROUND函数将结果四舍五入到2位小数。</t>
+          <t>XLOOKUP(查找值,查找数组,返回数组) 在姓名列中查找A7的值，返回对应的邮箱。MID(文本,开始位置,长度) 提取文本从第1位开始，长度为FIND("@",邮箱)找到@的位置减1，即提取@前面的字符。例如王五的邮箱是wang.wu@company.com，提取结果为wang.wu。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,407 +476,415 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：计算某区域销售总量（SUMIF）</t>
+          <t>第 1 题：第1题：计算指定日期的今日年龄</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>练习函数：SUMIF</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一个人员信息表，包含姓名和出生日期。需要计算每个人截至今天的年龄（周岁）。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家超市的经理，有一张本周各分店的销售额表。现在需要计算「东区」分店的总销售额。</t>
+          <t>任务：在C2单元格输入公式，计算张三的周岁年龄，并向下填充到C5。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>任务：在任意空白单元格（如D2）输入公式，计算「东区」的销售额总和。</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>出生日期</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>分店</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>销售额</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>1990-05-15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>东区</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>1200</v>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>1985-12-03</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>西区</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>800</v>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>2000-01-20</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>东区</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>1500</v>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>1995-07-08</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>南区</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>东区</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>900</v>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>北区</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>700</v>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：根据条件求和与计数</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>东区</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>1100</v>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一份销售记录表，包含产品、地区和销售额。需要按地区和产品汇总销售额和订单数量。</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>任务：在E2单元格输入公式，计算华东地区手机的总销售额；在F2单元格输入公式，计算华东地区手机的总订单数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>销售额</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>订单数</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：统计满足多条件的人数（COUNTIFS）</t>
-        </is>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIFS</t>
-        </is>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是一家培训机构的教务，有一份学员信息表，包含姓名、部门、是否完成作业（是/否）。现在需要统计「销售部」且完成作业为「是」的学员人数。</t>
-        </is>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>电脑</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>任务：在任意空白单元格（如E2）输入公式，统计部门为“销售部”且完成作业为“是”的人数。</t>
-        </is>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>电脑</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>18000</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>部门</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>完成作业</t>
-        </is>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>11000</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：查找匹配并返回对应信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>练习函数：XLOOKUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一个员工信息表，包含员工编号和姓名，以及一个单独的员工编号查询。需要根据编号查找姓名。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>任务：在E2单元格输入公式，根据D2单元格的员工编号102，查找对应的姓名，并显示在E2中。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>员工编号</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>部门</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
           <t>张三</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>销售部</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>李四</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>技术部</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>人事部</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>市场部</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>销售部</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>销售部</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>钱七</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>市场部</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>孙八</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>销售部</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：根据商品编码查找价格并处理错误（VLOOKUP + IFERROR）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>要求：你经营一家网店，有一份商品价格表（编码和价格）。另一份订单需要根据编码填写价格，但订单中可能存在价格表中不存在的编码，需要显示“查无此码”。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>任务：在订单表（从第6行到第9行）旁边增加一列，在F2单元格输入公式，向下填充，根据订单编码从价格表中查找价格，若找不到则显示“查无此码”。假设订单编码在A6:A9，价格表编码在A2:A5。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>编码</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>价格</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>A01</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>A02</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="n">
-        <v>22</v>
-      </c>
-    </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>A03</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>30</v>
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：提取字符串并判断</t>
+        </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>B01</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="n">
-        <v>10</v>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一份商品编码表，编码格式为"类别-年份-序号"，例如"A-2023-001"。需要根据编码提取类别和判断年份是否大于2020。</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>B02</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="n">
-        <v>18</v>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>任务：在B2单元格输入公式，提取商品编码的类别（第一个字符）；在C2单元格输入公式，判断年份是否大于2020，返回"是"或"否"。</t>
+        </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>编码</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>订单数量</t>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>商品编码</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>A02</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>3</v>
+          <t>A-2023-001</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>A05</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>1</v>
+          <t>B-2021-045</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>B01</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>2</v>
+          <t>C-2019-012</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>A01</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>5</v>
+          <t>A-2022-078</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -889,195 +897,82 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算员工入职年数并取整（DATEDIF + ROUND）</t>
+          <t>第 5 题：第5题：综合应用-物流到港天数计算</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家公司的人力资源，记录员工入职日期。需要计算每位员工截止今天（假设今天为2025-01-01）的工作年限，并保留1位小数（四舍五入）。</t>
+          <t>要求：你有一个物流跟踪表，包含发货日期和预计到港日期。需要计算运输天数（预计到港-发货），并处理缺失数据，同时显示四舍五入后的天数。</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>任务：在C2单元格输入公式，向下填充，计算每位员工的工作年限（年），结果保留1位小数。</t>
+          <t>任务：在C2单元格输入公式，计算运输天数，如果预计到港日期缺失，则返回错误提示"待定"，结果四舍五入到整数。</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>员工</t>
+          <t>发货日期</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>入职日期</t>
+          <t>预计到港日期</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>张伟</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>2018-06-15</t>
+          <t>2023-01-15</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>李娜</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>2019-11-01</t>
+          <t>2023-02-14</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>王强</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>2021-03-20</t>
-        </is>
-      </c>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>赵敏</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>2020-07-10</t>
+          <t>2023-04-25</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：根据姓名匹配部门并提取邮箱用户名（XLOOKUP + MID）</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是一家公司的行政，有一份员工邮箱列表（姓名和邮箱）。需要根据一个查询名单，找出对应员工的邮箱，并提取邮箱中@符号前面的用户名部分（例如邮箱是zhang@company.com，则返回zhang）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>任务：在B7单元格输入公式，向下填充，根据查询名单中的姓名，从邮箱列表中匹配邮箱，并提取@前的用户名。假设查询名单在A7:A8，姓名列在A2:A5，邮箱列在B2:B5。</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>邮箱</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>zhang.san@company.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>li.si@company.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>wang.wu@company.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>zhao.liu@company.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>查询名单</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1104,7 +999,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：计算某区域销售总量（SUMIF）</t>
+          <t>第 1 题：第1题：计算指定日期的今日年龄</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1010,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A8,"东区",B2:B8)</f>
+        <f>DATEDIF(B2,TODAY(),"Y")</f>
         <v/>
       </c>
     </row>
@@ -1129,7 +1024,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计满足多条件的人数（COUNTIFS）</t>
+          <t>第 2 题：第2题：根据条件求和与计数</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1035,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(B2:B7,"销售部",C2:C7,"是")</f>
+        <f>SUMIFS(C2:C7,A2:A7,"华东",B2:B7,"手机")；=COUNTIFS(A2:A7,"华东",B2:B7,"手机")</f>
         <v/>
       </c>
     </row>
@@ -1154,7 +1049,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据商品编码查找价格并处理错误（VLOOKUP + IFERROR）</t>
+          <t>第 3 题：第3题：查找匹配并返回对应信息</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1060,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>IFERROR(VLOOKUP(A6,$A$2:$B$5,2,FALSE),"查无此码")</f>
+        <f>XLOOKUP(D2,A2:A5,B2:B5)</f>
         <v/>
       </c>
     </row>
@@ -1179,7 +1074,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算员工入职年数并取整（DATEDIF + ROUND）</t>
+          <t>第 4 题：第4题：提取字符串并判断</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1085,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>ROUND(DATEDIF(B2,TODAY(),"d")/365,1)</f>
+        <f>LEFT(A2,1)；=IF(VALUE(MID(A2,3,4))&gt;2020,"是","否")</f>
         <v/>
       </c>
     </row>
@@ -1204,7 +1099,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据姓名匹配部门并提取邮箱用户名（XLOOKUP + MID）</t>
+          <t>第 5 题：第5题：综合应用-物流到港天数计算</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1110,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>MID(XLOOKUP(A7,A$2:A$5,B$2:B$5),1,FIND("@",XLOOKUP(A7,A$2:A$5,B$2:B$5))-1)</f>
+        <f>IFERROR(ROUND(MAX(B2-A2,0),0),"待定")</f>
         <v/>
       </c>
     </row>
@@ -1247,7 +1142,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：计算某区域销售总量（SUMIF）</t>
+          <t>第 1 题：第1题：计算指定日期的今日年龄</t>
         </is>
       </c>
     </row>
@@ -1259,14 +1154,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF(区域,条件,求和区域) 会对第一个区域中符合指定条件的行，对第二个区域中对应行求和。本公式中A2:A8是分店列，条件为"东区"，B2:B8是销售额列，因此结果等于所有东区销售额之和（4700）。</t>
+          <t>DATEDIF函数计算两个日期之间的差值，第一个参数是起始日期（出生日期），第二个参数是结束日期（使用TODAY()获取今天的日期），第三个参数"Y"表示返回完整的年数，即周岁。TODAY()会动态更新，所以结果每天自动变化。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计满足多条件的人数（COUNTIFS）</t>
+          <t>第 2 题：第2题：根据条件求和与计数</t>
         </is>
       </c>
     </row>
@@ -1278,14 +1173,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS(区域1,条件1,区域2,条件2) 可同时满足多个条件计数。本公式中区域1是部门列，条件1为"销售部"；区域2是完成作业列，条件2为"是"。符合条件的有张三、赵六、孙八，共3人。</t>
+          <t>SUMIFS用于多条件求和，第一个参数是求和区域（销售额），后面是条件区域和条件对。COUNTIFS用于多条件计数，只需指定条件区域和条件。这里条件区域是地区和产品列，条件分别为"华东"和"手机"。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据商品编码查找价格并处理错误（VLOOKUP + IFERROR）</t>
+          <t>第 3 题：第3题：查找匹配并返回对应信息</t>
         </is>
       </c>
     </row>
@@ -1297,14 +1192,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP(查找值,表格,列序号,精确/近似) 在表格第一列查找，返回指定列的值。这里用FALSE表示精确匹配。IFERROR(公式,出错返回值) 当VLOOKUP找不到时返回错误，则显示“查无此码”。例如A6是A02，返回22；A7是A05，返回“查无此码”。</t>
+          <t>XLOOKUP是新一代查找函数，第一个参数是要查找的值（D2），第二个参数是查找区域（员工编号列），第三个参数是返回区域（姓名列）。它不用像VLOOKUP担心列序号，而且支持精确匹配和容错。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算员工入职年数并取整（DATEDIF + ROUND）</t>
+          <t>第 4 题：第4题：提取字符串并判断</t>
         </is>
       </c>
     </row>
@@ -1316,14 +1211,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF(开始日期,结束日期,单位) 返回两个日期之间的天数（"d"）。用天数除以365得到年数，再用ROUND(数值,1)四舍五入保留1位小数。注意TODAY()会自动更新为今天日期，考试时也可手动输入2025-01-01。</t>
+          <t>LEFT提取左侧字符，这里是第一个字符。MID从中间提取，语法是MID(文本,起始位置,字符数)，这里从第3位开始提取4个字符就是年份。VALUE将文本转为数字，IF判断条件是否大于2020。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据姓名匹配部门并提取邮箱用户名（XLOOKUP + MID）</t>
+          <t>第 5 题：第5题：综合应用-物流到港天数计算</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1230,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP(查找值,查找数组,返回数组) 在姓名列中查找A7的值，返回对应的邮箱。MID(文本,开始位置,长度) 提取文本从第1位开始，长度为FIND("@",邮箱)找到@的位置减1，即提取@前面的字符。例如王五的邮箱是wang.wu@company.com，提取结果为wang.wu。</t>
+          <t>MAX确保天数不为负（如果日期异常则取0），ROUND四舍五入到0位小数，IFERROR处理错误，当B2为空时计算会出错，于是返回"待定"。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,503 +476,492 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：计算指定日期的今日年龄</t>
+          <t>第 1 题：第1题：统计某品类商品的销售数量</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一个人员信息表，包含姓名和出生日期。需要计算每个人截至今天的年龄（周岁）。</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>练习函数：SUMIF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>任务：在C2单元格输入公式，计算张三的周岁年龄，并向下填充到C5。</t>
+          <t>要求：你是一家小商店的店主，有一张商品销售记录表，包含商品名称和销售数量。现在需要统计“苹果”的总销售数量。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>出生日期</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 B7 单元格输入公式，计算所有“苹果”的销售数量总和。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>1990-05-15</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>商品</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>数量</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>1985-12-03</t>
-        </is>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>2000-01-20</t>
-        </is>
+          <t>香蕉</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>1995-07-08</t>
-        </is>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>梨</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：根据条件求和与计数</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一份销售记录表，包含产品、地区和销售额。需要按地区和产品汇总销售额和订单数量。</t>
-        </is>
-      </c>
-    </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>任务：在E2单元格输入公式，计算华东地区手机的总销售额；在F2单元格输入公式，计算华东地区手机的总订单数。</t>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：统计满足多个条件的订单数量</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>地区</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIFS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>要求：你负责管理一份订单表，包含客户名称、产品和订单状态。现在需要统计客户“张三”且状态为“已发货”的订单数量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 E2 单元格输入公式，统计客户为“张三”并且状态为“已发货”的订单数量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>客户</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>产品</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>销售额</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>订单数</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>12000</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>电脑</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>25</v>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>电脑</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>18000</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>35</v>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>9000</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>20</v>
+          <t>电脑</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
+          <t>平板</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>未发货</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
           <t>手机</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n">
-        <v>11000</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>未发货</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>电脑</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：查找匹配并返回对应信息</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>练习函数：XLOOKUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一个员工信息表，包含员工编号和姓名，以及一个单独的员工编号查询。需要根据编号查找姓名。</t>
-        </is>
-      </c>
-    </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>任务：在E2单元格输入公式，根据D2单元格的员工编号102，查找对应的姓名，并显示在E2中。</t>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：根据产品编号查找价格并处理错误</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>员工编号</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>部门</t>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一份产品价格表，包含产品编号和单价。现在需要根据产品编号查找价格，如果找不到编号，则显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n">
-        <v>101</v>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>销售部</t>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 B8 单元格输入公式，查找产品编号为“A002”的单价；然后在 B9 单元格输入公式，查找产品编号为“C999”的单价并显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>技术部</t>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>产品编号</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n">
-        <v>103</v>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>人事部</t>
-        </is>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
-        <v>104</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>市场部</t>
-        </is>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>B001</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：提取字符串并判断</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一份商品编码表，编码格式为"类别-年份-序号"，例如"A-2023-001"。需要根据编码提取类别和判断年份是否大于2020。</t>
-        </is>
-      </c>
-    </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>任务：在B2单元格输入公式，提取商品编码的类别（第一个字符）；在C2单元格输入公式，判断年份是否大于2020，返回"是"或"否"。</t>
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：计算两个日期之间的天数差</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>商品编码</t>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>练习函数：DATEDIF</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>A-2023-001</t>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一份货物到港记录表，包含到港日期和当前日期（假设今天是2023年9月1日）。需要计算每批货物已经到港的天数。</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>B-2021-045</t>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 C2 单元格输入公式，计算批次A的到港天数（从到港日期到今天的间隔天数），然后向下填充到 C4。</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>C-2019-012</t>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>货物批次</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>A-2022-078</t>
+          <t>批次A</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>2023/8/20</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>批次B</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>2023/8/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>批次C</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>2023/8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：综合应用-物流到港天数计算</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一个物流跟踪表，包含发货日期和预计到港日期。需要计算运输天数（预计到港-发货），并处理缺失数据，同时显示四舍五入后的天数。</t>
-        </is>
-      </c>
-    </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>任务：在C2单元格输入公式，计算运输天数，如果预计到港日期缺失，则返回错误提示"待定"，结果四舍五入到整数。</t>
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：根据产品名称匹配并返回单价（使用INDEX+MATCH）</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>发货日期</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>预计到港日期</t>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一张产品价格表，包含产品名称和单价。现在需要根据给定的产品名称，使用 INDEX 和 MATCH 函数查找对应的单价。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>2023-01-15</t>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 E2 单元格输入公式，查找产品名称为“显示器”的单价。</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>2023-02-01</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>2023-02-14</t>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr"/>
+          <t>键盘</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>2023-04-25</t>
-        </is>
+          <t>鼠标</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>显示器</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>耳机</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -999,7 +988,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：计算指定日期的今日年龄</t>
+          <t>第 1 题：第1题：统计某品类商品的销售数量</t>
         </is>
       </c>
     </row>
@@ -1010,7 +999,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>DATEDIF(B2,TODAY(),"Y")</f>
+        <f>SUMIF(A2:A6,"苹果",B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -1024,7 +1013,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：根据条件求和与计数</t>
+          <t>第 2 题：第2题：统计满足多个条件的订单数量</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1024,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>SUMIFS(C2:C7,A2:A7,"华东",B2:B7,"手机")；=COUNTIFS(A2:A7,"华东",B2:B7,"手机")</f>
+        <f>COUNTIFS(A2:A7,"张三",C2:C7,"已发货")</f>
         <v/>
       </c>
     </row>
@@ -1049,7 +1038,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查找匹配并返回对应信息</t>
+          <t>第 3 题：第3题：根据产品编号查找价格并处理错误</t>
         </is>
       </c>
     </row>
@@ -1059,9 +1048,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2">
-        <f>XLOOKUP(D2,A2:A5,B2:B5)</f>
-        <v/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>B8: =VLOOKUP("A002",A2:B5,2,FALSE)  B9: =IFERROR(VLOOKUP("C999",A2:B5,2,FALSE),"未找到")</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1074,7 +1064,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：提取字符串并判断</t>
+          <t>第 4 题：第4题：计算两个日期之间的天数差</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1075,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>LEFT(A2,1)；=IF(VALUE(MID(A2,3,4))&gt;2020,"是","否")</f>
+        <f>DATEDIF(B2,TODAY(),"D")</f>
         <v/>
       </c>
     </row>
@@ -1099,7 +1089,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：综合应用-物流到港天数计算</t>
+          <t>第 5 题：第5题：根据产品名称匹配并返回单价（使用INDEX+MATCH）</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1100,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>IFERROR(ROUND(MAX(B2-A2,0),0),"待定")</f>
+        <f>INDEX(B2:B5,MATCH("显示器",A2:A5,0))</f>
         <v/>
       </c>
     </row>
@@ -1142,7 +1132,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：计算指定日期的今日年龄</t>
+          <t>第 1 题：第1题：统计某品类商品的销售数量</t>
         </is>
       </c>
     </row>
@@ -1154,14 +1144,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF函数计算两个日期之间的差值，第一个参数是起始日期（出生日期），第二个参数是结束日期（使用TODAY()获取今天的日期），第三个参数"Y"表示返回完整的年数，即周岁。TODAY()会动态更新，所以结果每天自动变化。</t>
+          <t>SUMIF 函数用于根据指定条件对区域求和。语法为 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 A2:A6，条件是“苹果”，求和区域是 B2:B6，所以公式会只对商品为“苹果”的行对应的数量求和，结果为 5+7+4=16。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：根据条件求和与计数</t>
+          <t>第 2 题：第2题：统计满足多个条件的订单数量</t>
         </is>
       </c>
     </row>
@@ -1173,14 +1163,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS用于多条件求和，第一个参数是求和区域（销售额），后面是条件区域和条件对。COUNTIFS用于多条件计数，只需指定条件区域和条件。这里条件区域是地区和产品列，条件分别为"华东"和"手机"。</t>
+          <t>COUNTIFS 函数用于计算满足多个条件的单元格个数。语法为 COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2, ...)。这里第一个条件区域是客户列 A2:A7，条件“张三”；第二个条件区域是状态列 C2:C7，条件“已发货”。满足两个条件的行有第2行（张三/已发货）和第6行（张三/已发货），所以结果为 2。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查找匹配并返回对应信息</t>
+          <t>第 3 题：第3题：根据产品编号查找价格并处理错误</t>
         </is>
       </c>
     </row>
@@ -1192,14 +1182,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP是新一代查找函数，第一个参数是要查找的值（D2），第二个参数是查找区域（员工编号列），第三个参数是返回区域（姓名列）。它不用像VLOOKUP担心列序号，而且支持精确匹配和容错。</t>
+          <t>VLOOKUP 函数用于在表格首列查找指定值并返回对应行的某列值，语法为 VLOOKUP(查找值, 表格区域, 返回列号, 精确匹配)。FALSE 表示精确匹配。B8 返回 150。B9 中，VLOOKUP 查找不到 C999，会返回错误 #N/A，用 IFERROR 包裹后，当公式结果为错误时显示“未找到”，否则显示原结果。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：提取字符串并判断</t>
+          <t>第 4 题：第4题：计算两个日期之间的天数差</t>
         </is>
       </c>
     </row>
@@ -1211,14 +1201,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>LEFT提取左侧字符，这里是第一个字符。MID从中间提取，语法是MID(文本,起始位置,字符数)，这里从第3位开始提取4个字符就是年份。VALUE将文本转为数字，IF判断条件是否大于2020。</t>
+          <t>DATEDIF 函数用于计算两个日期之间的差值，语法为 DATEDIF(开始日期, 结束日期, 单位)。“D”表示天数。TODAY() 返回今天的日期。所以公式计算从到港日期到今天的完整天数。例如批次A：2023/8/20 到 2023/9/1 相差 12 天。向下填充即可得到批次B和C的天数。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：综合应用-物流到港天数计算</t>
+          <t>第 5 题：第5题：根据产品名称匹配并返回单价（使用INDEX+MATCH）</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1220,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MAX确保天数不为负（如果日期异常则取0），ROUND四舍五入到0位小数，IFERROR处理错误，当B2为空时计算会出错，于是返回"待定"。</t>
+          <t>MATCH 函数返回查找值在区域中的位置，语法为 MATCH(查找值, 查找区域, 匹配类型)。0 表示精确匹配。这里 MATCH("显示器", A2:A5, 0) 返回 3（因为显示器在第3行）。INDEX 函数根据行号返回区域中的值，语法为 INDEX(区域, 行号)。所以 INDEX(B2:B5, 3) 返回 B2:B5 区域中第3个值，即 1200。这种组合比 VLOOKUP 更灵活，尤其适合列位置变化的情况。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,91 +476,91 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某品类商品的销售数量</t>
+          <t>第 1 题：第1题：统计指定月份的销售总额</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIF</t>
+          <t>练习函数：SUMIFS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家小商店的店主，有一张商品销售记录表，包含商品名称和销售数量。现在需要统计“苹果”的总销售数量。</t>
+          <t>要求：你是一家小店的销售员，需要统计1月份的总销售额。表格中A列为日期，B列为销售额。请用SUMIFS函数计算1月份的销售额总和。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：请在 B7 单元格输入公式，计算所有“苹果”的销售数量总和。</t>
+          <t>任务：在E1单元格输入公式，计算所有日期在2024年1月的销售额总和。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>商品</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>销售额</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>2024-01-05</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>5</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>香蕉</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>3</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>7</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>梨</t>
+          <t>2024-01-20</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2</v>
+        <v>900</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>4</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="11">
@@ -573,395 +573,342 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计满足多个条件的订单数量</t>
+          <t>第 2 题：第2题：计算两个日期之间的天数</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIFS</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>要求：一个物流公司需要计算每批货物从发货到今天的仓储天数。A列是发货日期，请用DATEDIF和TODAY函数计算每批货物已存放的天数。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>要求：你负责管理一份订单表，包含客户名称、产品和订单状态。现在需要统计客户“张三”且状态为“已发货”的订单数量。</t>
+          <t>任务：在B2单元格输入公式，计算A2日期到今天的天数，并向下填充到B4。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 E2 单元格输入公式，统计客户为“张三”并且状态为“已发货”的订单数量。</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>发货日期</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>客户</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>产品</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-10</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>已发货</t>
+          <t>2024-02-20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>2024-03-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：查找员工的部门信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>要求：公司员工信息表中，A列为员工ID，B列为员工姓名，C列为部门。现在需要通过员工ID查找对应部门，若ID不存在则显示“未找到”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>任务：在F1单元格输入员工ID（如105），在G1单元格输入公式，根据F1的ID查找对应的部门，若不存在显示“未找到”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>员工ID</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>部门</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>销售部</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
           <t>李四</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>电脑</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>市场部</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>技术部</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：统计满足多个条件的订单数</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>要求：订单表中有产品类别（A列）、发货状态（B列）、订单金额（C列）。需要统计“电子产品”且“已发货”的订单数，并计算这些订单的金额总和。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>任务：在E1单元格输入公式计算“电子产品”且“已发货”的订单数量；在F1单元格输入公式计算这些订单的金额总和。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>电子产品</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>已发货</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>平板</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C35" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>服装</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>未发货</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C36" s="4" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>电子产品</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>已发货</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C37" s="4" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>电子产品</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>未发货</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>电脑</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>已发货</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="C39" s="4" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：根据产品编号查找价格并处理错误</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一份产品价格表，包含产品编号和单价。现在需要根据产品编号查找价格，如果找不到编号，则显示“未找到”。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 B8 单元格输入公式，查找产品编号为“A002”的单价；然后在 B9 单元格输入公式，查找产品编号为“C999”的单价并显示“未找到”。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>产品编号</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：提取并查找商品编码</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>要求：商品编码格式为“ABC-12345-XX”，其中中间部分为商品ID。需要从完整编码中提取商品ID，然后用VLOOKUP在价格表中查找对应价格。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>任务：在B2单元格输入公式提取商品ID（即从第5位开始取5位数字），然后向下填充；在D2单元格输入公式，用VLOOKUP根据B2的商品ID在价格表中查找价格（价格表为B2:C4区域，商品ID在B列，价格在C列）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>完整编码</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>商品ID</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>价格</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>ABC-12345-X</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr"/>
+      <c r="C46" s="4" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n">
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>ABC-67890-Y</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr"/>
+      <c r="C47" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>ABC-11111-Z</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr"/>
+      <c r="C48" s="4" t="n">
         <v>150</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>A003</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>B001</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：计算两个日期之间的天数差</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>练习函数：DATEDIF</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一份货物到港记录表，包含到港日期和当前日期（假设今天是2023年9月1日）。需要计算每批货物已经到港的天数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 C2 单元格输入公式，计算批次A的到港天数（从到港日期到今天的间隔天数），然后向下填充到 C4。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>货物批次</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>批次A</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>2023/8/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>批次B</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>2023/8/25</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>批次C</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>2023/8/28</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：根据产品名称匹配并返回单价（使用INDEX+MATCH）</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一张产品价格表，包含产品名称和单价。现在需要根据给定的产品名称，使用 INDEX 和 MATCH 函数查找对应的单价。</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 E2 单元格输入公式，查找产品名称为“显示器”的单价。</t>
-        </is>
-      </c>
-    </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>产品名称</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>键盘</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>鼠标</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>显示器</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>耳机</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -988,7 +935,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某品类商品的销售数量</t>
+          <t>第 1 题：第1题：统计指定月份的销售总额</t>
         </is>
       </c>
     </row>
@@ -999,7 +946,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"苹果",B2:B6)</f>
+        <f>SUMIFS(B2:B6,A2:A6,"&gt;=2024-01-01",A2:A6,"&lt;2024-02-01")</f>
         <v/>
       </c>
     </row>
@@ -1013,7 +960,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计满足多个条件的订单数量</t>
+          <t>第 2 题：第2题：计算两个日期之间的天数</t>
         </is>
       </c>
     </row>
@@ -1024,7 +971,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(A2:A7,"张三",C2:C7,"已发货")</f>
+        <f>DATEDIF(A2,TODAY(),"d")</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +985,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据产品编号查找价格并处理错误</t>
+          <t>第 3 题：第3题：查找员工的部门信息</t>
         </is>
       </c>
     </row>
@@ -1048,10 +995,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>B8: =VLOOKUP("A002",A2:B5,2,FALSE)  B9: =IFERROR(VLOOKUP("C999",A2:B5,2,FALSE),"未找到")</t>
-        </is>
+      <c r="B10" s="2">
+        <f>IFERROR(XLOOKUP(F1,A2:A4,C2:C4),"未找到")</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1064,7 +1010,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算两个日期之间的天数差</t>
+          <t>第 4 题：第4题：统计满足多个条件的订单数</t>
         </is>
       </c>
     </row>
@@ -1074,9 +1020,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <f>DATEDIF(B2,TODAY(),"D")</f>
-        <v/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>订单数：=COUNTIFS(A2:A6,"电子产品",B2:B6,"已发货")；金额总和：=SUMIFS(C2:C6,A2:A6,"电子产品",B2:B6,"已发货")</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1089,7 +1036,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据产品名称匹配并返回单价（使用INDEX+MATCH）</t>
+          <t>第 5 题：第5题：提取并查找商品编码</t>
         </is>
       </c>
     </row>
@@ -1099,9 +1046,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2">
-        <f>INDEX(B2:B5,MATCH("显示器",A2:A5,0))</f>
-        <v/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>提取ID：=MID(A2,5,5)；查找价格：=VLOOKUP(B2,$B$2:$C$4,2,FALSE)</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1132,7 +1080,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某品类商品的销售数量</t>
+          <t>第 1 题：第1题：统计指定月份的销售总额</t>
         </is>
       </c>
     </row>
@@ -1144,14 +1092,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 函数用于根据指定条件对区域求和。语法为 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是 A2:A6，条件是“苹果”，求和区域是 B2:B6，所以公式会只对商品为“苹果”的行对应的数量求和，结果为 5+7+4=16。</t>
+          <t>SUMIFS函数用于多条件求和，语法为SUMIFS(求和区域,条件区域1,条件1,条件区域2,条件2,...)。本题中求和区域是B2:B6，第一个条件区域是日期A2:A6，条件1是大于等于1月1日，第二个条件区域同样是A2:A6，条件2是小于2月1日，从而筛选出1月份的销售额。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计满足多个条件的订单数量</t>
+          <t>第 2 题：第2题：计算两个日期之间的天数</t>
         </is>
       </c>
     </row>
@@ -1163,14 +1111,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS 函数用于计算满足多个条件的单元格个数。语法为 COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2, ...)。这里第一个条件区域是客户列 A2:A7，条件“张三”；第二个条件区域是状态列 C2:C7，条件“已发货”。满足两个条件的行有第2行（张三/已发货）和第6行（张三/已发货），所以结果为 2。</t>
+          <t>DATEDIF函数计算两个日期的差值，语法为DATEDIF(开始日期,结束日期,单位)，单位"d"表示天数。TODAY()返回当前日期。所以公式计算从发货日期到今天的实际天数。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据产品编号查找价格并处理错误</t>
+          <t>第 3 题：第3题：查找员工的部门信息</t>
         </is>
       </c>
     </row>
@@ -1182,14 +1130,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP 函数用于在表格首列查找指定值并返回对应行的某列值，语法为 VLOOKUP(查找值, 表格区域, 返回列号, 精确匹配)。FALSE 表示精确匹配。B8 返回 150。B9 中，VLOOKUP 查找不到 C999，会返回错误 #N/A，用 IFERROR 包裹后，当公式结果为错误时显示“未找到”，否则显示原结果。</t>
+          <t>XLOOKUP函数语法为XLOOKUP(查找值,查找数组,返回数组)。这里用F1作为查找值，在A2:A4中查找，返回C2:C4中的部门。IFERROR函数捕获错误，当查找不到时显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算两个日期之间的天数差</t>
+          <t>第 4 题：第4题：统计满足多个条件的订单数</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1149,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF 函数用于计算两个日期之间的差值，语法为 DATEDIF(开始日期, 结束日期, 单位)。“D”表示天数。TODAY() 返回今天的日期。所以公式计算从到港日期到今天的完整天数。例如批次A：2023/8/20 到 2023/9/1 相差 12 天。向下填充即可得到批次B和C的天数。</t>
+          <t>COUNTIFS函数用于多条件计数，语法为COUNTIFS(条件区域1,条件1,条件区域2,条件2,...)，这里两个条件分别是类别为电子产品、状态为已发货。SUMIFS用于多条件求和，求和区域为C2:C6，条件同上。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据产品名称匹配并返回单价（使用INDEX+MATCH）</t>
+          <t>第 5 题：第5题：提取并查找商品编码</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1168,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MATCH 函数返回查找值在区域中的位置，语法为 MATCH(查找值, 查找区域, 匹配类型)。0 表示精确匹配。这里 MATCH("显示器", A2:A5, 0) 返回 3（因为显示器在第3行）。INDEX 函数根据行号返回区域中的值，语法为 INDEX(区域, 行号)。所以 INDEX(B2:B5, 3) 返回 B2:B5 区域中第3个值，即 1200。这种组合比 VLOOKUP 更灵活，尤其适合列位置变化的情况。</t>
+          <t>MID函数提取字符串中指定位置和长度的字符，语法为MID(文本,开始位置,字符个数)。本题编码从第5位开始是数字部分，取5位。VLOOKUP在区域中查找值，语法为VLOOKUP(查找值,区域,列号,精确匹配)，这里用B2作为查找值，在B2:C4区域中查找，返回第2列的价格，使用FALSE确保精确匹配。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -483,21 +483,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIFS</t>
+          <t>练习函数：SUMIF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家小店的销售员，需要统计1月份的总销售额。表格中A列为日期，B列为销售额。请用SUMIFS函数计算1月份的销售额总和。</t>
+          <t>要求：你是一家小超市的店主，有一张每日销售记录表，记录了1月和2月每天的销售额。现在你想知道1月份的总销售额是多少。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在E1单元格输入公式，计算所有日期在2024年1月的销售额总和。</t>
+          <t>任务：在E2单元格输入公式，计算1月份（2024-01-01到2024-01-31）的总销售额。</t>
         </is>
       </c>
     </row>
@@ -516,399 +516,480 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>1200</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>2024-01-02</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>800</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-01-03</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>1500</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2024-01-20</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>1100</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-03</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：计算两个日期之间的天数</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>要求：一个物流公司需要计算每批货物从发货到今天的仓储天数。A列是发货日期，请用DATEDIF和TODAY函数计算每批货物已存放的天数。</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：根据姓名查找员工部门</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>任务：在B2单元格输入公式，计算A2日期到今天的天数，并向下填充到B4。</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>练习函数：VLOOKUP</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>发货日期</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>要求：公司有一张员工名单表，包含工号、姓名和部门。你想根据某个员工的姓名快速查到其所属部门。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-10</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>任务：在F2单元格输入一个公式，根据E2单元格中的姓名（比如输入"李四"）查找并显示对应部门。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-20</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>工号</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>部门</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>销售部</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>人事部</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>技术部</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>财务部</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：查找员工的部门信息</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>要求：公司员工信息表中，A列为员工ID，B列为员工姓名，C列为部门。现在需要通过员工ID查找对应部门，若ID不存在则显示“未找到”。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>任务：在F1单元格输入员工ID（如105），在G1单元格输入公式，根据F1的ID查找对应的部门，若不存在显示“未找到”。</t>
-        </is>
-      </c>
-    </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>员工ID</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>部门</t>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：计算两个日期之间的天数</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
-        <v>101</v>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>销售部</t>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>练习函数：DATEDIF</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>市场部</t>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>要求：物流公司需要计算一批包裹从发货到送达所用的天数（到港天数）。你有发货日期和送达日期。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n">
-        <v>103</v>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>技术部</t>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>任务：在C2单元格输入公式，计算第一行包裹的到港天数（送达日期减去发货日期的完整天数），并下拉填充到C4。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>发货日期</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>送达日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：统计满足多个条件的订单数</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>要求：订单表中有产品类别（A列）、发货状态（B列）、订单金额（C列）。需要统计“电子产品”且“已发货”的订单数，并计算这些订单的金额总和。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>任务：在E1单元格输入公式计算“电子产品”且“已发货”的订单数量；在F1单元格输入公式计算这些订单的金额总和。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>类别</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-    </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：多条件统计数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIFS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是仓库管理员，有一份入库记录表，包含产品类别和入库日期。你想统计某一天内某类产品入库的记录条数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>任务：在G2单元格输入公式，统计产品类别为"电子产品"且入库日期为"2024-04-10"的记录条数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>产品类别</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>入库日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>已发货</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>服装</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>未发货</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>已发货</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>已发货</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>日用品</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>电子产品</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>未发货</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：提取并查找商品编码</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>要求：商品编码格式为“ABC-12345-XX”，其中中间部分为商品ID。需要从完整编码中提取商品ID，然后用VLOOKUP在价格表中查找对应价格。</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>任务：在B2单元格输入公式提取商品ID（即从第5位开始取5位数字），然后向下填充；在D2单元格输入公式，用VLOOKUP根据B2的商品ID在价格表中查找价格（价格表为B2:C4区域，商品ID在B列，价格在C列）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>完整编码</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>商品ID</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>价格</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>ABC-12345-X</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr"/>
-      <c r="C46" s="4" t="n">
-        <v>100</v>
-      </c>
-    </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>ABC-67890-Y</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr"/>
-      <c r="C47" s="4" t="n">
-        <v>200</v>
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：查找匹配并返回多列</t>
+        </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>ABC-11111-Z</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr"/>
-      <c r="C48" s="4" t="n">
-        <v>150</v>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一张产品价格表，包含产品编号、名称和单价。现在你想根据产品编号同时获取产品名称和单价，但不知道编号在表中的位置。</t>
+        </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>任务：在F2单元格输入公式，根据E2中填写的产品编号（如"A003"）返回对应的产品名称；在G2输入公式返回单价。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>产品编号</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>香蕉</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>橙子</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>葡萄</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -946,7 +1027,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIFS(B2:B6,A2:A6,"&gt;=2024-01-01",A2:A6,"&lt;2024-02-01")</f>
+        <f>SUMIF(A2:A7,"&gt;=2024-01-01",B2:B7)-SUMIF(A2:A7,"&gt;2024-01-31",B2:B7)</f>
         <v/>
       </c>
     </row>
@@ -960,7 +1041,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：计算两个日期之间的天数</t>
+          <t>第 2 题：第2题：根据姓名查找员工部门</t>
         </is>
       </c>
     </row>
@@ -971,7 +1052,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>DATEDIF(A2,TODAY(),"d")</f>
+        <f>VLOOKUP(E2,A2:C5,3,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -985,7 +1066,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查找员工的部门信息</t>
+          <t>第 3 题：第3题：计算两个日期之间的天数</t>
         </is>
       </c>
     </row>
@@ -996,7 +1077,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>IFERROR(XLOOKUP(F1,A2:A4,C2:C4),"未找到")</f>
+        <f>DATEDIF(A2,B2,"d")</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1091,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：统计满足多个条件的订单数</t>
+          <t>第 4 题：第4题：多条件统计数量</t>
         </is>
       </c>
     </row>
@@ -1020,10 +1101,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>订单数：=COUNTIFS(A2:A6,"电子产品",B2:B6,"已发货")；金额总和：=SUMIFS(C2:C6,A2:A6,"电子产品",B2:B6,"已发货")</t>
-        </is>
+      <c r="B14" s="2">
+        <f>COUNTIFS(A2:A6,"电子产品",B2:B6,"2024-04-10")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1036,7 +1116,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：提取并查找商品编码</t>
+          <t>第 5 题：第5题：查找匹配并返回多列</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1128,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>提取ID：=MID(A2,5,5)；查找价格：=VLOOKUP(B2,$B$2:$C$4,2,FALSE)</t>
+          <t>名称：=INDEX(B2:B5,MATCH(E2,A2:A5,0))；单价：=INDEX(C2:C5,MATCH(E2,A2:A5,0))</t>
         </is>
       </c>
     </row>
@@ -1092,14 +1172,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS函数用于多条件求和，语法为SUMIFS(求和区域,条件区域1,条件1,条件区域2,条件2,...)。本题中求和区域是B2:B6，第一个条件区域是日期A2:A6，条件1是大于等于1月1日，第二个条件区域同样是A2:A6，条件2是小于2月1日，从而筛选出1月份的销售额。</t>
+          <t>用SUMIF函数按条件求和。先对日期大于等于1月1日的销售额求和，再减去日期大于1月31日的销售额，得到1月总额。你也可以用SUMIFS函数，但此题练习SUMIF，注意条件写法用文本比较运算符。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：计算两个日期之间的天数</t>
+          <t>第 2 题：第2题：根据姓名查找员工部门</t>
         </is>
       </c>
     </row>
@@ -1111,14 +1191,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF函数计算两个日期的差值，语法为DATEDIF(开始日期,结束日期,单位)，单位"d"表示天数。TODAY()返回当前日期。所以公式计算从发货日期到今天的实际天数。</t>
+          <t>VLOOKUP语法：VLOOKUP(查找值, 表格区域, 返回列号, 精确匹配)。这里在A2:C5区域中查找E2的值，返回第3列（部门），FALSE表示精确匹配。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查找员工的部门信息</t>
+          <t>第 3 题：第3题：计算两个日期之间的天数</t>
         </is>
       </c>
     </row>
@@ -1130,14 +1210,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP函数语法为XLOOKUP(查找值,查找数组,返回数组)。这里用F1作为查找值，在A2:A4中查找，返回C2:C4中的部门。IFERROR函数捕获错误，当查找不到时显示“未找到”。</t>
+          <t>DATEDIF(开始日期,结束日期,"d")返回两个日期之间的整天数。这里用发货日期和送达日期相减，得到运输天数。注意结束日期必须大于开始日期。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：统计满足多个条件的订单数</t>
+          <t>第 4 题：第4题：多条件统计数量</t>
         </is>
       </c>
     </row>
@@ -1149,14 +1229,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS函数用于多条件计数，语法为COUNTIFS(条件区域1,条件1,条件区域2,条件2,...)，这里两个条件分别是类别为电子产品、状态为已发货。SUMIFS用于多条件求和，求和区域为C2:C6，条件同上。</t>
+          <t>COUNTIFS可以设置多个条件，每个条件对应一个区域。满足所有条件的单元格计数。这里两个条件：A列等于电子产品，B列等于指定日期。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：提取并查找商品编码</t>
+          <t>第 5 题：第5题：查找匹配并返回多列</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1248,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MID函数提取字符串中指定位置和长度的字符，语法为MID(文本,开始位置,字符个数)。本题编码从第5位开始是数字部分，取5位。VLOOKUP在区域中查找值，语法为VLOOKUP(查找值,区域,列号,精确匹配)，这里用B2作为查找值，在B2:C4区域中查找，返回第2列的价格，使用FALSE确保精确匹配。</t>
+          <t>MATCH(E2,A2:A5,0)找到编号在A列中的行号，INDEX再从对应列中取出该行号的值。与VLOOKUP相比更灵活，可返回任意列。注意MATCH的第三个参数0表示精确匹配。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定月份的销售总额</t>
+          <t>第 1 题：第1题：统计杭州仓库出库总量</t>
         </is>
       </c>
     </row>
@@ -490,87 +490,87 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家小超市的店主，有一张每日销售记录表，记录了1月和2月每天的销售额。现在你想知道1月份的总销售额是多少。</t>
+          <t>要求：你是一家电商公司的物流专员，需要统计杭州仓库当月的出库总数量。现有出库记录表，包含仓库、出库数量两列，请计算杭州仓库的出库数量合计。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格输入公式，计算1月份（2024-01-01到2024-01-31）的总销售额。</t>
+          <t>任务：在E2单元格输入公式，计算“杭州”仓库的出库数量总和。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>仓库</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>出库数量</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>300</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2024-01-03</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>450</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>600</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>350</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>700</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：根据姓名查找员工部门</t>
+          <t>第 2 题：第2题：核对员工工号并提取部门</t>
         </is>
       </c>
     </row>
@@ -597,14 +597,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>要求：公司有一张员工名单表，包含工号、姓名和部门。你想根据某个员工的姓名快速查到其所属部门。</t>
+          <t>要求：公司有两个表格：员工基本信息表（含工号、姓名、部门）和考勤表（含工号、出勤天数）。你需要根据考勤表中的工号，从基本信息表中查出对应员工的部门，填写到考勤表旁边。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>任务：在F2单元格输入一个公式，根据E2单元格中的姓名（比如输入"李四"）查找并显示对应部门。</t>
+          <t>任务：在考勤表（假设在G2单元格）输入公式，根据工号（G1单元格是工号）查找对应部门。考勤表工号列表在F2:F5，部门结果放在G2:G5。请写出在G2输入的公式（假设F2为A001）。</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>A001</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -645,7 +645,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>A002</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -655,14 +655,14 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>人事部</t>
+          <t>市场部</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>A003</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -672,14 +672,14 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>技术部</t>
+          <t>财务部</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>A004</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>财务部</t>
+          <t>人事部</t>
         </is>
       </c>
     </row>
@@ -703,184 +703,228 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算两个日期之间的天数</t>
+          <t>第 3 题：第3题：计算到港天数和延迟天数</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>练习函数：DATEDIF</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是港口调度员，需要跟踪每个集装箱的到港情况。表格包含集装箱号、预计到港日期、实际到港日期（有些未到港为空）。请计算今天距离预计到港日期的天数（若是今天之前已到港，则计算实际到港日期到今天的间隔天数？不，这里简化：计算预计到港日期到今天的间隔天数，用于判断是否延迟）。实际场景：计算每个集装箱从预计到港日期到今天已经过去多少天，以及实际到港是否延迟（用IF判断）。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>要求：物流公司需要计算一批包裹从发货到送达所用的天数（到港天数）。你有发货日期和送达日期。</t>
+          <t>任务：在D2单元格输入公式，计算C001的预计到港日期到今天的间隔天数（使用TODAY和DATEDIF）。假设今天为2025-03-10，请给出公式。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>任务：在C2单元格输入公式，计算第一行包裹的到港天数（送达日期减去发货日期的完整天数），并下拉填充到C4。</t>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>集装箱号</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>预计到港日期</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>实际到港日期</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>发货日期</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>送达日期</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>C002</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
-        </is>
-      </c>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>C003</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：按区域和月份汇总销售额</t>
+        </is>
+      </c>
+    </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：多条件统计数量</t>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>练习函数：SUMIFS</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIFS</t>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是一家销售公司的数据分析员，需要统计特定区域和特定月份的销售额总和。表格包含区域、销售日期、销售额。请计算“华东”区域在“2025年3月”的销售额合计。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>要求：你是仓库管理员，有一份入库记录表，包含产品类别和入库日期。你想统计某一天内某类产品入库的记录条数。</t>
+          <t>任务：在E2单元格输入公式，计算区域为“华东”且销售日期在2025年3月1日至3月31日之间的销售额总和。</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>任务：在G2单元格输入公式，统计产品类别为"电子产品"且入库日期为"2024-04-10"的记录条数。</t>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>销售日期</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>销售额</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>产品类别</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>入库日期</t>
-        </is>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>5000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
-        </is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>3000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
-        </is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>4500</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
-        </is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>6200</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>日用品</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
-        </is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>2100</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
-        </is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>7000</v>
       </c>
     </row>
     <row r="45">
@@ -893,38 +937,33 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：查找匹配并返回多列</t>
+          <t>第 5 题：第5题：提取员工姓名并查找绩效等级</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>要求：你有一张产品价格表，包含产品编号、名称和单价。现在你想根据产品编号同时获取产品名称和单价，但不知道编号在表中的位置。</t>
+          <t>要求：你有一份员工名单，但姓名被合并为“工号-姓名”格式（如“A001-张三”），需要提取出姓名，并根据姓名在绩效表中查找对应的绩效等级。同时，需要根据工号在另一张表中找到对应的部门（使用INDEX和MATCH）。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>任务：在F2单元格输入公式，根据E2中填写的产品编号（如"A003"）返回对应的产品名称；在G2输入公式返回单价。</t>
+          <t>任务：假设在A1单元格是“A001-张三”，在C2单元格输入公式提取姓名（使用RIGHT函数），然后在D2单元格输入公式根据姓名（C2）在绩效表（A1:B5）中查找绩效等级（使用INDEX和MATCH）。请分别写出C2和D2的公式。</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>产品编号</t>
+          <t>员工代码</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>产品名称</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
+          <t>绩效等级</t>
         </is>
       </c>
     </row>
@@ -936,11 +975,8 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>5.5</v>
+          <t>A</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -951,11 +987,8 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>香蕉</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>3.2</v>
+          <t>B</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -966,11 +999,8 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>橙子</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>4.8</v>
+          <t>C</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -981,11 +1011,8 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>葡萄</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>7.9</v>
+          <t>A</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -1016,7 +1043,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定月份的销售总额</t>
+          <t>第 1 题：第1题：统计杭州仓库出库总量</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1054,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A7,"&gt;=2024-01-01",B2:B7)-SUMIF(A2:A7,"&gt;2024-01-31",B2:B7)</f>
+        <f>SUMIF(A2:A7,"杭州",B2:B7)</f>
         <v/>
       </c>
     </row>
@@ -1041,7 +1068,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：根据姓名查找员工部门</t>
+          <t>第 2 题：第2题：核对员工工号并提取部门</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1079,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>VLOOKUP(E2,A2:C5,3,FALSE)</f>
+        <f>VLOOKUP(F2,A2:C5,3,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -1066,7 +1093,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算两个日期之间的天数</t>
+          <t>第 3 题：第3题：计算到港天数和延迟天数</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1104,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>DATEDIF(A2,B2,"d")</f>
+        <f>DATEDIF(B2,TODAY(),"d")</f>
         <v/>
       </c>
     </row>
@@ -1091,7 +1118,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：多条件统计数量</t>
+          <t>第 4 题：第4题：按区域和月份汇总销售额</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1129,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>COUNTIFS(A2:A6,"电子产品",B2:B6,"2024-04-10")</f>
+        <f>SUMIFS(C2:C7,A2:A7,"华东",B2:B7,"&gt;=2025-03-01",B2:B7,"&lt;=2025-03-31")</f>
         <v/>
       </c>
     </row>
@@ -1116,7 +1143,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：查找匹配并返回多列</t>
+          <t>第 5 题：第5题：提取员工姓名并查找绩效等级</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1155,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>名称：=INDEX(B2:B5,MATCH(E2,A2:A5,0))；单价：=INDEX(C2:C5,MATCH(E2,A2:A5,0))</t>
+          <t>C2: =RIGHT(A1,LEN(A1)-FIND("-",A1))；D2: =INDEX(B1:B5,MATCH(C2,A1:A5,0))</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1187,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定月份的销售总额</t>
+          <t>第 1 题：第1题：统计杭州仓库出库总量</t>
         </is>
       </c>
     </row>
@@ -1172,14 +1199,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>用SUMIF函数按条件求和。先对日期大于等于1月1日的销售额求和，再减去日期大于1月31日的销售额，得到1月总额。你也可以用SUMIFS函数，但此题练习SUMIF，注意条件写法用文本比较运算符。</t>
+          <t>SUMIF函数用于按条件求和，语法为SUMIF(条件区域, 条件, 求和区域)。这里条件区域是A2:A7（仓库列），条件是“杭州”，求和区域是B2:B7（出库数量）。函数会扫描A列中每个单元格，若等于“杭州”，则对应B列的数值累加。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：根据姓名查找员工部门</t>
+          <t>第 2 题：第2题：核对员工工号并提取部门</t>
         </is>
       </c>
     </row>
@@ -1191,14 +1218,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP语法：VLOOKUP(查找值, 表格区域, 返回列号, 精确匹配)。这里在A2:C5区域中查找E2的值，返回第3列（部门），FALSE表示精确匹配。</t>
+          <t>VLOOKUP用于垂直查找，语法为VLOOKUP(查找值, 表格区域, 返回列号, 匹配方式)。这里查找值F2（工号），表格区域A2:C5（基本信息表），返回第3列（部门），FALSE表示精确匹配。注意：查找值必须在表格区域的第一列。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算两个日期之间的天数</t>
+          <t>第 3 题：第3题：计算到港天数和延迟天数</t>
         </is>
       </c>
     </row>
@@ -1210,14 +1237,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF(开始日期,结束日期,"d")返回两个日期之间的整天数。这里用发货日期和送达日期相减，得到运输天数。注意结束日期必须大于开始日期。</t>
+          <t>DATEDIF计算两个日期之间的完整时间间隔，语法为DATEDIF(开始日期, 结束日期, 单位)。这里开始日期是B2（预计到港日期），结束日期是TODAY()（今天），单位"d"表示天数。TODAY()动态返回当前日期，每次打开文件自动更新。注意：DATEDIF在Excel中是一个隐藏函数，但可以直接使用。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：多条件统计数量</t>
+          <t>第 4 题：第4题：按区域和月份汇总销售额</t>
         </is>
       </c>
     </row>
@@ -1229,14 +1256,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS可以设置多个条件，每个条件对应一个区域。满足所有条件的单元格计数。这里两个条件：A列等于电子产品，B列等于指定日期。</t>
+          <t>SUMIFS用于多条件求和，语法为SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2, ...)。这里求和区域是C2:C7（销售额），第一个条件区域A2:A7，条件“华东”；第二个条件区域B2:B7，条件“&gt;=2025-03-01”；第三个条件区域B2:B7，条件“&lt;=2025-03-31”。注意：日期条件需要用双引号括起来，且日期格式要能被Excel识别。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：查找匹配并返回多列</t>
+          <t>第 5 题：第5题：提取员工姓名并查找绩效等级</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1275,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MATCH(E2,A2:A5,0)找到编号在A列中的行号，INDEX再从对应列中取出该行号的值。与VLOOKUP相比更灵活，可返回任意列。注意MATCH的第三个参数0表示精确匹配。</t>
+          <t>RIGHT函数提取字符串右侧指定长度的字符，语法RIGHT(文本, 字符个数)。这里需要动态计算姓名长度，用LEN(A1)得到总长度，FIND("-",A1)找到连字符位置，相减得到姓名长度。INDEX和MATCH组合：MATCH(C2,A1:A5,0)在A列中查找姓名所在行，返回位置；INDEX(B1:B5, 位置)返回该行对应的绩效等级。这是VLOOKUP的替代方案，更灵活。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计杭州仓库出库总量</t>
+          <t>第 1 题：第1题：计算某部门的总销售额（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -490,87 +490,122 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家电商公司的物流专员，需要统计杭州仓库当月的出库总数量。现有出库记录表，包含仓库、出库数量两列，请计算杭州仓库的出库数量合计。</t>
+          <t>要求：你是一家小公司的销售助理，需要统计“销售一部”的总销售额。表格中有销售部门、销售员和销售额三列数据。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格输入公式，计算“杭州”仓库的出库数量总和。</t>
+          <t>任务：在E1单元格输入公式，计算“销售一部”的总销售额。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>仓库</t>
+          <t>部门</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>出库数量</t>
+          <t>销售员</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>销售额</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>120</v>
+          <t>销售一部</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>12000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>80</v>
+          <t>销售二部</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>15000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>95</v>
+          <t>销售一部</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>8000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>60</v>
+          <t>销售三部</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>20000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>110</v>
+          <t>销售一部</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>孙七</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>9500</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>75</v>
+          <t>销售二部</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>周八</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>11000</v>
       </c>
     </row>
     <row r="12">
@@ -583,440 +618,434 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：核对员工工号并提取部门</t>
+          <t>第 2 题：第2题：统计某产品在特定日期的订单数量（COUNTIFS）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>练习函数：VLOOKUP</t>
+          <t>练习函数：COUNTIFS</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>要求：公司有两个表格：员工基本信息表（含工号、姓名、部门）和考勤表（含工号、出勤天数）。你需要根据考勤表中的工号，从基本信息表中查出对应员工的部门，填写到考勤表旁边。</t>
+          <t>要求：你管理一个电商订单表，需要统计在“2024-05-01”下单且产品为“手机”的订单数量。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>任务：在考勤表（假设在G2单元格）输入公式，根据工号（G1单元格是工号）查找对应部门。考勤表工号列表在F2:F5，部门结果放在G2:G5。请写出在G2输入的公式（假设F2为A001）。</t>
+          <t>任务：在E1单元格输入公式，统计日期为“2024-05-01”且产品为“手机”的订单数量（行数）。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>工号</t>
+          <t>订单日期</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>姓名</t>
+          <t>产品</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>部门</t>
+          <t>数量</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>销售部</t>
-        </is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>市场部</t>
-        </is>
+          <t>耳机</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>A003</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>财务部</t>
-        </is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>A004</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>人事部</t>
-        </is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>耳机</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>充电器</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：计算到港天数和延迟天数</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是港口调度员，需要跟踪每个集装箱的到港情况。表格包含集装箱号、预计到港日期、实际到港日期（有些未到港为空）。请计算今天距离预计到港日期的天数（若是今天之前已到港，则计算实际到港日期到今天的间隔天数？不，这里简化：计算预计到港日期到今天的间隔天数，用于判断是否延迟）。实际场景：计算每个集装箱从预计到港日期到今天已经过去多少天，以及实际到港是否延迟（用IF判断）。</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>任务：在D2单元格输入公式，计算C001的预计到港日期到今天的间隔天数（使用TODAY和DATEDIF）。假设今天为2025-03-10，请给出公式。</t>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：查找员工底薪并处理错误（XLOOKUP + IFERROR）</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>集装箱号</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>预计到港日期</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>实际到港日期</t>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一份员工薪资表，需要根据员工编号查找对应底薪。如果编号不存在，显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>C001</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>2025-02-28</t>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>任务：在E1单元格输入公式，根据F1单元格输入的员工编号（例如E003）查找底薪，如果找不到则显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>C002</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr"/>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>员工编号</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>底薪</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>C003</t>
+          <t>E001</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>2025-02-25</t>
-        </is>
+          <t>张伟</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>5000</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>E002</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>李娜</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>E003</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>王强</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>E004</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>赵敏</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：按区域和月份汇总销售额</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>练习函数：SUMIFS</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是一家销售公司的数据分析员，需要统计特定区域和特定月份的销售额总和。表格包含区域、销售日期、销售额。请计算“华东”区域在“2025年3月”的销售额合计。</t>
-        </is>
-      </c>
-    </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>任务：在E2单元格输入公式，计算区域为“华东”且销售日期在2025年3月1日至3月31日之间的销售额总和。</t>
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：计算员工入职天数（DATEDIF + TODAY）</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>区域</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>销售日期</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>销售额</t>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>要求：人力资源需要计算每位员工到今天的入职天数（以天为单位），表格中记录了入职日期。</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>5000</v>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>任务：在C2单元格输入公式，计算张三的入职天数（今天假设为2025-01-01），然后下拉填充到C4。</t>
+        </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>3000</v>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>员工姓名</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>入职日期</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>4500</v>
+          <t>2020-06-15</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>6200</v>
+          <t>2021-03-01</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>2100</v>
+          <t>2022-09-10</t>
+        </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：提取快递单号中的城市代码并匹配城市名（MID + VLOOKUP）</t>
+        </is>
+      </c>
+    </row>
     <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：提取员工姓名并查找绩效等级</t>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>要求：物流公司有一份快递单号，单号前4位是城市代码，例如“SH01”代表上海，“BJ02”代表北京。你需要从单号中提取城市代码，并根据代码查找对应城市名称。</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>要求：你有一份员工名单，但姓名被合并为“工号-姓名”格式（如“A001-张三”），需要提取出姓名，并根据姓名在绩效表中查找对应的绩效等级。同时，需要根据工号在另一张表中找到对应的部门（使用INDEX和MATCH）。</t>
+          <t>任务：在E1单元格输入公式，从F1单元格的快递单号（例如SH012024001）中提取前4位作为代码，然后在A2:C5区域查找对应的城市名。</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>任务：假设在A1单元格是“A001-张三”，在C2单元格输入公式提取姓名（使用RIGHT函数），然后在D2单元格输入公式根据姓名（C2）在绩效表（A1:B5）中查找绩效等级（使用INDEX和MATCH）。请分别写出C2和D2的公式。</t>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>快递单号</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>城市代码</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>城市名</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>员工代码</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>绩效等级</t>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>SH012024001</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>SH01</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>BJ022024002</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>BJ02</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>GZ032024003</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>GZ03</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>广州</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>A003</t>
+          <t>SZ042024004</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SZ04</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>深圳</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>A004</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1043,7 +1072,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计杭州仓库出库总量</t>
+          <t>第 1 题：第1题：计算某部门的总销售额（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1083,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A7,"杭州",B2:B7)</f>
+        <f>SUMIF(A2:A7,"销售一部",C2:C7)</f>
         <v/>
       </c>
     </row>
@@ -1068,7 +1097,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：核对员工工号并提取部门</t>
+          <t>第 2 题：第2题：统计某产品在特定日期的订单数量（COUNTIFS）</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1108,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>VLOOKUP(F2,A2:C5,3,FALSE)</f>
+        <f>COUNTIFS(A2:A7,"2024-05-01",B2:B7,"手机")</f>
         <v/>
       </c>
     </row>
@@ -1093,7 +1122,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算到港天数和延迟天数</t>
+          <t>第 3 题：第3题：查找员工底薪并处理错误（XLOOKUP + IFERROR）</t>
         </is>
       </c>
     </row>
@@ -1104,35 +1133,35 @@
         </is>
       </c>
       <c r="B10" s="2">
+        <f>IFERROR(XLOOKUP(F1,A2:A5,C2:C5),"未找到")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>（可直接复制公式到题目文件对应单元格验证）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：计算员工入职天数（DATEDIF + TODAY）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>答案：</t>
+        </is>
+      </c>
+      <c r="B14" s="2">
         <f>DATEDIF(B2,TODAY(),"d")</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>（可直接复制公式到题目文件对应单元格验证）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：按区域和月份汇总销售额</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>答案：</t>
-        </is>
-      </c>
-      <c r="B14" s="2">
-        <f>SUMIFS(C2:C7,A2:A7,"华东",B2:B7,"&gt;=2025-03-01",B2:B7,"&lt;=2025-03-31")</f>
-        <v/>
-      </c>
-    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
@@ -1143,7 +1172,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：提取员工姓名并查找绩效等级</t>
+          <t>第 5 题：第5题：提取快递单号中的城市代码并匹配城市名（MID + VLOOKUP）</t>
         </is>
       </c>
     </row>
@@ -1153,10 +1182,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>C2: =RIGHT(A1,LEN(A1)-FIND("-",A1))；D2: =INDEX(B1:B5,MATCH(C2,A1:A5,0))</t>
-        </is>
+      <c r="B18" s="2">
+        <f>VLOOKUP(MID(F1,1,4),A2:C5,3,FALSE)</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1187,7 +1215,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计杭州仓库出库总量</t>
+          <t>第 1 题：第1题：计算某部门的总销售额（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1199,14 +1227,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF函数用于按条件求和，语法为SUMIF(条件区域, 条件, 求和区域)。这里条件区域是A2:A7（仓库列），条件是“杭州”，求和区域是B2:B7（出库数量）。函数会扫描A列中每个单元格，若等于“杭州”，则对应B列的数值累加。</t>
+          <t>SUMIF函数用于按条件求和，语法为SUMIF(条件区域, 条件, 求和区域)。这里条件区域是A2:A7（部门列），条件是"销售一部"，求和区域是C2:C7（销售额列）。公式会找出所有部门为“销售一部”的行，并对应销售额求和，结果为12000+8000+9500=29500。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：核对员工工号并提取部门</t>
+          <t>第 2 题：第2题：统计某产品在特定日期的订单数量（COUNTIFS）</t>
         </is>
       </c>
     </row>
@@ -1218,14 +1246,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP用于垂直查找，语法为VLOOKUP(查找值, 表格区域, 返回列号, 匹配方式)。这里查找值F2（工号），表格区域A2:C5（基本信息表），返回第3列（部门），FALSE表示精确匹配。注意：查找值必须在表格区域的第一列。</t>
+          <t>COUNTIFS函数用于多条件计数，语法为COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2, ...)。这里第一个条件区域是A2:A7（日期列），条件是"2024-05-01"；第二个条件区域是B2:B7（产品列），条件是"手机"。公式统计同时满足两个条件的行数，第1行和第4行符合，结果为2。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算到港天数和延迟天数</t>
+          <t>第 3 题：第3题：查找员工底薪并处理错误（XLOOKUP + IFERROR）</t>
         </is>
       </c>
     </row>
@@ -1237,14 +1265,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF计算两个日期之间的完整时间间隔，语法为DATEDIF(开始日期, 结束日期, 单位)。这里开始日期是B2（预计到港日期），结束日期是TODAY()（今天），单位"d"表示天数。TODAY()动态返回当前日期，每次打开文件自动更新。注意：DATEDIF在Excel中是一个隐藏函数，但可以直接使用。</t>
+          <t>XLOOKUP函数用于查找，语法为XLOOKUP(查找值, 查找数组, 返回数组)。这里F1是查找值（员工编号），A2:A5是查找数组，C2:C5是返回数组（底薪）。IFERROR函数用于处理错误，如果XLOOKUP找不到（例如输入E999），会返回错误，IFERROR将其替换为“未找到”。当F1=E003时，公式返回5500。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按区域和月份汇总销售额</t>
+          <t>第 4 题：第4题：计算员工入职天数（DATEDIF + TODAY）</t>
         </is>
       </c>
     </row>
@@ -1256,14 +1284,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS用于多条件求和，语法为SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2, ...)。这里求和区域是C2:C7（销售额），第一个条件区域A2:A7，条件“华东”；第二个条件区域B2:B7，条件“&gt;=2025-03-01”；第三个条件区域B2:B7，条件“&lt;=2025-03-31”。注意：日期条件需要用双引号括起来，且日期格式要能被Excel识别。</t>
+          <t>DATEDIF函数计算两个日期之间的差值，语法为DATEDIF(开始日期, 结束日期, 单位)。这里开始日期是B2（入职日期），结束日期是TODAY()（今天），单位"d"表示天数。TODAY()返回当前日期。如果今天是2025-01-01，张三入职2020-06-15，则结果为1661天（具体天数随今天变化）。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：提取员工姓名并查找绩效等级</t>
+          <t>第 5 题：第5题：提取快递单号中的城市代码并匹配城市名（MID + VLOOKUP）</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1303,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>RIGHT函数提取字符串右侧指定长度的字符，语法RIGHT(文本, 字符个数)。这里需要动态计算姓名长度，用LEN(A1)得到总长度，FIND("-",A1)找到连字符位置，相减得到姓名长度。INDEX和MATCH组合：MATCH(C2,A1:A5,0)在A列中查找姓名所在行，返回位置；INDEX(B1:B5, 位置)返回该行对应的绩效等级。这是VLOOKUP的替代方案，更灵活。</t>
+          <t>MID函数用于提取字符串中的子串，语法为MID(文本, 开始位置, 字符个数)。这里MID(F1,1,4)提取F1的前4个字符，例如SH01。VLOOKUP函数在表格中查找，语法为VLOOKUP(查找值, 表格区域, 列号, 匹配方式)。这里查找值是MID结果，表格区域是A2:C5，列号3（城市名列），FALSE表示精确匹配。公式会返回“上海”。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：计算某部门的总销售额（SUMIF）</t>
+          <t>第 1 题：第1题：统计指定商品的销售数量</t>
         </is>
       </c>
     </row>
@@ -490,122 +490,87 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家小公司的销售助理，需要统计“销售一部”的总销售额。表格中有销售部门、销售员和销售额三列数据。</t>
+          <t>要求：你有一份商品销售明细表，包含商品名称和销售数量。现在需要统计“苹果”的总销售数量。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在E1单元格输入公式，计算“销售一部”的总销售额。</t>
+          <t>任务：在单元格 B8 中输入公式，统计所有“苹果”的销售数量总和。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>部门</t>
+          <t>商品名称</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>销售员</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>销售额</t>
+          <t>销售数量</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>销售一部</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>12000</v>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>销售二部</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>15000</v>
+          <t>香蕉</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>销售一部</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>8000</v>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>销售三部</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>20000</v>
+          <t>橙子</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>销售一部</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>孙七</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>9500</v>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>销售二部</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>周八</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>11000</v>
+          <t>香蕉</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="12">
@@ -618,434 +583,334 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计某产品在特定日期的订单数量（COUNTIFS）</t>
+          <t>第 2 题：第2题：计算指定日期范围内的销售额</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIFS</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是一家小店的店主，有一份订单记录表，包含订单日期和销售额。现在需要统计今天及以后（包括今天）的销售额总和。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>要求：你管理一个电商订单表，需要统计在“2024-05-01”下单且产品为“手机”的订单数量。</t>
+          <t>任务：在单元格 B8 中输入公式，统计订单日期 &gt;= 今天的销售额总和（假设今天是2025-03-18）。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>任务：在E1单元格输入公式，统计日期为“2024-05-01”且产品为“手机”的订单数量（行数）。</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>订单日期</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>销售额</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>订单日期</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>产品</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>2</v>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>耳机</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>5</v>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>1</v>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>420</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>3</v>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>260</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>耳机</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>2</v>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>充电器</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：查找商品价格并处理错误</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：查找员工底薪并处理错误（XLOOKUP + IFERROR）</t>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一份商品价格表，现在需要根据商品名称查找价格。如果商品不存在，则显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>要求：你有一份员工薪资表，需要根据员工编号查找对应底薪。如果编号不存在，显示“未找到”。</t>
+          <t>任务：在单元格 E2 中输入公式，根据 D2 单元格中的商品名称（例如“梨”），从价格表中查找价格，如果找不到则显示“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>任务：在E1单元格输入公式，根据F1单元格输入的员工编号（例如E003）查找底薪，如果找不到则显示“未找到”。</t>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>商品</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>价格</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>员工编号</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>底薪</t>
-        </is>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>E001</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>张伟</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>5000</v>
+          <t>香蕉</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>E002</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>李娜</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>6000</v>
+          <t>橙子</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>E003</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>王强</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>5500</v>
+          <t>葡萄</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>E004</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>赵敏</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>6500</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：计算员工工龄和到岗天数</t>
+        </is>
+      </c>
+    </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：计算员工入职天数（DATEDIF + TODAY）</t>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一份员工入职日期表，需要计算每位员工到今天的工龄（年数）和到岗天数，方便人事统计。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>要求：人力资源需要计算每位员工到今天的入职天数（以天为单位），表格中记录了入职日期。</t>
+          <t>任务：在单元格 C2 中输入公式，计算张三的到岗天数（从入职日期到今天的总天数，假设今天是2025-03-18）；在单元格 D2 中输入公式，计算张三的工龄（完整年数）。</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>任务：在C2单元格输入公式，计算张三的入职天数（今天假设为2025-01-01），然后下拉填充到C4。</t>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>员工姓名</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>入职日期</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>员工姓名</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>入职日期</t>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>2020-06-15</t>
+          <t>2019-06-01</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-03-10</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>2022-09-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：提取货物编码并匹配仓库位置</t>
+        </is>
+      </c>
+    </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：提取快递单号中的城市代码并匹配城市名（MID + VLOOKUP）</t>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一份物流货物清单，货物编码格式为“仓-区-编号”（例如 A-01-123）。需要提取编码中的仓库区号（第3、4个字符），然后根据区号匹配仓库位置表，返回仓库区域名称。</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>要求：物流公司有一份快递单号，单号前4位是城市代码，例如“SH01”代表上海，“BJ02”代表北京。你需要从单号中提取城市代码，并根据代码查找对应城市名称。</t>
+          <t>任务：在单元格 E2 中输入公式，根据 D2 单元格中的区号（例如 "01"），在仓库位置表中查找对应的仓库区域名称。仓库位置表在 G2:H4 区域（见下方说明）。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>任务：在E1单元格输入公式，从F1单元格的快递单号（例如SH012024001）中提取前4位作为代码，然后在A2:C5区域查找对应的城市名。</t>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>货物编码</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>重量</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>快递单号</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>城市代码</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>城市名</t>
-        </is>
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>A-01-123</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>SH012024001</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>SH01</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
+          <t>B-02-456</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>BJ022024002</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>BJ02</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
+          <t>C-03-789</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>GZ032024003</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>GZ03</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
+          <t>A-04-111</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>SZ042024004</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>SZ04</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1072,7 +937,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：计算某部门的总销售额（SUMIF）</t>
+          <t>第 1 题：第1题：统计指定商品的销售数量</t>
         </is>
       </c>
     </row>
@@ -1083,7 +948,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A7,"销售一部",C2:C7)</f>
+        <f>SUMIF(A2:A7,"苹果",B2:B7)</f>
         <v/>
       </c>
     </row>
@@ -1097,7 +962,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计某产品在特定日期的订单数量（COUNTIFS）</t>
+          <t>第 2 题：第2题：计算指定日期范围内的销售额</t>
         </is>
       </c>
     </row>
@@ -1108,7 +973,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(A2:A7,"2024-05-01",B2:B7,"手机")</f>
+        <f>SUMIFS(B2:B7, A2:A7, "&gt;="&amp;TODAY())</f>
         <v/>
       </c>
     </row>
@@ -1122,7 +987,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查找员工底薪并处理错误（XLOOKUP + IFERROR）</t>
+          <t>第 3 题：第3题：查找商品价格并处理错误</t>
         </is>
       </c>
     </row>
@@ -1133,7 +998,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>IFERROR(XLOOKUP(F1,A2:A5,C2:C5),"未找到")</f>
+        <f>IFERROR(VLOOKUP(D2, A2:B5, 2, FALSE), "未找到")</f>
         <v/>
       </c>
     </row>
@@ -1147,7 +1012,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算员工入职天数（DATEDIF + TODAY）</t>
+          <t>第 4 题：第4题：计算员工工龄和到岗天数</t>
         </is>
       </c>
     </row>
@@ -1157,9 +1022,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <f>DATEDIF(B2,TODAY(),"d")</f>
-        <v/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>C2: =DATEDIF(B2, TODAY(), "d")；D2: =DATEDIF(B2, TODAY(), "y")</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1172,7 +1038,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：提取快递单号中的城市代码并匹配城市名（MID + VLOOKUP）</t>
+          <t>第 5 题：第5题：提取货物编码并匹配仓库位置</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1049,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>VLOOKUP(MID(F1,1,4),A2:C5,3,FALSE)</f>
+        <f>XLOOKUP(MID(A2,3,2), G2:G4, H2:H4)</f>
         <v/>
       </c>
     </row>
@@ -1215,7 +1081,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：计算某部门的总销售额（SUMIF）</t>
+          <t>第 1 题：第1题：统计指定商品的销售数量</t>
         </is>
       </c>
     </row>
@@ -1227,14 +1093,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF函数用于按条件求和，语法为SUMIF(条件区域, 条件, 求和区域)。这里条件区域是A2:A7（部门列），条件是"销售一部"，求和区域是C2:C7（销售额列）。公式会找出所有部门为“销售一部”的行，并对应销售额求和，结果为12000+8000+9500=29500。</t>
+          <t>SUMIF 函数用于按条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。本例中，条件区域是商品名称列 A2:A7，条件是“苹果”，求和区域是销售数量列 B2:B7，所以公式会累加所有商品名称为“苹果”的销售数量，得到 10+15+12=37。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计某产品在特定日期的订单数量（COUNTIFS）</t>
+          <t>第 2 题：第2题：计算指定日期范围内的销售额</t>
         </is>
       </c>
     </row>
@@ -1246,14 +1112,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS函数用于多条件计数，语法为COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2, ...)。这里第一个条件区域是A2:A7（日期列），条件是"2024-05-01"；第二个条件区域是B2:B7（产品列），条件是"手机"。公式统计同时满足两个条件的行数，第1行和第4行符合，结果为2。</t>
+          <t>SUMIFS 函数用于多条件求和，语法为 SUMIFS(求和区域, 条件区域1, 条件1, ...)。本例中，求和区域是销售额 B2:B7，条件区域1是日期列 A2:A7，条件1是 "&gt;="&amp;TODAY()，其中 TODAY() 返回今天的日期，用 &amp; 连接比较运算符。公式会累加日期在今天及之后的销售额，即 420+260+300=980。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查找员工底薪并处理错误（XLOOKUP + IFERROR）</t>
+          <t>第 3 题：第3题：查找商品价格并处理错误</t>
         </is>
       </c>
     </row>
@@ -1265,14 +1131,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP函数用于查找，语法为XLOOKUP(查找值, 查找数组, 返回数组)。这里F1是查找值（员工编号），A2:A5是查找数组，C2:C5是返回数组（底薪）。IFERROR函数用于处理错误，如果XLOOKUP找不到（例如输入E999），会返回错误，IFERROR将其替换为“未找到”。当F1=E003时，公式返回5500。</t>
+          <t>VLOOKUP 函数用于垂直查找，语法为 VLOOKUP(查找值, 表区域, 返回列号, 精确/近似)。本例中查找 D2 的值，在 A2:B5 区域中查找，返回第2列的价格。IFERROR 函数用于捕获错误，如果 VLOOKUP 返回 #N/A（找不到），则返回“未找到”。假设 D2 是“梨”，则结果“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算员工入职天数（DATEDIF + TODAY）</t>
+          <t>第 4 题：第4题：计算员工工龄和到岗天数</t>
         </is>
       </c>
     </row>
@@ -1284,14 +1150,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF函数计算两个日期之间的差值，语法为DATEDIF(开始日期, 结束日期, 单位)。这里开始日期是B2（入职日期），结束日期是TODAY()（今天），单位"d"表示天数。TODAY()返回当前日期。如果今天是2025-01-01，张三入职2020-06-15，则结果为1661天（具体天数随今天变化）。</t>
+          <t>DATEDIF 函数用于计算两个日期之间的差值，语法为 DATEDIF(开始日期, 结束日期, 单位)。单位 "d" 表示天数，"y" 表示完整年数。本例中，开始日期是入职日期 B2，结束日期是 TODAY()（今天）。天数结果约为 1889（具体根据实际日期），年数结果为 5。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：提取快递单号中的城市代码并匹配城市名（MID + VLOOKUP）</t>
+          <t>第 5 题：第5题：提取货物编码并匹配仓库位置</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1169,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MID函数用于提取字符串中的子串，语法为MID(文本, 开始位置, 字符个数)。这里MID(F1,1,4)提取F1的前4个字符，例如SH01。VLOOKUP函数在表格中查找，语法为VLOOKUP(查找值, 表格区域, 列号, 匹配方式)。这里查找值是MID结果，表格区域是A2:C5，列号3（城市名列），FALSE表示精确匹配。公式会返回“上海”。</t>
+          <t>MID 函数用于从文本中提取子串，语法为 MID(文本, 起始位置, 长度)。本例中，从 A2 的货物编码中提取第3和第4个字符（即区号，如 "01"）。XLOOKUP 函数用于查找并返回，语法为 XLOOKUP(查找值, 查找数组, 返回数组)。这里查找区号在 G2:G4 中匹配，返回 H2:H4 中的区域名称。例如 D2 是 "01"，则返回"东区"。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定商品的销售数量</t>
+          <t>第 1 题：第1题：统计指定商品的销售总量</t>
         </is>
       </c>
     </row>
@@ -490,26 +490,26 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你有一份商品销售明细表，包含商品名称和销售数量。现在需要统计“苹果”的总销售数量。</t>
+          <t>要求：你是一家小商店的店主，有一份本周销售记录表，包含商品名称和销售数量。请统计“苹果”的总销量。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在单元格 B8 中输入公式，统计所有“苹果”的销售数量总和。</t>
+          <t>任务：在E2单元格输入公式，统计“苹果”的总销量。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>商品名称</t>
+          <t>商品</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>销售数量</t>
+          <t>数量</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -583,334 +583,358 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：计算指定日期范围内的销售额</t>
+          <t>第 2 题：第2题：计算两个日期之间的天数</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是一家小店的店主，有一份订单记录表，包含订单日期和销售额。现在需要统计今天及以后（包括今天）的销售额总和。</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>练习函数：DATEDIF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：在单元格 B8 中输入公式，统计订单日期 &gt;= 今天的销售额总和（假设今天是2025-03-18）。</t>
+          <t>要求：你负责记录公司项目的周期。下表列出了每个项目的开始日期和结束日期，请计算每个项目持续的天数（以“天”为单位）。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>订单日期</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>销售额</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>任务：在D2单元格输入公式，计算项目A的持续天数，并向下填充到D4。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>200</v>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>开始日期</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>结束日期</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>350</v>
+          <t>项目A</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-15</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>180</v>
+          <t>项目B</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-10</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>420</v>
+          <t>项目C</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>300</v>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：按条件统计订单数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIFS</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：查找商品价格并处理错误</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>要求：你在一家电商公司工作，有一份订单表，包含客户城市和订单金额。请统计“上海”且金额大于100元的订单数量。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>要求：你有一份商品价格表，现在需要根据商品名称查找价格。如果商品不存在，则显示“未找到”。</t>
+          <t>任务：在E2单元格输入公式，计算满足“城市为上海且金额大于100”的订单数量。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>任务：在单元格 E2 中输入公式，根据 D2 单元格中的商品名称（例如“梨”），从价格表中查找价格，如果找不到则显示“未找到”。</t>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>商品</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>价格</t>
-        </is>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>香蕉</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>3</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>橙子</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>6</v>
+        <v>200</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>葡萄</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>8</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：计算员工工龄和到岗天数</t>
-        </is>
-      </c>
-    </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一份员工入职日期表，需要计算每位员工到今天的工龄（年数）和到岗天数，方便人事统计。</t>
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：根据产品编号查找价格</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>任务：在单元格 C2 中输入公式，计算张三的到岗天数（从入职日期到今天的总天数，假设今天是2025-03-18）；在单元格 D2 中输入公式，计算张三的工龄（完整年数）。</t>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>练习函数：XLOOKUP</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>员工姓名</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>入职日期</t>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一份产品价格表，包含产品编号和单价。现在需要根据给定的产品编号（如P002）查找对应的单价。</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>2020-01-15</t>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>任务：在E2单元格输入公式，查找产品编号P002的单价。</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>2019-06-01</t>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>产品编号</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>2021-03-10</t>
-        </is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：提取货物编码并匹配仓库位置</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一份物流货物清单，货物编码格式为“仓-区-编号”（例如 A-01-123）。需要提取编码中的仓库区号（第3、4个字符），然后根据区号匹配仓库位置表，返回仓库区域名称。</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>任务：在单元格 E2 中输入公式，根据 D2 单元格中的区号（例如 "01"），在仓库位置表中查找对应的仓库区域名称。仓库位置表在 G2:H4 区域（见下方说明）。</t>
-        </is>
-      </c>
-    </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>货物编码</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>重量</t>
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：提取订单号中的日期并计算距今天数</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>A-01-123</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="n">
-        <v>50</v>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一份物流订单表，订单号格式为“ORD-20240101”，最后8位是日期（YYYYMMDD）。请提取每个订单的日期，并计算该日期到今天的天数（假设今天是2024年3月1日）。</t>
+        </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>B-02-456</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>30</v>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>任务：在B2单元格输入公式，提取订单号中的日期并计算与今天的间隔天数（用TODAY函数），并向下填充到B5。</t>
+        </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>C-03-789</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>20</v>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>A-04-111</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n">
-        <v>60</v>
+          <t>ORD-20240115</t>
+        </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>ORD-20240201</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>ORD-20240220</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>ORD-20240301</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -937,7 +961,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定商品的销售数量</t>
+          <t>第 1 题：第1题：统计指定商品的销售总量</t>
         </is>
       </c>
     </row>
@@ -962,7 +986,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：计算指定日期范围内的销售额</t>
+          <t>第 2 题：第2题：计算两个日期之间的天数</t>
         </is>
       </c>
     </row>
@@ -973,7 +997,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>SUMIFS(B2:B7, A2:A7, "&gt;="&amp;TODAY())</f>
+        <f>DATEDIF(B2,C2,"d")</f>
         <v/>
       </c>
     </row>
@@ -987,7 +1011,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查找商品价格并处理错误</t>
+          <t>第 3 题：第3题：按条件统计订单数量</t>
         </is>
       </c>
     </row>
@@ -998,7 +1022,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>IFERROR(VLOOKUP(D2, A2:B5, 2, FALSE), "未找到")</f>
+        <f>COUNTIFS(A2:A7,"上海",B2:B7,"&gt;100")</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算员工工龄和到岗天数</t>
+          <t>第 4 题：第4题：根据产品编号查找价格</t>
         </is>
       </c>
     </row>
@@ -1022,10 +1046,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>C2: =DATEDIF(B2, TODAY(), "d")；D2: =DATEDIF(B2, TODAY(), "y")</t>
-        </is>
+      <c r="B14" s="2">
+        <f>XLOOKUP("P002",A2:A5,B2:B5)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1038,7 +1061,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：提取货物编码并匹配仓库位置</t>
+          <t>第 5 题：第5题：提取订单号中的日期并计算距今天数</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1072,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>XLOOKUP(MID(A2,3,2), G2:G4, H2:H4)</f>
+        <f>DATEDIF(DATE(RIGHT(A2,4),MID(A2,7,2),RIGHT(A2,2)),TODAY(),"d")</f>
         <v/>
       </c>
     </row>
@@ -1081,7 +1104,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定商品的销售数量</t>
+          <t>第 1 题：第1题：统计指定商品的销售总量</t>
         </is>
       </c>
     </row>
@@ -1093,14 +1116,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 函数用于按条件求和，语法为 SUMIF(条件区域, 条件, 求和区域)。本例中，条件区域是商品名称列 A2:A7，条件是“苹果”，求和区域是销售数量列 B2:B7，所以公式会累加所有商品名称为“苹果”的销售数量，得到 10+15+12=37。</t>
+          <t>SUMIF函数用于按条件求和。语法：SUMIF(条件区域, 条件, 求和区域)。这里条件区域是商品列A2:A7，条件是“苹果”，求和区域是数量列B2:B7，得到所有苹果数量之和10+7+12=29。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：计算指定日期范围内的销售额</t>
+          <t>第 2 题：第2题：计算两个日期之间的天数</t>
         </is>
       </c>
     </row>
@@ -1112,14 +1135,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 函数用于多条件求和，语法为 SUMIFS(求和区域, 条件区域1, 条件1, ...)。本例中，求和区域是销售额 B2:B7，条件区域1是日期列 A2:A7，条件1是 "&gt;="&amp;TODAY()，其中 TODAY() 返回今天的日期，用 &amp; 连接比较运算符。公式会累加日期在今天及之后的销售额，即 420+260+300=980。</t>
+          <t>DATEDIF函数计算两个日期之间的差值。语法：DATEDIF(开始日期, 结束日期, 单位)，单位"d"表示天数。项目A：2024-01-01到2024-01-15相差14天。注意：Excel中日期需为真正的日期格式，可先用DATE函数或文本输入，但建议用日期格式。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查找商品价格并处理错误</t>
+          <t>第 3 题：第3题：按条件统计订单数量</t>
         </is>
       </c>
     </row>
@@ -1131,14 +1154,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP 函数用于垂直查找，语法为 VLOOKUP(查找值, 表区域, 返回列号, 精确/近似)。本例中查找 D2 的值，在 A2:B5 区域中查找，返回第2列的价格。IFERROR 函数用于捕获错误，如果 VLOOKUP 返回 #N/A（找不到），则返回“未找到”。假设 D2 是“梨”，则结果“未找到”。</t>
+          <t>COUNTIFS函数用于多条件计数。语法：COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2,...)。这里第一个条件城市列A2:A7为"上海"，第二个条件金额列B2:B7为"&gt;100"，计数满足两个条件的行：上海且金额&gt;100的有150和120两行，结果为2。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算员工工龄和到岗天数</t>
+          <t>第 4 题：第4题：根据产品编号查找价格</t>
         </is>
       </c>
     </row>
@@ -1150,14 +1173,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF 函数用于计算两个日期之间的差值，语法为 DATEDIF(开始日期, 结束日期, 单位)。单位 "d" 表示天数，"y" 表示完整年数。本例中，开始日期是入职日期 B2，结束日期是 TODAY()（今天）。天数结果约为 1889（具体根据实际日期），年数结果为 5。</t>
+          <t>XLOOKUP函数用于查找并返回匹配值。语法：XLOOKUP(查找值, 查找数组, 返回数组)。这里查找值"P002"在A2:A5中查找，返回对应B2:B5的值，得到48。注意：XLOOKUP在Excel 2021或Office 365中可用，若版本低可用VLOOKUP替代：=VLOOKUP("P002",A2:B5,2,FALSE)。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：提取货物编码并匹配仓库位置</t>
+          <t>第 5 题：第5题：提取订单号中的日期并计算距今天数</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1192,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MID 函数用于从文本中提取子串，语法为 MID(文本, 起始位置, 长度)。本例中，从 A2 的货物编码中提取第3和第4个字符（即区号，如 "01"）。XLOOKUP 函数用于查找并返回，语法为 XLOOKUP(查找值, 查找数组, 返回数组)。这里查找区号在 G2:G4 中匹配，返回 H2:H4 中的区域名称。例如 D2 是 "01"，则返回"东区"。</t>
+          <t>先用RIGHT(A2,4)提取年份（后4位），用MID(A2,7,2)提取月份（第7-8位），用RIGHT(A2,2)提取日（后2位），然后用DATE函数组合成真正的日期。再用DATEDIF计算该日期到TODAY()的天数。注意：TODAY()是动态的，会随当前日期变化。假设今天是2024-03-01，则第一个订单2024-01-15到3月1日间隔46天。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,101 +476,136 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定商品的销售总量</t>
+          <t>第 1 题：第1题：统计指定月份的销售总额</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIF</t>
+          <t>练习函数：SUMIFS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家小商店的店主，有一份本周销售记录表，包含商品名称和销售数量。请统计“苹果”的总销量。</t>
+          <t>要求：你有一张销售记录表，包含销售日期、产品名称和销售额。现在需要统计3月份的总销售额，以便了解春季销售情况。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格输入公式，统计“苹果”的总销量。</t>
+          <t>任务：在E1单元格输入公式，计算3月份（日期为2024年3月）的销售额总和。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>商品</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>销售额</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>10</v>
+          <t>2024/3/1</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>笔记本</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>香蕉</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>5</v>
+          <t>2024/3/5</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>钢笔</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>7</v>
+          <t>2024/4/2</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>笔记本</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>橙子</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>3</v>
+          <t>2024/3/10</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>文件夹</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>12</v>
+          <t>2024/4/15</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>钢笔</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>香蕉</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>8</v>
+          <t>2024/3/20</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>笔记本</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -583,358 +618,311 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：计算两个日期之间的天数</t>
+          <t>第 2 题：第2题：查询员工部门并处理错误</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>练习函数：DATEDIF</t>
+          <t>练习函数：XLOOKUP</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>要求：你负责记录公司项目的周期。下表列出了每个项目的开始日期和结束日期，请计算每个项目持续的天数（以“天”为单位）。</t>
+          <t>要求：你有一个员工花名册，包含员工编号和姓名。现在要根据员工编号查找对应姓名，但有些编号不在表中，需要显示"未找到"。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>任务：在D2单元格输入公式，计算项目A的持续天数，并向下填充到D4。</t>
+          <t>任务：在E1单元格输入公式，根据D1单元格输入的员工编号（例如105）查找姓名，若找不到则显示"未找到"。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>项目</t>
+          <t>员工编号</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>开始日期</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>结束日期</t>
+          <t>姓名</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>项目A</t>
-        </is>
+      <c r="A19" s="4" t="n">
+        <v>101</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-15</t>
+          <t>张三</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>项目B</t>
-        </is>
+      <c r="A20" s="4" t="n">
+        <v>102</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-05</t>
+          <t>李四</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>项目C</t>
-        </is>
+      <c r="A21" s="4" t="n">
+        <v>103</v>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>2024-04-01</t>
+          <t>王五</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：按条件统计订单数量</t>
-        </is>
-      </c>
-    </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIFS</t>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：计算员工入职天数并格式化</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>要求：你在一家电商公司工作，有一份订单表，包含客户城市和订单金额。请统计“上海”且金额大于100元的订单数量。</t>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>练习函数：TODAY</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格输入公式，计算满足“城市为上海且金额大于100”的订单数量。</t>
+          <t>要求：公司需要计算每位员工从入职日期到今天的工作天数，以便核算工龄补贴。入职日期已记录，今天是动态的。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>城市</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>任务：在C2单元格输入公式计算张三的入职天数（今天-入职日期），并显示为整数（用ROUND向下取整）。然后下拉填充到C3:C4。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>150</v>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>员工姓名</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>入职日期</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>80</v>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>2020/5/15</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n">
-        <v>90</v>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>2018/3/20</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>200</v>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2022/7/1</t>
+        </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>60</v>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：用VLOOKUP匹配价格并处理错误</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>练习函数：VLOOKUP</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：根据产品编号查找价格</t>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一个商品价目表，包含商品编码和单价。另一张表是订单明细，需要根据商品编码匹配单价，但有些编码不存在，要显示"错误"。</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>练习函数：XLOOKUP</t>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>任务：在订单明细的C列（假设已有订单数据在E列和F列，例如E2为商品编码A001，F2为数量），在G2输入公式根据E2的编码查找单价，若找不到显示"错误"，并计算总价（单价*数量）。</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一份产品价格表，包含产品编号和单价。现在需要根据给定的产品编号（如P002）查找对应的单价。</t>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>商品编码</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>任务：在E2单元格输入公式，查找产品编号P002的单价。</t>
-        </is>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>产品编号</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>P001</t>
+          <t>A003</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>A004</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>P003</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>P004</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="n">
-        <v>8</v>
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：使用MID和RIGHT提取物流单号信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>要求：物流单号格式为"ABC-12345678-地区码"，例如"ABC-12345678-CN"。你需要提取中间的8位数字（订单号）和后两位地区码，用于分类统计。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：提取订单号中的日期并计算距今天数</t>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>任务：在B2单元格输入公式提取物流单号中的8位数字订单号（即第5到第12个字符），在C2输入公式提取后两位地区码（最后2个字符）。然后填充到B3:C4。</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一份物流订单表，订单号格式为“ORD-20240101”，最后8位是日期（YYYYMMDD）。请提取每个订单的日期，并计算该日期到今天的天数（假设今天是2024年3月1日）。</t>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>物流单号</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>任务：在B2单元格输入公式，提取订单号中的日期并计算与今天的间隔天数（用TODAY函数），并向下填充到B5。</t>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>ABC-12345678-CN</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>XYZ-87654321-US</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>ORD-20240115</t>
+          <t>LMN-11223344-JP</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>ORD-20240201</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>ORD-20240220</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>ORD-20240301</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -961,7 +949,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定商品的销售总量</t>
+          <t>第 1 题：第1题：统计指定月份的销售总额</t>
         </is>
       </c>
     </row>
@@ -972,7 +960,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A7,"苹果",B2:B7)</f>
+        <f>SUMIFS(C2:C7,A2:A7,"&gt;=2024/3/1",A2:A7,"&lt;=2024/3/31")</f>
         <v/>
       </c>
     </row>
@@ -986,7 +974,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：计算两个日期之间的天数</t>
+          <t>第 2 题：第2题：查询员工部门并处理错误</t>
         </is>
       </c>
     </row>
@@ -997,7 +985,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>DATEDIF(B2,C2,"d")</f>
+        <f>XLOOKUP(D1,A2:A5,B2:B5,"未找到")</f>
         <v/>
       </c>
     </row>
@@ -1011,7 +999,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按条件统计订单数量</t>
+          <t>第 3 题：第3题：计算员工入职天数并格式化</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1010,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIFS(A2:A7,"上海",B2:B7,"&gt;100")</f>
+        <f>ROUND(TODAY()-B2,0)</f>
         <v/>
       </c>
     </row>
@@ -1036,7 +1024,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：根据产品编号查找价格</t>
+          <t>第 4 题：第4题：用VLOOKUP匹配价格并处理错误</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1035,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>XLOOKUP("P002",A2:A5,B2:B5)</f>
+        <f>IFERROR(VLOOKUP(E2,$A$2:$B$5,2,FALSE)*F2,"错误")</f>
         <v/>
       </c>
     </row>
@@ -1061,7 +1049,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：提取订单号中的日期并计算距今天数</t>
+          <t>第 5 题：第5题：使用MID和RIGHT提取物流单号信息</t>
         </is>
       </c>
     </row>
@@ -1071,9 +1059,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2">
-        <f>DATEDIF(DATE(RIGHT(A2,4),MID(A2,7,2),RIGHT(A2,2)),TODAY(),"d")</f>
-        <v/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>B2: =MID(A2,5,8)  C2: =RIGHT(A2,2)</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1104,7 +1093,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定商品的销售总量</t>
+          <t>第 1 题：第1题：统计指定月份的销售总额</t>
         </is>
       </c>
     </row>
@@ -1116,14 +1105,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF函数用于按条件求和。语法：SUMIF(条件区域, 条件, 求和区域)。这里条件区域是商品列A2:A7，条件是“苹果”，求和区域是数量列B2:B7，得到所有苹果数量之和10+7+12=29。</t>
+          <t>SUMIFS用于多条件求和。语法为SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。这里求和区域是销售额列C2:C7，条件区域是日期列A2:A7，第一个条件是日期&gt;=2024年3月1日，第二个条件是日期&lt;=2024年3月31日。公式会自动筛选出3月的行并求和，结果为395。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：计算两个日期之间的天数</t>
+          <t>第 2 题：第2题：查询员工部门并处理错误</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1124,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF函数计算两个日期之间的差值。语法：DATEDIF(开始日期, 结束日期, 单位)，单位"d"表示天数。项目A：2024-01-01到2024-01-15相差14天。注意：Excel中日期需为真正的日期格式，可先用DATE函数或文本输入，但建议用日期格式。</t>
+          <t>XLOOKUP是查找函数，语法为XLOOKUP(查找值, 查找数组, 返回数组, [未找到值])。这里查找值是D1中的编号，在A2:A5中查找，找到后返回对应的B2:B5中的姓名。第四个参数"未找到"表示当找不到时显示该文本。如果D1=105，则结果返回"未找到"。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：按条件统计订单数量</t>
+          <t>第 3 题：第3题：计算员工入职天数并格式化</t>
         </is>
       </c>
     </row>
@@ -1154,14 +1143,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS函数用于多条件计数。语法：COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2,...)。这里第一个条件城市列A2:A7为"上海"，第二个条件金额列B2:B7为"&gt;100"，计数满足两个条件的行：上海且金额&gt;100的有150和120两行，结果为2。</t>
+          <t>TODAY()返回当前日期。入职天数等于今日日期减去入职日期（日期相减得到天数）。ROUND函数对结果四舍五入到0位小数，确保显示整数。例如，若今天是2025年3月1日，张三的入职天数为ROUND(2025/3/1 - 2020/5/15, 0) = 1730天左右。注意日期相减结果可能是小数，ROUND可处理。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：根据产品编号查找价格</t>
+          <t>第 4 题：第4题：用VLOOKUP匹配价格并处理错误</t>
         </is>
       </c>
     </row>
@@ -1173,14 +1162,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP函数用于查找并返回匹配值。语法：XLOOKUP(查找值, 查找数组, 返回数组)。这里查找值"P002"在A2:A5中查找，返回对应B2:B5的值，得到48。注意：XLOOKUP在Excel 2021或Office 365中可用，若版本低可用VLOOKUP替代：=VLOOKUP("P002",A2:B5,2,FALSE)。</t>
+          <t>VLOOKUP语法：VLOOKUP(查找值, 表格区域, 列序号, [匹配方式])。这里查找E2中的编码，在$A$2:$B$5区域中精确匹配（FALSE），返回第2列单价。IFERROR捕获错误，如果VLOOKUP找不到则返回错误值，IFERROR将其替换为"错误"。然后乘以F2数量得到总价。注意用$锁定区域以便填充。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：提取订单号中的日期并计算距今天数</t>
+          <t>第 5 题：第5题：使用MID和RIGHT提取物流单号信息</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1181,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>先用RIGHT(A2,4)提取年份（后4位），用MID(A2,7,2)提取月份（第7-8位），用RIGHT(A2,2)提取日（后2位），然后用DATE函数组合成真正的日期。再用DATEDIF计算该日期到TODAY()的天数。注意：TODAY()是动态的，会随当前日期变化。假设今天是2024-03-01，则第一个订单2024-01-15到3月1日间隔46天。</t>
+          <t>MID函数用于从文本中间提取字符，语法MID(文本, 开始位置, 字符个数)。单号格式固定，第5个字符开始是8位数字，所以MID(A2,5,8)。RIGHT函数提取从右边开始的字符，语法RIGHT(文本, 个数)，提取后两位用RIGHT(A2,2)。这两个函数常用于处理固定格式编码。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,52 +476,57 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定月份的销售总额</t>
+          <t>第 1 题：第1题：计算某业务员的销售总额</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIFS</t>
+          <t>练习函数：SUMIF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你有一张销售记录表，包含销售日期、产品名称和销售额。现在需要统计3月份的总销售额，以便了解春季销售情况。</t>
+          <t>要求：你是一家小公司的销售助理，需要根据销售记录统计指定业务员的销售额。下表是本月部分销售记录，包含业务员、产品、销售额和日期。请统计“张三”的总销售额。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在E1单元格输入公式，计算3月份（日期为2024年3月）的销售额总和。</t>
+          <t>任务：在E2单元格输入公式，统计“张三”的总销售额。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>业务员</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>销售额</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>日期</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>产品</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>销售额</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2024/3/1</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -530,13 +535,18 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>120</v>
+        <v>1200</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2024/3/5</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -545,58 +555,78 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>45</v>
+        <v>300</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2024/4/2</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>笔记本</t>
+          <t>文件夹</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>150</v>
+        <v>450</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-03</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2024/3/10</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>文件夹</t>
+          <t>打印机</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>30</v>
+        <v>2500</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2024/4/15</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>钢笔</t>
+          <t>订书机</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>60</v>
+        <v>80</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2024/3/20</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -605,324 +635,483 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>200</v>
+        <v>1100</v>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>标签纸</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：查询员工部门并处理错误</t>
-        </is>
-      </c>
-    </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>练习函数：XLOOKUP</t>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：统计超过平均重量的包裹数量</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一个员工花名册，包含员工编号和姓名。现在要根据员工编号查找对应姓名，但有些编号不在表中，需要显示"未找到"。</t>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIF</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>任务：在E1单元格输入公式，根据D1单元格输入的员工编号（例如105）查找姓名，若找不到则显示"未找到"。</t>
+          <t>要求：你在一家快递站点工作，需要分析当天收件包裹的重量情况。下表是10个包裹的重量（kg）。请统计重量大于5kg的包裹有多少个。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>员工编号</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>任务：在C2单元格输入公式，统计重量大于5kg的包裹个数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>包裹编号</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>P010</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：根据员工编号查找姓名和部门并处理错误</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>要求：你负责人事档案管理，需要根据员工编号快速查找员工信息。下表是员工信息表。请根据编号“A004”查找对应姓名，如果找不到则显示“未找到”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>任务：在F2单元格输入公式，根据E2单元格输入的编号（假设输入A004）查找姓名，若找不到则显示“未找到”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>姓名</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>101</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>103</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="n">
-        <v>104</v>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：计算员工入职天数并格式化</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>练习函数：TODAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>要求：公司需要计算每位员工从入职日期到今天的工作天数，以便核算工龄补贴。入职日期已记录，今天是动态的。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>任务：在C2单元格输入公式计算张三的入职天数（今天-入职日期），并显示为整数（用ROUND向下取整）。然后下拉填充到C3:C4。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>员工姓名</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>入职日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>2020/5/15</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>2018/3/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>2022/7/1</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：用VLOOKUP匹配价格并处理错误</t>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>部门</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>练习函数：VLOOKUP</t>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>赵敏</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>销售部</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一个商品价目表，包含商品编码和单价。另一张表是订单明细，需要根据商品编码匹配单价，但有些编码不存在，要显示"错误"。</t>
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>周杰</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>技术部</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>任务：在订单明细的C列（假设已有订单数据在E列和F列，例如E2为商品编码A001，F2为数量），在G2输入公式根据E2的编码查找单价，若找不到显示"错误"，并计算总价（单价*数量）。</t>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>吴倩</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>市场部</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>商品编码</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>郑爽</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>财务部</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>50</v>
+          <t>A005</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>王磊</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>行政部</t>
+        </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>A003</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>20</v>
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>A004</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>15</v>
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：计算员工在职天数并处理日期差异</t>
+        </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>要求：你负责人力资源统计，需要计算员工从入职到今天的在职天数。下表是部分员工的入职日期。请计算第一行员工（陈晨）的在职天数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>任务：在C2单元格输入公式，计算陈晨从入职日期到今天的在职天数（假设今天是2025-03-15）。</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：使用MID和RIGHT提取物流单号信息</t>
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>入职日期</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流单号格式为"ABC-12345678-地区码"，例如"ABC-12345678-CN"。你需要提取中间的8位数字（订单号）和后两位地区码，用于分类统计。</t>
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>陈晨</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>2020-06-15</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>任务：在B2单元格输入公式提取物流单号中的8位数字订单号（即第5到第12个字符），在C2输入公式提取后两位地区码（最后2个字符）。然后填充到B3:C4。</t>
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>李芳</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>2021-03-10</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>物流单号</t>
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>张伟</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>2019-11-01</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>ABC-12345678-CN</t>
+          <t>刘娜</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>2022-08-20</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>XYZ-87654321-US</t>
+          <t>王强</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-05</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>LMN-11223344-JP</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：从订单编号提取区域代码并匹配区域名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>要求：你在一家电商公司做运营，订单编号格式是“区域代码-日期-序号”，例如"A-20250315-001"，其中区域代码只有1位字母。你需要根据区域代码从区域表中匹配出区域名称。下表是订单列表和区域对照表。请提取第一条订单的区域名称。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>任务：在B2单元格输入公式，从A2的订单编号中提取区域代码，并根据区域代码匹配区域名称。区域对照表位于D2:E5区域（D列代码，E列区域名称），数据为：D2=A, E2=华东区；D3=B, E3=华北区；D4=C, E4=华南区；D5=D, E5=西南区。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>订单编号</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>B-20250315-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>C-20250315-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>A-20250315-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>B-20250316-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>D-20250316-005</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -949,7 +1138,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定月份的销售总额</t>
+          <t>第 1 题：第1题：计算某业务员的销售总额</t>
         </is>
       </c>
     </row>
@@ -960,7 +1149,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIFS(C2:C7,A2:A7,"&gt;=2024/3/1",A2:A7,"&lt;=2024/3/31")</f>
+        <f>SUMIF(A2:A8,"张三",C2:C8)</f>
         <v/>
       </c>
     </row>
@@ -974,7 +1163,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：查询员工部门并处理错误</t>
+          <t>第 2 题：第2题：统计超过平均重量的包裹数量</t>
         </is>
       </c>
     </row>
@@ -985,7 +1174,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>XLOOKUP(D1,A2:A5,B2:B5,"未找到")</f>
+        <f>COUNTIF(B2:B11,"&gt;5")</f>
         <v/>
       </c>
     </row>
@@ -999,7 +1188,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算员工入职天数并格式化</t>
+          <t>第 3 题：第3题：根据员工编号查找姓名和部门并处理错误</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1199,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>ROUND(TODAY()-B2,0)</f>
+        <f>IFERROR(VLOOKUP(E2,A2:C6,2,FALSE),"未找到")</f>
         <v/>
       </c>
     </row>
@@ -1024,7 +1213,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：用VLOOKUP匹配价格并处理错误</t>
+          <t>第 4 题：第4题：计算员工在职天数并处理日期差异</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1224,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>IFERROR(VLOOKUP(E2,$A$2:$B$5,2,FALSE)*F2,"错误")</f>
+        <f>DATEDIF(B2,TODAY(),"d")</f>
         <v/>
       </c>
     </row>
@@ -1049,7 +1238,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：使用MID和RIGHT提取物流单号信息</t>
+          <t>第 5 题：第5题：从订单编号提取区域代码并匹配区域名称</t>
         </is>
       </c>
     </row>
@@ -1059,10 +1248,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>B2: =MID(A2,5,8)  C2: =RIGHT(A2,2)</t>
-        </is>
+      <c r="B18" s="2">
+        <f>XLOOKUP(MID(A2,1,1),D2:D5,E2:E5)</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1093,7 +1281,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定月份的销售总额</t>
+          <t>第 1 题：第1题：计算某业务员的销售总额</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1293,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS用于多条件求和。语法为SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。这里求和区域是销售额列C2:C7，条件区域是日期列A2:A7，第一个条件是日期&gt;=2024年3月1日，第二个条件是日期&lt;=2024年3月31日。公式会自动筛选出3月的行并求和，结果为395。</t>
+          <t>SUMIF函数用于按条件求和。语法为SUMIF(条件区域, 条件, 求和区域)。本题中，条件区域是A2:A8（业务员列），条件是"张三"，求和区域是C2:C8（销售额列）。函数会遍历条件区域，凡等于"张三"的行，将其对应销售额相加，结果为1200+450+80+150=1880。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：查询员工部门并处理错误</t>
+          <t>第 2 题：第2题：统计超过平均重量的包裹数量</t>
         </is>
       </c>
     </row>
@@ -1124,14 +1312,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP是查找函数，语法为XLOOKUP(查找值, 查找数组, 返回数组, [未找到值])。这里查找值是D1中的编号，在A2:A5中查找，找到后返回对应的B2:B5中的姓名。第四个参数"未找到"表示当找不到时显示该文本。如果D1=105，则结果返回"未找到"。</t>
+          <t>COUNTIF函数用于按条件计数。语法为COUNTIF(计数区域, 条件)。本题中，计数区域是B2:B11（重量列），条件是"&gt;5"（注意条件用双引号包裹）。函数会统计该区域内大于5的数值个数，结果为4（6.8、9.1、7.4、5.6、8.2共5个，但5.6&gt;5，所以一共5个？再检查：6.8、9.1、7.4、5.6、8.2共5个）。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算员工入职天数并格式化</t>
+          <t>第 3 题：第3题：根据员工编号查找姓名和部门并处理错误</t>
         </is>
       </c>
     </row>
@@ -1143,14 +1331,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>TODAY()返回当前日期。入职天数等于今日日期减去入职日期（日期相减得到天数）。ROUND函数对结果四舍五入到0位小数，确保显示整数。例如，若今天是2025年3月1日，张三的入职天数为ROUND(2025/3/1 - 2020/5/15, 0) = 1730天左右。注意日期相减结果可能是小数，ROUND可处理。</t>
+          <t>VLOOKUP函数用于垂直查找，语法为VLOOKUP(查找值, 表格区域, 返回列号, 精确匹配)。本题中，查找值是E2（编号A004），表格区域是A2:C6，返回列号是2（姓名列），FALSE表示精确匹配。如果查找不到会返回错误，IFERROR函数可以捕获错误并返回指定内容"未找到"。这里A004存在，返回"郑爽"。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：用VLOOKUP匹配价格并处理错误</t>
+          <t>第 4 题：第4题：计算员工在职天数并处理日期差异</t>
         </is>
       </c>
     </row>
@@ -1162,14 +1350,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP语法：VLOOKUP(查找值, 表格区域, 列序号, [匹配方式])。这里查找E2中的编码，在$A$2:$B$5区域中精确匹配（FALSE），返回第2列单价。IFERROR捕获错误，如果VLOOKUP找不到则返回错误值，IFERROR将其替换为"错误"。然后乘以F2数量得到总价。注意用$锁定区域以便填充。</t>
+          <t>DATEDIF函数计算两个日期之间的间隔，语法为DATEDIF(开始日期, 结束日期, 单位)，单位"d"表示天数。TODAY()函数返回当前日期。本题中，开始日期是B2（2020-06-15），结束日期是TODAY()（2025-03-15），所以返回两个日期相差的天数（约1735天，具体以系统当天为准）。注意DATEDIF在Excel中不是标准函数但可用，若不可用可用=TODAY()-B2代替。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：使用MID和RIGHT提取物流单号信息</t>
+          <t>第 5 题：第5题：从订单编号提取区域代码并匹配区域名称</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1369,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MID函数用于从文本中间提取字符，语法MID(文本, 开始位置, 字符个数)。单号格式固定，第5个字符开始是8位数字，所以MID(A2,5,8)。RIGHT函数提取从右边开始的字符，语法RIGHT(文本, 个数)，提取后两位用RIGHT(A2,2)。这两个函数常用于处理固定格式编码。</t>
+          <t>MID函数用于从文本中提取子串，语法为MID(文本, 开始位置, 长度)。本题中，订单编号"B-20250315-001"，从第1位开始取1个字符，得到"B"。XLOOKUP是Excel新函数，语法为XLOOKUP(查找值, 查找区域, 返回区域)。这里查找值是从MID得到的"B"，查找区域是D2:D5（代码列），返回区域是E2:E5（区域名称列），匹配到"华北区"。如果没有XLOOKUP可用VLOOKUP替代：=VLOOKUP(MID(A2,1,1),D2:E5,2,FALSE)。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,642 +476,453 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：计算某业务员的销售总额</t>
+          <t>第 1 题：第1题：统计指定月份的销售总额</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIF</t>
+          <t>练习函数：SUMIFS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家小公司的销售助理，需要根据销售记录统计指定业务员的销售额。下表是本月部分销售记录，包含业务员、产品、销售额和日期。请统计“张三”的总销售额。</t>
+          <t>要求：你是一家小店的店主，有一张2024年1-3月的销售记录表，列A为'月份'（文本格式，如'2024-01'），列B为'销售额'（数字）。现在需要快速统计出2024年2月份的销售总额。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格输入公式，统计“张三”的总销售额。</t>
+          <t>任务：在E2单元格输入公式，统计月份为'2024-02'的销售额总和。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>业务员</t>
+          <t>月份</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>产品</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
           <t>销售额</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>日期</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>笔记本</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
         <v>1200</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-01</t>
-        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>钢笔</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-02</t>
-        </is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>文件夹</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>450</v>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-03</t>
-        </is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>800</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>打印机</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-04</t>
-        </is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>订书机</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-05</t>
-        </is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>950</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>笔记本</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
         <v>1100</v>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-06</t>
-        </is>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>标签纸</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：统计满足多个条件的订单数量</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：统计超过平均重量的包裹数量</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIFS</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIF</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是仓库管理员，有一张订单表，列A为'产品'，列B为'数量'。需要统计产品为'键盘'且数量大于等于5的订单有多少个。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>要求：你在一家快递站点工作，需要分析当天收件包裹的重量情况。下表是10个包裹的重量（kg）。请统计重量大于5kg的包裹有多少个。</t>
+          <t>任务：在E2单元格输入公式，统计产品为'键盘'且数量&gt;=5的订单数。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>任务：在C2单元格输入公式，统计重量大于5kg的包裹个数。</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>数量</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>包裹编号</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
-        </is>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>鼠标</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>P001</t>
+          <t>键盘</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>键盘</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>6.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>P003</t>
+          <t>显示器</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>键盘</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>9.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>键盘</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>P006</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>P007</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>5.6</v>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>P008</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>1.9</v>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：根据客户编号查询客户姓名（使用VLOOKUP）</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>P009</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>8.199999999999999</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>练习函数：VLOOKUP</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>P010</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>4.8</v>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一张客户信息表，列A为'客户编号'，列B为'客户姓名'。现在需要根据一个给定的编号（例如'C002'）查出对应的姓名。</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>任务：在E2单元格输入公式，根据E1单元格中的编号（输入'C002'）查找对应姓名，结果显示在E2。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>客户编号</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>客户姓名</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>C002</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>C003</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>C004</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：根据员工编号查找姓名和部门并处理错误</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>要求：你负责人事档案管理，需要根据员工编号快速查找员工信息。下表是员工信息表。请根据编号“A004”查找对应姓名，如果找不到则显示“未找到”。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>任务：在F2单元格输入公式，根据E2单元格输入的编号（假设输入A004）查找姓名，若找不到则显示“未找到”。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>编号</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>部门</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>赵敏</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>销售部</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>周杰</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>技术部</t>
-        </is>
-      </c>
-    </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>A003</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>吴倩</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>市场部</t>
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：计算两个日期之间的天数（使用DATEDIF）</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>A004</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>郑爽</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>财务部</t>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>练习函数：DATEDIF</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>A005</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>王磊</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>行政部</t>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>要求：你记录了一批货物的到港日期（列A）和离港日期（列B），需要计算每次运输的持续天数（按整天计算）。</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>任务：在C2单元格输入公式，计算A2到B2之间的天数，并下拉填充到C4。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>离港日期</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-15</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：计算员工在职天数并处理日期差异</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>要求：你负责人力资源统计，需要计算员工从入职到今天的在职天数。下表是部分员工的入职日期。请计算第一行员工（陈晨）的在职天数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>任务：在C2单元格输入公式，计算陈晨从入职日期到今天的在职天数（假设今天是2025-03-15）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>入职日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>陈晨</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>2020-06-15</t>
-        </is>
-      </c>
-    </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>李芳</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>2021-03-10</t>
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：提取员工编号中的部门代码并匹配部门名称（综合使用MID和XLOOKUP）</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>张伟</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>2019-11-01</t>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一个员工名单，列A为'员工编号'，编号格式为'部门代码-员工序号'（例如'HR-001'，其中'HR'是部门代码）。另有一张部门代码对照表（列D为部门代码，列E为部门名称）。需要根据员工编号提取部门代码，并自动匹配出部门名称。</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>刘娜</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>2022-08-20</t>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>任务：在B2单元格输入公式，提取A2中的部门代码（前两个字符），并在C2单元格用XLOOKUP根据该代码查找部门名称（部门对照表为D1:E4），下拉填充到B5和C5。</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>王强</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>2023-01-05</t>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>员工编号</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>HR-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>IT-002</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：从订单编号提取区域代码并匹配区域名称</t>
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>FIN-003</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>要求：你在一家电商公司做运营，订单编号格式是“区域代码-日期-序号”，例如"A-20250315-001"，其中区域代码只有1位字母。你需要根据区域代码从区域表中匹配出区域名称。下表是订单列表和区域对照表。请提取第一条订单的区域名称。</t>
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>MKT-004</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>任务：在B2单元格输入公式，从A2的订单编号中提取区域代码，并根据区域代码匹配区域名称。区域对照表位于D2:E5区域（D列代码，E列区域名称），数据为：D2=A, E2=华东区；D3=B, E3=华北区；D4=C, E4=华南区；D5=D, E5=西南区。</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>订单编号</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>B-20250315-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>C-20250315-002</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>A-20250315-003</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>B-20250316-004</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>D-20250316-005</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1138,7 +949,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：计算某业务员的销售总额</t>
+          <t>第 1 题：第1题：统计指定月份的销售总额</t>
         </is>
       </c>
     </row>
@@ -1149,7 +960,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A8,"张三",C2:C8)</f>
+        <f>SUMIFS(B2:B7, A2:A7, "2024-02")</f>
         <v/>
       </c>
     </row>
@@ -1163,7 +974,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计超过平均重量的包裹数量</t>
+          <t>第 2 题：第2题：统计满足多个条件的订单数量</t>
         </is>
       </c>
     </row>
@@ -1174,7 +985,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF(B2:B11,"&gt;5")</f>
+        <f>COUNTIFS(A2:A7, "键盘", B2:B7, "&gt;=5")</f>
         <v/>
       </c>
     </row>
@@ -1188,7 +999,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据员工编号查找姓名和部门并处理错误</t>
+          <t>第 3 题：第3题：根据客户编号查询客户姓名（使用VLOOKUP）</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1010,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>IFERROR(VLOOKUP(E2,A2:C6,2,FALSE),"未找到")</f>
+        <f>VLOOKUP(E1, A2:B5, 2, FALSE)</f>
         <v/>
       </c>
     </row>
@@ -1213,7 +1024,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算员工在职天数并处理日期差异</t>
+          <t>第 4 题：第4题：计算两个日期之间的天数（使用DATEDIF）</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1035,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>DATEDIF(B2,TODAY(),"d")</f>
+        <f>DATEDIF(A2, B2, "d")</f>
         <v/>
       </c>
     </row>
@@ -1238,7 +1049,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：从订单编号提取区域代码并匹配区域名称</t>
+          <t>第 5 题：第5题：提取员工编号中的部门代码并匹配部门名称（综合使用MID和XLOOKUP）</t>
         </is>
       </c>
     </row>
@@ -1248,9 +1059,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2">
-        <f>XLOOKUP(MID(A2,1,1),D2:D5,E2:E5)</f>
-        <v/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>B2: =LEFT(A2,2)  或者 =MID(A2,1,2) ；C2: =XLOOKUP(B2, D2:D5, E2:E5)</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1281,7 +1093,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：计算某业务员的销售总额</t>
+          <t>第 1 题：第1题：统计指定月份的销售总额</t>
         </is>
       </c>
     </row>
@@ -1293,14 +1105,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF函数用于按条件求和。语法为SUMIF(条件区域, 条件, 求和区域)。本题中，条件区域是A2:A8（业务员列），条件是"张三"，求和区域是C2:C8（销售额列）。函数会遍历条件区域，凡等于"张三"的行，将其对应销售额相加，结果为1200+450+80+150=1880。</t>
+          <t>SUMIFS函数用于多条件求和，语法为SUMIFS(求和区域, 条件区域1, 条件1, ...)。本题中B2:B7是求和区域，A2:A7是条件区域，条件为"2024-02"，表示只对该月份对应的销售额求和。注意条件文本需要用双引号括起来。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计超过平均重量的包裹数量</t>
+          <t>第 2 题：第2题：统计满足多个条件的订单数量</t>
         </is>
       </c>
     </row>
@@ -1312,14 +1124,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF函数用于按条件计数。语法为COUNTIF(计数区域, 条件)。本题中，计数区域是B2:B11（重量列），条件是"&gt;5"（注意条件用双引号包裹）。函数会统计该区域内大于5的数值个数，结果为4（6.8、9.1、7.4、5.6、8.2共5个，但5.6&gt;5，所以一共5个？再检查：6.8、9.1、7.4、5.6、8.2共5个）。</t>
+          <t>COUNTIFS函数用于多条件计数，语法为COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2, ...)。本题两个条件：A列等于'键盘'，B列&gt;=5。条件区域与条件必须成对出现，条件中比较运算符要加引号。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据员工编号查找姓名和部门并处理错误</t>
+          <t>第 3 题：第3题：根据客户编号查询客户姓名（使用VLOOKUP）</t>
         </is>
       </c>
     </row>
@@ -1331,14 +1143,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP函数用于垂直查找，语法为VLOOKUP(查找值, 表格区域, 返回列号, 精确匹配)。本题中，查找值是E2（编号A004），表格区域是A2:C6，返回列号是2（姓名列），FALSE表示精确匹配。如果查找不到会返回错误，IFERROR函数可以捕获错误并返回指定内容"未找到"。这里A004存在，返回"郑爽"。</t>
+          <t>VLOOKUP是垂直查找函数，语法为VLOOKUP(查找值, 查找区域, 返回列序号, 精确/近似)。本题在A2:B5区域中查找E1的值，找到后返回该行第2列（姓名列）。第四个参数FALSE表示精确匹配，避免近似错误。注意查找值必须在区域的第一列。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算员工在职天数并处理日期差异</t>
+          <t>第 4 题：第4题：计算两个日期之间的天数（使用DATEDIF）</t>
         </is>
       </c>
     </row>
@@ -1350,14 +1162,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF函数计算两个日期之间的间隔，语法为DATEDIF(开始日期, 结束日期, 单位)，单位"d"表示天数。TODAY()函数返回当前日期。本题中，开始日期是B2（2020-06-15），结束日期是TODAY()（2025-03-15），所以返回两个日期相差的天数（约1735天，具体以系统当天为准）。注意DATEDIF在Excel中不是标准函数但可用，若不可用可用=TODAY()-B2代替。</t>
+          <t>DATEDIF用于计算两个日期之间的差值，语法为DATEDIF(开始日期, 结束日期, 单位)。单位"d"表示天数。注意开始日期要早于结束日期，否则会出错。此函数在Excel中不显示在函数列表里，但可以手动输入。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：从订单编号提取区域代码并匹配区域名称</t>
+          <t>第 5 题：第5题：提取员工编号中的部门代码并匹配部门名称（综合使用MID和XLOOKUP）</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1181,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MID函数用于从文本中提取子串，语法为MID(文本, 开始位置, 长度)。本题中，订单编号"B-20250315-001"，从第1位开始取1个字符，得到"B"。XLOOKUP是Excel新函数，语法为XLOOKUP(查找值, 查找区域, 返回区域)。这里查找值是从MID得到的"B"，查找区域是D2:D5（代码列），返回区域是E2:E5（区域名称列），匹配到"华北区"。如果没有XLOOKUP可用VLOOKUP替代：=VLOOKUP(MID(A2,1,1),D2:E5,2,FALSE)。</t>
+          <t>MID函数用于从文本中提取子串，语法为MID(文本, 开始位置, 字符数)。这里从第1位开始取2个字符得到部门代码。XLOOKUP是新一代查找函数，语法为XLOOKUP(查找值, 查找数组, 返回数组)，比VLOOKUP更灵活，不要求查找列在首列。本题先用MID提取代码，再在D列查找并返回E列对应的部门名称。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,35 +476,35 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定月份的销售总额</t>
+          <t>第 1 题：第1题：统计指定部门的总销售额（SUMIF）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIFS</t>
+          <t>练习函数：SUMIF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家小店的店主，有一张2024年1-3月的销售记录表，列A为'月份'（文本格式，如'2024-01'），列B为'销售额'（数字）。现在需要快速统计出2024年2月份的销售总额。</t>
+          <t>要求：你是一家小公司的销售助理，有一张销售记录表，包含部门、销售额两列。现在需要统计"销售一部"的总销售额。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格输入公式，统计月份为'2024-02'的销售额总和。</t>
+          <t>任务：在单元格 D2 中输入公式，统计"销售一部"的总销售额。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>月份</t>
+          <t>部门</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -516,413 +516,437 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>销售一部</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>1200</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>销售二部</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>1500</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>销售一部</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>800</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>销售三部</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>销售一部</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>950</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>2024-02</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：计算订单到今天的逾期天数（IF、TODAY）</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：统计满足多个条件的订单数量</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>要求：你管理一批物流订单，每单有应到货日期。今天日期自动获取，需要判断每单是否逾期，并计算逾期天数，未逾期则显示"未逾期"。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIFS</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>任务：在C2单元格输入公式，判断A001订单是否逾期（假设今天为2025-04-12）。若应到日期早于今天，则显示逾期天数，否则显示"未逾期"。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是仓库管理员，有一张订单表，列A为'产品'，列B为'数量'。需要统计产品为'键盘'且数量大于等于5的订单有多少个。</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>应到日期</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>任务：在E2单元格输入公式，统计产品为'键盘'且数量&gt;=5的订单数。</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>产品</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>数量</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>鼠标</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>3</v>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>键盘</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>5</v>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>键盘</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>显示器</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>1</v>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>键盘</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>8</v>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：多条件统计-按区域和产品汇总销量（SUMIFS）</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>键盘</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>4</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>练习函数：SUMIFS</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一份商品销售明细表，包含区域、产品、销量。需要统计"华东区"的"手机"总销量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>任务：在单元格 E2 中输入公式，统计区域为"华东"且产品为"手机"的销量总和。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：根据客户编号查询客户姓名（使用VLOOKUP）</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>销量</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>练习函数：VLOOKUP</t>
-        </is>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一张客户信息表，列A为'客户编号'，列B为'客户姓名'。现在需要根据一个给定的编号（例如'C002'）查出对应的姓名。</t>
-        </is>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>任务：在E2单元格输入公式，根据E1单元格中的编号（输入'C002'）查找对应姓名，结果显示在E2。</t>
-        </is>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>电脑</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>客户编号</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>客户姓名</t>
-        </is>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>C001</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
-        </is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>C002</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：按姓名查找手机号并处理错误（VLOOKUP、IFERROR）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一份员工通讯录，需要根据员工姓名查找对应的手机号。若姓名不存在，显示"查无此人"。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 B6 单元格输入公式，查找"赵六"的手机号（赵六不在表中），要求显示"查无此人"。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>手机号</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>13800001111</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
           <t>李四</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>C003</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>13900002222</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>王五</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>C004</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>13700003333</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：计算两个日期之间的天数（使用DATEDIF）</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>练习函数：DATEDIF</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>要求：你记录了一批货物的到港日期（列A）和离港日期（列B），需要计算每次运输的持续天数（按整天计算）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>任务：在C2单元格输入公式，计算A2到B2之间的天数，并下拉填充到C4。</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>离港日期</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-01</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-15</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>2024-02-20</t>
-        </is>
-      </c>
-    </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-01</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-05</t>
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：提取员工编号并计算工龄（RIGHT、MID、DATEDIF）</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有人事档案表，包含员工编号（格式：部门-入厂年份-序号，例如"销售-2018-001"）和入职日期。需要提取入厂年份和计算工龄（整年）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 C2 单元格输入公式，从编号中提取年份（第5-8位，即4位数字），在 D2 单元格输入公式计算工龄（整年，截止今天2025-04-12）。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：提取员工编号中的部门代码并匹配部门名称（综合使用MID和XLOOKUP）</t>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>员工编号</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>入职日期</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一个员工名单，列A为'员工编号'，编号格式为'部门代码-员工序号'（例如'HR-001'，其中'HR'是部门代码）。另有一张部门代码对照表（列D为部门代码，列E为部门名称）。需要根据员工编号提取部门代码，并自动匹配出部门名称。</t>
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>销售-2018-001</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>2018-06-15</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>任务：在B2单元格输入公式，提取A2中的部门代码（前两个字符），并在C2单元格用XLOOKUP根据该代码查找部门名称（部门对照表为D1:E4），下拉填充到B5和C5。</t>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>生产-2020-023</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>2020-03-01</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>员工编号</t>
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>行政-2015-108</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>2015-11-20</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>HR-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>IT-002</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>FIN-003</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>MKT-004</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -949,7 +973,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定月份的销售总额</t>
+          <t>第 1 题：第1题：统计指定部门的总销售额（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -960,7 +984,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIFS(B2:B7, A2:A7, "2024-02")</f>
+        <f>SUMIF(A2:A6,"销售一部",B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -974,7 +998,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计满足多个条件的订单数量</t>
+          <t>第 2 题：第2题：计算订单到今天的逾期天数（IF、TODAY）</t>
         </is>
       </c>
     </row>
@@ -985,7 +1009,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIFS(A2:A7, "键盘", B2:B7, "&gt;=5")</f>
+        <f>IF(B2&lt;TODAY(),TODAY()-B2,"未逾期")</f>
         <v/>
       </c>
     </row>
@@ -999,7 +1023,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据客户编号查询客户姓名（使用VLOOKUP）</t>
+          <t>第 3 题：第3题：多条件统计-按区域和产品汇总销量（SUMIFS）</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1034,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>VLOOKUP(E1, A2:B5, 2, FALSE)</f>
+        <f>SUMIFS(C2:C7,A2:A7,"华东",B2:B7,"手机")</f>
         <v/>
       </c>
     </row>
@@ -1024,7 +1048,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算两个日期之间的天数（使用DATEDIF）</t>
+          <t>第 4 题：第4题：按姓名查找手机号并处理错误（VLOOKUP、IFERROR）</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1059,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>DATEDIF(A2, B2, "d")</f>
+        <f>IFERROR(VLOOKUP("赵六",A2:B4,2,FALSE),"查无此人")</f>
         <v/>
       </c>
     </row>
@@ -1049,7 +1073,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：提取员工编号中的部门代码并匹配部门名称（综合使用MID和XLOOKUP）</t>
+          <t>第 5 题：第5题：提取员工编号并计算工龄（RIGHT、MID、DATEDIF）</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1085,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>B2: =LEFT(A2,2)  或者 =MID(A2,1,2) ；C2: =XLOOKUP(B2, D2:D5, E2:E5)</t>
+          <t>C2: =MID(A2,5,4)  D2: =DATEDIF(B2,TODAY(),"y")</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1117,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定月份的销售总额</t>
+          <t>第 1 题：第1题：统计指定部门的总销售额（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1129,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS函数用于多条件求和，语法为SUMIFS(求和区域, 条件区域1, 条件1, ...)。本题中B2:B7是求和区域，A2:A7是条件区域，条件为"2024-02"，表示只对该月份对应的销售额求和。注意条件文本需要用双引号括起来。</t>
+          <t>SUMIF函数用于按条件求和，语法为SUMIF(条件区域, 条件, 求和区域)。这里条件区域是部门列A2:A6，条件是"销售一部"，求和区域是销售额列B2:B6，结果等于29500。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计满足多个条件的订单数量</t>
+          <t>第 2 题：第2题：计算订单到今天的逾期天数（IF、TODAY）</t>
         </is>
       </c>
     </row>
@@ -1124,14 +1148,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIFS函数用于多条件计数，语法为COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2, ...)。本题两个条件：A列等于'键盘'，B列&gt;=5。条件区域与条件必须成对出现，条件中比较运算符要加引号。</t>
+          <t>IF函数判断条件B2&lt;TODAY()是否成立，成立则用TODAY()-B2计算逾期天数，否则返回文本"未逾期"。TODAY()返回当前日期，日期相减得到天数。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据客户编号查询客户姓名（使用VLOOKUP）</t>
+          <t>第 3 题：第3题：多条件统计-按区域和产品汇总销量（SUMIFS）</t>
         </is>
       </c>
     </row>
@@ -1143,14 +1167,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP是垂直查找函数，语法为VLOOKUP(查找值, 查找区域, 返回列序号, 精确/近似)。本题在A2:B5区域中查找E1的值，找到后返回该行第2列（姓名列）。第四个参数FALSE表示精确匹配，避免近似错误。注意查找值必须在区域的第一列。</t>
+          <t>SUMIFS用于多条件求和，语法为SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。这里求和区域C2:C7，条件区域1为A2:A7等于"华东"，条件区域2为B2:B7等于"手机"，结果=50+70+10=130。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算两个日期之间的天数（使用DATEDIF）</t>
+          <t>第 4 题：第4题：按姓名查找手机号并处理错误（VLOOKUP、IFERROR）</t>
         </is>
       </c>
     </row>
@@ -1162,14 +1186,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF用于计算两个日期之间的差值，语法为DATEDIF(开始日期, 结束日期, 单位)。单位"d"表示天数。注意开始日期要早于结束日期，否则会出错。此函数在Excel中不显示在函数列表里，但可以手动输入。</t>
+          <t>VLOOKUP函数在A2:B4中查找"赵六"，返回第2列手机号，FALSE表示精确匹配。IFERROR捕获错误，如果查不到会返回#N/A，则显示"查无此人"。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：提取员工编号中的部门代码并匹配部门名称（综合使用MID和XLOOKUP）</t>
+          <t>第 5 题：第5题：提取员工编号并计算工龄（RIGHT、MID、DATEDIF）</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1205,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MID函数用于从文本中提取子串，语法为MID(文本, 开始位置, 字符数)。这里从第1位开始取2个字符得到部门代码。XLOOKUP是新一代查找函数，语法为XLOOKUP(查找值, 查找数组, 返回数组)，比VLOOKUP更灵活，不要求查找列在首列。本题先用MID提取代码，再在D列查找并返回E列对应的部门名称。</t>
+          <t>MID函数提取文本中指定位置开始的字符：MID(文本,开始位置,字符个数)，这里从第5位开始取4位得到"2018"。DATEDIF计算两个日期之间的完整年数，语法为DATEDIF(开始日期,结束日期,"y")，返回整年数，B2是入职日期，TODAY()是今天，2018-06-15到2025-04-12是6个完整年。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定部门的总销售额（SUMIF）</t>
+          <t>第 1 题：第1题：统计某仓库的入库总数量</t>
         </is>
       </c>
     </row>
@@ -490,238 +490,228 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家小公司的销售助理，有一张销售记录表，包含部门、销售额两列。现在需要统计"销售一部"的总销售额。</t>
+          <t>要求：你是一家小仓库的管理员，有一张入库记录表，记录了每种商品的入库数量。现在需要快速统计出“苹果”的总入库数量。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在单元格 D2 中输入公式，统计"销售一部"的总销售额。</t>
+          <t>任务：在E2单元格输入公式，统计“苹果”的总入库数量。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>部门</t>
+          <t>商品</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>入库数量</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>销售一部</t>
+          <t>苹果</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>12000</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>销售二部</t>
+          <t>香蕉</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>15000</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>销售一部</t>
+          <t>苹果</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>8000</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>销售三部</t>
+          <t>橙子</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>20000</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>销售一部</t>
+          <t>苹果</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9500</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>香蕉</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：计算订单到今天的逾期天数（IF、TODAY）</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>要求：你管理一批物流订单，每单有应到货日期。今天日期自动获取，需要判断每单是否逾期，并计算逾期天数，未逾期则显示"未逾期"。</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：计算员工入职到今天的年数</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>任务：在C2单元格输入公式，判断A001订单是否逾期（假设今天为2025-04-12）。若应到日期早于今天，则显示逾期天数，否则显示"未逾期"。</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>练习函数：DATEDIF</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>应到日期</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是一家公司的HR，需要计算每位员工从入职日期到今天的在职年数，用于年假统计。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-01</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>任务：在C2单元格输入公式，计算张三的在职年数（按整年计算），并向下填充到C3、C4。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-15</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>入职日期</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A003</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2019-06-15</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>A004</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2021-09-01</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>2022-03-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：多条件统计-按区域和产品汇总销量（SUMIFS）</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>练习函数：SUMIFS</t>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：根据订单号查找发货重量</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一份商品销售明细表，包含区域、产品、销量。需要统计"华东区"的"手机"总销量。</t>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>练习函数：VLOOKUP</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>任务：在单元格 E2 中输入公式，统计区域为"华东"且产品为"手机"的销量总和。</t>
+          <t>要求：你有一个订单发货表，包含订单号、商品、发货重量。现在收到一批新查询，需要根据订单号快速找到对应的发货重量。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>区域</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>产品</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>销量</t>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>任务：在F2单元格输入公式，根据E2单元格中的订单号（例如A1003）查找其发货重量。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>50</v>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>商品</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>发货重量</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>A1001</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -730,223 +720,232 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>30</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>A1002</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>电脑</t>
+          <t>平板</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>20</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>A1003</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>笔记本</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>70</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>A1004</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>耳机</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>40</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：统计各业务员的订单金额（含错误处理）</t>
+        </is>
+      </c>
+    </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：按姓名查找手机号并处理错误（VLOOKUP、IFERROR）</t>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是销售助理，有一张销售明细表，包含业务员、产品、金额。需要统计每个业务员的总金额，但某些业务员可能没有订单，希望显示为0而不是错误。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>要求：你有一份员工通讯录，需要根据员工姓名查找对应的手机号。若姓名不存在，显示"查无此人"。</t>
+          <t>任务：在F2单元格输入公式，统计业务员“小张”的总金额，如果找不到则返回0。</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 B6 单元格输入公式，查找"赵六"的手机号（赵六不在表中），要求显示"查无此人"。</t>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>业务员</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>手机号</t>
-        </is>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>小张</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>小李</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>13800001111</t>
-        </is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>小张</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>13900002222</t>
-        </is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>小王</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>13700003333</t>
-        </is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>小李</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：提取员工编号并计算工龄（RIGHT、MID、DATEDIF）</t>
-        </is>
-      </c>
-    </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有人事档案表，包含员工编号（格式：部门-入厂年份-序号，例如"销售-2018-001"）和入职日期。需要提取入厂年份和计算工龄（整年）。</t>
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：从商品编码中提取信息</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>任务：在 C2 单元格输入公式，从编号中提取年份（第5-8位，即4位数字），在 D2 单元格输入公式计算工龄（整年，截止今天2025-04-12）。</t>
+          <t>要求：你的商品编码包含多种信息，如第1-3位是类别，第4-6位是型号，最后2位是颜色代码。现在需要从编码中提取型号和颜色。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>员工编号</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>入职日期</t>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>任务：在B2单元格输入公式提取编码A01-456-RD中的型号（第5-7位，即“456”），在C2单元格提取颜色代码（最后2位，即“RD”），然后向下填充。</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>销售-2018-001</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>2018-06-15</t>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>商品编码</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>生产-2020-023</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>2020-03-01</t>
+          <t>A01-456-RD</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>行政-2015-108</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>2015-11-20</t>
+          <t>B02-123-BL</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>C03-789-GR</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -973,7 +972,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定部门的总销售额（SUMIF）</t>
+          <t>第 1 题：第1题：统计某仓库的入库总数量</t>
         </is>
       </c>
     </row>
@@ -984,7 +983,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"销售一部",B2:B6)</f>
+        <f>SUMIF(A2:A7,"苹果",B2:B7)</f>
         <v/>
       </c>
     </row>
@@ -998,7 +997,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：计算订单到今天的逾期天数（IF、TODAY）</t>
+          <t>第 2 题：第2题：计算员工入职到今天的年数</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1008,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>IF(B2&lt;TODAY(),TODAY()-B2,"未逾期")</f>
+        <f>DATEDIF(B2,TODAY(),"Y")</f>
         <v/>
       </c>
     </row>
@@ -1023,7 +1022,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：多条件统计-按区域和产品汇总销量（SUMIFS）</t>
+          <t>第 3 题：第3题：根据订单号查找发货重量</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1033,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>SUMIFS(C2:C7,A2:A7,"华东",B2:B7,"手机")</f>
+        <f>VLOOKUP(E2,A2:C5,3,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -1048,7 +1047,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按姓名查找手机号并处理错误（VLOOKUP、IFERROR）</t>
+          <t>第 4 题：第4题：统计各业务员的订单金额（含错误处理）</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1058,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>IFERROR(VLOOKUP("赵六",A2:B4,2,FALSE),"查无此人")</f>
+        <f>IFERROR(SUMIFS(C2:C6,A2:A6,"小张"),0)</f>
         <v/>
       </c>
     </row>
@@ -1073,7 +1072,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：提取员工编号并计算工龄（RIGHT、MID、DATEDIF）</t>
+          <t>第 5 题：第5题：从商品编码中提取信息</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1084,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>C2: =MID(A2,5,4)  D2: =DATEDIF(B2,TODAY(),"y")</t>
+          <t>B2: =MID(A2,5,3)  C2: =RIGHT(A2,2)</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1116,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定部门的总销售额（SUMIF）</t>
+          <t>第 1 题：第1题：统计某仓库的入库总数量</t>
         </is>
       </c>
     </row>
@@ -1129,14 +1128,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF函数用于按条件求和，语法为SUMIF(条件区域, 条件, 求和区域)。这里条件区域是部门列A2:A6，条件是"销售一部"，求和区域是销售额列B2:B6，结果等于29500。</t>
+          <t>SUMIF函数用于对满足条件的单元格求和。语法为：SUMIF(条件区域, 条件, 求和区域)。这里条件区域是A2:A7，条件是“苹果”，求和区域是B2:B7，结果为70（30+15+25）。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：计算订单到今天的逾期天数（IF、TODAY）</t>
+          <t>第 2 题：第2题：计算员工入职到今天的年数</t>
         </is>
       </c>
     </row>
@@ -1148,14 +1147,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>IF函数判断条件B2&lt;TODAY()是否成立，成立则用TODAY()-B2计算逾期天数，否则返回文本"未逾期"。TODAY()返回当前日期，日期相减得到天数。</t>
+          <t>DATEDIF函数计算两个日期之间的差值，语法为DATEDIF(开始日期, 结束日期, 单位)。单位"Y"表示整年数。TODAY()返回今天的日期，所以公式计算的是从入职日到今天经过的完整年数。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：多条件统计-按区域和产品汇总销量（SUMIFS）</t>
+          <t>第 3 题：第3题：根据订单号查找发货重量</t>
         </is>
       </c>
     </row>
@@ -1167,14 +1166,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS用于多条件求和，语法为SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。这里求和区域C2:C7，条件区域1为A2:A7等于"华东"，条件区域2为B2:B7等于"手机"，结果=50+70+10=130。</t>
+          <t>VLOOKUP函数在表格第一列查找值，返回同一行指定列的值。语法：VLOOKUP(查找值, 区域, 列号, 精确匹配)。这里在A2:C5区域的第一列查找E2的订单号，返回第3列的发货重量，FALSE表示精确查找。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：按姓名查找手机号并处理错误（VLOOKUP、IFERROR）</t>
+          <t>第 4 题：第4题：统计各业务员的订单金额（含错误处理）</t>
         </is>
       </c>
     </row>
@@ -1186,14 +1185,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP函数在A2:B4中查找"赵六"，返回第2列手机号，FALSE表示精确匹配。IFERROR捕获错误，如果查不到会返回#N/A，则显示"查无此人"。</t>
+          <t>SUMIFS函数按多个条件求和，这里条件区域A2:A6等于“小张”，求和区域C2:C6。IFERROR函数捕获错误（例如如果条件无匹配，SUMIFS不会出错，但若数据为空可能出错），这里用于防止意外错误，若出错返回0。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：提取员工编号并计算工龄（RIGHT、MID、DATEDIF）</t>
+          <t>第 5 题：第5题：从商品编码中提取信息</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1204,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MID函数提取文本中指定位置开始的字符：MID(文本,开始位置,字符个数)，这里从第5位开始取4位得到"2018"。DATEDIF计算两个日期之间的完整年数，语法为DATEDIF(开始日期,结束日期,"y")，返回整年数，B2是入职日期，TODAY()是今天，2018-06-15到2025-04-12是6个完整年。</t>
+          <t>MID函数从一个文本中间提取指定长度的字符，语法MID(文本, 开始位置, 长度)。这里从A2的第5个字符开始提取3个字符，得到“456”。RIGHT函数从文本右侧提取指定个数字符，RIGHT(A2,2)得到最后2个字符“RD”。注意编码格式是“字母数字-数字-字母”，第5位是数字开始。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某仓库的入库总数量</t>
+          <t>第 1 题：第1题：商品销售数据汇总（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -490,133 +490,136 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家小仓库的管理员，有一张入库记录表，记录了每种商品的入库数量。现在需要快速统计出“苹果”的总入库数量。</t>
+          <t>要求：你是一家零食商店的老板，有一张一周的销售记录表，包含商品名称和销售额。你需要统计“巧克力”这一种商品的总销售额，以便了解它的销售情况。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格输入公式，统计“苹果”的总入库数量。</t>
+          <t>任务：请在E2单元格输入公式，计算出“巧克力”的总销售额。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>商品</t>
+          <t>商品名称</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>入库数量</t>
+          <t>销售额</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>巧克力</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>香蕉</t>
+          <t>薯片</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>巧克力</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>15</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>橙子</t>
+          <t>饼干</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>巧克力</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>香蕉</t>
+          <t>薯片</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>巧克力</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：计算员工入职到今天的年数</t>
-        </is>
-      </c>
-    </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>练习函数：DATEDIF</t>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：员工考勤统计（COUNTIF 与 ROUND）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家公司的HR，需要计算每位员工从入职日期到今天的在职年数，用于年假统计。</t>
+          <t>要求：你是一家公司的人力资源专员，有一个员工迟到记录表，记录了每位员工当月的迟到次数。你需要统计迟到超过2次的员工人数，并将平均迟到次数保留一位小数。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>任务：在C2单元格输入公式，计算张三的在职年数（按整年计算），并向下填充到C3、C4。</t>
+          <t>任务：请在E2单元格输入公式统计迟到次数大于2的员工人数；在E4单元格输入公式计算平均迟到次数（保留1位小数）。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>姓名</t>
+          <t>员工姓名</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>入职日期</t>
+          <t>迟到次数</t>
         </is>
       </c>
     </row>
@@ -626,10 +629,8 @@
           <t>张三</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>2019-06-15</t>
-        </is>
+      <c r="B19" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -638,10 +639,8 @@
           <t>李四</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>2021-09-01</t>
-        </is>
+      <c r="B20" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -650,302 +649,380 @@
           <t>王五</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>2022-03-20</t>
-        </is>
+      <c r="B21" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>孙七</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>周八</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>吴九</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：根据订单号查找发货重量</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>练习函数：VLOOKUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一个订单发货表，包含订单号、商品、发货重量。现在收到一批新查询，需要根据订单号快速找到对应的发货重量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>任务：在F2单元格输入公式，根据E2单元格中的订单号（例如A1003）查找其发货重量。</t>
-        </is>
-      </c>
-    </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>商品</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>发货重量</t>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：物流到港天数计算（TODAY 与 DATEDIF）</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>A1001</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>0.8</v>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>要求：你在一家货代公司工作，需要跟踪一批货物的到港情况。你有一张货物到港记录表，记录了每批货物的实际到港日期。你需要计算每批货物从到港到今天已经过去了多少天（用于计算堆存费）。</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>A1002</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>平板</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>1.2</v>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在C2单元格输入公式计算A1001货单从到港日期到今天的天数（假设今天是2025-03-25），并将公式下拉填充到C5。</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>A1003</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>笔记本</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>2.5</v>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>货单号</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
+          <t>A1001</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>A1002</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>A1003</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
           <t>A1004</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>耳机</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：统计各业务员的订单金额（含错误处理）</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是销售助理，有一张销售明细表，包含业务员、产品、金额。需要统计每个业务员的总金额，但某些业务员可能没有订单，希望显示为0而不是错误。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>任务：在F2单元格输入公式，统计业务员“小张”的总金额，如果找不到则返回0。</t>
-        </is>
-      </c>
-    </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>业务员</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>产品</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：订单价格查询（VLOOKUP 与 IFERROR）</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>小张</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>100</v>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>要求：你经营一家网店，有一个客户订单表和一个商品价格表。订单表中只有商品编号，你需要根据商品编号从价格表中查出单价，并计算订单金额。如果商品编号不存在，则显示“未找到”。</t>
+        </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>小李</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>200</v>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>任务：价格表已放在G1:H3区域（G1为表头“商品编号”，H1为“单价”），G2:H3分别为：P100,10；P200,20；P300,30。请在C2单元格输入公式查找单价，并下拉到C5，然后在D2输入公式计算订单金额（数量*单价），若找不到则显示“未找到”。</t>
+        </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>小张</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>150</v>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>商品编号</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>小王</t>
+          <t>D001</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>P100</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>300</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>小李</t>
+          <t>D002</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>P200</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>250</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>P300</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>P999</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：从商品编码中提取信息</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>要求：你的商品编码包含多种信息，如第1-3位是类别，第4-6位是型号，最后2位是颜色代码。现在需要从编码中提取型号和颜色。</t>
-        </is>
-      </c>
-    </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>任务：在B2单元格输入公式提取编码A01-456-RD中的型号（第5-7位，即“456”），在C2单元格提取颜色代码（最后2位，即“RD”），然后向下填充。</t>
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：多条件汇总与动态查找（SUMIFS 与 INDEX/MATCH）</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>商品编码</t>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是一家物流公司的调度员，有一张运输费用明细表，包含线路、运输方式和费用。你需要：1）统计“华东”线路且运输方式为“卡车”的总费用；2）根据给定的线路名称和运输方式，动态查找对应的费用（例如查找“华南”和“铁路”的费用）。</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>A01-456-RD</t>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在G2单元格输入公式统计“华东”且“卡车”的总费用；在G5和G6单元格分别输入线路名称“华南”和运输方式“铁路”，然后在G7单元格输入公式查找对应的费用。</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>B02-123-BL</t>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>线路</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>运输方式</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>费用</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>C03-789-GR</t>
-        </is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>卡车</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>5000</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>铁路</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>卡车</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>铁路</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>卡车</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>5100</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>华北</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>铁路</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -972,7 +1049,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某仓库的入库总数量</t>
+          <t>第 1 题：第1题：商品销售数据汇总（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -983,7 +1060,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A7,"苹果",B2:B7)</f>
+        <f>SUMIF(A2:A8,"巧克力",B2:B8)</f>
         <v/>
       </c>
     </row>
@@ -997,7 +1074,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：计算员工入职到今天的年数</t>
+          <t>第 2 题：第2题：员工考勤统计（COUNTIF 与 ROUND）</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1085,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>DATEDIF(B2,TODAY(),"Y")</f>
+        <f>COUNTIF(B2:B8,"&gt;2") 和 =ROUND(AVERAGE(B2:B8),1)</f>
         <v/>
       </c>
     </row>
@@ -1022,7 +1099,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据订单号查找发货重量</t>
+          <t>第 3 题：第3题：物流到港天数计算（TODAY 与 DATEDIF）</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1110,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>VLOOKUP(E2,A2:C5,3,FALSE)</f>
+        <f>DATEDIF(B2,TODAY(),"d")</f>
         <v/>
       </c>
     </row>
@@ -1047,7 +1124,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：统计各业务员的订单金额（含错误处理）</t>
+          <t>第 4 题：第4题：订单价格查询（VLOOKUP 与 IFERROR）</t>
         </is>
       </c>
     </row>
@@ -1057,9 +1134,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <f>IFERROR(SUMIFS(C2:C6,A2:A6,"小张"),0)</f>
-        <v/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>C2: =IFERROR(VLOOKUP(B2,$G$2:$H$3,2,FALSE),"未找到") ; D2: =IFERROR(C2*A2,"未找到")</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1072,7 +1150,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：从商品编码中提取信息</t>
+          <t>第 5 题：第5题：多条件汇总与动态查找（SUMIFS 与 INDEX/MATCH）</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1162,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>B2: =MID(A2,5,3)  C2: =RIGHT(A2,2)</t>
+          <t>G2: =SUMIFS(C2:C7, A2:A7,"华东", B2:B7,"卡车") ; G7: =INDEX(C2:C7, MATCH(1, (A2:A7=G5)*(B2:B7=G6), 0))</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1194,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某仓库的入库总数量</t>
+          <t>第 1 题：第1题：商品销售数据汇总（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1128,14 +1206,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF函数用于对满足条件的单元格求和。语法为：SUMIF(条件区域, 条件, 求和区域)。这里条件区域是A2:A7，条件是“苹果”，求和区域是B2:B7，结果为70（30+15+25）。</t>
+          <t>SUMIF函数用于按条件求和，语法为：SUMIF(条件区域, 条件, 求和区域)。本题中，条件区域是A2:A8（商品名称），条件是“巧克力”，求和区域是B2:B8（销售额）。公式会遍历A列，每当遇到“巧克力”就累加对应的销售额，结果得到120+200+150+175=645。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：计算员工入职到今天的年数</t>
+          <t>第 2 题：第2题：员工考勤统计（COUNTIF 与 ROUND）</t>
         </is>
       </c>
     </row>
@@ -1147,14 +1225,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF函数计算两个日期之间的差值，语法为DATEDIF(开始日期, 结束日期, 单位)。单位"Y"表示整年数。TODAY()返回今天的日期，所以公式计算的是从入职日到今天经过的完整年数。</t>
+          <t>COUNTIF函数用于按条件计数，语法为：COUNTIF(区域, 条件)。这里区域是B2:B8，条件“&gt;2”表示大于2，得到人数为4（张三、王五、孙七、吴九）。ROUND函数用于四舍五入，语法为：ROUND(数值, 小数位数)。先用AVERAGE计算平均迟到次数 (3+1+4+2+5+0+3)/7≈2.5714，再用ROUND保留1位小数得到2.6。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据订单号查找发货重量</t>
+          <t>第 3 题：第3题：物流到港天数计算（TODAY 与 DATEDIF）</t>
         </is>
       </c>
     </row>
@@ -1166,14 +1244,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP函数在表格第一列查找值，返回同一行指定列的值。语法：VLOOKUP(查找值, 区域, 列号, 精确匹配)。这里在A2:C5区域的第一列查找E2的订单号，返回第3列的发货重量，FALSE表示精确查找。</t>
+          <t>DATEDIF函数计算两个日期之间的差值，语法为：DATEDIF(开始日期, 结束日期, 单位)。这里开始日期是到港日期B2，结束日期是今天的日期TODAY()，单位"d"表示天数。公式会返回从B2到今天的间隔天数。例如若今天是2025-03-25，则A1001的天数为24天。注意TODAY()是动态的，每天打开表格会更新。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：统计各业务员的订单金额（含错误处理）</t>
+          <t>第 4 题：第4题：订单价格查询（VLOOKUP 与 IFERROR）</t>
         </is>
       </c>
     </row>
@@ -1185,14 +1263,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS函数按多个条件求和，这里条件区域A2:A6等于“小张”，求和区域C2:C6。IFERROR函数捕获错误（例如如果条件无匹配，SUMIFS不会出错，但若数据为空可能出错），这里用于防止意外错误，若出错返回0。</t>
+          <t>VLOOKUP函数在表格首列查找值并返回指定列的值，语法为：VLOOKUP(查找值, 表格区域, 列索引, 精确匹配)。这里查找B2的商品编号，区域是$G$2:$H$3，列索引2表示单价，精确匹配用FALSE。IFERROR函数捕获错误：如果VLOOKUP找不到（会返回#N/A），则显示“未找到”。D列公式用C2乘以数量，若C2为“未找到”文本，则IFERROR也返回“未找到”。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：从商品编码中提取信息</t>
+          <t>第 5 题：第5题：多条件汇总与动态查找（SUMIFS 与 INDEX/MATCH）</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1282,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MID函数从一个文本中间提取指定长度的字符，语法MID(文本, 开始位置, 长度)。这里从A2的第5个字符开始提取3个字符，得到“456”。RIGHT函数从文本右侧提取指定个数字符，RIGHT(A2,2)得到最后2个字符“RD”。注意编码格式是“字母数字-数字-字母”，第5位是数字开始。</t>
+          <t>SUMIFS函数多条件求和，语法为：SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2,...)。这里求和区域C2:C7，条件区域1是A2:A7（线路）条件"华东"，条件区域2是B2:B7（方式）条件"卡车"，结果为5000。INDEX+MATCH组合实现动态查找：MATCH函数查找满足多个条件的位置，这里使用数组公式写法 MATCH(1, (A2:A7=G5)*(B2:B7=G6), 0) 会计算一个由1和0组成的数组，当线路和方式同时匹配时为1，MATCH找到那个1的位置；然后INDEX从C2:C7中取出对应行的费用。注意输入G7公式后需按Ctrl+Shift+Enter确认（在某些Excel版本中）或直接回车（Office 365动态数组）。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：商品销售数据汇总（SUMIF）</t>
+          <t>第 1 题：第1题：统计指定商品的销售总量</t>
         </is>
       </c>
     </row>
@@ -490,539 +490,446 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家零食商店的老板，有一张一周的销售记录表，包含商品名称和销售额。你需要统计“巧克力”这一种商品的总销售额，以便了解它的销售情况。</t>
+          <t>要求：你是一家小商店的店主，记录了每天的销售明细。现在需要统计‘苹果’这种商品卖出的总数量。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：请在E2单元格输入公式，计算出“巧克力”的总销售额。</t>
+          <t>任务：在E2单元格输入公式，统计出‘苹果’的总数量。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>商品名称</t>
+          <t>商品</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>数量</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>巧克力</t>
+          <t>苹果</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>120</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>薯片</t>
+          <t>香蕉</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>巧克力</t>
+          <t>苹果</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>200</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>饼干</t>
+          <t>橙子</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>巧克力</t>
+          <t>苹果</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>150</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>薯片</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>巧克力</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>175</v>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：计算两个日期之间的工作天数</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>练习函数：DATEDIF</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：员工考勤统计（COUNTIF 与 ROUND）</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>要求：公司需要计算员工入职到今天的在职天数（按整天计算）。今天是2025年4月1日，但为了练习，请用DATEDIF函数计算。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家公司的人力资源专员，有一个员工迟到记录表，记录了每位员工当月的迟到次数。你需要统计迟到超过2次的员工人数，并将平均迟到次数保留一位小数。</t>
+          <t>任务：在C2单元格输入公式，计算张三从入职日期到今天的实际天数（使用TODAY函数作为结束日期）。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在E2单元格输入公式统计迟到次数大于2的员工人数；在E4单元格输入公式计算平均迟到次数（保留1位小数）。</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>员工姓名</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>入职日期</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>员工姓名</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>迟到次数</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2023/5/10</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>2024/1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：根据产品编号查找价格（精确匹配）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>练习函数：VLOOKUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一份产品价格表，需要通过产品编号查找对应的单价。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>任务：在G2单元格输入公式，根据F2单元格输入的产品编号（例如B200）查找对应单价。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>产品编号</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>笔记本</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>钢笔</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>C300</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>橡皮</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>D400</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>尺子</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：统计不同仓库的入库数量并处理错误</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>练习函数：SUMIFS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>要求：物流公司记录了多批次货物入库，需要统计指定仓库、指定日期的入库总量，如果找不到数据则显示为0。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>任务：在F2单元格输入公式，统计'上海仓'在'2025/3/2'的入库总量，如果结果为0或没有匹配，则显示0。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>仓库</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>入库数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>2025/3/1</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>北京仓</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>2025/3/1</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>2025/3/2</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>广州仓</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>2025/3/3</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：组合查找商品单价并处理缺失（MATCH+INDEX）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>要求：你需要根据产品名称查找单价，但产品名称可能不在列表中，要求找不到时返回'未找到'。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>任务：在E2单元格输入公式，根据D2单元格的名称（例如'苹果'）查找对应单价，如果找不到则显示'未找到'。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>香蕉</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>橙子</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>孙七</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>周八</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>吴九</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：物流到港天数计算（TODAY 与 DATEDIF）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>要求：你在一家货代公司工作，需要跟踪一批货物的到港情况。你有一张货物到港记录表，记录了每批货物的实际到港日期。你需要计算每批货物从到港到今天已经过去了多少天（用于计算堆存费）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在C2单元格输入公式计算A1001货单从到港日期到今天的天数（假设今天是2025-03-25），并将公式下拉填充到C5。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>货单号</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>A1001</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>A1002</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>A1003</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>A1004</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：订单价格查询（VLOOKUP 与 IFERROR）</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>要求：你经营一家网店，有一个客户订单表和一个商品价格表。订单表中只有商品编号，你需要根据商品编号从价格表中查出单价，并计算订单金额。如果商品编号不存在，则显示“未找到”。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>任务：价格表已放在G1:H3区域（G1为表头“商品编号”，H1为“单价”），G2:H3分别为：P100,10；P200,20；P300,30。请在C2单元格输入公式查找单价，并下拉到C5，然后在D2输入公式计算订单金额（数量*单价），若找不到则显示“未找到”。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>商品编号</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>D001</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>P100</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>D002</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>P200</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>D003</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>P300</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>D004</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>P999</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：多条件汇总与动态查找（SUMIFS 与 INDEX/MATCH）</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是一家物流公司的调度员，有一张运输费用明细表，包含线路、运输方式和费用。你需要：1）统计“华东”线路且运输方式为“卡车”的总费用；2）根据给定的线路名称和运输方式，动态查找对应的费用（例如查找“华南”和“铁路”的费用）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在G2单元格输入公式统计“华东”且“卡车”的总费用；在G5和G6单元格分别输入线路名称“华南”和运输方式“铁路”，然后在G7单元格输入公式查找对应的费用。</t>
-        </is>
-      </c>
-    </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>线路</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>运输方式</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>费用</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>卡车</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>铁路</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>4200</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>卡车</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>4800</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>铁路</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>3900</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>卡车</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>5100</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>铁路</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1049,7 +956,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：商品销售数据汇总（SUMIF）</t>
+          <t>第 1 题：第1题：统计指定商品的销售总量</t>
         </is>
       </c>
     </row>
@@ -1060,7 +967,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A8,"巧克力",B2:B8)</f>
+        <f>SUMIF(A2:A6,"苹果",B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -1074,7 +981,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：员工考勤统计（COUNTIF 与 ROUND）</t>
+          <t>第 2 题：第2题：计算两个日期之间的工作天数</t>
         </is>
       </c>
     </row>
@@ -1085,7 +992,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF(B2:B8,"&gt;2") 和 =ROUND(AVERAGE(B2:B8),1)</f>
+        <f>DATEDIF(B2,TODAY(),"d")</f>
         <v/>
       </c>
     </row>
@@ -1099,7 +1006,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：物流到港天数计算（TODAY 与 DATEDIF）</t>
+          <t>第 3 题：第3题：根据产品编号查找价格（精确匹配）</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1017,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>DATEDIF(B2,TODAY(),"d")</f>
+        <f>VLOOKUP(F2,A2:C5,3,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -1124,7 +1031,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：订单价格查询（VLOOKUP 与 IFERROR）</t>
+          <t>第 4 题：第4题：统计不同仓库的入库数量并处理错误</t>
         </is>
       </c>
     </row>
@@ -1134,10 +1041,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>C2: =IFERROR(VLOOKUP(B2,$G$2:$H$3,2,FALSE),"未找到") ; D2: =IFERROR(C2*A2,"未找到")</t>
-        </is>
+      <c r="B14" s="2">
+        <f>IFERROR(SUMIFS(C2:C5,A2:A5,"上海仓",B2:B5,"2025/3/2"),0)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1150,7 +1056,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：多条件汇总与动态查找（SUMIFS 与 INDEX/MATCH）</t>
+          <t>第 5 题：第5题：组合查找商品单价并处理缺失（MATCH+INDEX）</t>
         </is>
       </c>
     </row>
@@ -1160,10 +1066,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>G2: =SUMIFS(C2:C7, A2:A7,"华东", B2:B7,"卡车") ; G7: =INDEX(C2:C7, MATCH(1, (A2:A7=G5)*(B2:B7=G6), 0))</t>
-        </is>
+      <c r="B18" s="2">
+        <f>IFERROR(INDEX(B2:B4,MATCH(D2,A2:A4,0)),"未找到")</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1194,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：商品销售数据汇总（SUMIF）</t>
+          <t>第 1 题：第1题：统计指定商品的销售总量</t>
         </is>
       </c>
     </row>
@@ -1206,14 +1111,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF函数用于按条件求和，语法为：SUMIF(条件区域, 条件, 求和区域)。本题中，条件区域是A2:A8（商品名称），条件是“巧克力”，求和区域是B2:B8（销售额）。公式会遍历A列，每当遇到“巧克力”就累加对应的销售额，结果得到120+200+150+175=645。</t>
+          <t>SUMIF函数用于按条件求和，语法为SUMIF(条件区域, 条件, 求和区域)。本题中条件区域是A2:A6，条件是“苹果”，求和区域是B2:B6，结果等于10+8+12=30。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：员工考勤统计（COUNTIF 与 ROUND）</t>
+          <t>第 2 题：第2题：计算两个日期之间的工作天数</t>
         </is>
       </c>
     </row>
@@ -1225,14 +1130,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF函数用于按条件计数，语法为：COUNTIF(区域, 条件)。这里区域是B2:B8，条件“&gt;2”表示大于2，得到人数为4（张三、王五、孙七、吴九）。ROUND函数用于四舍五入，语法为：ROUND(数值, 小数位数)。先用AVERAGE计算平均迟到次数 (3+1+4+2+5+0+3)/7≈2.5714，再用ROUND保留1位小数得到2.6。</t>
+          <t>DATEDIF函数计算两个日期之差，语法为DATEDIF(开始日期, 结束日期, 单位)。单位"d"表示天数。此题用TODAY()作为结束日期，动态更新。如果今天是2025年4月1日，结果为688天（可自行验证）。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：物流到港天数计算（TODAY 与 DATEDIF）</t>
+          <t>第 3 题：第3题：根据产品编号查找价格（精确匹配）</t>
         </is>
       </c>
     </row>
@@ -1244,14 +1149,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF函数计算两个日期之间的差值，语法为：DATEDIF(开始日期, 结束日期, 单位)。这里开始日期是到港日期B2，结束日期是今天的日期TODAY()，单位"d"表示天数。公式会返回从B2到今天的间隔天数。例如若今天是2025-03-25，则A1001的天数为24天。注意TODAY()是动态的，每天打开表格会更新。</t>
+          <t>VLOOKUP函数按列查找，语法为VLOOKUP(查找值, 表区域, 返回列号, 匹配方式)。这里查找F2的值，在A2:C5范围内，返回第3列（单价），FALSE表示精确匹配。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：订单价格查询（VLOOKUP 与 IFERROR）</t>
+          <t>第 4 题：第4题：统计不同仓库的入库数量并处理错误</t>
         </is>
       </c>
     </row>
@@ -1263,14 +1168,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP函数在表格首列查找值并返回指定列的值，语法为：VLOOKUP(查找值, 表格区域, 列索引, 精确匹配)。这里查找B2的商品编号，区域是$G$2:$H$3，列索引2表示单价，精确匹配用FALSE。IFERROR函数捕获错误：如果VLOOKUP找不到（会返回#N/A），则显示“未找到”。D列公式用C2乘以数量，若C2为“未找到”文本，则IFERROR也返回“未找到”。</t>
+          <t>SUMIFS函数多条件求和，语法为SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2)。本题求和区域为C2:C5，条件1为仓库=上海仓，条件2为日期=2025/3/2。由于日期是文本格式，直接写字符串。IFERROR包裹，若出错则返回0。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：多条件汇总与动态查找（SUMIFS 与 INDEX/MATCH）</t>
+          <t>第 5 题：第5题：组合查找商品单价并处理缺失（MATCH+INDEX）</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1187,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS函数多条件求和，语法为：SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2,...)。这里求和区域C2:C7，条件区域1是A2:A7（线路）条件"华东"，条件区域2是B2:B7（方式）条件"卡车"，结果为5000。INDEX+MATCH组合实现动态查找：MATCH函数查找满足多个条件的位置，这里使用数组公式写法 MATCH(1, (A2:A7=G5)*(B2:B7=G6), 0) 会计算一个由1和0组成的数组，当线路和方式同时匹配时为1，MATCH找到那个1的位置；然后INDEX从C2:C7中取出对应行的费用。注意输入G7公式后需按Ctrl+Shift+Enter确认（在某些Excel版本中）或直接回车（Office 365动态数组）。</t>
+          <t>MATCH函数查找位置，INDEX返回指定位置的值。MATCH(D2,A2:A4,0)找到名称所在行号，INDEX(B2:B4,行号)返回单价。IFERROR处理错误，当名称不存在时显示'未找到'。这是比VLOOKUP更灵活的查找组合。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定商品的销售总量</t>
+          <t>第 1 题：第1题：统计销售总量</t>
         </is>
       </c>
     </row>
@@ -490,14 +490,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家小商店的店主，记录了每天的销售明细。现在需要统计‘苹果’这种商品卖出的总数量。</t>
+          <t>要求：你是某店铺的店员，需要统计指定商品的销售总量。表中列出了各商品的销售额，请使用SUMIF函数快速汇总。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格输入公式，统计出‘苹果’的总数量。</t>
+          <t>任务：在E2单元格输入公式，计算商品为‘苹果’的销售总额。</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>销售额</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
@@ -540,17 +540,17 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>8</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>橙子</t>
+          <t>香蕉</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>6</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10">
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>12</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">
@@ -573,363 +573,442 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：计算两个日期之间的工作天数</t>
+          <t>第 2 题：第2题：统计到货次数</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>练习函数：DATEDIF</t>
+          <t>练习函数：COUNTIF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>要求：公司需要计算员工入职到今天的在职天数（按整天计算）。今天是2025年4月1日，但为了练习，请用DATEDIF函数计算。</t>
+          <t>要求：仓库收到一批货物的到货记录，需要统计其中“正常”状态的货物数量。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：在C2单元格输入公式，计算张三从入职日期到今天的实际天数（使用TODAY函数作为结束日期）。</t>
+          <t>任务：在E2单元格输入公式，统计状态为‘正常’的货物个数。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>员工姓名</t>
+          <t>货物编号</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>入职日期</t>
+          <t>状态</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>A001</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2023/5/10</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>A002</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2024/1/15</t>
+          <t>破损</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>延迟</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>A005</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：根据产品编号查找价格（精确匹配）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：查找员工部门</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>练习函数：VLOOKUP</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一份产品价格表，需要通过产品编号查找对应的单价。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>任务：在G2单元格输入公式，根据F2单元格输入的产品编号（例如B200）查找对应单价。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>产品编号</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>产品名称</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>A100</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>笔记本</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>15</v>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>要求：公司有员工信息表，需要根据员工姓名查找其所属部门。</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>B200</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>钢笔</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>8</v>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>任务：在F2单元格输入公式，根据E2单元格的姓名（例如“王五”）查找对应的部门。</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>C300</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>橡皮</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>2</v>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>工号</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>部门</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>D400</t>
+          <t>001</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>尺子</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>5</v>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>销售部</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>市场部</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>财务部</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>人事部</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：统计不同仓库的入库数量并处理错误</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>练习函数：SUMIFS</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流公司记录了多批次货物入库，需要统计指定仓库、指定日期的入库总量，如果找不到数据则显示为0。</t>
-        </is>
-      </c>
-    </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>任务：在F2单元格输入公式，统计'上海仓'在'2025/3/2'的入库总量，如果结果为0或没有匹配，则显示0。</t>
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：计算账龄天数</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>仓库</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>入库数量</t>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>练习函数：DATEDIF</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>2025/3/1</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>100</v>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>要求：财务需要计算每笔账款的账龄天数（从发票日期到今天的间隔天数）。请使用TODAY函数和DATEDIF函数。</t>
+        </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>北京仓</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>2025/3/1</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>150</v>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>任务：在C2单元格输入公式，计算第一笔账款的账龄天数，并下拉填充。</t>
+        </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>2025/3/2</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>120</v>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>发票日期</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>广州仓</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>2025/3/3</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n">
+          <t>2024-01-15</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-10</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：综合条件汇总与错误处理</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>要求：销售数据表包含产品、区域、销量。需要统计指定区域和产品的销售总和，但若没有数据，避免显示错误，而是返回0。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>任务：在G2单元格输入公式，统计区域为‘华东’且产品为‘手机’的总销量，若无数据则返回0。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>销量</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>电脑</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
         <v>80</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：组合查找商品单价并处理缺失（MATCH+INDEX）</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>要求：你需要根据产品名称查找单价，但产品名称可能不在列表中，要求找不到时返回'未找到'。</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>任务：在E2单元格输入公式，根据D2单元格的名称（例如'苹果'）查找对应单价，如果找不到则显示'未找到'。</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>产品名称</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>苹果</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>香蕉</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>橙子</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>电脑</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>平板</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -956,7 +1035,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定商品的销售总量</t>
+          <t>第 1 题：第1题：统计销售总量</t>
         </is>
       </c>
     </row>
@@ -981,7 +1060,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：计算两个日期之间的工作天数</t>
+          <t>第 2 题：第2题：统计到货次数</t>
         </is>
       </c>
     </row>
@@ -992,7 +1071,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>DATEDIF(B2,TODAY(),"d")</f>
+        <f>COUNTIF(B2:B6,"正常")</f>
         <v/>
       </c>
     </row>
@@ -1006,7 +1085,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据产品编号查找价格（精确匹配）</t>
+          <t>第 3 题：第3题：查找员工部门</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1096,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>VLOOKUP(F2,A2:C5,3,FALSE)</f>
+        <f>VLOOKUP(E2,A2:C5,3,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -1031,7 +1110,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：统计不同仓库的入库数量并处理错误</t>
+          <t>第 4 题：第4题：计算账龄天数</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1121,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>IFERROR(SUMIFS(C2:C5,A2:A5,"上海仓",B2:B5,"2025/3/2"),0)</f>
+        <f>DATEDIF(A2,TODAY(),"d")</f>
         <v/>
       </c>
     </row>
@@ -1056,7 +1135,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：组合查找商品单价并处理缺失（MATCH+INDEX）</t>
+          <t>第 5 题：第5题：综合条件汇总与错误处理</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1146,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>IFERROR(INDEX(B2:B4,MATCH(D2,A2:A4,0)),"未找到")</f>
+        <f>IFERROR(SUMIFS(C2:C6,A2:A6,"手机",B2:B6,"华东"),0)</f>
         <v/>
       </c>
     </row>
@@ -1099,7 +1178,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定商品的销售总量</t>
+          <t>第 1 题：第1题：统计销售总量</t>
         </is>
       </c>
     </row>
@@ -1111,14 +1190,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF函数用于按条件求和，语法为SUMIF(条件区域, 条件, 求和区域)。本题中条件区域是A2:A6，条件是“苹果”，求和区域是B2:B6，结果等于10+8+12=30。</t>
+          <t>SUMIF(条件区域,条件,求和区域)。条件区域A2:A6与条件"苹果"匹配，然后对B2:B6中对应的行求和，结果为120+150+130=400。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：计算两个日期之间的工作天数</t>
+          <t>第 2 题：第2题：统计到货次数</t>
         </is>
       </c>
     </row>
@@ -1130,14 +1209,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF函数计算两个日期之差，语法为DATEDIF(开始日期, 结束日期, 单位)。单位"d"表示天数。此题用TODAY()作为结束日期，动态更新。如果今天是2025年4月1日，结果为688天（可自行验证）。</t>
+          <t>COUNTIF(计数区域,条件)。在B2:B6范围内，统计等于"正常"的单元格个数，结果为3。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据产品编号查找价格（精确匹配）</t>
+          <t>第 3 题：第3题：查找员工部门</t>
         </is>
       </c>
     </row>
@@ -1149,14 +1228,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP函数按列查找，语法为VLOOKUP(查找值, 表区域, 返回列号, 匹配方式)。这里查找F2的值，在A2:C5范围内，返回第3列（单价），FALSE表示精确匹配。</t>
+          <t>VLOOKUP(查找值,表区域,返回列号,精确匹配)。在A2:C5中查找E2的姓名，返回第3列部门，FALSE表示精确查找。结果为“财务部”。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：统计不同仓库的入库数量并处理错误</t>
+          <t>第 4 题：第4题：计算账龄天数</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1247,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS函数多条件求和，语法为SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2)。本题求和区域为C2:C5，条件1为仓库=上海仓，条件2为日期=2025/3/2。由于日期是文本格式，直接写字符串。IFERROR包裹，若出错则返回0。</t>
+          <t>DATEDIF(开始日期,结束日期,单位)。开始日期为A2，结束日期为今天的日期TODAY()，单位"d"表示天数。返回从发票日到今天的整天天数。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：组合查找商品单价并处理缺失（MATCH+INDEX）</t>
+          <t>第 5 题：第5题：综合条件汇总与错误处理</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1266,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MATCH函数查找位置，INDEX返回指定位置的值。MATCH(D2,A2:A4,0)找到名称所在行号，INDEX(B2:B4,行号)返回单价。IFERROR处理错误，当名称不存在时显示'未找到'。这是比VLOOKUP更灵活的查找组合。</t>
+          <t>SUMIFS(求和区域,条件区域1,条件1,[条件区域2,条件2]...)，先求和C2:C6中产品为“手机”且区域为“华东”的总销量。IFERROR函数捕获可能的错误（如无匹配返回0？），但SUMIFS不会出错，但若返回0则正常；此处IFERROR确保如果出现任何错误则显示0，实际结果100。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计销售总量</t>
+          <t>第 1 题：计算华南区销售总额</t>
         </is>
       </c>
     </row>
@@ -490,21 +490,21 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是某店铺的店员，需要统计指定商品的销售总量。表中列出了各商品的销售额，请使用SUMIF函数快速汇总。</t>
+          <t>要求：你有一张某公司各销售区域的订单表，包含区域和销售额。现在需要统计“华南区”的总销售额。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格输入公式，计算商品为‘苹果’的销售总额。</t>
+          <t>任务：请在 E1 单元格输入公式，计算“华南区”的销售额总和。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>商品</t>
+          <t>区域</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -516,499 +516,442 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>120</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>香蕉</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>80</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>150</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>香蕉</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>95</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>130</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：统计到货次数</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIF</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：查询订单的客户名称</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>要求：仓库收到一批货物的到货记录，需要统计其中“正常”状态的货物数量。</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>练习函数：VLOOKUP</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格输入公式，统计状态为‘正常’的货物个数。</t>
+          <t>要求：你有一份订单明细表和一份客户信息表。订单表中有客户编号，需要根据客户编号从客户信息表中匹配客户名称。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>货物编号</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 D2 单元格输入公式，根据客户编号 C01 在表中查找对应的客户名称。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>正常</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>订单编号</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>客户编号</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>客户名称</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>A001</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>破损</t>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>张三公司</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>A003</t>
+          <t>A002</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>李四公司</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>A004</t>
+          <t>A003</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>延迟</t>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>王五公司</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>张三公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
           <t>A005</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>李四公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：查找员工部门</t>
-        </is>
-      </c>
-    </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>练习函数：VLOOKUP</t>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：计算订单到港天数</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>要求：公司有员工信息表，需要根据员工姓名查找其所属部门。</t>
+          <t>要求：物流场景：你有一批进口货物的订单，每个订单有预计到港日期（未来日期）。你需要计算今天距离每个预计到港日期还有多少天（当天差）。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>任务：在F2单元格输入公式，根据E2单元格的姓名（例如“王五”）查找对应的部门。</t>
+          <t>任务：请在 C2 单元格输入公式，计算今天（假设今天是2025-3-1）距离L001的到港日期还有多少天。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>工号</t>
+          <t>订单号</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>部门</t>
+          <t>预计到港日期</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>L001</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>销售部</t>
+          <t>2025-3-10</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>L002</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>市场部</t>
+          <t>2025-3-15</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>L003</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>财务部</t>
+          <t>2025-3-20</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>004</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>人事部</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：提取并寻找最大重量对应的物流单号</t>
+        </is>
+      </c>
+    </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：计算账龄天数</t>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>要求：物流仓库有一批包裹，包含物流单号和重量（公斤）。你需要找出最重包裹的重量，并返回对应的物流单号。</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>练习函数：DATEDIF</t>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 D1 单元格输入公式，计算最大重量；在 D2 单元格输入公式，返回最大重量对应的物流单号。</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>要求：财务需要计算每笔账款的账龄天数（从发票日期到今天的间隔天数）。请使用TODAY函数和DATEDIF函数。</t>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>物流单号</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>重量</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>任务：在C2单元格输入公式，计算第一笔账款的账龄天数，并下拉填充。</t>
-        </is>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>EX001</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>12.5</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>发票日期</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>EX002</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2024-01-15</t>
+          <t>EX003</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>500</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>EX004</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>300</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>EX005</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>700</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-15</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="n">
-        <v>450</v>
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：统计并处理错误数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>要求：某公司每日销售记录表，包含销售额和成本率。你需要计算利润（销售额*（1-成本率）），但有些成本率数据缺失或错误（如出现文本），导致公式出错。要求：如果出错则显示“数据有误”，否则保留一位小数。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：综合条件汇总与错误处理</t>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 C2 单元格输入公式，计算第一个利润并实现错误处理，然后向下填充。最终显示结果。</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>要求：销售数据表包含产品、区域、销量。需要统计指定区域和产品的销售总和，但若没有数据，避免显示错误，而是返回0。</t>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>销售额</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>成本率</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>任务：在G2单元格输入公式，统计区域为‘华东’且产品为‘手机’的总销量，若无数据则返回0。</t>
-        </is>
+      <c r="A50" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>产品</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>区域</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>销量</t>
-        </is>
+      <c r="A51" s="4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>手机</t>
-        </is>
+      <c r="A52" s="4" t="n">
+        <v>1500</v>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>100</v>
+          <t>无效</t>
+        </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>120</v>
+      <c r="A53" s="4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>电脑</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>电脑</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>平板</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1035,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计销售总量</t>
+          <t>第 1 题：计算华南区销售总额</t>
         </is>
       </c>
     </row>
@@ -1046,7 +989,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"苹果",B2:B6)</f>
+        <f>SUMIF(A2:A7,"华南",B2:B7)</f>
         <v/>
       </c>
     </row>
@@ -1060,7 +1003,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计到货次数</t>
+          <t>第 2 题：查询订单的客户名称</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1014,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF(B2:B6,"正常")</f>
+        <f>VLOOKUP(B2,$A$2:$C$6,3,FALSE)</f>
         <v/>
       </c>
     </row>
@@ -1085,7 +1028,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查找员工部门</t>
+          <t>第 3 题：计算订单到港天数</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1039,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>VLOOKUP(E2,A2:C5,3,FALSE)</f>
+        <f>DATEDIF(TODAY(),B2,"d")</f>
         <v/>
       </c>
     </row>
@@ -1110,7 +1053,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算账龄天数</t>
+          <t>第 4 题：提取并寻找最大重量对应的物流单号</t>
         </is>
       </c>
     </row>
@@ -1120,9 +1063,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <f>DATEDIF(A2,TODAY(),"d")</f>
-        <v/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>D1: =MAX(B2:B6)  D2: =INDEX(A2:A6,MATCH(D1,B2:B6,0))</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1135,7 +1079,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：综合条件汇总与错误处理</t>
+          <t>第 5 题：统计并处理错误数据</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1090,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>IFERROR(SUMIFS(C2:C6,A2:A6,"手机",B2:B6,"华东"),0)</f>
+        <f>IFERROR(ROUND(B2*C2,1),"数据有误") 注意：这里C2为利润列，但题目中C列不存在，所以请把公式放在C列，假设C2对应第一个数据。实际公式应为：=IFERROR(ROUND(B2*(1-B2),1),"数据有误") 但B2是销售额，需要成本率在B列？请调整：假设销售额在A列，成本率在B列，利润公式=IFERROR(ROUND(A2*(1-B2),1),"数据有误")。</f>
         <v/>
       </c>
     </row>
@@ -1178,7 +1122,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计销售总量</t>
+          <t>第 1 题：计算华南区销售总额</t>
         </is>
       </c>
     </row>
@@ -1190,14 +1134,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF(条件区域,条件,求和区域)。条件区域A2:A6与条件"苹果"匹配，然后对B2:B6中对应的行求和，结果为120+150+130=400。</t>
+          <t>SUMIF 函数用于按条件求和。语法：SUMIF(条件区域, 条件, 求和区域)。这里条件区域是A2:A7，条件是“华南”，求和区域是B2:B7。函数会扫描条件区域中所有等于“华南”的行，并对应求和区域的数值。本题中结果为 15000+22000+13000=50000。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：统计到货次数</t>
+          <t>第 2 题：查询订单的客户名称</t>
         </is>
       </c>
     </row>
@@ -1209,14 +1153,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF(计数区域,条件)。在B2:B6范围内，统计等于"正常"的单元格个数，结果为3。</t>
+          <t>VLOOKUP 函数用于垂直查找。语法：VLOOKUP(查找值, 表格区域, 返回列号, 精确/近似)。这里查找值是B2（客户编号C01），表格区域是$A$2:$C$6（整个表格，加绝对引用），返回列号3（因为客户名称在第三列），精确匹配用FALSE。公式会找到第一行C01对应的“张三公司”。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查找员工部门</t>
+          <t>第 3 题：计算订单到港天数</t>
         </is>
       </c>
     </row>
@@ -1228,14 +1172,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP(查找值,表区域,返回列号,精确匹配)。在A2:C5中查找E2的姓名，返回第3列部门，FALSE表示精确查找。结果为“财务部”。</t>
+          <t>DATEDIF 函数计算两个日期之间的差值。语法：DATEDIF(开始日期, 结束日期, 单位)，单位"d"表示天。TODAY()返回当前日期。这里开始是今天，结束是B2的日期。公式返回从今天到该日期的天数差。如果今天是2025-3-1，B2是2025-3-10，结果为9天。注意：DATEDIF要求开始日期早于结束日期，否则会返回错误。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算账龄天数</t>
+          <t>第 4 题：提取并寻找最大重量对应的物流单号</t>
         </is>
       </c>
     </row>
@@ -1247,14 +1191,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF(开始日期,结束日期,单位)。开始日期为A2，结束日期为今天的日期TODAY()，单位"d"表示天数。返回从发票日到今天的整天天数。</t>
+          <t>MAX函数返回区域中的最大值：B2:B6最大为20.1。然后使用MATCH找到最大值在重量区域的位置（第3行），MATCH(查找值, 区域, 0)精确匹配返回位置。INDEX函数根据位置从单号区域取第3个值“EX003”。组合公式=INDEX(A2:A6,MATCH(MAX(B2:B6),B2:B6,0))也可以一步完成。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：综合条件汇总与错误处理</t>
+          <t>第 5 题：统计并处理错误数据</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1210,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS(求和区域,条件区域1,条件1,[条件区域2,条件2]...)，先求和C2:C6中产品为“手机”且区域为“华东”的总销量。IFERROR函数捕获可能的错误（如无匹配返回0？），但SUMIFS不会出错，但若返回0则正常；此处IFERROR确保如果出现任何错误则显示0，实际结果100。</t>
+          <t>IFERROR函数捕获错误，如果公式结果错误则返回第二参数。ROUND四舍五入保留1位小数。IF用于判断条件但这里不直接用。例如A2*（1-B2）如果B2是文本“无效”，数学运算会返回#VALUE!错误，IFERROR捕获后显示“数据有误”。正确公式：=IFERROR(ROUND(A2*(1-B2),1),"数据有误")。当B2=0.3时，A2*(1-0.3)=1000*0.7=700，保留一位700.0。若B2是“无效”，则显示“数据有误”。注意：题目中成本率是小数，但实际是百分比？这里用小数。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,38 +476,43 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：计算华南区销售总额</t>
+          <t>第 1 题：第1题：统计某销售员在指定月份的总销售额</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIF</t>
+          <t>练习函数：SUMIFS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你有一张某公司各销售区域的订单表，包含区域和销售额。现在需要统计“华南区”的总销售额。</t>
+          <t>要求：你是一家销售公司的助理，需要从销售明细表中快速统计出'张伟'在'2024年3月'的总销售额。表格中有销售员、销售日期和销售额三列，共10条记录。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：请在 E1 单元格输入公式，计算“华南区”的销售额总和。</t>
+          <t>任务：请在单元格E2输入公式，计算销售员为“张伟”且销售日期在2024年3月1日至3月31日之间的销售额总和。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>区域</t>
+          <t>销售员</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>销售日期</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>销售额</t>
         </is>
@@ -516,364 +521,415 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>12000</v>
+          <t>张伟</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>15000</v>
+          <t>李娜</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>800</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>华北</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>8000</v>
+          <t>张伟</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>22000</v>
+          <t>王强</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-15</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>900</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>西南</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>9000</v>
+          <t>张伟</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>13000</v>
+          <t>李娜</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>1100</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>张伟</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>王强</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>2024-04-02</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>李娜</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>2024-04-05</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>张伟</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：查询订单的客户名称</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>练习函数：VLOOKUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一份订单明细表和一份客户信息表。订单表中有客户编号，需要根据客户编号从客户信息表中匹配客户名称。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 D2 单元格输入公式，根据客户编号 C01 在表中查找对应的客户名称。</t>
-        </is>
-      </c>
-    </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>订单编号</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>客户编号</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>客户名称</t>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：计算员工自入职以来的工作年数</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>张三公司</t>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>练习函数：DATEDIF</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>C02</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>李四公司</t>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>要求：你负责公司人事档案，需要计算每位员工从入职日期到今天为止的工作年数（满年数，不满一年不算）。今天是2024年5月15日，表格中列出了部分员工的入职日期。</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>A003</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>C03</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>王五公司</t>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在C2单元格输入公式，根据入职日期（B2）计算截至今天（2024-05-15）的工作年数，并下拉填充到C6。</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>A004</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>张三公司</t>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>员工姓名</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>入职日期</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>A005</t>
+          <t>赵敏</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>C02</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>李四公司</t>
+          <t>2019-03-10</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>钱进</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>孙丽</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>2022-11-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>李浩</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>周芳</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>2023-05-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：计算订单到港天数</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流场景：你有一批进口货物的订单，每个订单有预计到港日期（未来日期）。你需要计算今天距离每个预计到港日期还有多少天（当天差）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 C2 单元格输入公式，计算今天（假设今天是2025-3-1）距离L001的到港日期还有多少天。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>预计到港日期</t>
-        </is>
-      </c>
-    </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>L001</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>2025-3-10</t>
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：查找物料单价并计算含税总价（四舍五入）</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>L002</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>2025-3-15</t>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>练习函数：XLOOKUP</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>L003</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>2025-3-20</t>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>要求：你在一家贸易公司，需要根据客户订单中的物料编码，从价格表中查找对应单价，再计算每个订单的含税总价（单价×数量×1.13），并保留2位小数。价格表如下（数据区A1:B5）。订单表在下方（数据区从第7行开始）。</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在订单表的E9单元格（对应第1个订单）输入公式，查找该订单物料编码的单价，并计算含税总价（单价×数量×1.13），结果四舍五入到2位小数。之后可下拉填充至E12。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>物料编码</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：提取并寻找最大重量对应的物流单号</t>
-        </is>
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>A101</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>25.5</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流仓库有一批包裹，包含物流单号和重量（公斤）。你需要找出最重包裹的重量，并返回对应的物流单号。</t>
-        </is>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>A102</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 D1 单元格输入公式，计算最大重量；在 D2 单元格输入公式，返回最大重量对应的物流单号。</t>
-        </is>
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>B201</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>15.8</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>物流单号</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>重量</t>
-        </is>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>B202</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>60.25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>EX001</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>12.5</v>
+          <t>订单序号</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>物料编码</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>EX002</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>8.300000000000001</v>
+      <c r="A40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>A101</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>EX003</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>20.1</v>
+      <c r="A41" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>B202</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>EX004</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>15.7</v>
+      <c r="A42" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>A102</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>EX005</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>9.800000000000001</v>
+      <c r="A43" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>B201</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="44">
@@ -886,72 +942,248 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：统计并处理错误数据</t>
+          <t>第 4 题：第4题：从物流单号中提取区域代码和客户编号</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>要求：某公司每日销售记录表，包含销售额和成本率。你需要计算利润（销售额*（1-成本率）），但有些成本率数据缺失或错误（如出现文本），导致公式出错。要求：如果出错则显示“数据有误”，否则保留一位小数。</t>
+          <t>要求：你在物流公司做数据录入，每张运单的运单号有固定格式：前2位是区域代码，第3-6位是客户编号，最后4位是包裹序号。例如'SH1034-221'中区域SH，客户1034，包裹序号221。现在需要从运单号中提取区域代码和客户编号。</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>任务：请在 C2 单元格输入公式，计算第一个利润并实现错误处理，然后向下填充。最终显示结果。</t>
+          <t>任务：请在B2输入公式提取区域代码（前2位），在C2输入公式提取客户编号（第3-6位，共4位），下拉填充至第6行。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>成本率</t>
+          <t>运单号</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>0.3</v>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>SH1034-221</t>
+        </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n">
-        <v>2000</v>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>0.45</v>
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>BJ2087-045</t>
+        </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="n">
-        <v>1500</v>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>无效</t>
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>GZ3319-882</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="n">
-        <v>3000</v>
-      </c>
-      <c r="B53" s="4" t="n">
-        <v>0.2</v>
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>SZ4190-556</t>
+        </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>CD2251-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：根据班级和排名返回学生姓名（INDEX+MATCH）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是一位老师，需要根据学生所在班级和考试排名，快速查找对应学生的姓名。现有学生名单表（A1:C10），包含班级、排名、姓名。请你实现通过输入班级和排名，自动返回姓名。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在E2输入班级（如“B班”），在F2输入排名（如2），然后在G2输入公式，根据E2和F2的值返回对应学生姓名。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>班级</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>A班</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>张小明</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>A班</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>李小红</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>A班</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>王大力</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>B班</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>赵小刚</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>B班</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>陈静</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>B班</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>刘洋</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>C班</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>孙悦</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>C班</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>周杰</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>C班</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>吴倩</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -978,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：计算华南区销售总额</t>
+          <t>第 1 题：第1题：统计某销售员在指定月份的总销售额</t>
         </is>
       </c>
     </row>
@@ -989,7 +1221,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A7,"华南",B2:B7)</f>
+        <f>SUMIFS(C2:C11, A2:A11, "张伟", B2:B11, "&gt;=2024-03-01", B2:B11, "&lt;=2024-03-31")</f>
         <v/>
       </c>
     </row>
@@ -1003,7 +1235,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：查询订单的客户名称</t>
+          <t>第 2 题：第2题：计算员工自入职以来的工作年数</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1246,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>VLOOKUP(B2,$A$2:$C$6,3,FALSE)</f>
+        <f>DATEDIF(B2, TODAY(), "Y")</f>
         <v/>
       </c>
     </row>
@@ -1028,7 +1260,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：计算订单到港天数</t>
+          <t>第 3 题：第3题：查找物料单价并计算含税总价（四舍五入）</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1271,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>DATEDIF(TODAY(),B2,"d")</f>
+        <f>ROUND(XLOOKUP(B9, $A$2:$A$5, $B$2:$B$5) * C9 * 1.13, 2)</f>
         <v/>
       </c>
     </row>
@@ -1053,7 +1285,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：提取并寻找最大重量对应的物流单号</t>
+          <t>第 4 题：第4题：从物流单号中提取区域代码和客户编号</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1297,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>D1: =MAX(B2:B6)  D2: =INDEX(A2:A6,MATCH(D1,B2:B6,0))</t>
+          <t>B2公式：=LEFT(A2,2)；C2公式：=MID(A2,3,4)</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1311,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：统计并处理错误数据</t>
+          <t>第 5 题：第5题：根据班级和排名返回学生姓名（INDEX+MATCH）</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1322,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>IFERROR(ROUND(B2*C2,1),"数据有误") 注意：这里C2为利润列，但题目中C列不存在，所以请把公式放在C列，假设C2对应第一个数据。实际公式应为：=IFERROR(ROUND(B2*(1-B2),1),"数据有误") 但B2是销售额，需要成本率在B列？请调整：假设销售额在A列，成本率在B列，利润公式=IFERROR(ROUND(A2*(1-B2),1),"数据有误")。</f>
+        <f>INDEX(C2:C10, MATCH(1, (A2:A10=E2)*(B2:B10=F2), 0))</f>
         <v/>
       </c>
     </row>
@@ -1122,7 +1354,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：计算华南区销售总额</t>
+          <t>第 1 题：第1题：统计某销售员在指定月份的总销售额</t>
         </is>
       </c>
     </row>
@@ -1134,14 +1366,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 函数用于按条件求和。语法：SUMIF(条件区域, 条件, 求和区域)。这里条件区域是A2:A7，条件是“华南”，求和区域是B2:B7。函数会扫描条件区域中所有等于“华南”的行，并对应求和区域的数值。本题中结果为 15000+22000+13000=50000。</t>
+          <t>SUMIFS函数用于根据多个条件求和。语法为：SUMIFS(求和区域, 条件区域1, 条件1, [条件区域2, 条件2], ...)。本题中求和区域是销售额C2:C11，第一个条件区域是销售员A列，条件为'张伟'；第二个条件区域是日期B列，条件需同时满足大于等于3月1日和小于等于3月31日（用两个条件区域对同一列进行限制）。注意日期要用英文双引号括起来，Excel会识别为日期格式。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：查询订单的客户名称</t>
+          <t>第 2 题：第2题：计算员工自入职以来的工作年数</t>
         </is>
       </c>
     </row>
@@ -1153,14 +1385,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP 函数用于垂直查找。语法：VLOOKUP(查找值, 表格区域, 返回列号, 精确/近似)。这里查找值是B2（客户编号C01），表格区域是$A$2:$C$6（整个表格，加绝对引用），返回列号3（因为客户名称在第三列），精确匹配用FALSE。公式会找到第一行C01对应的“张三公司”。</t>
+          <t>DATEDIF用于计算两个日期之间的差值，语法：DATEDIF(开始日期, 结束日期, 单位)。单位"Y"表示完整年数，"M"为月，"D"为天。TODAY()函数自动返回当前日期。注意：若开始日期晚于结束日期会返回错误。本例中“周芳”入职2023-05-16，到2024-05-15刚好不满一年，结果为0。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：计算订单到港天数</t>
+          <t>第 3 题：第3题：查找物料单价并计算含税总价（四舍五入）</t>
         </is>
       </c>
     </row>
@@ -1172,14 +1404,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF 函数计算两个日期之间的差值。语法：DATEDIF(开始日期, 结束日期, 单位)，单位"d"表示天。TODAY()返回当前日期。这里开始是今天，结束是B2的日期。公式返回从今天到该日期的天数差。如果今天是2025-3-1，B2是2025-3-10，结果为9天。注意：DATEDIF要求开始日期早于结束日期，否则会返回错误。</t>
+          <t>XLOOKUP语法：XLOOKUP(查找值, 查找数组, 返回数组)。这里查找B9的物料编码，在价格表的A2:A5中查找，返回对应的B2:B5单价。然后乘以数量C9再乘1.13，得到含税总价。ROUND函数将结果四舍五入到指定小数位，ROUND(数值, 2)保留2位小数。注意锁定查找区域时用$符号。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：提取并寻找最大重量对应的物流单号</t>
+          <t>第 4 题：第4题：从物流单号中提取区域代码和客户编号</t>
         </is>
       </c>
     </row>
@@ -1191,14 +1423,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>MAX函数返回区域中的最大值：B2:B6最大为20.1。然后使用MATCH找到最大值在重量区域的位置（第3行），MATCH(查找值, 区域, 0)精确匹配返回位置。INDEX函数根据位置从单号区域取第3个值“EX003”。组合公式=INDEX(A2:A6,MATCH(MAX(B2:B6),B2:B6,0))也可以一步完成。</t>
+          <t>MID(text, start_num, num_chars)从指定位置开始提取指定长度字符。RIGHT(text, num_chars)从右侧提取字符。例如MID(A2,3,4)从第3位开始取4个字符得到客户编号。RIGHT(A2,3)取最后3位得到包裹序号。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：统计并处理错误数据</t>
+          <t>第 5 题：第5题：根据班级和排名返回学生姓名（INDEX+MATCH）</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1442,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>IFERROR函数捕获错误，如果公式结果错误则返回第二参数。ROUND四舍五入保留1位小数。IF用于判断条件但这里不直接用。例如A2*（1-B2）如果B2是文本“无效”，数学运算会返回#VALUE!错误，IFERROR捕获后显示“数据有误”。正确公式：=IFERROR(ROUND(A2*(1-B2),1),"数据有误")。当B2=0.3时，A2*(1-0.3)=1000*0.7=700，保留一位700.0。若B2是“无效”，则显示“数据有误”。注意：题目中成本率是小数，但实际是百分比？这里用小数。</t>
+          <t>INDEX(数组, 行号)返回数组中指定行的值。MATCH(查找值, 查找数组, 匹配类型)返回位置。这里需要同时满足班级和排名两个条件，所以用数组公式：MATCH(1, (条件1)*(条件2), 0) 只有当两个条件都满足时乘积才为1。输入公式后需按Ctrl+Shift+Enter确认（Excel 365中普通回车也可能自动识别，但建议使用数组公式）。INDEX返回C列对应行的姓名。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某销售员在指定月份的总销售额</t>
+          <t>第 1 题：第1题：统计某仓库指定日期前的发货总件数</t>
         </is>
       </c>
     </row>
@@ -490,700 +490,468 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家销售公司的助理，需要从销售明细表中快速统计出'张伟'在'2024年3月'的总销售额。表格中有销售员、销售日期和销售额三列，共10条记录。</t>
+          <t>要求：你是一家电商仓库的运营人员，有一张发货记录表，记录了每笔发货的日期和件数。现在需要统计“2024年3月1日之前”（不包含当天）的所有发货总件数。请根据以下样例数据完成统计。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：请在单元格E2输入公式，计算销售员为“张伟”且销售日期在2024年3月1日至3月31日之间的销售额总和。</t>
+          <t>任务：请在单元格B8输入公式，统计日期小于2024-03-01的件数总和。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>销售员</t>
+          <t>发货日期</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>销售日期</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>销售额</t>
+          <t>发货件数</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>张伟</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-05</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>1200</v>
+          <t>2024-02-20</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>李娜</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-08</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>800</v>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>张伟</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-12</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>1500</v>
+          <t>2024-02-15</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>王强</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-15</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>900</v>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>张伟</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>2000</v>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>李娜</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-20</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>1100</v>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>张伟</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-28</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>王强</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>2024-04-02</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>1300</v>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>李娜</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>2024-04-05</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>950</v>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：查询员工所在部门并处理查找失败情况</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>张伟</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>2024-04-10</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>1850</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>练习函数：XLOOKUP</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>要求：你在一家公司的行政部工作，有一份员工基本信息表，包含员工姓名和部门。现有一个员工名单，需要根据姓名查找对应部门，如果找不到则显示“未找到”。请根据以下数据完成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>任务：在单元格E2输入公式，查找“王五”的部门；在E3输入公式查找“陈七”的部门，要求找不到时显示“未找到”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>部门</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>销售部</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>市场部</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>技术部</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>财务部</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：计算员工自入职以来的工作年数</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>练习函数：DATEDIF</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>要求：你负责公司人事档案，需要计算每位员工从入职日期到今天为止的工作年数（满年数，不满一年不算）。今天是2024年5月15日，表格中列出了部分员工的入职日期。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在C2单元格输入公式，根据入职日期（B2）计算截至今天（2024-05-15）的工作年数，并下拉填充到C6。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：计算员工在司工作年数并处理错误</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是人力资源专员，需要计算每位员工的在司年数（从入职日期到今天，满年数取整数）。由于部分员工入职日期录入缺失，需要处理可能出现的错误，缺失时显示“日期缺失”。请根据以下数据完成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>任务：在C2:C5区域输入公式，计算每位员工的司龄（年数），如果入职日期为空，则显示“日期缺失”。假设今天是2025-04-01，在公式中使用TODAY()。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>员工姓名</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>入职日期</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>赵敏</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>2019-03-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>钱进</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>2021-07-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>孙丽</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>2022-11-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>李浩</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>2020-01-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>周芳</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>2023-05-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>2015-06-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>2019-11-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2021-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：查找物料单价并计算含税总价（四舍五入）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>练习函数：XLOOKUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>要求：你在一家贸易公司，需要根据客户订单中的物料编码，从价格表中查找对应单价，再计算每个订单的含税总价（单价×数量×1.13），并保留2位小数。价格表如下（数据区A1:B5）。订单表在下方（数据区从第7行开始）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在订单表的E9单元格（对应第1个订单）输入公式，查找该订单物料编码的单价，并计算含税总价（单价×数量×1.13），结果四舍五入到2位小数。之后可下拉填充至E12。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>物料编码</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="n"/>
-    </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>A101</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="n">
-        <v>25.5</v>
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：根据产品编码提取信息并计算运费折扣</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>A102</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="n">
-        <v>40</v>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是一家物流公司的跟单员，产品编码有固定格式：前两位是仓库代码（如AB），中间四位是产品类别（如CD01），最后两位是重量等级（如X1）。公司规定运费折扣：如果重量等级为“X1”则折扣为5%，否则无折扣。此外，需要从编码中提取出产品类别。请根据以下数据完成。</t>
+        </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>B201</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="n">
-        <v>15.8</v>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>任务：在B列提取每个编码的后两位（重量等级），在C列提取中间四位（产品类别），在D列计算折扣（X1为5%，否则为0%，用IF函数）。请在B2:D5输入公式。</t>
+        </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>B202</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>60.25</v>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>产品编码</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>订单序号</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>物料编码</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>数量</t>
+          <t>ABCD01X1</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>A101</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>10</v>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>EFCD02Y2</t>
+        </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>B202</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>5</v>
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>GHCD03X1</t>
+        </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>A102</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>20</v>
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>IJCD04Y3</t>
+        </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>B201</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：按条件筛选并计算销售总额</t>
+        </is>
+      </c>
+    </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：从物流单号中提取区域代码和客户编号</t>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是一家分公司的销售助理，管理一份销售明细表，包含销售员、产品类别和销售额。现在需要统计“销售员为’李四’且产品类别为’办公用品’”的销售额总和。如果计算过程中有错误，请显示0。请根据以下数据完成。</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>要求：你在物流公司做数据录入，每张运单的运单号有固定格式：前2位是区域代码，第3-6位是客户编号，最后4位是包裹序号。例如'SH1034-221'中区域SH，客户1034，包裹序号221。现在需要从运单号中提取区域代码和客户编号。</t>
+          <t>任务：在单元格E2输入公式，计算满足条件的销售额总和，并用IFERROR包裹使错误时返回0。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在B2输入公式提取区域代码（前2位），在C2输入公式提取客户编号（第3-6位，共4位），下拉填充至第6行。</t>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>销售员</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>产品类别</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>销售额</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>运单号</t>
-        </is>
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>办公用品</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>SH1034-221</t>
-        </is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>办公用品</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>BJ2087-045</t>
-        </is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>电子产品</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>800</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>GZ3319-882</t>
-        </is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>办公用品</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>SZ4190-556</t>
-        </is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>电子设备</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>950</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>CD2251-003</t>
-        </is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>办公用品</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：根据班级和排名返回学生姓名（INDEX+MATCH）</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是一位老师，需要根据学生所在班级和考试排名，快速查找对应学生的姓名。现有学生名单表（A1:C10），包含班级、排名、姓名。请你实现通过输入班级和排名，自动返回姓名。</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在E2输入班级（如“B班”），在F2输入排名（如2），然后在G2输入公式，根据E2和F2的值返回对应学生姓名。</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>班级</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>排名</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>A班</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>张小明</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>A班</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>李小红</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>A班</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>王大力</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>B班</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>赵小刚</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>B班</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>陈静</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>B班</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>刘洋</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>C班</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>孙悦</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>C班</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>周杰</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>C班</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>吴倩</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1210,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某销售员在指定月份的总销售额</t>
+          <t>第 1 题：第1题：统计某仓库指定日期前的发货总件数</t>
         </is>
       </c>
     </row>
@@ -1221,7 +989,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIFS(C2:C11, A2:A11, "张伟", B2:B11, "&gt;=2024-03-01", B2:B11, "&lt;=2024-03-31")</f>
+        <f>SUMIFS(B2:B7,A2:A7,"&lt;2024-03-01")</f>
         <v/>
       </c>
     </row>
@@ -1235,7 +1003,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：计算员工自入职以来的工作年数</t>
+          <t>第 2 题：第2题：查询员工所在部门并处理查找失败情况</t>
         </is>
       </c>
     </row>
@@ -1245,9 +1013,11 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B6" s="2">
-        <f>DATEDIF(B2, TODAY(), "Y")</f>
-        <v/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>E2: =XLOOKUP("王五",A2:A5,B2:B5)
+E3: =XLOOKUP("陈七",A2:A5,B2:B5,"未找到")</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1260,7 +1030,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查找物料单价并计算含税总价（四舍五入）</t>
+          <t>第 3 题：第3题：计算员工在司工作年数并处理错误</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1041,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>ROUND(XLOOKUP(B9, $A$2:$A$5, $B$2:$B$5) * C9 * 1.13, 2)</f>
+        <f>IFERROR(DATEDIF(B2,TODAY(),"Y"),"日期缺失")</f>
         <v/>
       </c>
     </row>
@@ -1285,7 +1055,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：从物流单号中提取区域代码和客户编号</t>
+          <t>第 4 题：第4题：根据产品编码提取信息并计算运费折扣</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1067,9 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>B2公式：=LEFT(A2,2)；C2公式：=MID(A2,3,4)</t>
+          <t>B2: =RIGHT(A2,2)
+C2: =MID(A2,3,4)
+D2: =IF(B2="X1",5%,0%)</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1083,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据班级和排名返回学生姓名（INDEX+MATCH）</t>
+          <t>第 5 题：第5题：按条件筛选并计算销售总额</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1094,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>INDEX(C2:C10, MATCH(1, (A2:A10=E2)*(B2:B10=F2), 0))</f>
+        <f>IFERROR(SUMIFS(C2:C7,A2:A7,"李四",B2:B7,"办公用品"),0)</f>
         <v/>
       </c>
     </row>
@@ -1354,7 +1126,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某销售员在指定月份的总销售额</t>
+          <t>第 1 题：第1题：统计某仓库指定日期前的发货总件数</t>
         </is>
       </c>
     </row>
@@ -1366,14 +1138,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS函数用于根据多个条件求和。语法为：SUMIFS(求和区域, 条件区域1, 条件1, [条件区域2, 条件2], ...)。本题中求和区域是销售额C2:C11，第一个条件区域是销售员A列，条件为'张伟'；第二个条件区域是日期B列，条件需同时满足大于等于3月1日和小于等于3月31日（用两个条件区域对同一列进行限制）。注意日期要用英文双引号括起来，Excel会识别为日期格式。</t>
+          <t>SUMIFS函数用于按多个条件求和，语法为SUMIFS(求和区域, 条件区域1, 条件1, ...)。本例中，求和区域是发货件数列B2:B7，条件区域是日期列A2:A7，条件是小于“2024-03-01”即"&lt;2024-03-01"。函数会筛选出符合条件的所有行，并累加对应的件数，结果为50+20+60=130。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：计算员工自入职以来的工作年数</t>
+          <t>第 2 题：第2题：查询员工所在部门并处理查找失败情况</t>
         </is>
       </c>
     </row>
@@ -1385,14 +1157,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF用于计算两个日期之间的差值，语法：DATEDIF(开始日期, 结束日期, 单位)。单位"Y"表示完整年数，"M"为月，"D"为天。TODAY()函数自动返回当前日期。注意：若开始日期晚于结束日期会返回错误。本例中“周芳”入职2023-05-16，到2024-05-15刚好不满一年，结果为0。</t>
+          <t>XLOOKUP函数语法为XLOOKUP(查找值, 查找数组, 返回数组, [未找到时的返回值])。第一题中直接查找返回对应部门；第二题添加了第四参数“未找到”，当找不到时显示该文本，避免#N/A错误。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查找物料单价并计算含税总价（四舍五入）</t>
+          <t>第 3 题：第3题：计算员工在司工作年数并处理错误</t>
         </is>
       </c>
     </row>
@@ -1404,14 +1176,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP语法：XLOOKUP(查找值, 查找数组, 返回数组)。这里查找B9的物料编码，在价格表的A2:A5中查找，返回对应的B2:B5单价。然后乘以数量C9再乘1.13，得到含税总价。ROUND函数将结果四舍五入到指定小数位，ROUND(数值, 2)保留2位小数。注意锁定查找区域时用$符号。</t>
+          <t>DATEDIF函数计算两个日期之间的年数，语法为DATEDIF(开始日期,结束日期,"Y")返回整年数。IFERROR函数用于捕获错误，如果B2为空，DATEDIF会返回#VALUE!，IFERROR则返回第二参数“日期缺失”。注意：公式要向下填充。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：从物流单号中提取区域代码和客户编号</t>
+          <t>第 4 题：第4题：根据产品编码提取信息并计算运费折扣</t>
         </is>
       </c>
     </row>
@@ -1423,14 +1195,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>MID(text, start_num, num_chars)从指定位置开始提取指定长度字符。RIGHT(text, num_chars)从右侧提取字符。例如MID(A2,3,4)从第3位开始取4个字符得到客户编号。RIGHT(A2,3)取最后3位得到包裹序号。</t>
+          <t>RIGHT(文本,2)提取右侧两个字符；MID(文本,开始位置,长度)提取中间字符，本例从第3位开始提取4位。IF函数判断B列是否为“X1”，是则返回5%，否则0%。注意D列需设置为百分比格式或直接用0.05、0。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：根据班级和排名返回学生姓名（INDEX+MATCH）</t>
+          <t>第 5 题：第5题：按条件筛选并计算销售总额</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1214,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>INDEX(数组, 行号)返回数组中指定行的值。MATCH(查找值, 查找数组, 匹配类型)返回位置。这里需要同时满足班级和排名两个条件，所以用数组公式：MATCH(1, (条件1)*(条件2), 0) 只有当两个条件都满足时乘积才为1。输入公式后需按Ctrl+Shift+Enter确认（Excel 365中普通回车也可能自动识别，但建议使用数组公式）。INDEX返回C列对应行的姓名。</t>
+          <t>SUMIFS函数多条件求和，条件区域1为销售员列，条件为“李四”；条件区域2为产品类别列，条件为“办公用品”。求和区域为销售额列。本例中符合条件的行是第3行和第5行，总和为1500+2000=3500。IFERROR用于避免无匹配等错误，但本例通常不会有错误，仅做练习。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某仓库指定日期前的发货总件数</t>
+          <t>第 1 题：第1题：统计指定月份的销售金额</t>
         </is>
       </c>
     </row>
@@ -490,87 +490,87 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家电商仓库的运营人员，有一张发货记录表，记录了每笔发货的日期和件数。现在需要统计“2024年3月1日之前”（不包含当天）的所有发货总件数。请根据以下样例数据完成统计。</t>
+          <t>要求：你是一家小店的销售记录，需要根据销售日期，统计2025年3月份的总销售金额。样例数据中A列是销售日期（格式为YYYY-MM-DD），B列是销售金额。请使用SUMIFS函数统计日期在2025年3月1日至2025年3月31日之间的金额总和。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：请在单元格B8输入公式，统计日期小于2024-03-01的件数总和。</t>
+          <t>任务：在E1单元格输入公式，统计2025年3月（即日期从2025-03-01到2025-03-31）的销售金额总和。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>发货日期</t>
+          <t>销售日期</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>发货件数</t>
+          <t>销售金额</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>30</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>20</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>40</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>15</v>
+        <v>450</v>
       </c>
     </row>
     <row r="12">
@@ -583,89 +583,84 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：查询员工所在部门并处理查找失败情况</t>
+          <t>第 2 题：第2题：计算每个业务员的业绩排名得分</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>练习函数：XLOOKUP</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是公司销售主管，需要根据每位业务员的销售业绩计算提成得分。规则是：如果业绩达到50000元及以上，提成比例为5%；如果业绩未达到50000元，则提成比例为3%。提成金额保留两位小数。样例数据：A列为业务员姓名，B列为销售业绩（元）。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>要求：你在一家公司的行政部工作，有一份员工基本信息表，包含员工姓名和部门。现有一个员工名单，需要根据姓名查找对应部门，如果找不到则显示“未找到”。请根据以下数据完成。</t>
+          <t>任务：在C2单元格输入公式，计算张伟的提成金额（保留两位小数），然后下拉填充到C6。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>任务：在单元格E2输入公式，查找“王五”的部门；在E3输入公式查找“陈七”的部门，要求找不到时显示“未找到”。</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>业务员</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>销售业绩</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>部门</t>
-        </is>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>张伟</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>52000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>销售部</t>
-        </is>
+          <t>李娜</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>48000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>市场部</t>
-        </is>
+          <t>王强</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>63000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>技术部</t>
-        </is>
+          <t>赵敏</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>财务部</t>
-        </is>
+          <t>陈杰</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>55000</v>
       </c>
     </row>
     <row r="23">
@@ -678,276 +673,328 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算员工在司工作年数并处理错误</t>
+          <t>第 3 题：第3题：查找客户订单的物流状态</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是人力资源专员，需要计算每位员工的在司年数（从入职日期到今天，满年数取整数）。由于部分员工入职日期录入缺失，需要处理可能出现的错误，缺失时显示“日期缺失”。请根据以下数据完成。</t>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>练习函数：XLOOKUP</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>任务：在C2:C5区域输入公式，计算每位员工的司龄（年数），如果入职日期为空，则显示“日期缺失”。假设今天是2025-04-01，在公式中使用TODAY()。</t>
+          <t>要求：你在物流公司工作，有一个订单状态表。现在需要根据订单编号快速查询某个订单的物流状态。样例数据中A列为订单编号（文本），B列为物流状态。请使用XLOOKUP函数查找指定订单的状态。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>员工姓名</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>入职日期</t>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>任务：在D1单元格输入订单编号"ORD003"，在E1单元格输入公式，根据D1的订单编号查找B列的物流状态。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>2015-06-15</t>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>订单编号</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>物流状态</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>ORD001</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>2019-11-01</t>
+          <t>已发货</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr"/>
+          <t>ORD002</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>运输中</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>赵六</t>
+          <t>ORD003</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>2021-03-10</t>
+          <t>已签收</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>ORD004</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>待揽收</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>ORD005</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：根据产品编码提取信息并计算运费折扣</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是一家物流公司的跟单员，产品编码有固定格式：前两位是仓库代码（如AB），中间四位是产品类别（如CD01），最后两位是重量等级（如X1）。公司规定运费折扣：如果重量等级为“X1”则折扣为5%，否则无折扣。此外，需要从编码中提取出产品类别。请根据以下数据完成。</t>
-        </is>
-      </c>
-    </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>任务：在B列提取每个编码的后两位（重量等级），在C列提取中间四位（产品类别），在D列计算折扣（X1为5%，否则为0%，用IF函数）。请在B2:D5输入公式。</t>
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：计算员工工龄和退休倒计时</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>产品编码</t>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>要求：你负责人力资源，需要计算员工的入职年限和预计退休天数（假设男性退休年龄为60岁）。样例数据：A列为员工姓名，B列为出生日期，C列为入职日期（日期格式均为YYYY-MM-DD）。请计算每人的入职天数（从入职日期到今天），以及距离退休的天数（假设60岁生日当天退休，如果已超过60岁则显示0）。</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>ABCD01X1</t>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>任务：在D2单元格输入公式，计算张三的入职天数（到今天为止的天数）；在E2单元格输入公式，计算张三距离60周岁退休的天数（如果已超过60岁则为0）。然后下拉填充至D5:E5。今天日期用TODAY函数获取。</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>EFCD02Y2</t>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>出生日期</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>入职日期</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>GHCD03X1</t>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>1975-06-15</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>2005-03-01</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>IJCD04Y3</t>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>1980-11-20</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>2010-07-12</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>1970-01-05</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>1998-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>1990-08-30</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>2020-02-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：按条件筛选并计算销售总额</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是一家分公司的销售助理，管理一份销售明细表，包含销售员、产品类别和销售额。现在需要统计“销售员为’李四’且产品类别为’办公用品’”的销售额总和。如果计算过程中有错误，请显示0。请根据以下数据完成。</t>
-        </is>
-      </c>
-    </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>任务：在单元格E2输入公式，计算满足条件的销售额总和，并用IFERROR包裹使错误时返回0。</t>
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：多条件匹配产品价格</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>销售员</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>产品类别</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>销售额</t>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>要求：你在一家供应链公司，需要根据产品名称和客户等级来查找对应的单价。样例数据是一个价格表：A列是产品名称，第1行是客户等级（普通、VIP、VVIP），中间区域是单价。请使用INDEX+MATCH组合，根据给定的产品名称和客户等级，返回对应的单价。</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>办公用品</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>1200</v>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>任务：在G1单元格输入产品名称"橙子"，在G2单元格输入客户等级"VIP"，在G3单元格输入公式，根据G1和G2查找对应的单价。</t>
+        </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>办公用品</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>1500</v>
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>产品</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>VVIP</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>电子产品</t>
-        </is>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>5</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>800</v>
+        <v>4.5</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>办公用品</t>
-        </is>
+          <t>香蕉</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>3</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>2000</v>
+        <v>2.8</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>电子设备</t>
-        </is>
+          <t>橙子</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="C53" s="4" t="n">
-        <v>950</v>
+        <v>3.5</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>办公用品</t>
-        </is>
+          <t>葡萄</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>8</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>600</v>
+        <v>7</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="55">
@@ -978,7 +1025,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某仓库指定日期前的发货总件数</t>
+          <t>第 1 题：第1题：统计指定月份的销售金额</t>
         </is>
       </c>
     </row>
@@ -989,7 +1036,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIFS(B2:B7,A2:A7,"&lt;2024-03-01")</f>
+        <f>SUMIFS(B2:B7,A2:A7,"&gt;=2025-03-01",A2:A7,"&lt;=2025-03-31")</f>
         <v/>
       </c>
     </row>
@@ -1003,7 +1050,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：查询员工所在部门并处理查找失败情况</t>
+          <t>第 2 题：第2题：计算每个业务员的业绩排名得分</t>
         </is>
       </c>
     </row>
@@ -1013,11 +1060,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>E2: =XLOOKUP("王五",A2:A5,B2:B5)
-E3: =XLOOKUP("陈七",A2:A5,B2:B5,"未找到")</t>
-        </is>
+      <c r="B6" s="2">
+        <f>ROUND(IF(B2&gt;=50000,B2*0.05,B2*0.03),2)</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1030,7 +1075,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算员工在司工作年数并处理错误</t>
+          <t>第 3 题：第3题：查找客户订单的物流状态</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1086,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>IFERROR(DATEDIF(B2,TODAY(),"Y"),"日期缺失")</f>
+        <f>XLOOKUP(D1,A2:A6,B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -1055,7 +1100,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：根据产品编码提取信息并计算运费折扣</t>
+          <t>第 4 题：第4题：计算员工工龄和退休倒计时</t>
         </is>
       </c>
     </row>
@@ -1067,9 +1112,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>B2: =RIGHT(A2,2)
-C2: =MID(A2,3,4)
-D2: =IF(B2="X1",5%,0%)</t>
+          <t>D2: =DATEDIF(C2,TODAY(),"d")  E2: =IF(DATEDIF(B2,TODAY(),"y")&gt;=60,0,DATEDIF(TODAY(),DATE(YEAR(B2)+60,MONTH(B2),DAY(B2)),"d"))</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1126,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：按条件筛选并计算销售总额</t>
+          <t>第 5 题：第5题：多条件匹配产品价格</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1137,7 @@
         </is>
       </c>
       <c r="B18" s="2">
-        <f>IFERROR(SUMIFS(C2:C7,A2:A7,"李四",B2:B7,"办公用品"),0)</f>
+        <f>INDEX(A2:D5,MATCH(G1,A2:A5,0),MATCH(G2,A1:D1,0))</f>
         <v/>
       </c>
     </row>
@@ -1126,7 +1169,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某仓库指定日期前的发货总件数</t>
+          <t>第 1 题：第1题：统计指定月份的销售金额</t>
         </is>
       </c>
     </row>
@@ -1138,14 +1181,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS函数用于按多个条件求和，语法为SUMIFS(求和区域, 条件区域1, 条件1, ...)。本例中，求和区域是发货件数列B2:B7，条件区域是日期列A2:A7，条件是小于“2024-03-01”即"&lt;2024-03-01"。函数会筛选出符合条件的所有行，并累加对应的件数，结果为50+20+60=130。</t>
+          <t>SUMIFS函数用于根据多个条件求和。语法：SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。这里求和区域是B2:B7（金额列），条件区域是A2:A7（日期列），第一个条件是日期大于等于2025-03-01，第二个条件是日期小于等于2025-03-31，两个条件需同时满足，返回满足条件的金额之和。公式结果为1000（120+250+180+450）。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：查询员工所在部门并处理查找失败情况</t>
+          <t>第 2 题：第2题：计算每个业务员的业绩排名得分</t>
         </is>
       </c>
     </row>
@@ -1157,14 +1200,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP函数语法为XLOOKUP(查找值, 查找数组, 返回数组, [未找到时的返回值])。第一题中直接查找返回对应部门；第二题添加了第四参数“未找到”，当找不到时显示该文本，避免#N/A错误。</t>
+          <t>IF函数用于条件判断：IF(条件, 真值, 假值)。这里条件为B2&gt;=50000，如果成立则用业绩乘以5%，否则乘以3%。ROUND函数将计算结果四舍五入保留两位小数。张伟业绩52000&gt;=50000，所以提成为52000*5%=2600。公式结果为2600。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：计算员工在司工作年数并处理错误</t>
+          <t>第 3 题：第3题：查找客户订单的物流状态</t>
         </is>
       </c>
     </row>
@@ -1176,14 +1219,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF函数计算两个日期之间的年数，语法为DATEDIF(开始日期,结束日期,"Y")返回整年数。IFERROR函数用于捕获错误，如果B2为空，DATEDIF会返回#VALUE!，IFERROR则返回第二参数“日期缺失”。注意：公式要向下填充。</t>
+          <t>XLOOKUP是Excel 365/2021中的函数，语法：XLOOKUP(查找值, 查找数组, 返回数组)。它在A2:A6中查找D1的值"ORD003"，找到后返回同一行B2:B6中的值。结果返回"已签收"。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：根据产品编码提取信息并计算运费折扣</t>
+          <t>第 4 题：第4题：计算员工工龄和退休倒计时</t>
         </is>
       </c>
     </row>
@@ -1195,14 +1238,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>RIGHT(文本,2)提取右侧两个字符；MID(文本,开始位置,长度)提取中间字符，本例从第3位开始提取4位。IF函数判断B列是否为“X1”，是则返回5%，否则0%。注意D列需设置为百分比格式或直接用0.05、0。</t>
+          <t>DATEDIF函数计算两个日期之间的差值，语法：DATEDIF(开始日期, 结束日期, 单位)。"d"表示天数。D2计算入职到今天的实际天数。E2先判断年龄是否达到60岁：DATEDIF(B2,TODAY(),"y")返回整年数，若&gt;=60则结果为0；否则用DATE函数构造60岁生日日期，再用DATEDIF(TODAY(),生日,"d")得到距离生日的天数。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：按条件筛选并计算销售总额</t>
+          <t>第 5 题：第5题：多条件匹配产品价格</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1257,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS函数多条件求和，条件区域1为销售员列，条件为“李四”；条件区域2为产品类别列，条件为“办公用品”。求和区域为销售额列。本例中符合条件的行是第3行和第5行，总和为1500+2000=3500。IFERROR用于避免无匹配等错误，但本例通常不会有错误，仅做练习。</t>
+          <t>INDEX函数返回指定行列交叉处的值，语法：INDEX(区域, 行号, 列号)。MATCH函数返回查找值在区域中的位置，语法：MATCH(查找值, 查找区域, 匹配类型)。这里MATCH(G1,A2:A5,0)在A2:A5中找到"橙子"返回行号3，MATCH(G2,A1:D1,0)在第一行找到"VIP"返回列号3，然后用INDEX返回区域A2:D5的第3行第3列交叉值，结果为3.5。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,47 +476,47 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定月份的销售金额</t>
+          <t>第 1 题：第1题：统计某天之后的总销售额（SUMIF）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>练习函数：SUMIFS</t>
+          <t>练习函数：SUMIF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家小店的销售记录，需要根据销售日期，统计2025年3月份的总销售金额。样例数据中A列是销售日期（格式为YYYY-MM-DD），B列是销售金额。请使用SUMIFS函数统计日期在2025年3月1日至2025年3月31日之间的金额总和。</t>
+          <t>要求：你是一家小型超市的收银员，需要快速统计5月6日及以后的总销售额（含5月6日）。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在E1单元格输入公式，统计2025年3月（即日期从2025-03-01到2025-03-31）的销售金额总和。</t>
+          <t>任务：在B8单元格输入公式，计算日期为2024-05-06及之后的销售额总和（注意日期在Excel中是数字，需用日期函数或用大于等于指定日期）。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>销售日期</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>销售金额</t>
+          <t>销售额</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
@@ -526,361 +526,367 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>250</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>300</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>90</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：根据订单号查找客户名（VLOOKUP）</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：计算每个业务员的业绩排名得分</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>练习函数：VLOOKUP</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>要求：你是公司销售主管，需要根据每位业务员的销售业绩计算提成得分。规则是：如果业绩达到50000元及以上，提成比例为5%；如果业绩未达到50000元，则提成比例为3%。提成金额保留两位小数。样例数据：A列为业务员姓名，B列为销售业绩（元）。</t>
+          <t>要求：你手上有一张订单明细表和一个客户订单对照表。需要根据订单编号查找对应的客户名称，用于后续处理。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：在C2单元格输入公式，计算张伟的提成金额（保留两位小数），然后下拉填充到C6。</t>
+          <t>任务：在D2单元格输入公式，根据A2的订单编号（A100）查找客户名，结果应为“张三”。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>业务员</t>
+          <t>订单编号</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>销售业绩</t>
+          <t>客户名</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>金额</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>张伟</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>52000</v>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>560</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>李娜</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>48000</v>
+          <t>A101</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>230</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>王强</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>63000</v>
+          <t>A102</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>890</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>赵敏</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>45000</v>
+          <t>A103</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>陈杰</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>55000</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：根据重量计算运费并四舍五入（ROUND）</t>
+        </is>
+      </c>
+    </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：查找客户订单的物流状态</t>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>练习函数：ROUND</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>练习函数：XLOOKUP</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>要求：物流公司按重量计费：每公斤运费为3.7元，重量保留到小数点后1位（不足0.1kg按0.1kg算，但本题直接使用给定重量）。你有一批货物重量清单，需要计算每票的运费金额，并四舍五入到元。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>要求：你在物流公司工作，有一个订单状态表。现在需要根据订单编号快速查询某个订单的物流状态。样例数据中A列为订单编号（文本），B列为物流状态。请使用XLOOKUP函数查找指定订单的状态。</t>
+          <t>任务：在C2单元格输入公式，计算K001的运费（重量*3.7），结果四舍五入到整数。K001重量2.3，运费=8.51，四舍五入后为9。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>任务：在D1单元格输入订单编号"ORD003"，在E1单元格输入公式，根据D1的订单编号查找B列的物流状态。</t>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>快件编号</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>订单编号</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>物流状态</t>
-        </is>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>K001</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>ORD001</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>已发货</t>
-        </is>
+          <t>K002</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>5.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>ORD002</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>运输中</t>
-        </is>
+          <t>K003</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>ORD003</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>已签收</t>
-        </is>
+          <t>K004</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>9.1</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>ORD004</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>待揽收</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>ORD005</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>已发货</t>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：筛选符合多条件的订单总和（SUMIFS）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>练习函数：SUMIFS</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：计算员工工龄和退休倒计时</t>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>要求：你拥有一家网店的销售记录，需要统计“华东区”在“2024年5月”的总销售额（日期为5月1日至5月31日）。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>要求：你负责人力资源，需要计算员工的入职年限和预计退休天数（假设男性退休年龄为60岁）。样例数据：A列为员工姓名，B列为出生日期，C列为入职日期（日期格式均为YYYY-MM-DD）。请计算每人的入职天数（从入职日期到今天），以及距离退休的天数（假设60岁生日当天退休，如果已超过60岁则显示0）。</t>
+          <t>任务：在B8单元格输入公式，计算区域为“华东”且日期在2024-05-01到2024-05-31之间的销售额总和（注意日期格式为文本或数字）。</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>任务：在D2单元格输入公式，计算张三的入职天数（到今天为止的天数）；在E2单元格输入公式，计算张三距离60周岁退休的天数（如果已超过60岁则为0）。然后下拉填充至D5:E5。今天日期用TODAY函数获取。</t>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>销售额</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>出生日期</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>入职日期</t>
-        </is>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>1975-06-15</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>2005-03-01</t>
-        </is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>1980-11-20</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>2010-07-12</t>
-        </is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>700</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>1970-01-05</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>1998-09-01</t>
-        </is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>赵六</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>1990-08-30</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>2020-02-17</t>
-        </is>
+          <t>华东</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="45">
@@ -893,112 +899,74 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：多条件匹配产品价格</t>
+          <t>第 5 题：第5题：从身份证号提取出生日期并用TODAY计算年龄（MID、DATEDIF、TODAY）</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>要求：你在一家供应链公司，需要根据产品名称和客户等级来查找对应的单价。样例数据是一个价格表：A列是产品名称，第1行是客户等级（普通、VIP、VVIP），中间区域是单价。请使用INDEX+MATCH组合，根据给定的产品名称和客户等级，返回对应的单价。</t>
+          <t>要求：你是人事专员，需要从员工的身份证号（18位）中提取出生日期（第7-14位，格式为YYYYMMDD），然后计算每位员工截至今天的实际年龄（完成年数）。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>任务：在G1单元格输入产品名称"橙子"，在G2单元格输入客户等级"VIP"，在G3单元格输入公式，根据G1和G2查找对应的单价。</t>
+          <t>任务：在C2单元格输入公式，根据B2身份证号计算张伟的出生日期（以日期格式显示）？再在D2输入公式计算其年龄（用TODAY()）。注意：MID函数提取的是文本，需要转换为日期。</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>产品</t>
+          <t>员工姓名</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>VIP</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>VVIP</t>
+          <t>身份证号</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>4</v>
+          <t>张伟</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>110101199005126789</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>香蕉</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="D52" s="4" t="n">
-        <v>2.5</v>
+          <t>李娜</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>310101198512231234</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>橙子</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D53" s="4" t="n">
-        <v>3</v>
+          <t>王强</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>440101200005123456</t>
+        </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>葡萄</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1025,7 +993,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定月份的销售金额</t>
+          <t>第 1 题：第1题：统计某天之后的总销售额（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1004,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIFS(B2:B7,A2:A7,"&gt;=2025-03-01",A2:A7,"&lt;=2025-03-31")</f>
+        <f>SUMIF(A2:A6, "&gt;=2024-05-06", B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -1050,7 +1018,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：计算每个业务员的业绩排名得分</t>
+          <t>第 2 题：第2题：根据订单号查找客户名（VLOOKUP）</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1029,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>ROUND(IF(B2&gt;=50000,B2*0.05,B2*0.03),2)</f>
+        <f>VLOOKUP(A2, A2:B5, 2, FALSE)</f>
         <v/>
       </c>
     </row>
@@ -1075,7 +1043,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查找客户订单的物流状态</t>
+          <t>第 3 题：第3题：根据重量计算运费并四舍五入（ROUND）</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1054,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>XLOOKUP(D1,A2:A6,B2:B6)</f>
+        <f>ROUND(B2*3.7, 0)</f>
         <v/>
       </c>
     </row>
@@ -1100,7 +1068,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算员工工龄和退休倒计时</t>
+          <t>第 4 题：第4题：筛选符合多条件的订单总和（SUMIFS）</t>
         </is>
       </c>
     </row>
@@ -1110,10 +1078,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>D2: =DATEDIF(C2,TODAY(),"d")  E2: =IF(DATEDIF(B2,TODAY(),"y")&gt;=60,0,DATEDIF(TODAY(),DATE(YEAR(B2)+60,MONTH(B2),DAY(B2)),"d"))</t>
-        </is>
+      <c r="B14" s="2">
+        <f>SUMIFS(C2:C6, B2:B6, "华东", A2:A6, "&gt;=2024-05-01", A2:A6, "&lt;=2024-05-31")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1126,7 +1093,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：多条件匹配产品价格</t>
+          <t>第 5 题：第5题：从身份证号提取出生日期并用TODAY计算年龄（MID、DATEDIF、TODAY）</t>
         </is>
       </c>
     </row>
@@ -1136,9 +1103,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2">
-        <f>INDEX(A2:D5,MATCH(G1,A2:A5,0),MATCH(G2,A1:D1,0))</f>
-        <v/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>出生日期：=DATE(MID(B2,7,4),MID(B2,11,2),MID(B2,13,2)) ；年龄：=DATEDIF(DATE(MID(B2,7,4),MID(B2,11,2),MID(B2,13,2)),TODAY(),"Y")</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1169,7 +1137,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计指定月份的销售金额</t>
+          <t>第 1 题：第1题：统计某天之后的总销售额（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1181,14 +1149,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS函数用于根据多个条件求和。语法：SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。这里求和区域是B2:B7（金额列），条件区域是A2:A7（日期列），第一个条件是日期大于等于2025-03-01，第二个条件是日期小于等于2025-03-31，两个条件需同时满足，返回满足条件的金额之和。公式结果为1000（120+250+180+450）。</t>
+          <t>SUMIF(条件区域, 条件, 求和区域)。条件写成"&gt;=2024-05-06"，Excel会自动将文本日期转为日期序列号，因此可以正确比较。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：计算每个业务员的业绩排名得分</t>
+          <t>第 2 题：第2题：根据订单号查找客户名（VLOOKUP）</t>
         </is>
       </c>
     </row>
@@ -1200,14 +1168,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>IF函数用于条件判断：IF(条件, 真值, 假值)。这里条件为B2&gt;=50000，如果成立则用业绩乘以5%，否则乘以3%。ROUND函数将计算结果四舍五入保留两位小数。张伟业绩52000&gt;=50000，所以提成为52000*5%=2600。公式结果为2600。</t>
+          <t>VLOOKUP(查找值, 表区域, 返回列序号, 精确匹配/近似匹配)。这里用FALSE表示精确查找，区域A2:B5的第一列是订单编号，返回第二列客户名。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：查找客户订单的物流状态</t>
+          <t>第 3 题：第3题：根据重量计算运费并四舍五入（ROUND）</t>
         </is>
       </c>
     </row>
@@ -1219,14 +1187,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP是Excel 365/2021中的函数，语法：XLOOKUP(查找值, 查找数组, 返回数组)。它在A2:A6中查找D1的值"ORD003"，找到后返回同一行B2:B6中的值。结果返回"已签收"。</t>
+          <t>ROUND(数字, 小数位数)。0表示保留整数位。先算乘法再四舍五入。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：计算员工工龄和退休倒计时</t>
+          <t>第 4 题：第4题：筛选符合多条件的订单总和（SUMIFS）</t>
         </is>
       </c>
     </row>
@@ -1238,14 +1206,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF函数计算两个日期之间的差值，语法：DATEDIF(开始日期, 结束日期, 单位)。"d"表示天数。D2计算入职到今天的实际天数。E2先判断年龄是否达到60岁：DATEDIF(B2,TODAY(),"y")返回整年数，若&gt;=60则结果为0；否则用DATE函数构造60岁生日日期，再用DATEDIF(TODAY(),生日,"d")得到距离生日的天数。</t>
+          <t>SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2,...)。这里设置两个条件：区域等于“华东”，日期大于等于5月1日且小于等于5月31日。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：多条件匹配产品价格</t>
+          <t>第 5 题：第5题：从身份证号提取出生日期并用TODAY计算年龄（MID、DATEDIF、TODAY）</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1225,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>INDEX函数返回指定行列交叉处的值，语法：INDEX(区域, 行号, 列号)。MATCH函数返回查找值在区域中的位置，语法：MATCH(查找值, 查找区域, 匹配类型)。这里MATCH(G1,A2:A5,0)在A2:A5中找到"橙子"返回行号3，MATCH(G2,A1:D1,0)在第一行找到"VIP"返回列号3，然后用INDEX返回区域A2:D5的第3行第3列交叉值，结果为3.5。</t>
+          <t>MID(文本,起始位置,长度)提取身份证的年份、月份、日期子串，再用DATE函数组合成日期。DATEDIF(开始日期,结束日期,"Y")返回整年数，用TODAY()作为结束日期即可得到真实年龄。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某天之后的总销售额（SUMIF）</t>
+          <t>第 1 题：统计特定销售员的销售额总和</t>
         </is>
       </c>
     </row>
@@ -490,21 +490,21 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是一家小型超市的收银员，需要快速统计5月6日及以后的总销售额（含5月6日）。</t>
+          <t>要求：你有一张销售记录表，包含销售员姓名和对应的销售额。现在需要统计“张三”的总销售额。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在B8单元格输入公式，计算日期为2024-05-06及之后的销售额总和（注意日期在Excel中是数字，需用日期函数或用大于等于指定日期）。</t>
+          <t>任务：在E2单元格输入公式，计算销售员为“张三”的总销售额。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>销售员</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -516,457 +516,454 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>120</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>85</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>210</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>150</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>300</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：第2题：根据订单号查找客户名（VLOOKUP）</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：根据商品编号查找单价并计算总价</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>练习函数：VLOOKUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>要求：你手上有一张订单明细表和一个客户订单对照表。需要根据订单编号查找对应的客户名称，用于后续处理。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>任务：在D2单元格输入公式，根据A2的订单编号（A100）查找客户名，结果应为“张三”。</t>
+          <t>要求：你有一个商品单价表（商品编号和单价），另一个是销售明细表（含商品编号和数量）。需要从单价表中匹配单价，然后计算每种商品的总价。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>订单编号</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>客户名</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>金额</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>任务：在F7单元格输入公式，查找销售明细中第一个商品（A02）的单价，再在G7计算总价（单价乘数量）。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>A100</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>560</v>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>商品编号</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A101</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>230</v>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>A102</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>890</v>
+          <t>A02</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>A103</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>150</v>
+          <t>A03</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>销售明细</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>商品编号</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>A02</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>A03</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：根据重量计算运费并四舍五入（ROUND）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>练习函数：ROUND</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流公司按重量计费：每公斤运费为3.7元，重量保留到小数点后1位（不足0.1kg按0.1kg算，但本题直接使用给定重量）。你有一批货物重量清单，需要计算每票的运费金额，并四舍五入到元。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>任务：在C2单元格输入公式，计算K001的运费（重量*3.7），结果四舍五入到整数。K001重量2.3，运费=8.51，四舍五入后为9。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>快件编号</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
-        </is>
-      </c>
-    </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>K001</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>2.3</v>
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：统计迟到次数和早退次数</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>K002</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>5.6</v>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一张员工考勤表，记录每个员工的打卡状态（正常、迟到、早退）。需要统计每个状态的次数，以及“张三”的迟到次数。</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>K003</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n">
-        <v>1.8</v>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>任务：在E2计算“迟到”总次数，在E3计算“张三”的迟到次数。</t>
+        </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>K004</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>9.1</v>
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>员工</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>迟到</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>早退</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>迟到</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>迟到</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>早退</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：筛选符合多条件的订单总和（SUMIFS）</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>练习函数：SUMIFS</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>要求：你拥有一家网店的销售记录，需要统计“华东区”在“2024年5月”的总销售额（日期为5月1日至5月31日）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>任务：在B8单元格输入公式，计算区域为“华东”且日期在2024-05-01到2024-05-31之间的销售额总和（注意日期格式为文本或数字）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>区域</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>销售额</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-02</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>300</v>
-      </c>
-    </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>700</v>
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：计算员工工龄（月数）和精确工龄（年+月）</t>
+        </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-15</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>200</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>练习函数：DATEDIF</t>
+        </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>2024-06-01</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>100</v>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一张员工入职日期表，需要计算每个员工截至今天（假设今天为2025/3/20）的工龄月数，以及精确的年数和月数。</t>
+        </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>任务：在C2单元格输入公式计算第一个员工的总工龄月数，在D2计算“X年Y个月”的文本。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>员工</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>入职日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>2018-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：从身份证号提取出生日期并用TODAY计算年龄（MID、DATEDIF、TODAY）</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是人事专员，需要从员工的身份证号（18位）中提取出生日期（第7-14位，格式为YYYYMMDD），然后计算每位员工截至今天的实际年龄（完成年数）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>任务：在C2单元格输入公式，根据B2身份证号计算张伟的出生日期（以日期格式显示）？再在D2输入公式计算其年龄（用TODAY()）。注意：MID函数提取的是文本，需要转换为日期。</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>员工姓名</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>身份证号</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>张伟</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>110101199005126789</t>
-        </is>
-      </c>
-    </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>李娜</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>310101198512231234</t>
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：从发票号中提取日期和金额</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>王强</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>440101200005123456</t>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一批发票数据，发票号格式为“INV-20250315-1234”，其中包含日期（第5-12位）和最后4位数字（金额代码）。需要从发票号中提取日期，并处理错误情况。</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>任务：在B2输入公式提取第一个发票号中间的日期部分（格式YYYYMMDD），在C2提取最后4位数字，并确保当发票号不是预定格式时显示“格式错误”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>发票号</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>INV-20250315-1234</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>INV-20241231-5698</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>INV-20230618-9999</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -993,7 +990,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某天之后的总销售额（SUMIF）</t>
+          <t>第 1 题：统计特定销售员的销售额总和</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1001,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6, "&gt;=2024-05-06", B2:B6)</f>
+        <f>SUMIF(A2:A7,"张三",B2:B7)</f>
         <v/>
       </c>
     </row>
@@ -1018,7 +1015,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：根据订单号查找客户名（VLOOKUP）</t>
+          <t>第 2 题：根据商品编号查找单价并计算总价</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1026,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>VLOOKUP(A2, A2:B5, 2, FALSE)</f>
+        <f>VLOOKUP(A7,$A$2:$B$4,2,FALSE)  ,  在G7输入 =F7*B7</f>
         <v/>
       </c>
     </row>
@@ -1043,7 +1040,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据重量计算运费并四舍五入（ROUND）</t>
+          <t>第 3 题：统计迟到次数和早退次数</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1051,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>ROUND(B2*3.7, 0)</f>
+        <f>COUNTIF(B2:B8,"迟到")  ,  =COUNTIFS(A2:A8,"张三",B2:B8,"迟到")</f>
         <v/>
       </c>
     </row>
@@ -1068,7 +1065,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：筛选符合多条件的订单总和（SUMIFS）</t>
+          <t>第 4 题：计算员工工龄（月数）和精确工龄（年+月）</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1076,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>SUMIFS(C2:C6, B2:B6, "华东", A2:A6, "&gt;=2024-05-01", A2:A6, "&lt;=2024-05-31")</f>
+        <f>DATEDIF(B2,TODAY(),"m")  ,  =DATEDIF(B2,TODAY(),"y")&amp;"年"&amp;DATEDIF(B2,TODAY(),"ym")&amp;"个月"</f>
         <v/>
       </c>
     </row>
@@ -1093,7 +1090,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：从身份证号提取出生日期并用TODAY计算年龄（MID、DATEDIF、TODAY）</t>
+          <t>第 5 题：从发票号中提取日期和金额</t>
         </is>
       </c>
     </row>
@@ -1103,10 +1100,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>出生日期：=DATE(MID(B2,7,4),MID(B2,11,2),MID(B2,13,2)) ；年龄：=DATEDIF(DATE(MID(B2,7,4),MID(B2,11,2),MID(B2,13,2)),TODAY(),"Y")</t>
-        </is>
+      <c r="B18" s="2">
+        <f>MID(A2,5,8)  ,  =IFERROR(RIGHT(A2,4),"格式错误")</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1137,7 +1133,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：统计某天之后的总销售额（SUMIF）</t>
+          <t>第 1 题：统计特定销售员的销售额总和</t>
         </is>
       </c>
     </row>
@@ -1149,14 +1145,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF(条件区域, 条件, 求和区域)。条件写成"&gt;=2024-05-06"，Excel会自动将文本日期转为日期序列号，因此可以正确比较。</t>
+          <t>SUMIF函数用于按条件求和，语法为SUMIF(条件区域,条件,求和区域)。本例中，条件区域是A2:A7（销售员列），条件是“张三”，求和区域是B2:B7（销售额列）。函数会遍历销售员列，凡等于“张三”的行，对应销售额相加。现在张三的销售额为1500+1800+1200=4500。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：根据订单号查找客户名（VLOOKUP）</t>
+          <t>第 2 题：根据商品编号查找单价并计算总价</t>
         </is>
       </c>
     </row>
@@ -1168,14 +1164,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP(查找值, 表区域, 返回列序号, 精确匹配/近似匹配)。这里用FALSE表示精确查找，区域A2:B5的第一列是订单编号，返回第二列客户名。</t>
+          <t>VLOOKUP语法为VLOOKUP(查找值,表格区域,返回列号,精确匹配)。其中A7是A02，查找区域是$A$2:$B$4（单价表），返回第2列单价，FALSE表示精确匹配。得到单价25后，乘以数量3得总价75。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：根据重量计算运费并四舍五入（ROUND）</t>
+          <t>第 3 题：统计迟到次数和早退次数</t>
         </is>
       </c>
     </row>
@@ -1187,14 +1183,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ROUND(数字, 小数位数)。0表示保留整数位。先算乘法再四舍五入。</t>
+          <t>COUNTIF用于单条件计数，统计B列中等于“迟到”的个数，结果为2。COUNTIFS支持多条件，语法为COUNTIFS(条件区域1,条件1,条件区域2,条件2)。这里条件1是员工列A2:A8中“张三”，条件2是状态列中“迟到”，满足两条件的行数为2。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：筛选符合多条件的订单总和（SUMIFS）</t>
+          <t>第 4 题：计算员工工龄（月数）和精确工龄（年+月）</t>
         </is>
       </c>
     </row>
@@ -1206,14 +1202,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2,...)。这里设置两个条件：区域等于“华东”，日期大于等于5月1日且小于等于5月31日。</t>
+          <t>DATEDIF计算两个日期差，语法：DATEDIF(开始日期,结束日期,单位)。单位“m”返回整月数，“y”返回整年数，“ym”返回扣除整年后的剩余月数。张三从2020-1-15到2025-3-20共62个月，年数5年（2020-2025），剩余2个月（因为3月比1月多2个月），所以结果为“5年2个月”。注意：TODAY()会随当天日期变化，但答案基于2025/3/20。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：从身份证号提取出生日期并用TODAY计算年龄（MID、DATEDIF、TODAY）</t>
+          <t>第 5 题：从发票号中提取日期和金额</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1221,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MID(文本,起始位置,长度)提取身份证的年份、月份、日期子串，再用DATE函数组合成日期。DATEDIF(开始日期,结束日期,"Y")返回整年数，用TODAY()作为结束日期即可得到真实年龄。</t>
+          <t>MID函数提取文本中间部分，语法MID(文本,起始位置,长度)。发票号第5位开始是8位日期，所以=MID(A2,5,8)得到“20250315”。RIGHT函数提取右侧字符，=RIGHT(A2,4)得到“1234”。但为了防错，用IFERROR包裹，若提取出错（如长度不足）则显示“格式错误”。这里所有数据格式合法，所以直接提取成功。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：统计特定销售员的销售额总和</t>
+          <t>第 1 题：第1题：仓库重量汇总</t>
         </is>
       </c>
     </row>
@@ -490,480 +490,542 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你有一张销售记录表，包含销售员姓名和对应的销售额。现在需要统计“张三”的总销售额。</t>
+          <t>要求：你是仓库文员，需要按商品名称汇总入库重量。请根据A列商品名称和B列重量，在E2单元格计算“苹果”的总重量。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格输入公式，计算销售员为“张三”的总销售额。</t>
+          <t>任务：在E2单元格输入公式，计算商品名称为“苹果”的重量总和。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>销售员</t>
+          <t>商品名称</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>重量</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>1500</v>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>2300</v>
+          <t>香蕉</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>1800</v>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>2100</v>
+          <t>橙子</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>1200</v>
+          <t>苹果</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>2600</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>第 2 题：第2题：订单数量计数</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>第 2 题：根据商品编号查找单价并计算总价</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIF</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>练习函数：VLOOKUP</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是电商客服，需要统计“已发货”状态的订单数量。请根据A列订单状态，在D2单元格计算已发货订单数。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>要求：你有一个商品单价表（商品编号和单价），另一个是销售明细表（含商品编号和数量）。需要从单价表中匹配单价，然后计算每种商品的总价。</t>
+          <t>任务：在D2单元格输入公式，统计状态为“已发货”的订单数量。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>任务：在F7单元格输入公式，查找销售明细中第一个商品（A02）的单价，再在G7计算总价（单价乘数量）。</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>商品编号</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A01</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>10</v>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>待发货</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>A02</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>25</v>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>A03</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>8</v>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>已取消</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>销售明细</t>
+          <t>A005</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>已发货</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>商品编号</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>A02</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>3</v>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>A01</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>5</v>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：多条件筛选汇总</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>A03</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>2</v>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是物流调度员，需要统计“上海”发往“北京”的运费总额，以及这种线路的订单笔数。请根据A列出发地、B列目的地、C列运费，在F2和F3分别计算。</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>任务：在F2单元格计算出发地为“上海”且目的地为“北京”的运费总额；在F3单元格计算同样条件的订单笔数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>出发地</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>目的地</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>运费</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：统计迟到次数和早退次数</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>120</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一张员工考勤表，记录每个员工的打卡状态（正常、迟到、早退）。需要统计每个状态的次数，以及“张三”的迟到次数。</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>任务：在E2计算“迟到”总次数，在E3计算“张三”的迟到次数。</t>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>150</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>员工</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>迟到</t>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>早退</t>
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>迟到</t>
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：到港天数与错误处理</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>迟到</t>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是外贸跟单员，需要根据预计到港日期计算距离今天还有多少天。如果日期已过或为空，则显示“已到港”。请根据A列订单号、B列预计到港日期，在D2向下填充公式。</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>早退</t>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>任务：在D2单元格输入公式，计算B2距离今天的天数；如果B2为空或日期已过，则显示“已到港”。公式需能向下填充。</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>正常</t>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>预计到港日期</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>PO001</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>PO002</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>PO003</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>PO004</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：计算员工工龄（月数）和精确工龄（年+月）</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>练习函数：DATEDIF</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一张员工入职日期表，需要计算每个员工截至今天（假设今天为2025/3/20）的工龄月数，以及精确的年数和月数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>任务：在C2单元格输入公式计算第一个员工的总工龄月数，在D2计算“X年Y个月”的文本。</t>
-        </is>
-      </c>
-    </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>员工</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>入职日期</t>
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：产品价格查询与灵活匹配</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>2020-01-15</t>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是采购助理，需要根据产品编号查询单价。请根据A列产品编号、B列产品名称、C列单价，在F2用VLOOKUP查询编号“P003”的单价；在F3用INDEX+MATCH查询编号“P005”的产品名称。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>2018-05-20</t>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>任务：在F2单元格用VLOOKUP查询产品编号“P003”的单价；在F3单元格用INDEX+MATCH查询产品编号“P005”的产品名称。</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>2022-11-01</t>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>产品编号</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>螺丝</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>螺母</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>0.3</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：从发票号中提取日期和金额</t>
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>垫片</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>0.2</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>要求：你有一批发票数据，发票号格式为“INV-20250315-1234”，其中包含日期（第5-12位）和最后4位数字（金额代码）。需要从发票号中提取日期，并处理错误情况。</t>
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>扳手</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>任务：在B2输入公式提取第一个发票号中间的日期部分（格式YYYYMMDD），在C2提取最后4位数字，并确保当发票号不是预定格式时显示“格式错误”。</t>
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>钳子</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>发票号</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>INV-20250315-1234</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>INV-20241231-5698</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>INV-20230618-9999</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -990,7 +1052,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：统计特定销售员的销售额总和</t>
+          <t>第 1 题：第1题：仓库重量汇总</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1063,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A7,"张三",B2:B7)</f>
+        <f>SUMIF(A2:A6,"苹果",B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -1015,7 +1077,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：根据商品编号查找单价并计算总价</t>
+          <t>第 2 题：第2题：订单数量计数</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1088,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>VLOOKUP(A7,$A$2:$B$4,2,FALSE)  ,  在G7输入 =F7*B7</f>
+        <f>COUNTIF(B2:B6,"已发货")</f>
         <v/>
       </c>
     </row>
@@ -1040,7 +1102,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：统计迟到次数和早退次数</t>
+          <t>第 3 题：第3题：多条件筛选汇总</t>
         </is>
       </c>
     </row>
@@ -1050,9 +1112,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2">
-        <f>COUNTIF(B2:B8,"迟到")  ,  =COUNTIFS(A2:A8,"张三",B2:B8,"迟到")</f>
-        <v/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>F2：=SUMIFS(C2:C6,A2:A6,"上海",B2:B6,"北京")；F3：=COUNTIFS(A2:A6,"上海",B2:B6,"北京")</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1065,7 +1128,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：计算员工工龄（月数）和精确工龄（年+月）</t>
+          <t>第 4 题：第4题：到港天数与错误处理</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1139,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>DATEDIF(B2,TODAY(),"m")  ,  =DATEDIF(B2,TODAY(),"y")&amp;"年"&amp;DATEDIF(B2,TODAY(),"ym")&amp;"个月"</f>
+        <f>IFERROR(IF(DATEDIF(TODAY(),B2,"d")&gt;=0,DATEDIF(TODAY(),B2,"d"),"已到港"),"已到港")</f>
         <v/>
       </c>
     </row>
@@ -1090,7 +1153,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：从发票号中提取日期和金额</t>
+          <t>第 5 题：第5题：产品价格查询与灵活匹配</t>
         </is>
       </c>
     </row>
@@ -1100,9 +1163,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2">
-        <f>MID(A2,5,8)  ,  =IFERROR(RIGHT(A2,4),"格式错误")</f>
-        <v/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>F2：=VLOOKUP("P003",A2:C6,3,FALSE)；F3：=INDEX(B2:B6,MATCH("P005",A2:A6,0))</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1133,7 +1197,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：统计特定销售员的销售额总和</t>
+          <t>第 1 题：第1题：仓库重量汇总</t>
         </is>
       </c>
     </row>
@@ -1145,14 +1209,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF函数用于按条件求和，语法为SUMIF(条件区域,条件,求和区域)。本例中，条件区域是A2:A7（销售员列），条件是“张三”，求和区域是B2:B7（销售额列）。函数会遍历销售员列，凡等于“张三”的行，对应销售额相加。现在张三的销售额为1500+1800+1200=4500。</t>
+          <t>SUMIF函数用于按条件求和，语法为：SUMIF(条件区域, 条件, 求和区域)。这里条件区域是A2:A6，条件是“苹果”，求和区域是B2:B6，表示只把A列等于苹果的对应B列重量相加。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：根据商品编号查找单价并计算总价</t>
+          <t>第 2 题：第2题：订单数量计数</t>
         </is>
       </c>
     </row>
@@ -1164,14 +1228,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP语法为VLOOKUP(查找值,表格区域,返回列号,精确匹配)。其中A7是A02，查找区域是$A$2:$B$4（单价表），返回第2列单价，FALSE表示精确匹配。得到单价25后，乘以数量3得总价75。</t>
+          <t>COUNTIF函数用于按条件计数，语法为：COUNTIF(条件区域, 条件)。这里统计B2:B6区域中等于“已发货”的单元格个数。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：统计迟到次数和早退次数</t>
+          <t>第 3 题：第3题：多条件筛选汇总</t>
         </is>
       </c>
     </row>
@@ -1183,14 +1247,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF用于单条件计数，统计B列中等于“迟到”的个数，结果为2。COUNTIFS支持多条件，语法为COUNTIFS(条件区域1,条件1,条件区域2,条件2)。这里条件1是员工列A2:A8中“张三”，条件2是状态列中“迟到”，满足两条件的行数为2。</t>
+          <t>SUMIFS用于多条件求和，语法为：SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。COUNTIFS用于多条件计数，语法类似。这里同时限制出发地和目的地两个条件。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：计算员工工龄（月数）和精确工龄（年+月）</t>
+          <t>第 4 题：第4题：到港天数与错误处理</t>
         </is>
       </c>
     </row>
@@ -1202,14 +1266,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF计算两个日期差，语法：DATEDIF(开始日期,结束日期,单位)。单位“m”返回整月数，“y”返回整年数，“ym”返回扣除整年后的剩余月数。张三从2020-1-15到2025-3-20共62个月，年数5年（2020-2025），剩余2个月（因为3月比1月多2个月），所以结果为“5年2个月”。注意：TODAY()会随当天日期变化，但答案基于2025/3/20。</t>
+          <t>DATEDIF(start_date,end_date,"d")计算两个日期之间的天数；TODAY()返回今天日期。如果B2日期早于今天，DATEDIF会返回错误或负数，所以用IF判断是否大于等于0，再用IFERROR兜底，空日期或错误时显示“已到港”。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：从发票号中提取日期和金额</t>
+          <t>第 5 题：第5题：产品价格查询与灵活匹配</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1285,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MID函数提取文本中间部分，语法MID(文本,起始位置,长度)。发票号第5位开始是8位日期，所以=MID(A2,5,8)得到“20250315”。RIGHT函数提取右侧字符，=RIGHT(A2,4)得到“1234”。但为了防错，用IFERROR包裹，若提取出错（如长度不足）则显示“格式错误”。这里所有数据格式合法，所以直接提取成功。</t>
+          <t>VLOOKUP语法为：VLOOKUP(查找值, 表格区域, 返回列号, 精确匹配)。这里在A2:C6中查找P003，返回第3列单价。INDEX+MATCH更灵活：MATCH找到P005在A2:A6中的位置，INDEX再按该位置从B2:B6返回产品名称。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库重量汇总</t>
+          <t>第 1 题：第1题：仓库入库重量汇总（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -490,87 +490,107 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是仓库文员，需要按商品名称汇总入库重量。请根据A列商品名称和B列重量，在E2单元格计算“苹果”的总重量。</t>
+          <t>要求：你是仓库管理员，需要按「商品类别」汇总入库重量。请用 SUMIF 计算「日用品」的总重量。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在E2单元格输入公式，计算商品名称为“苹果”的重量总和。</t>
+          <t>任务：在空白单元格（例如 E2）输入公式，计算「商品类别」为“日用品”的入库重量合计。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>商品类别</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
           <t>商品名称</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>重量</t>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>入库重量</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>日用品</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
+          <t>抽纸</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>香蕉</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
+          <t>饼干</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>日用品</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
+          <t>洗衣液</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>橙子</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>90</t>
-        </is>
+          <t>电风扇</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>苹果</t>
+          <t>日用品</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
+          <t>牙膏</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -583,449 +603,664 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：订单数量计数</t>
+          <t>第 2 题：第2题：物流到港天数计算（TODAY、DATEDIF）</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIF</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>要求：物流台账中记录了每票货物的到港日期。请计算每票货物从到港日到今天已经过去的天数。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>要求：你是电商客服，需要统计“已发货”状态的订单数量。请根据A列订单状态，在D2单元格计算已发货订单数。</t>
+          <t>任务：在 C2 输入公式并向下填充，计算 B2 到港日期距离今天的天数。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>任务：在D2单元格输入公式，统计状态为“已发货”的订单数量。</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>运单号</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YD001</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>YD002</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>已发货</t>
+          <t>2024-05-10</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>YD003</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：订单金额判断与错误处理（IF、IFERROR）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>要求：销售表中记录了订单金额。若金额大于等于 1000 元标记为“大单”，否则标记为“普通单”；如果金额不是数字或无法计算，则显示“待核对”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 C2 输入公式并向下填充，根据 B2 的订单金额判断订单类型；若出错则返回“待核对”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>订单金额</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
           <t>A002</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>待发货</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="B27" s="4" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>A003</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>已发货</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>A004</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>已取消</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>A005</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>已发货</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：多条件筛选汇总</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是物流调度员，需要统计“上海”发往“北京”的运费总额，以及这种线路的订单笔数。请根据A列出发地、B列目的地、C列运费，在F2和F3分别计算。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>任务：在F2单元格计算出发地为“上海”且目的地为“北京”的运费总额；在F3单元格计算同样条件的订单笔数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>出发地</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>目的地</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>运费</t>
-        </is>
+      <c r="B28" s="4" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>A004</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>120</t>
+          <t>缺失</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>150</t>
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>200</t>
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：快递数量统计与最大值（COUNTIF、MAX）</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>80</t>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>要求：快递站点记录了各快递员当日派件量。请统计派件量大于等于 80 的人数，并找出最高派件量。</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 E2 统计派件量大于等于 80 的人数；在 E3 找出最高派件量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>快递员</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>派件量</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：到港天数与错误处理</t>
-        </is>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是外贸跟单员，需要根据预计到港日期计算距离今天还有多少天。如果日期已过或为空，则显示“已到港”。请根据A列订单号、B列预计到港日期，在D2向下填充公式。</t>
-        </is>
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>任务：在D2单元格输入公式，计算B2距离今天的天数；如果B2为空或日期已过，则显示“已到港”。公式需能向下填充。</t>
-        </is>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>88</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>预计到港日期</t>
-        </is>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>PO001</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
+          <t>钱七</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>PO002</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>PO003</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr"/>
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>PO004</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>2025-08-15</t>
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：商品单价查询（XLOOKUP 或 VLOOKUP、INDEX、MATCH）</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>要求：价格表中列出了商品编号和单价。请根据给定的商品编号查询对应单价。可以用 XLOOKUP，也可以用 VLOOKUP，或用 INDEX+MATCH。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 E2 输入商品编号“P003”，在 F2 输入公式查询该商品单价。</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：产品价格查询与灵活匹配</t>
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>商品编号</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>单价</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>要求：你是采购助理，需要根据产品编号查询单价。请根据A列产品编号、B列产品名称、C列单价，在F2用VLOOKUP查询编号“P003”的单价；在F3用INDEX+MATCH查询编号“P005”的产品名称。</t>
-        </is>
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>抽纸</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>12.5</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>任务：在F2单元格用VLOOKUP查询产品编号“P003”的单价；在F3单元格用INDEX+MATCH查询产品编号“P005”的产品名称。</t>
-        </is>
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>洗衣液</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>产品编号</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>产品名称</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
-        </is>
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>饼干</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>P001</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>螺丝</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+          <t>电风扇</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>199</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>P002</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>螺母</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>P003</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>垫片</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>0.2</t>
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>P004</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>扳手</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>第 6 题：第6题：重量区间汇总与四舍五入（SUMIFS、ROUND）</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>P005</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>钳子</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>25</t>
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>要求：称重台账记录了不同仓库、不同品类的重量。请汇总“上海仓”且“水果”的总重量，并将结果保留 1 位小数。</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>任务：在空白单元格（例如 E2）输入公式，汇总“上海仓”且“水果”的重量，并四舍五入保留 1 位小数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>仓库</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>品类</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>重量</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>水果</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>12.36</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>北京仓</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>水果</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>蔬菜</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>上海仓</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>水果</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>7.84</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>广州仓</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>水果</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>第 7 题：第7题：多条件计数（COUNTIFS）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIFS</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>要求：客服工单表中记录了工单状态和优先级。请统计状态为“已完成”且优先级为“高”的工单数量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>任务：在空白单元格（例如 E2）输入公式，统计状态为“已完成”且优先级为“高”的工单数量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>工单号</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>T001</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>T002</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>处理中</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>T003</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>T004</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>T005</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>已取消</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>第 8 题：第8题：提取商品编码（RIGHT、MID）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>要求：商品编码规则为：前 2 位是仓库代码，中间 3 位是品类代码，最后 4 位是流水号。请从编码中提取品类代码。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>任务：在 B2 输入公式并向下填充，从 A2 的商品编码中提取中间 3 位品类代码。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>商品编码</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>SH0012024</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>BJ0022024</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>GZ0032025</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1042,7 +1277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1052,7 +1287,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库重量汇总</t>
+          <t>第 1 题：第1题：仓库入库重量汇总（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1298,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"苹果",B2:B6)</f>
+        <f>SUMIF(A2:A6,"日用品",C2:C6)</f>
         <v/>
       </c>
     </row>
@@ -1077,7 +1312,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：订单数量计数</t>
+          <t>第 2 题：第2题：物流到港天数计算（TODAY、DATEDIF）</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1323,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF(B2:B6,"已发货")</f>
+        <f>DATEDIF(B2,TODAY(),"d")</f>
         <v/>
       </c>
     </row>
@@ -1102,7 +1337,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：多条件筛选汇总</t>
+          <t>第 3 题：第3题：订单金额判断与错误处理（IF、IFERROR）</t>
         </is>
       </c>
     </row>
@@ -1112,10 +1347,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>F2：=SUMIFS(C2:C6,A2:A6,"上海",B2:B6,"北京")；F3：=COUNTIFS(A2:A6,"上海",B2:B6,"北京")</t>
-        </is>
+      <c r="B10" s="2">
+        <f>IFERROR(IF(B2&gt;=1000,"大单","普通单"),"待核对")</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1128,7 +1362,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：到港天数与错误处理</t>
+          <t>第 4 题：第4题：快递数量统计与最大值（COUNTIF、MAX）</t>
         </is>
       </c>
     </row>
@@ -1138,9 +1372,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <f>IFERROR(IF(DATEDIF(TODAY(),B2,"d")&gt;=0,DATEDIF(TODAY(),B2,"d"),"已到港"),"已到港")</f>
-        <v/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>E2：=COUNTIF(B2:B6,"&gt;=80")；E3：=MAX(B2:B6)</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1153,7 +1388,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：产品价格查询与灵活匹配</t>
+          <t>第 5 题：第5题：商品单价查询（XLOOKUP 或 VLOOKUP、INDEX、MATCH）</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1400,87 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>F2：=VLOOKUP("P003",A2:C6,3,FALSE)；F3：=INDEX(B2:B6,MATCH("P005",A2:A6,0))</t>
+          <t>F2：=XLOOKUP(E2,A2:A5,C2:C5)；或 =VLOOKUP(E2,A2:C5,3,FALSE)；或 =INDEX(C2:C5,MATCH(E2,A2:A5,0))</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
+        <is>
+          <t>（可直接复制公式到题目文件对应单元格验证）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>第 6 题：第6题：重量区间汇总与四舍五入（SUMIFS、ROUND）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>答案：</t>
+        </is>
+      </c>
+      <c r="B22" s="2">
+        <f>ROUND(SUMIFS(C2:C6,A2:A6,"上海仓",B2:B6,"水果"),1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>（可直接复制公式到题目文件对应单元格验证）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>第 7 题：第7题：多条件计数（COUNTIFS）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>答案：</t>
+        </is>
+      </c>
+      <c r="B26" s="2">
+        <f>COUNTIFS(B2:B6,"已完成",C2:C6,"高")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>（可直接复制公式到题目文件对应单元格验证）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>第 8 题：第8题：提取商品编码（RIGHT、MID）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>答案：</t>
+        </is>
+      </c>
+      <c r="B30" s="2">
+        <f>MID(A2,3,3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>（可直接复制公式到题目文件对应单元格验证）</t>
         </is>
@@ -1187,7 +1497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1197,7 +1507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库重量汇总</t>
+          <t>第 1 题：第1题：仓库入库重量汇总（SUMIF）</t>
         </is>
       </c>
     </row>
@@ -1209,14 +1519,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF函数用于按条件求和，语法为：SUMIF(条件区域, 条件, 求和区域)。这里条件区域是A2:A6，条件是“苹果”，求和区域是B2:B6，表示只把A列等于苹果的对应B列重量相加。</t>
+          <t>SUMIF 语法：SUMIF(条件区域,条件,求和区域)。这里条件区域是 A2:A6 的商品类别，条件是“日用品”，求和区域是 C2:C6 的入库重量。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：订单数量计数</t>
+          <t>第 2 题：第2题：物流到港天数计算（TODAY、DATEDIF）</t>
         </is>
       </c>
     </row>
@@ -1228,14 +1538,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF函数用于按条件计数，语法为：COUNTIF(条件区域, 条件)。这里统计B2:B6区域中等于“已发货”的单元格个数。</t>
+          <t>TODAY() 返回当天日期；DATEDIF(开始日期,结束日期,"d") 计算两个日期之间相差的完整天数。这里开始日期是 B2，结束日期是 TODAY()，单位用 "d" 表示天。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：多条件筛选汇总</t>
+          <t>第 3 题：第3题：订单金额判断与错误处理（IF、IFERROR）</t>
         </is>
       </c>
     </row>
@@ -1247,14 +1557,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS用于多条件求和，语法为：SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)。COUNTIFS用于多条件计数，语法类似。这里同时限制出发地和目的地两个条件。</t>
+          <t>IF(条件,真值,假值) 用于条件判断；IFERROR(表达式,出错时返回的值) 用于捕获公式错误。先判断 B2 是否大于等于 1000，再用 IFERROR 包裹，遇到“缺失”等无法比较的情况时显示“待核对”。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：到港天数与错误处理</t>
+          <t>第 4 题：第4题：快递数量统计与最大值（COUNTIF、MAX）</t>
         </is>
       </c>
     </row>
@@ -1266,14 +1576,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>DATEDIF(start_date,end_date,"d")计算两个日期之间的天数；TODAY()返回今天日期。如果B2日期早于今天，DATEDIF会返回错误或负数，所以用IF判断是否大于等于0，再用IFERROR兜底，空日期或错误时显示“已到港”。</t>
+          <t>COUNTIF(区域,条件) 统计满足条件的单元格个数，条件写 "&gt;=80" 表示大于等于 80。MAX(区域) 返回区域中的最大值。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：产品价格查询与灵活匹配</t>
+          <t>第 5 题：第5题：商品单价查询（XLOOKUP 或 VLOOKUP、INDEX、MATCH）</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1595,64 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>VLOOKUP语法为：VLOOKUP(查找值, 表格区域, 返回列号, 精确匹配)。这里在A2:C6中查找P003，返回第3列单价。INDEX+MATCH更灵活：MATCH找到P005在A2:A6中的位置，INDEX再按该位置从B2:B6返回产品名称。</t>
+          <t>XLOOKUP(查找值,查找区域,返回区域) 可直接按商品编号返回单价。VLOOKUP(查找值,表格区域,返回第几列,FALSE) 中 3 表示返回第 3 列单价，FALSE 表示精确匹配。INDEX+MATCH 中 MATCH 找位置，INDEX 按位置取值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>第 6 题：第6题：重量区间汇总与四舍五入（SUMIFS、ROUND）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>讲解：</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SUMIFS(求和区域,条件区域1,条件1,条件区域2,条件2) 可进行多条件求和。ROUND(数值,小数位数) 用于四舍五入，这里保留 1 位小数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>第 7 题：第7题：多条件计数（COUNTIFS）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>讲解：</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>COUNTIFS(条件区域1,条件1,条件区域2,条件2) 用于多条件计数。这里统计 B 列状态为“已完成”且 C 列优先级为“高”的行数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>第 8 题：第8题：提取商品编码（RIGHT、MID）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>讲解：</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>MID(文本,开始位置,提取长度) 从文本指定位置开始提取指定长度。这里从第 3 位开始提取 3 位，即中间的品类代码。也可理解为前 2 位仓库代码之后、后 4 位流水号之前的部分。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C83"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库入库重量汇总（SUMIF）</t>
+          <t>第 1 题：第1题：用 SUMIF 汇总某客户的发货重量</t>
         </is>
       </c>
     </row>
@@ -490,107 +490,117 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你是仓库管理员，需要按「商品类别」汇总入库重量。请用 SUMIF 计算「日用品」的总重量。</t>
+          <t>要求：你在一家物流公司做客服，手头有一张发货台账。需要快速算出「客户A」的总发货重量，方便回复客户对账。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：在空白单元格（例如 E2）输入公式，计算「商品类别」为“日用品”的入库重量合计。</t>
+          <t>任务：请在 G2 单元格输入公式，计算「客户A」的发货总重量。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>商品类别</t>
+          <t>客户</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>商品名称</t>
+          <t>货物</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>入库重量</t>
+          <t>重量(kg)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>日用品</t>
+          <t>客户A</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>抽纸</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>12</v>
+          <t>纸箱</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>客户B</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>饼干</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>8</v>
+          <t>木箱</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>日用品</t>
+          <t>客户A</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>洗衣液</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>20</v>
+          <t>托盘</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>客户C</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>电风扇</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>6</v>
+          <t>纸箱</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>日用品</t>
+          <t>客户A</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>牙膏</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>5</v>
+          <t>木箱</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -603,664 +613,492 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：物流到港天数计算（TODAY、DATEDIF）</t>
+          <t>第 2 题：第2题：用 COUNTIF 统计“已签收”的运单数量</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>要求：物流台账中记录了每票货物的到港日期。请计算每票货物从到港日到今天已经过去的天数。</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>练习函数：COUNTIF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>任务：在 C2 输入公式并向下填充，计算 B2 到港日期距离今天的天数。</t>
+          <t>要求：物流客服每天要统计当天运单里已经签收的数量，用来汇报进度。表格里记录了每张运单的状态。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 G2 单元格输入公式，统计「状态」为「已签收」的运单数量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>运单号</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>YD001</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>城市</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>YD002</t>
+          <t>YD001</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>YD002</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>运输中</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t>YD003</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>2024-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>YD004</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>YD005</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>派送中</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：订单金额判断与错误处理（IF、IFERROR）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>要求：销售表中记录了订单金额。若金额大于等于 1000 元标记为“大单”，否则标记为“普通单”；如果金额不是数字或无法计算，则显示“待核对”。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 C2 输入公式并向下填充，根据 B2 的订单金额判断订单类型；若出错则返回“待核对”。</t>
-        </is>
-      </c>
-    </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>订单金额</t>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：用 SUMIFS + COUNTIFS 汇总“上海”且“已签收”的重量与单量</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>A001</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>1200</v>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>要求：主管要你按城市和状态做一个小统计：既要算「上海 + 已签收」的总重量，也要算「上海 + 已签收」的运单数量。这需要用多条件求和与多条件计数。</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>A002</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>300</v>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 G2 输入公式算「上海且已签收」的总重量；在 G3 输入公式算「上海且已签收」的运单数量。</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>A003</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>1000</v>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>运单号</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>A004</t>
+          <t>YD001</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>YD002</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>运输中</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>YD003</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>YD004</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>YD005</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>派送中</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：快递数量统计与最大值（COUNTIF、MAX）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>要求：快递站点记录了各快递员当日派件量。请统计派件量大于等于 80 的人数，并找出最高派件量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 E2 统计派件量大于等于 80 的人数；在 E3 找出最高派件量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>快递员</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>派件量</t>
-        </is>
-      </c>
-    </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="n">
-        <v>95</v>
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：用 TODAY + DATEDIF 计算在库天数，并用 IFERROR 兜底</t>
+        </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="n">
-        <v>78</v>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>要求：仓库台账里记录了入库日期。你想知道每批货到现在已经放了多少天，还要避免空日期或错误日期导致显示错误。</t>
+        </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>88</v>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 C2 单元格输入公式，计算 A01 批次从入库到今天的天数；然后向下填充到 C5。遇到空日期时不要显示错误，而是显示「待补录」。</t>
+        </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>80</v>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>批次</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>入库日期</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>钱七</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>60</v>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>A02</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>A03</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>A04</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：商品单价查询（XLOOKUP 或 VLOOKUP、INDEX、MATCH）</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>要求：价格表中列出了商品编号和单价。请根据给定的商品编号查询对应单价。可以用 XLOOKUP，也可以用 VLOOKUP，或用 INDEX+MATCH。</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 E2 输入商品编号“P003”，在 F2 输入公式查询该商品单价。</t>
-        </is>
-      </c>
-    </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>商品编号</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>商品名称</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>单价</t>
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：用 XLOOKUP / VLOOKUP + INDEX + MATCH 做到港信息查表</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>P001</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>抽纸</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>12.5</v>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>要求：国际物流场景：你有一张到港信息表，包含船名、到港日期、重量。现在要根据船名查出重量，并计算最大重量以及保留一位小数的结果。</t>
+        </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>P002</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>洗衣液</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>35</v>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>任务：请在 G2 输入 XLOOKUP 公式，根据 G1 中的船名「Ocean3」查出对应重量；在 G3 输入 VLOOKUP 公式实现同样查询；在 G4 用 INDEX+MATCH 实现同样查询；在 G5 用 MAX 求最大重量；在 G6 用 ROUND 把 G2 结果保留一位小数。</t>
+        </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>P003</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>饼干</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>8.800000000000001</v>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>船名</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>到港日期</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>Ocean1</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>电风扇</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>199</v>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>1200.456</t>
+        </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Ocean2</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>980.789</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Ocean3</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>1500.123</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>第 6 题：第6题：重量区间汇总与四舍五入（SUMIFS、ROUND）</t>
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Ocean4</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>760.5</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>要求：称重台账记录了不同仓库、不同品类的重量。请汇总“上海仓”且“水果”的总重量，并将结果保留 1 位小数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>任务：在空白单元格（例如 E2）输入公式，汇总“上海仓”且“水果”的重量，并四舍五入保留 1 位小数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>仓库</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>品类</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>重量</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>水果</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>12.36</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>北京仓</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>水果</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>蔬菜</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>上海仓</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>水果</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="n">
-        <v>7.84</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>广州仓</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>水果</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="n">
-        <v>9.1</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr">
-        <is>
-          <t>第 7 题：第7题：多条件计数（COUNTIFS）</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIFS</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>要求：客服工单表中记录了工单状态和优先级。请统计状态为“已完成”且优先级为“高”的工单数量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>任务：在空白单元格（例如 E2）输入公式，统计状态为“已完成”且优先级为“高”的工单数量。</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>工单号</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>优先级</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>T001</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>T002</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>处理中</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>T003</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>T004</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>T005</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>已取消</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="inlineStr">
-        <is>
-          <t>第 8 题：第8题：提取商品编码（RIGHT、MID）</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>要求：商品编码规则为：前 2 位是仓库代码，中间 3 位是品类代码，最后 4 位是流水号。请从编码中提取品类代码。</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>任务：在 B2 输入公式并向下填充，从 A2 的商品编码中提取中间 3 位品类代码。</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>商品编码</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>SH0012024</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>BJ0022024</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>GZ0032025</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1277,7 +1115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1287,7 +1125,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库入库重量汇总（SUMIF）</t>
+          <t>第 1 题：第1题：用 SUMIF 汇总某客户的发货重量</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1136,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"日用品",C2:C6)</f>
+        <f>SUMIF(A2:A6,"客户A",C2:C6)</f>
         <v/>
       </c>
     </row>
@@ -1312,7 +1150,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：物流到港天数计算（TODAY、DATEDIF）</t>
+          <t>第 2 题：第2题：用 COUNTIF 统计“已签收”的运单数量</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1161,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>DATEDIF(B2,TODAY(),"d")</f>
+        <f>COUNTIF(B2:B6,"已签收")</f>
         <v/>
       </c>
     </row>
@@ -1337,7 +1175,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：订单金额判断与错误处理（IF、IFERROR）</t>
+          <t>第 3 题：第3题：用 SUMIFS + COUNTIFS 汇总“上海”且“已签收”的重量与单量</t>
         </is>
       </c>
     </row>
@@ -1347,9 +1185,10 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2">
-        <f>IFERROR(IF(B2&gt;=1000,"大单","普通单"),"待核对")</f>
-        <v/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>G2：=SUMIFS(D2:D6,C2:C6,"上海",B2:B6,"已签收")；G3：=COUNTIFS(C2:C6,"上海",B2:B6,"已签收")</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1362,7 +1201,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：快递数量统计与最大值（COUNTIF、MAX）</t>
+          <t>第 4 题：第4题：用 TODAY + DATEDIF 计算在库天数，并用 IFERROR 兜底</t>
         </is>
       </c>
     </row>
@@ -1372,10 +1211,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>E2：=COUNTIF(B2:B6,"&gt;=80")；E3：=MAX(B2:B6)</t>
-        </is>
+      <c r="B14" s="2">
+        <f>IFERROR(DATEDIF(B2,TODAY(),"d"),"待补录")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1388,7 +1226,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：商品单价查询（XLOOKUP 或 VLOOKUP、INDEX、MATCH）</t>
+          <t>第 5 题：第5题：用 XLOOKUP / VLOOKUP + INDEX + MATCH 做到港信息查表</t>
         </is>
       </c>
     </row>
@@ -1400,87 +1238,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>F2：=XLOOKUP(E2,A2:A5,C2:C5)；或 =VLOOKUP(E2,A2:C5,3,FALSE)；或 =INDEX(C2:C5,MATCH(E2,A2:A5,0))</t>
+          <t>G2：=XLOOKUP(G1,A2:A5,C2:C5)；G3：=VLOOKUP(G1,A2:C5,3,FALSE)；G4：=INDEX(C2:C5,MATCH(G1,A2:A5,0))；G5：=MAX(C2:C5)；G6：=ROUND(G2,1)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
-        <is>
-          <t>（可直接复制公式到题目文件对应单元格验证）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>第 6 题：第6题：重量区间汇总与四舍五入（SUMIFS、ROUND）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>答案：</t>
-        </is>
-      </c>
-      <c r="B22" s="2">
-        <f>ROUND(SUMIFS(C2:C6,A2:A6,"上海仓",B2:B6,"水果"),1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>（可直接复制公式到题目文件对应单元格验证）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>第 7 题：第7题：多条件计数（COUNTIFS）</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>答案：</t>
-        </is>
-      </c>
-      <c r="B26" s="2">
-        <f>COUNTIFS(B2:B6,"已完成",C2:C6,"高")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>（可直接复制公式到题目文件对应单元格验证）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>第 8 题：第8题：提取商品编码（RIGHT、MID）</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>答案：</t>
-        </is>
-      </c>
-      <c r="B30" s="2">
-        <f>MID(A2,3,3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
         <is>
           <t>（可直接复制公式到题目文件对应单元格验证）</t>
         </is>
@@ -1497,7 +1260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1507,7 +1270,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：仓库入库重量汇总（SUMIF）</t>
+          <t>第 1 题：第1题：用 SUMIF 汇总某客户的发货重量</t>
         </is>
       </c>
     </row>
@@ -1519,14 +1282,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 语法：SUMIF(条件区域,条件,求和区域)。这里条件区域是 A2:A6 的商品类别，条件是“日用品”，求和区域是 C2:C6 的入库重量。</t>
+          <t>SUMIF 用于按一个条件求和，语法是 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是客户列 A2:A6，条件是「客户A」，求和区域是重量列 C2:C6。它会找出所有客户A所在的行，并把对应重量相加，结果为 120+200+30=350。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：物流到港天数计算（TODAY、DATEDIF）</t>
+          <t>第 2 题：第2题：用 COUNTIF 统计“已签收”的运单数量</t>
         </is>
       </c>
     </row>
@@ -1538,14 +1301,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TODAY() 返回当天日期；DATEDIF(开始日期,结束日期,"d") 计算两个日期之间相差的完整天数。这里开始日期是 B2，结束日期是 TODAY()，单位用 "d" 表示天。</t>
+          <t>COUNTIF 用于按条件计数，语法是 COUNTIF(条件区域, 条件)。这里统计 B2:B6 中等于「已签收」的单元格个数，结果是 3。注意：条件里的文字通常要用英文双引号括起来。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：订单金额判断与错误处理（IF、IFERROR）</t>
+          <t>第 3 题：第3题：用 SUMIFS + COUNTIFS 汇总“上海”且“已签收”的重量与单量</t>
         </is>
       </c>
     </row>
@@ -1557,14 +1320,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>IF(条件,真值,假值) 用于条件判断；IFERROR(表达式,出错时返回的值) 用于捕获公式错误。先判断 B2 是否大于等于 1000，再用 IFERROR 包裹，遇到“缺失”等无法比较的情况时显示“待核对”。</t>
+          <t>SUMIFS 是多条件求和，语法是 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)，注意求和区域在最前面。COUNTIFS 是多条件计数，语法是 COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2...)。本题要求城市=上海且状态=已签收，所以重量为 12+20=32，单量为 2。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：快递数量统计与最大值（COUNTIF、MAX）</t>
+          <t>第 4 题：第4题：用 TODAY + DATEDIF 计算在库天数，并用 IFERROR 兜底</t>
         </is>
       </c>
     </row>
@@ -1576,14 +1339,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF(区域,条件) 统计满足条件的单元格个数，条件写 "&gt;=80" 表示大于等于 80。MAX(区域) 返回区域中的最大值。</t>
+          <t>TODAY() 返回今天的日期；DATEDIF(开始日期, 结束日期, "d") 返回两个日期之间的整天数，这里的 "d" 表示按天计算。IFERROR(公式, 出错时的值) 用来在公式报错时显示替代内容。B3 是空日期，DATEDIF 会出错，因此用 IFERROR 把它显示为「待补录」。实际天数会随当天日期变化。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：商品单价查询（XLOOKUP 或 VLOOKUP、INDEX、MATCH）</t>
+          <t>第 5 题：第5题：用 XLOOKUP / VLOOKUP + INDEX + MATCH 做到港信息查表</t>
         </is>
       </c>
     </row>
@@ -1595,64 +1358,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP(查找值,查找区域,返回区域) 可直接按商品编号返回单价。VLOOKUP(查找值,表格区域,返回第几列,FALSE) 中 3 表示返回第 3 列单价，FALSE 表示精确匹配。INDEX+MATCH 中 MATCH 找位置，INDEX 按位置取值。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>第 6 题：第6题：重量区间汇总与四舍五入（SUMIFS、ROUND）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>讲解：</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>SUMIFS(求和区域,条件区域1,条件1,条件区域2,条件2) 可进行多条件求和。ROUND(数值,小数位数) 用于四舍五入，这里保留 1 位小数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>第 7 题：第7题：多条件计数（COUNTIFS）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>讲解：</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>COUNTIFS(条件区域1,条件1,条件区域2,条件2) 用于多条件计数。这里统计 B 列状态为“已完成”且 C 列优先级为“高”的行数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>第 8 题：第8题：提取商品编码（RIGHT、MID）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>讲解：</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>MID(文本,开始位置,提取长度) 从文本指定位置开始提取指定长度。这里从第 3 位开始提取 3 位，即中间的品类代码。也可理解为前 2 位仓库代码之后、后 4 位流水号之前的部分。</t>
+          <t>XLOOKUP(查找值, 查找区域, 返回区域) 是最新查表函数，默认精确匹配，写法简单。VLOOKUP(查找值, 表格区域, 返回第几列, FALSE) 是经典查表函数，FALSE 表示精确匹配；这里返回区域第3列是重量。INDEX(返回区域, 行号) + MATCH(查找值, 查找区域, 0) 是先定位行号再取值，0 表示精确匹配。MAX(区域) 求最大值。ROUND(数值, 1) 表示保留一位小数。Ocean3 的重量约为 1500.123，保留一位小数为 1500.1，最大重量为 1500.123。</t>
         </is>
       </c>
     </row>

--- a/excel/latest.xlsx
+++ b/excel/latest.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：用 SUMIF 汇总某客户的发货重量</t>
+          <t>第 1 题：第1题：物流台账重量汇总</t>
         </is>
       </c>
     </row>
@@ -490,29 +490,24 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>要求：你在一家物流公司做客服，手头有一张发货台账。需要快速算出「客户A」的总发货重量，方便回复客户对账。</t>
+          <t>要求：你是一家物流公司的文员，现有一份到货台账，需要按货物类型汇总重量。请用 SUMIF 函数统计「电子产品」的总重量。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>任务：请在 G2 单元格输入公式，计算「客户A」的发货总重量。</t>
+          <t>任务：假设数据在 A1:B6，请在 D2 单元格输入公式，计算「电子产品」的总重量。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>客户</t>
+          <t>货物类型</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>货物</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>重量(kg)</t>
         </is>
@@ -521,86 +516,51 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>客户A</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>纸箱</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
+          <t>电子产品</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>客户B</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>木箱</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+          <t>日用品</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>客户A</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>托盘</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+          <t>电子产品</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>客户C</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>纸箱</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>客户A</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>木箱</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+          <t>电子产品</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -613,492 +573,412 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：用 COUNTIF 统计“已签收”的运单数量</t>
+          <t>第 2 题：第2题：到港台账计数与最大重量</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>练习函数：COUNTIF</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>要求：你负责港口到港记录，需要统计「已到港」的批次数，并找出所有货物中的最大重量。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>要求：物流客服每天要统计当天运单里已经签收的数量，用来汇报进度。表格里记录了每张运单的状态。</t>
+          <t>任务：假设数据在 A1:C5，请在 E2 单元格统计「已到港」的批次数，在 E3 单元格找出最大重量。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 G2 单元格输入公式，统计「状态」为「已签收」的运单数量。</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>批次号</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>运单号</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>城市</t>
-        </is>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>B001</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>已到港</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>YD001</t>
+          <t>B002</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>已签收</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
+          <t>未到港</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>320</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>YD002</t>
+          <t>B003</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>运输中</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
+          <t>已到港</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>760</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>YD003</t>
+          <t>B004</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>已签收</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
+          <t>已到港</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>YD004</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>已签收</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>YD005</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>派送中</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>深圳</t>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>第 3 题：第3题：多条件重量汇总与四舍五入</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>要求：你有一份仓库入库明细，需要统计「华东仓」且「食品」的总重量，并将结果四舍五入保留 1 位小数。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>第 3 题：第3题：用 SUMIFS + COUNTIFS 汇总“上海”且“已签收”的重量与单量</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>任务：假设数据在 A1:C6，请在 E2 单元格统计「华东仓」且「食品」的总重量，并四舍五入保留 1 位小数。</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>要求：主管要你按城市和状态做一个小统计：既要算「上海 + 已签收」的总重量，也要算「上海 + 已签收」的运单数量。这需要用多条件求和与多条件计数。</t>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>仓库</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>品类</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>重量(kg)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 G2 输入公式算「上海且已签收」的总重量；在 G3 输入公式算「上海且已签收」的运单数量。</t>
-        </is>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>华东仓</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>125.36</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>运单号</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>城市</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
-        </is>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>华北仓</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>200.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>YD001</t>
+          <t>华东仓</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>已签收</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+          <t>日用品</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>80.25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>YD002</t>
+          <t>华东仓</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>运输中</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>99.87</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>YD003</t>
+          <t>华南仓</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>已签收</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>150.4</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>YD004</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>已签收</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>YD005</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>派送中</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>第 4 题：第4题：入职天数与错误处理</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>要求：你是一名人事实习生，需要根据员工入职日期计算截至今天的在职天数；如果日期缺失或错误，则显示「日期有误」。</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>第 4 题：第4题：用 TODAY + DATEDIF 计算在库天数，并用 IFERROR 兜底</t>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>任务：假设数据在 A1:B5，请在 C2:C5 单元格输入公式，计算每位员工截至今天的入职天数，日期缺失时显示「日期有误」。</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>要求：仓库台账里记录了入库日期。你想知道每批货到现在已经放了多少天，还要避免空日期或错误日期导致显示错误。</t>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>入职日期</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 C2 单元格输入公式，计算 A01 批次从入库到今天的天数；然后向下填充到 C5。遇到空日期时不要显示错误，而是显示「待补录」。</t>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>2022-03-15</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>批次</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>入库日期</t>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>A01</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>2024-01-01</t>
-        </is>
-      </c>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>赵六</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2021-11-20</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>A03</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>A04</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>2024-03-10</t>
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>第 5 题：第5题：运单查询与双向匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>要求：你负责运单查询，需要根据运单号自动带出目的地和运费。先用 XLOOKUP 查目的地，再用 INDEX+MATCH 查运费。</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>第 5 题：第5题：用 XLOOKUP / VLOOKUP + INDEX + MATCH 做到港信息查表</t>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>任务：假设数据在 A1:C5，请在 E2 输入运单号「YD003」；在 F2 用 XLOOKUP 查目的地，在 G2 用 INDEX+MATCH 查运费。</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>要求：国际物流场景：你有一张到港信息表，包含船名、到港日期、重量。现在要根据船名查出重量，并计算最大重量以及保留一位小数的结果。</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>运单号</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>目的地</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>运费(元)</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>任务：请在 G2 输入 XLOOKUP 公式，根据 G1 中的船名「Ocean3」查出对应重量；在 G3 输入 VLOOKUP 公式实现同样查询；在 G4 用 INDEX+MATCH 实现同样查询；在 G5 用 MAX 求最大重量；在 G6 用 ROUND 把 G2 结果保留一位小数。</t>
-        </is>
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>YD001</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>船名</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>到港日期</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>重量(kg)</t>
-        </is>
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>YD002</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Ocean1</t>
+          <t>YD003</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>1200.456</t>
-        </is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Ocean2</t>
+          <t>YD004</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>980.789</t>
-        </is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>Ocean3</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-06</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>1500.123</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>Ocean4</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>2024-05-08</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>760.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>↓ 你的公式 / 答案（在下方单元格输入）：</t>
         </is>
@@ -1125,7 +1005,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：用 SUMIF 汇总某客户的发货重量</t>
+          <t>第 1 题：第1题：物流台账重量汇总</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1016,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIF(A2:A6,"客户A",C2:C6)</f>
+        <f>SUMIF(A2:A6,"电子产品",B2:B6)</f>
         <v/>
       </c>
     </row>
@@ -1150,7 +1030,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：用 COUNTIF 统计“已签收”的运单数量</t>
+          <t>第 2 题：第2题：到港台账计数与最大重量</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1041,7 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>COUNTIF(B2:B6,"已签收")</f>
+        <f>COUNTIF(B2:B5,"已到港")，=MAX(C2:C5)</f>
         <v/>
       </c>
     </row>
@@ -1175,7 +1055,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：用 SUMIFS + COUNTIFS 汇总“上海”且“已签收”的重量与单量</t>
+          <t>第 3 题：第3题：多条件重量汇总与四舍五入</t>
         </is>
       </c>
     </row>
@@ -1185,10 +1065,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>G2：=SUMIFS(D2:D6,C2:C6,"上海",B2:B6,"已签收")；G3：=COUNTIFS(C2:C6,"上海",B2:B6,"已签收")</t>
-        </is>
+      <c r="B10" s="2">
+        <f>ROUND(SUMIFS(C2:C6,A2:A6,"华东仓",B2:B6,"食品"),1)</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1201,7 +1080,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：用 TODAY + DATEDIF 计算在库天数，并用 IFERROR 兜底</t>
+          <t>第 4 题：第4题：入职天数与错误处理</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1091,7 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>IFERROR(DATEDIF(B2,TODAY(),"d"),"待补录")</f>
+        <f>IFERROR(DATEDIF(B2,TODAY(),"D"),"日期有误")</f>
         <v/>
       </c>
     </row>
@@ -1226,7 +1105,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用 XLOOKUP / VLOOKUP + INDEX + MATCH 做到港信息查表</t>
+          <t>第 5 题：第5题：运单查询与双向匹配</t>
         </is>
       </c>
     </row>
@@ -1236,10 +1115,9 @@
           <t>答案：</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>G2：=XLOOKUP(G1,A2:A5,C2:C5)；G3：=VLOOKUP(G1,A2:C5,3,FALSE)；G4：=INDEX(C2:C5,MATCH(G1,A2:A5,0))；G5：=MAX(C2:C5)；G6：=ROUND(G2,1)</t>
-        </is>
+      <c r="B18" s="2">
+        <f>XLOOKUP(E2,A2:A5,B2:B5)，=INDEX(C2:C5,MATCH(E2,A2:A5,0))</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1270,7 +1148,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第 1 题：第1题：用 SUMIF 汇总某客户的发货重量</t>
+          <t>第 1 题：第1题：物流台账重量汇总</t>
         </is>
       </c>
     </row>
@@ -1282,14 +1160,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SUMIF 用于按一个条件求和，语法是 SUMIF(条件区域, 条件, 求和区域)。这里条件区域是客户列 A2:A6，条件是「客户A」，求和区域是重量列 C2:C6。它会找出所有客户A所在的行，并把对应重量相加，结果为 120+200+30=350。</t>
+          <t>SUMIF 语法：=SUMIF(条件区域, 条件, 求和区域)。这里 A2:A6 是货物类型，条件是「电子产品」，B2:B6 是重量。结果应为 120+95+70=285。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>第 2 题：第2题：用 COUNTIF 统计“已签收”的运单数量</t>
+          <t>第 2 题：第2题：到港台账计数与最大重量</t>
         </is>
       </c>
     </row>
@@ -1301,14 +1179,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>COUNTIF 用于按条件计数，语法是 COUNTIF(条件区域, 条件)。这里统计 B2:B6 中等于「已签收」的单元格个数，结果是 3。注意：条件里的文字通常要用英文双引号括起来。</t>
+          <t>COUNTIF 语法：=COUNTIF(区域, 条件)，统计满足条件的单元格个数，E2 结果为 3。MAX 语法：=MAX(数值区域)，返回最大值，E3 结果为 760。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>第 3 题：第3题：用 SUMIFS + COUNTIFS 汇总“上海”且“已签收”的重量与单量</t>
+          <t>第 3 题：第3题：多条件重量汇总与四舍五入</t>
         </is>
       </c>
     </row>
@@ -1320,14 +1198,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SUMIFS 是多条件求和，语法是 SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2...)，注意求和区域在最前面。COUNTIFS 是多条件计数，语法是 COUNTIFS(条件区域1, 条件1, 条件区域2, 条件2...)。本题要求城市=上海且状态=已签收，所以重量为 12+20=32，单量为 2。</t>
+          <t>SUMIFS 语法：=SUMIFS(求和区域, 条件区域1, 条件1, 条件区域2, 条件2)。这里求 C2:C6，条件为 A 列「华东仓」且 B 列「食品」。ROUND 语法：=ROUND(数值, 小数位数)，将 225.23 四舍五入为 225.2。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>第 4 题：第4题：用 TODAY + DATEDIF 计算在库天数，并用 IFERROR 兜底</t>
+          <t>第 4 题：第4题：入职天数与错误处理</t>
         </is>
       </c>
     </row>
@@ -1339,14 +1217,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>TODAY() 返回今天的日期；DATEDIF(开始日期, 结束日期, "d") 返回两个日期之间的整天数，这里的 "d" 表示按天计算。IFERROR(公式, 出错时的值) 用来在公式报错时显示替代内容。B3 是空日期，DATEDIF 会出错，因此用 IFERROR 把它显示为「待补录」。实际天数会随当天日期变化。</t>
+          <t>DATEDIF 语法：=DATEDIF(开始日期, 结束日期, "D")，返回两个日期之间的天数。TODAY() 返回当天日期。IFERROR 语法：=IFERROR(值, 错误时显示内容)，当 B 列为空时 DATEDIF 出错，显示「日期有误」。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>第 5 题：第5题：用 XLOOKUP / VLOOKUP + INDEX + MATCH 做到港信息查表</t>
+          <t>第 5 题：第5题：运单查询与双向匹配</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1236,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XLOOKUP(查找值, 查找区域, 返回区域) 是最新查表函数，默认精确匹配，写法简单。VLOOKUP(查找值, 表格区域, 返回第几列, FALSE) 是经典查表函数，FALSE 表示精确匹配；这里返回区域第3列是重量。INDEX(返回区域, 行号) + MATCH(查找值, 查找区域, 0) 是先定位行号再取值，0 表示精确匹配。MAX(区域) 求最大值。ROUND(数值, 1) 表示保留一位小数。Ocean3 的重量约为 1500.123，保留一位小数为 1500.1，最大重量为 1500.123。</t>
+          <t>XLOOKUP 语法：=XLOOKUP(查找值, 查找区域, 返回区域)，F2 返回「广州」。INDEX 语法：=INDEX(返回区域, 行号)，MATCH 语法：=MATCH(查找值, 查找区域, 0) 返回精确位置；G2 先定位 YD003 在第 3 行，再取 C2:C5 第 3 个值，结果为 50。</t>
         </is>
       </c>
     </row>
